--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -30553,10 +30553,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.02730117575042</v>
+        <v>26.02730117575039</v>
       </c>
       <c r="C4" t="n">
-        <v>28.90206609405679</v>
+        <v>28.90206609405676</v>
       </c>
       <c r="D4" t="n">
         <v>152.2214650059671</v>
@@ -30565,7 +30565,7 @@
         <v>9.283984024749472</v>
       </c>
       <c r="F4" t="n">
-        <v>21.02872370862951</v>
+        <v>21.02872370862949</v>
       </c>
     </row>
     <row r="5">

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -478,7 +478,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -563,7 +563,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -619,7 +619,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -663,7 +663,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -685,7 +685,7 @@
         <v>-3.159722222222224</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>8.600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -466,19 +466,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F3" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -607,19 +607,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F7" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -651,19 +651,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F8" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4444444444444458</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.201388888888888</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.159722222222224</v>
+        <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>8.600000000000001</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -472,10 +472,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -557,10 +557,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>7</v>
@@ -591,10 +591,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>7</v>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
@@ -635,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>-3.5</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -472,10 +472,10 @@
         <v>-15</v>
       </c>
       <c r="D2" t="n">
-        <v>-20.19821280725481</v>
+        <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>13.898735815423</v>
+        <v>-4.3</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -492,10 +492,10 @@
         <v>-1</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.895651713581624</v>
+        <v>-15.08041566639237</v>
       </c>
       <c r="E3" t="n">
-        <v>6.354495823142667</v>
+        <v>-10.1</v>
       </c>
       <c r="F3" t="n">
         <v>-18.5</v>
@@ -512,10 +512,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-16.32436400290355</v>
+        <v>-16.24192719111304</v>
       </c>
       <c r="E4" t="n">
-        <v>7.920393828358663</v>
+        <v>-13.2</v>
       </c>
       <c r="F4" t="n">
         <v>-18.5</v>
@@ -532,10 +532,10 @@
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.546088933772412</v>
+        <v>-18.76282389482354</v>
       </c>
       <c r="E5" t="n">
-        <v>8.594032848321</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>-3.5</v>
@@ -552,10 +552,10 @@
         <v>-11</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.141068244025071</v>
+        <v>-9.011605956684511</v>
       </c>
       <c r="E6" t="n">
-        <v>11.084942878291</v>
+        <v>-10.1</v>
       </c>
       <c r="F6" t="n">
         <v>-12.5</v>
@@ -572,10 +572,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.316038517532435</v>
+        <v>-16.88493498782972</v>
       </c>
       <c r="E7" t="n">
-        <v>8.994610261443</v>
+        <v>-5</v>
       </c>
       <c r="F7" t="n">
         <v>-12.5</v>
@@ -595,7 +595,7 @@
         <v>-22.1585517447926</v>
       </c>
       <c r="E8" t="n">
-        <v>13.03517965648966</v>
+        <v>-5</v>
       </c>
       <c r="F8" t="n">
         <v>-8</v>
@@ -612,10 +612,10 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.162402159714231</v>
+        <v>-14.86028872807583</v>
       </c>
       <c r="E9" t="n">
-        <v>4.667832044884999</v>
+        <v>-7.199999999999999</v>
       </c>
       <c r="F9" t="n">
         <v>-11</v>
@@ -632,10 +632,10 @@
         <v>-3</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.996891234062604</v>
+        <v>-16.66542535497044</v>
       </c>
       <c r="E10" t="n">
-        <v>7.227921027130001</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="n">
         <v>-2</v>
@@ -652,10 +652,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.21574900317417</v>
+        <v>-16.50768248317392</v>
       </c>
       <c r="E11" t="n">
-        <v>7.976898808093332</v>
+        <v>4.8</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
@@ -672,10 +672,10 @@
         <v>-9</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.24449063287788</v>
+        <v>-22.1585747570583</v>
       </c>
       <c r="E12" t="n">
-        <v>24.54957008676466</v>
+        <v>13.9</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5</v>
@@ -692,10 +692,10 @@
         <v>-17</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.20390865874995</v>
+        <v>-16.07701479937518</v>
       </c>
       <c r="E13" t="n">
-        <v>16.43480089552299</v>
+        <v>-2.1</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5</v>
@@ -715,7 +715,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E14" t="n">
-        <v>3.018313872154333</v>
+        <v>1.9</v>
       </c>
       <c r="F14" t="n">
         <v>-5</v>
@@ -732,10 +732,10 @@
         <v>-9</v>
       </c>
       <c r="D15" t="n">
-        <v>-14.63892570324918</v>
+        <v>-14.49481384471911</v>
       </c>
       <c r="E15" t="n">
-        <v>14.39324788963533</v>
+        <v>-2.300000000000001</v>
       </c>
       <c r="F15" t="n">
         <v>-18.5</v>
@@ -752,10 +752,10 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-19.5324389802231</v>
+        <v>-19.39923887184475</v>
       </c>
       <c r="E16" t="n">
-        <v>14.69255887276833</v>
+        <v>-4.299999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>-12.5</v>
@@ -772,10 +772,10 @@
         <v>-1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.835830261063638</v>
+        <v>-15.21056902635355</v>
       </c>
       <c r="E17" t="n">
-        <v>7.912303931734667</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>-12.5</v>
@@ -792,10 +792,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.67819322583435</v>
+        <v>-18.66489425226396</v>
       </c>
       <c r="E18" t="n">
-        <v>12.199345315083</v>
+        <v>-0.3000000000000003</v>
       </c>
       <c r="F18" t="n">
         <v>-11</v>
@@ -812,10 +812,10 @@
         <v>-5</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.02880543719705</v>
+        <v>-9.011666353277461</v>
       </c>
       <c r="E19" t="n">
-        <v>21.14368214706834</v>
+        <v>13.9</v>
       </c>
       <c r="F19" t="n">
         <v>-12.5</v>
@@ -832,10 +832,10 @@
         <v>-15</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.14604997201443</v>
+        <v>-12.42194598309683</v>
       </c>
       <c r="E20" t="n">
-        <v>19.886627168467</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
         <v>-8</v>
@@ -852,10 +852,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.950591733672964</v>
+        <v>-8.344026407773633</v>
       </c>
       <c r="E21" t="n">
-        <v>8.637061988032</v>
+        <v>-8.5</v>
       </c>
       <c r="F21" t="n">
         <v>-17</v>
@@ -872,10 +872,10 @@
         <v>-7</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.278353320193048</v>
+        <v>-10.61191573078219</v>
       </c>
       <c r="E22" t="n">
-        <v>11.77289756261567</v>
+        <v>-12.1</v>
       </c>
       <c r="F22" t="n">
         <v>-5</v>
@@ -892,10 +892,10 @@
         <v>-5</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.872362357256527</v>
+        <v>-13.76809791504057</v>
       </c>
       <c r="E23" t="n">
-        <v>17.81696559055967</v>
+        <v>12.8</v>
       </c>
       <c r="F23" t="n">
         <v>-21.5</v>
@@ -912,10 +912,10 @@
         <v>-13</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.77736632081545</v>
+        <v>-13.61382958064067</v>
       </c>
       <c r="E24" t="n">
-        <v>14.35478487425233</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-9.5</v>
@@ -932,10 +932,10 @@
         <v>-7</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.06369912228829</v>
+        <v>-17.04709742089801</v>
       </c>
       <c r="E25" t="n">
-        <v>13.77641279303433</v>
+        <v>4.8</v>
       </c>
       <c r="F25" t="n">
         <v>-5</v>
@@ -952,10 +952,10 @@
         <v>-7</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.19031335353988</v>
+        <v>-11.45515617083332</v>
       </c>
       <c r="E26" t="n">
-        <v>15.181716239529</v>
+        <v>-0.1</v>
       </c>
       <c r="F26" t="n">
         <v>-9.5</v>
@@ -972,10 +972,10 @@
         <v>-15</v>
       </c>
       <c r="D27" t="n">
-        <v>-22.41062404108411</v>
+        <v>-22.65071637595969</v>
       </c>
       <c r="E27" t="n">
-        <v>17.21923457534067</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="F27" t="n">
         <v>-12.5</v>
@@ -995,7 +995,7 @@
         <v>-18.723853564575</v>
       </c>
       <c r="E28" t="n">
-        <v>9.503147726130331</v>
+        <v>1.9</v>
       </c>
       <c r="F28" t="n">
         <v>-6.5</v>
@@ -1012,10 +1012,10 @@
         <v>-19</v>
       </c>
       <c r="D29" t="n">
-        <v>-18.90628538106688</v>
+        <v>-19.58043031028957</v>
       </c>
       <c r="E29" t="n">
-        <v>15.87304126134967</v>
+        <v>-2.1</v>
       </c>
       <c r="F29" t="n">
         <v>-11</v>
@@ -1032,10 +1032,10 @@
         <v>-9</v>
       </c>
       <c r="D30" t="n">
-        <v>-20.73646040087543</v>
+        <v>-21.81599222693938</v>
       </c>
       <c r="E30" t="n">
-        <v>17.85469793370567</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1052,10 +1052,10 @@
         <v>-5</v>
       </c>
       <c r="D31" t="n">
-        <v>-11.75301534056597</v>
+        <v>-12.33207495069766</v>
       </c>
       <c r="E31" t="n">
-        <v>23.274611839256</v>
+        <v>12.8</v>
       </c>
       <c r="F31" t="n">
         <v>-9.5</v>
@@ -1072,10 +1072,10 @@
         <v>-5</v>
       </c>
       <c r="D32" t="n">
-        <v>-10.32830532139622</v>
+        <v>-12.07550353950178</v>
       </c>
       <c r="E32" t="n">
-        <v>20.83299272046166</v>
+        <v>3.9</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-13.90485239821728</v>
+        <v>-13.9055061383892</v>
       </c>
       <c r="E33" t="n">
-        <v>11.46750084730033</v>
+        <v>1.7</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -1112,10 +1112,10 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>-19.57198377287025</v>
+        <v>-20.68298851778319</v>
       </c>
       <c r="E34" t="n">
-        <v>13.18125623784867</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5</v>
@@ -1132,10 +1132,10 @@
         <v>-19</v>
       </c>
       <c r="D35" t="n">
-        <v>-13.3941853316858</v>
+        <v>-13.67390778367567</v>
       </c>
       <c r="E35" t="n">
-        <v>21.24587165833066</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
         <v>-9.5</v>
@@ -1152,10 +1152,10 @@
         <v>-21</v>
       </c>
       <c r="D36" t="n">
-        <v>-10.06817487793678</v>
+        <v>-9.665718240118361</v>
       </c>
       <c r="E36" t="n">
-        <v>18.31777246814066</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="F36" t="n">
         <v>-20</v>
@@ -1172,10 +1172,10 @@
         <v>-19</v>
       </c>
       <c r="D37" t="n">
-        <v>-15.43576245903176</v>
+        <v>-15.36778170122901</v>
       </c>
       <c r="E37" t="n">
-        <v>20.81933163205267</v>
+        <v>7</v>
       </c>
       <c r="F37" t="n">
         <v>-12.5</v>
@@ -1192,10 +1192,10 @@
         <v>-19</v>
       </c>
       <c r="D38" t="n">
-        <v>-10.68299217024175</v>
+        <v>-12.35413898216171</v>
       </c>
       <c r="E38" t="n">
-        <v>17.085405008345</v>
+        <v>1.9</v>
       </c>
       <c r="F38" t="n">
         <v>-21.5</v>
@@ -1212,10 +1212,10 @@
         <v>-7</v>
       </c>
       <c r="D39" t="n">
-        <v>-14.85336344465047</v>
+        <v>-16.22217341588913</v>
       </c>
       <c r="E39" t="n">
-        <v>17.319858669693</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
@@ -1232,10 +1232,10 @@
         <v>-9</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.292395089655468</v>
+        <v>-10.00948967549725</v>
       </c>
       <c r="E40" t="n">
-        <v>22.30241650833799</v>
+        <v>18.8</v>
       </c>
       <c r="F40" t="n">
         <v>-17</v>
@@ -1252,10 +1252,10 @@
         <v>-21</v>
       </c>
       <c r="D41" t="n">
-        <v>-14.14685580942684</v>
+        <v>-15.10350776269546</v>
       </c>
       <c r="E41" t="n">
-        <v>15.602644368825</v>
+        <v>-1</v>
       </c>
       <c r="F41" t="n">
         <v>-17</v>
@@ -1272,10 +1272,10 @@
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>-13.5429621372321</v>
+        <v>-13.62641184742081</v>
       </c>
       <c r="E42" t="n">
-        <v>16.77564644879467</v>
+        <v>-1.199999999999999</v>
       </c>
       <c r="F42" t="n">
         <v>-12.5</v>
@@ -1292,10 +1292,10 @@
         <v>-5</v>
       </c>
       <c r="D43" t="n">
-        <v>-14.82015919217503</v>
+        <v>-14.71610395027719</v>
       </c>
       <c r="E43" t="n">
-        <v>17.881038256138</v>
+        <v>-0.3000000000000003</v>
       </c>
       <c r="F43" t="n">
         <v>-11</v>
@@ -1312,10 +1312,10 @@
         <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>-13.67266214735814</v>
+        <v>-17.32238709223246</v>
       </c>
       <c r="E44" t="n">
-        <v>9.814280217365001</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="F44" t="n">
         <v>-6.5</v>
@@ -1332,10 +1332,10 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>-18.39745458992846</v>
+        <v>-18.3985178425561</v>
       </c>
       <c r="E45" t="n">
-        <v>12.999020313292</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="F45" t="n">
         <v>2.5</v>
@@ -1352,10 +1352,10 @@
         <v>-11</v>
       </c>
       <c r="D46" t="n">
-        <v>-13.73593028071477</v>
+        <v>-13.92117656900311</v>
       </c>
       <c r="E46" t="n">
-        <v>20.24320445076633</v>
+        <v>3.9</v>
       </c>
       <c r="F46" t="n">
         <v>-11</v>
@@ -1372,10 +1372,10 @@
         <v>-17</v>
       </c>
       <c r="D47" t="n">
-        <v>-10.98321251947801</v>
+        <v>-11.07952799310252</v>
       </c>
       <c r="E47" t="n">
-        <v>27.33236426068567</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>-8</v>
@@ -1392,10 +1392,10 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>-17.01967755644079</v>
+        <v>-17.00931480520146</v>
       </c>
       <c r="E48" t="n">
-        <v>14.12728650513833</v>
+        <v>4.6</v>
       </c>
       <c r="F48" t="n">
         <v>-18.5</v>
@@ -1412,10 +1412,10 @@
         <v>-13</v>
       </c>
       <c r="D49" t="n">
-        <v>-7.688214412220143</v>
+        <v>-12.51496523440635</v>
       </c>
       <c r="E49" t="n">
-        <v>16.597579638721</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1432,10 +1432,10 @@
         <v>-13</v>
       </c>
       <c r="D50" t="n">
-        <v>-10.55517089152359</v>
+        <v>-12.56933176486039</v>
       </c>
       <c r="E50" t="n">
-        <v>22.19805995671967</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
         <v>-2</v>
@@ -1455,7 +1455,7 @@
         <v>-18.61042700136766</v>
       </c>
       <c r="E51" t="n">
-        <v>8.430479964408665</v>
+        <v>5.9</v>
       </c>
       <c r="F51" t="n">
         <v>-9.5</v>
@@ -1472,10 +1472,10 @@
         <v>-7</v>
       </c>
       <c r="D52" t="n">
-        <v>-17.13129629292315</v>
+        <v>-19.98298420591642</v>
       </c>
       <c r="E52" t="n">
-        <v>21.378690489308</v>
+        <v>6.8</v>
       </c>
       <c r="F52" t="n">
         <v>-18.5</v>
@@ -1492,10 +1492,10 @@
         <v>-15</v>
       </c>
       <c r="D53" t="n">
-        <v>-5.421374293330286</v>
+        <v>-6.672983718717866</v>
       </c>
       <c r="E53" t="n">
-        <v>16.1106462198</v>
+        <v>-2.3</v>
       </c>
       <c r="F53" t="n">
         <v>-8</v>
@@ -1512,10 +1512,10 @@
         <v>-7</v>
       </c>
       <c r="D54" t="n">
-        <v>-15.33469390091668</v>
+        <v>-15.35638027898899</v>
       </c>
       <c r="E54" t="n">
-        <v>15.75274082350266</v>
+        <v>-4.1</v>
       </c>
       <c r="F54" t="n">
         <v>-11</v>
@@ -1532,10 +1532,10 @@
         <v>-11</v>
       </c>
       <c r="D55" t="n">
-        <v>-12.18567960639962</v>
+        <v>-15.19729180569158</v>
       </c>
       <c r="E55" t="n">
-        <v>16.18631850834467</v>
+        <v>-1</v>
       </c>
       <c r="F55" t="n">
         <v>-5</v>
@@ -1552,10 +1552,10 @@
         <v>-3</v>
       </c>
       <c r="D56" t="n">
-        <v>-14.58331016546108</v>
+        <v>-14.51951403443939</v>
       </c>
       <c r="E56" t="n">
-        <v>14.240481895773</v>
+        <v>1.9</v>
       </c>
       <c r="F56" t="n">
         <v>-14</v>
@@ -1572,10 +1572,10 @@
         <v>-21</v>
       </c>
       <c r="D57" t="n">
-        <v>-16.18139179848832</v>
+        <v>-16.3915095915476</v>
       </c>
       <c r="E57" t="n">
-        <v>16.18687967924033</v>
+        <v>5</v>
       </c>
       <c r="F57" t="n">
         <v>-9.5</v>
@@ -1592,10 +1592,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>-16.72732274548168</v>
+        <v>-16.72760094092684</v>
       </c>
       <c r="E58" t="n">
-        <v>6.882341769758667</v>
+        <v>-7</v>
       </c>
       <c r="F58" t="n">
         <v>-9.5</v>
@@ -1612,10 +1612,10 @@
         <v>-5</v>
       </c>
       <c r="D59" t="n">
-        <v>-8.124846139024989</v>
+        <v>-11.78050191422369</v>
       </c>
       <c r="E59" t="n">
-        <v>28.63493696186867</v>
+        <v>17.9</v>
       </c>
       <c r="F59" t="n">
         <v>-9.5</v>
@@ -1632,10 +1632,10 @@
         <v>-9</v>
       </c>
       <c r="D60" t="n">
-        <v>-12.81492952387297</v>
+        <v>-13.16902826441466</v>
       </c>
       <c r="E60" t="n">
-        <v>24.81826870500267</v>
+        <v>13.7</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5</v>
@@ -1652,10 +1652,10 @@
         <v>-19</v>
       </c>
       <c r="D61" t="n">
-        <v>-18.43349924205394</v>
+        <v>-18.54419594854977</v>
       </c>
       <c r="E61" t="n">
-        <v>17.075788109581</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="F61" t="n">
         <v>-11</v>
@@ -1672,10 +1672,10 @@
         <v>-11</v>
       </c>
       <c r="D62" t="n">
-        <v>-7.130901491740826</v>
+        <v>-8.807644726031004</v>
       </c>
       <c r="E62" t="n">
-        <v>19.182133683135</v>
+        <v>2.8</v>
       </c>
       <c r="F62" t="n">
         <v>-11</v>
@@ -1692,10 +1692,10 @@
         <v>13</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1678684575510436</v>
+        <v>-14.28909157388709</v>
       </c>
       <c r="E63" t="n">
-        <v>5.244624144632334</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>-8</v>
@@ -1712,10 +1712,10 @@
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>-15.87994626256206</v>
+        <v>-15.86301331944633</v>
       </c>
       <c r="E64" t="n">
-        <v>16.15119817240367</v>
+        <v>11.9</v>
       </c>
       <c r="F64" t="n">
         <v>-9.5</v>
@@ -1732,10 +1732,10 @@
         <v>-15</v>
       </c>
       <c r="D65" t="n">
-        <v>-14.29592679949054</v>
+        <v>-16.55071283344781</v>
       </c>
       <c r="E65" t="n">
-        <v>23.84100273579933</v>
+        <v>9.9</v>
       </c>
       <c r="F65" t="n">
         <v>-0.5</v>
@@ -1752,10 +1752,10 @@
         <v>-7</v>
       </c>
       <c r="D66" t="n">
-        <v>-17.91472571980827</v>
+        <v>-17.9336097374753</v>
       </c>
       <c r="E66" t="n">
-        <v>22.25645596461367</v>
+        <v>5.9</v>
       </c>
       <c r="F66" t="n">
         <v>-17</v>
@@ -1772,10 +1772,10 @@
         <v>-21</v>
       </c>
       <c r="D67" t="n">
-        <v>-11.74155818525312</v>
+        <v>-11.96824934592622</v>
       </c>
       <c r="E67" t="n">
-        <v>22.77040231934501</v>
+        <v>9.9</v>
       </c>
       <c r="F67" t="n">
         <v>-3.5</v>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>-11.99441666998782</v>
+        <v>-11.58305819485098</v>
       </c>
       <c r="E68" t="n">
-        <v>17.25285194102034</v>
+        <v>3.9</v>
       </c>
       <c r="F68" t="n">
         <v>-6.5</v>
@@ -1812,10 +1812,10 @@
         <v>-11</v>
       </c>
       <c r="D69" t="n">
-        <v>-15.93350791355592</v>
+        <v>-16.96770942927208</v>
       </c>
       <c r="E69" t="n">
-        <v>20.99004684252033</v>
+        <v>2.8</v>
       </c>
       <c r="F69" t="n">
         <v>-5</v>
@@ -1832,10 +1832,10 @@
         <v>-3</v>
       </c>
       <c r="D70" t="n">
-        <v>-12.61580781439891</v>
+        <v>-13.70594101887073</v>
       </c>
       <c r="E70" t="n">
-        <v>7.576114246237332</v>
+        <v>3.9</v>
       </c>
       <c r="F70" t="n">
         <v>-11</v>
@@ -1852,10 +1852,10 @@
         <v>-9</v>
       </c>
       <c r="D71" t="n">
-        <v>-13.55425138755535</v>
+        <v>-13.35983540697217</v>
       </c>
       <c r="E71" t="n">
-        <v>9.457923695013667</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>-11</v>
@@ -1872,10 +1872,10 @@
         <v>-1</v>
       </c>
       <c r="D72" t="n">
-        <v>-13.68525862075747</v>
+        <v>-13.73945420010882</v>
       </c>
       <c r="E72" t="n">
-        <v>21.73001718738433</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F72" t="n">
         <v>-9.5</v>
@@ -1892,10 +1892,10 @@
         <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>-21.4438172351039</v>
+        <v>-21.43215273472283</v>
       </c>
       <c r="E73" t="n">
-        <v>14.75451338167233</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F73" t="n">
         <v>-14</v>
@@ -1912,10 +1912,10 @@
         <v>-5</v>
       </c>
       <c r="D74" t="n">
-        <v>-19.80746021765057</v>
+        <v>-19.93026650520378</v>
       </c>
       <c r="E74" t="n">
-        <v>21.83180953545166</v>
+        <v>7</v>
       </c>
       <c r="F74" t="n">
         <v>-6.5</v>
@@ -1932,10 +1932,10 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>-13.5564562376107</v>
+        <v>-13.63373489971633</v>
       </c>
       <c r="E75" t="n">
-        <v>19.88920461725033</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="F75" t="n">
         <v>-9.5</v>
@@ -1952,10 +1952,10 @@
         <v>-5</v>
       </c>
       <c r="D76" t="n">
-        <v>-14.70871378055858</v>
+        <v>-14.70893704404678</v>
       </c>
       <c r="E76" t="n">
-        <v>13.35976880777533</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="F76" t="n">
         <v>2.5</v>
@@ -1972,10 +1972,10 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>-20.41696905718009</v>
+        <v>-20.41126671783134</v>
       </c>
       <c r="E77" t="n">
-        <v>8.429306415368668</v>
+        <v>-6.1</v>
       </c>
       <c r="F77" t="n">
         <v>-2</v>
@@ -1992,10 +1992,10 @@
         <v>-9</v>
       </c>
       <c r="D78" t="n">
-        <v>-7.73702591954847</v>
+        <v>-8.298668334372483</v>
       </c>
       <c r="E78" t="n">
-        <v>10.084945780137</v>
+        <v>-2.5</v>
       </c>
       <c r="F78" t="n">
         <v>-9.5</v>
@@ -2012,10 +2012,10 @@
         <v>-11</v>
       </c>
       <c r="D79" t="n">
-        <v>-11.38001899243352</v>
+        <v>-11.09414578630654</v>
       </c>
       <c r="E79" t="n">
-        <v>23.43885354952466</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="F79" t="n">
         <v>-3.5</v>
@@ -2032,10 +2032,10 @@
         <v>-9</v>
       </c>
       <c r="D80" t="n">
-        <v>-14.76955041138785</v>
+        <v>-14.76956546226694</v>
       </c>
       <c r="E80" t="n">
-        <v>12.179825230828</v>
+        <v>-5</v>
       </c>
       <c r="F80" t="n">
         <v>-5</v>
@@ -2052,10 +2052,10 @@
         <v>-13</v>
       </c>
       <c r="D81" t="n">
-        <v>-11.41574054082313</v>
+        <v>-14.11114333061668</v>
       </c>
       <c r="E81" t="n">
-        <v>18.92853246077233</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F81" t="n">
         <v>-11</v>
@@ -2072,10 +2072,10 @@
         <v>-15</v>
       </c>
       <c r="D82" t="n">
-        <v>-16.72221113799518</v>
+        <v>-17.36533220259155</v>
       </c>
       <c r="E82" t="n">
-        <v>22.915714251432</v>
+        <v>7.9</v>
       </c>
       <c r="F82" t="n">
         <v>-9.5</v>
@@ -2092,10 +2092,10 @@
         <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>-14.38170079192778</v>
+        <v>-14.29537266647307</v>
       </c>
       <c r="E83" t="n">
-        <v>18.37938946173867</v>
+        <v>9.500000000000002</v>
       </c>
       <c r="F83" t="n">
         <v>-11</v>
@@ -2112,10 +2112,10 @@
         <v>-11</v>
       </c>
       <c r="D84" t="n">
-        <v>-15.33141092962045</v>
+        <v>-15.52673225528131</v>
       </c>
       <c r="E84" t="n">
-        <v>18.61965328852933</v>
+        <v>5.9</v>
       </c>
       <c r="F84" t="n">
         <v>-2</v>
@@ -2132,10 +2132,10 @@
         <v>-13</v>
       </c>
       <c r="D85" t="n">
-        <v>-10.13363093248354</v>
+        <v>-10.61618120478381</v>
       </c>
       <c r="E85" t="n">
-        <v>18.34780331000733</v>
+        <v>3.9</v>
       </c>
       <c r="F85" t="n">
         <v>-6.5</v>
@@ -2152,10 +2152,10 @@
         <v>-1</v>
       </c>
       <c r="D86" t="n">
-        <v>-9.01141848963092</v>
+        <v>-9.558453099269794</v>
       </c>
       <c r="E86" t="n">
-        <v>21.30637250166467</v>
+        <v>7</v>
       </c>
       <c r="F86" t="n">
         <v>-3.5</v>
@@ -2172,10 +2172,10 @@
         <v>-3</v>
       </c>
       <c r="D87" t="n">
-        <v>-10.21619053275584</v>
+        <v>-11.95578259847385</v>
       </c>
       <c r="E87" t="n">
-        <v>12.30280492595667</v>
+        <v>-6.3</v>
       </c>
       <c r="F87" t="n">
         <v>-2</v>
@@ -2192,10 +2192,10 @@
         <v>-15</v>
       </c>
       <c r="D88" t="n">
-        <v>-14.29310794037701</v>
+        <v>-14.53892114818133</v>
       </c>
       <c r="E88" t="n">
-        <v>26.50430716718933</v>
+        <v>17</v>
       </c>
       <c r="F88" t="n">
         <v>-0.5</v>
@@ -2212,10 +2212,10 @@
         <v>-7</v>
       </c>
       <c r="D89" t="n">
-        <v>-15.84787695399365</v>
+        <v>-14.98567711898332</v>
       </c>
       <c r="E89" t="n">
-        <v>22.94076351765533</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
         <v>-2</v>
@@ -2232,10 +2232,10 @@
         <v>-1</v>
       </c>
       <c r="D90" t="n">
-        <v>-2.115832138646711</v>
+        <v>-8.626986066168405</v>
       </c>
       <c r="E90" t="n">
-        <v>19.47272649423</v>
+        <v>17.7</v>
       </c>
       <c r="F90" t="n">
         <v>-9.5</v>
@@ -2252,10 +2252,10 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>-14.46908807888709</v>
+        <v>-14.42115485021459</v>
       </c>
       <c r="E91" t="n">
-        <v>11.07800405891333</v>
+        <v>-4.1</v>
       </c>
       <c r="F91" t="n">
         <v>-2</v>
@@ -2272,10 +2272,10 @@
         <v>-1</v>
       </c>
       <c r="D92" t="n">
-        <v>-14.85980115446774</v>
+        <v>-14.81963907250334</v>
       </c>
       <c r="E92" t="n">
-        <v>10.67964067307733</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F92" t="n">
         <v>-8</v>
@@ -2292,10 +2292,10 @@
         <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>-13.51954355877752</v>
+        <v>-18.27445887317804</v>
       </c>
       <c r="E93" t="n">
-        <v>12.65361379575333</v>
+        <v>10.8</v>
       </c>
       <c r="F93" t="n">
         <v>-0.5</v>
@@ -2312,10 +2312,10 @@
         <v>11</v>
       </c>
       <c r="D94" t="n">
-        <v>-8.647285579192291</v>
+        <v>-14.01149006572236</v>
       </c>
       <c r="E94" t="n">
-        <v>17.68361722252267</v>
+        <v>3.299999999999999</v>
       </c>
       <c r="F94" t="n">
         <v>-2</v>
@@ -2332,10 +2332,10 @@
         <v>-17</v>
       </c>
       <c r="D95" t="n">
-        <v>-9.537141254099046</v>
+        <v>-11.76638385536769</v>
       </c>
       <c r="E95" t="n">
-        <v>27.09069394614767</v>
+        <v>15.9</v>
       </c>
       <c r="F95" t="n">
         <v>-5</v>
@@ -2352,10 +2352,10 @@
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>-6.817570286522825</v>
+        <v>-9.413356115683376</v>
       </c>
       <c r="E96" t="n">
-        <v>19.70625646914667</v>
+        <v>14.8</v>
       </c>
       <c r="F96" t="n">
         <v>-5</v>
@@ -2372,10 +2372,10 @@
         <v>-3</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.411651203573772</v>
+        <v>-14.28585576463446</v>
       </c>
       <c r="E97" t="n">
-        <v>8.234165938308667</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
         <v>2.5</v>
@@ -2392,10 +2392,10 @@
         <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>-11.83539534757797</v>
+        <v>-11.85349409751063</v>
       </c>
       <c r="E98" t="n">
-        <v>18.28262532206033</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F98" t="n">
         <v>-3.5</v>
@@ -2412,10 +2412,10 @@
         <v>-13</v>
       </c>
       <c r="D99" t="n">
-        <v>-12.32622067114353</v>
+        <v>-15.24029031651793</v>
       </c>
       <c r="E99" t="n">
-        <v>21.68555818120733</v>
+        <v>3.9</v>
       </c>
       <c r="F99" t="n">
         <v>-5</v>
@@ -2432,10 +2432,10 @@
         <v>-11</v>
       </c>
       <c r="D100" t="n">
-        <v>-16.64959313198185</v>
+        <v>-16.01872556029471</v>
       </c>
       <c r="E100" t="n">
-        <v>25.17941489144534</v>
+        <v>11.9</v>
       </c>
       <c r="F100" t="n">
         <v>-2</v>
@@ -2452,10 +2452,10 @@
         <v>-15</v>
       </c>
       <c r="D101" t="n">
-        <v>-11.55974187018094</v>
+        <v>-11.30979160160691</v>
       </c>
       <c r="E101" t="n">
-        <v>22.84366553648633</v>
+        <v>19</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2472,10 +2472,10 @@
         <v>-9</v>
       </c>
       <c r="D102" t="n">
-        <v>-13.46944371130065</v>
+        <v>-15.21465658295874</v>
       </c>
       <c r="E102" t="n">
-        <v>21.431641607559</v>
+        <v>5</v>
       </c>
       <c r="F102" t="n">
         <v>-9.5</v>
@@ -2492,10 +2492,10 @@
         <v>-7</v>
       </c>
       <c r="D103" t="n">
-        <v>-12.02206667891779</v>
+        <v>-11.91209159844877</v>
       </c>
       <c r="E103" t="n">
-        <v>16.93459431245666</v>
+        <v>15.7</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2512,10 +2512,10 @@
         <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>-6.67440025881412</v>
+        <v>-18.47233524338426</v>
       </c>
       <c r="E104" t="n">
-        <v>9.562152280071667</v>
+        <v>13.7</v>
       </c>
       <c r="F104" t="n">
         <v>-11</v>
@@ -2532,10 +2532,10 @@
         <v>17</v>
       </c>
       <c r="D105" t="n">
-        <v>-8.683843009138711</v>
+        <v>-15.99683898329127</v>
       </c>
       <c r="E105" t="n">
-        <v>14.38685245624967</v>
+        <v>23.7</v>
       </c>
       <c r="F105" t="n">
         <v>4</v>
@@ -2552,10 +2552,10 @@
         <v>-1</v>
       </c>
       <c r="D106" t="n">
-        <v>-9.899298359670187</v>
+        <v>-11.78397827839792</v>
       </c>
       <c r="E106" t="n">
-        <v>25.56670832068967</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F106" t="n">
         <v>-12.5</v>
@@ -2572,10 +2572,10 @@
         <v>-5</v>
       </c>
       <c r="D107" t="n">
-        <v>-13.26111331963317</v>
+        <v>-14.09994806721748</v>
       </c>
       <c r="E107" t="n">
-        <v>17.14101788134967</v>
+        <v>-1</v>
       </c>
       <c r="F107" t="n">
         <v>-14</v>
@@ -2592,10 +2592,10 @@
         <v>-5</v>
       </c>
       <c r="D108" t="n">
-        <v>-13.26692097127029</v>
+        <v>-13.11527797743044</v>
       </c>
       <c r="E108" t="n">
-        <v>9.247416842123666</v>
+        <v>-13.2</v>
       </c>
       <c r="F108" t="n">
         <v>-9.5</v>
@@ -2612,10 +2612,10 @@
         <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>-10.45906779666581</v>
+        <v>-10.20573754684604</v>
       </c>
       <c r="E109" t="n">
-        <v>12.64052793864534</v>
+        <v>0.6000000000000005</v>
       </c>
       <c r="F109" t="n">
         <v>-11</v>
@@ -2632,10 +2632,10 @@
         <v>-5</v>
       </c>
       <c r="D110" t="n">
-        <v>-11.97838730841862</v>
+        <v>-12.319581041081</v>
       </c>
       <c r="E110" t="n">
-        <v>19.055377936779</v>
+        <v>5</v>
       </c>
       <c r="F110" t="n">
         <v>-5</v>
@@ -2652,10 +2652,10 @@
         <v>-3</v>
       </c>
       <c r="D111" t="n">
-        <v>-5.592546999363587</v>
+        <v>-6.059953702883841</v>
       </c>
       <c r="E111" t="n">
-        <v>17.12828259170033</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="F111" t="n">
         <v>-0.5</v>
@@ -2672,10 +2672,10 @@
         <v>13</v>
       </c>
       <c r="D112" t="n">
-        <v>-2.986050174715062</v>
+        <v>-13.07604183385386</v>
       </c>
       <c r="E112" t="n">
-        <v>15.07332567166633</v>
+        <v>7.9</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -2692,10 +2692,10 @@
         <v>-5</v>
       </c>
       <c r="D113" t="n">
-        <v>-11.95785971855255</v>
+        <v>-12.00565567818595</v>
       </c>
       <c r="E113" t="n">
-        <v>23.35396894972066</v>
+        <v>11.9</v>
       </c>
       <c r="F113" t="n">
         <v>-6.5</v>
@@ -2712,10 +2712,10 @@
         <v>13</v>
       </c>
       <c r="D114" t="n">
-        <v>-8.179983338709782</v>
+        <v>-18.23586872181258</v>
       </c>
       <c r="E114" t="n">
-        <v>3.359138810888334</v>
+        <v>7.9</v>
       </c>
       <c r="F114" t="n">
         <v>-2</v>
@@ -2732,10 +2732,10 @@
         <v>-11</v>
       </c>
       <c r="D115" t="n">
-        <v>-15.58341654025278</v>
+        <v>-16.23673636012176</v>
       </c>
       <c r="E115" t="n">
-        <v>12.756647347742</v>
+        <v>-4.1</v>
       </c>
       <c r="F115" t="n">
         <v>-0.5</v>
@@ -2752,10 +2752,10 @@
         <v>-3</v>
       </c>
       <c r="D116" t="n">
-        <v>-6.184043928692694</v>
+        <v>-9.138045441859136</v>
       </c>
       <c r="E116" t="n">
-        <v>19.53631738604366</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="F116" t="n">
         <v>-6.5</v>
@@ -2772,10 +2772,10 @@
         <v>-5</v>
       </c>
       <c r="D117" t="n">
-        <v>-8.675008135172202</v>
+        <v>-8.735620769461221</v>
       </c>
       <c r="E117" t="n">
-        <v>16.72625298344967</v>
+        <v>1.9</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -2792,10 +2792,10 @@
         <v>-1</v>
       </c>
       <c r="D118" t="n">
-        <v>-3.264109395615427</v>
+        <v>-3.275988466822424</v>
       </c>
       <c r="E118" t="n">
-        <v>22.66972957244867</v>
+        <v>7.9</v>
       </c>
       <c r="F118" t="n">
         <v>-2</v>
@@ -2812,10 +2812,10 @@
         <v>15</v>
       </c>
       <c r="D119" t="n">
-        <v>-21.46705823054874</v>
+        <v>-21.46730196390546</v>
       </c>
       <c r="E119" t="n">
-        <v>12.871887875098</v>
+        <v>9</v>
       </c>
       <c r="F119" t="n">
         <v>-8</v>
@@ -2832,10 +2832,10 @@
         <v>5</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.3878233520043121</v>
+        <v>-9.30602509382889</v>
       </c>
       <c r="E120" t="n">
-        <v>13.09022868998767</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F120" t="n">
         <v>-2</v>
@@ -2852,10 +2852,10 @@
         <v>-9</v>
       </c>
       <c r="D121" t="n">
-        <v>-13.68680103644119</v>
+        <v>-15.45651431364378</v>
       </c>
       <c r="E121" t="n">
-        <v>22.03804669900333</v>
+        <v>9.9</v>
       </c>
       <c r="F121" t="n">
         <v>-2</v>
@@ -2872,10 +2872,10 @@
         <v>-7</v>
       </c>
       <c r="D122" t="n">
-        <v>-5.391214271259628</v>
+        <v>-6.65815148548338</v>
       </c>
       <c r="E122" t="n">
-        <v>26.179159768272</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
         <v>-8</v>
@@ -2892,10 +2892,10 @@
         <v>-11</v>
       </c>
       <c r="D123" t="n">
-        <v>-6.896146535592099</v>
+        <v>-6.936543698335337</v>
       </c>
       <c r="E123" t="n">
-        <v>27.78018451306901</v>
+        <v>17.9</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -2912,10 +2912,10 @@
         <v>-15</v>
       </c>
       <c r="D124" t="n">
-        <v>-8.376066631276625</v>
+        <v>-11.38242419822538</v>
       </c>
       <c r="E124" t="n">
-        <v>29.508425716247</v>
+        <v>21</v>
       </c>
       <c r="F124" t="n">
         <v>-6.5</v>
@@ -2932,10 +2932,10 @@
         <v>-9</v>
       </c>
       <c r="D125" t="n">
-        <v>-15.10458536669034</v>
+        <v>-15.10018684775595</v>
       </c>
       <c r="E125" t="n">
-        <v>29.05950761689733</v>
+        <v>21</v>
       </c>
       <c r="F125" t="n">
         <v>-3.5</v>
@@ -2952,10 +2952,10 @@
         <v>-1</v>
       </c>
       <c r="D126" t="n">
-        <v>-14.92219742234849</v>
+        <v>-14.27988774904433</v>
       </c>
       <c r="E126" t="n">
-        <v>27.85567439425933</v>
+        <v>21.7</v>
       </c>
       <c r="F126" t="n">
         <v>-5</v>
@@ -2972,10 +2972,10 @@
         <v>7</v>
       </c>
       <c r="D127" t="n">
-        <v>-6.145790651936738</v>
+        <v>-6.334648954400722</v>
       </c>
       <c r="E127" t="n">
-        <v>16.527468549306</v>
+        <v>2.6</v>
       </c>
       <c r="F127" t="n">
         <v>-12.5</v>
@@ -2992,10 +2992,10 @@
         <v>-7</v>
       </c>
       <c r="D128" t="n">
-        <v>-13.61360195682419</v>
+        <v>-13.5475756767352</v>
       </c>
       <c r="E128" t="n">
-        <v>14.42913230461833</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>-6.5</v>
@@ -3012,10 +3012,10 @@
         <v>-13</v>
       </c>
       <c r="D129" t="n">
-        <v>-10.9038479745474</v>
+        <v>-11.66477267457763</v>
       </c>
       <c r="E129" t="n">
-        <v>23.66839785449666</v>
+        <v>11.9</v>
       </c>
       <c r="F129" t="n">
         <v>-3.5</v>
@@ -3032,10 +3032,10 @@
         <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>-8.60854976738568</v>
+        <v>-14.70454073338186</v>
       </c>
       <c r="E130" t="n">
-        <v>18.21004447454833</v>
+        <v>23</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3052,10 +3052,10 @@
         <v>-3</v>
       </c>
       <c r="D131" t="n">
-        <v>2.45470394781958</v>
+        <v>-11.29764528453063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.409881838271</v>
+        <v>25.9</v>
       </c>
       <c r="F131" t="n">
         <v>-5</v>
@@ -3072,10 +3072,10 @@
         <v>-9</v>
       </c>
       <c r="D132" t="n">
-        <v>-8.204562074621915</v>
+        <v>-9.092734146744514</v>
       </c>
       <c r="E132" t="n">
-        <v>17.574811265056</v>
+        <v>1.9</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3092,10 +3092,10 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.234951708901501</v>
+        <v>-7.953307220522068</v>
       </c>
       <c r="E133" t="n">
-        <v>16.04818772253567</v>
+        <v>15.5</v>
       </c>
       <c r="F133" t="n">
         <v>-5</v>
@@ -3112,10 +3112,10 @@
         <v>-3</v>
       </c>
       <c r="D134" t="n">
-        <v>-5.517184239742335</v>
+        <v>-8.629619074258962</v>
       </c>
       <c r="E134" t="n">
-        <v>17.53354924003267</v>
+        <v>3.9</v>
       </c>
       <c r="F134" t="n">
         <v>-6.5</v>
@@ -3132,10 +3132,10 @@
         <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>-12.52169092779617</v>
+        <v>-12.45493151160171</v>
       </c>
       <c r="E135" t="n">
-        <v>9.117497176693332</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F135" t="n">
         <v>5.5</v>
@@ -3152,10 +3152,10 @@
         <v>17</v>
       </c>
       <c r="D136" t="n">
-        <v>-15.36484428134311</v>
+        <v>-15.35178539224633</v>
       </c>
       <c r="E136" t="n">
-        <v>15.02054741734034</v>
+        <v>17.9</v>
       </c>
       <c r="F136" t="n">
         <v>-3.5</v>
@@ -3172,10 +3172,10 @@
         <v>9</v>
       </c>
       <c r="D137" t="n">
-        <v>-2.235544847140266</v>
+        <v>-14.42757650544786</v>
       </c>
       <c r="E137" t="n">
-        <v>9.804688773460331</v>
+        <v>18.6</v>
       </c>
       <c r="F137" t="n">
         <v>-11</v>
@@ -3192,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>-13.03248938588418</v>
+        <v>-13.78355315746163</v>
       </c>
       <c r="E138" t="n">
-        <v>20.03173118493434</v>
+        <v>5</v>
       </c>
       <c r="F138" t="n">
         <v>-5</v>
@@ -3212,10 +3212,10 @@
         <v>-13</v>
       </c>
       <c r="D139" t="n">
-        <v>-11.37278560673306</v>
+        <v>-11.16316554267884</v>
       </c>
       <c r="E139" t="n">
-        <v>21.93583674735733</v>
+        <v>14.8</v>
       </c>
       <c r="F139" t="n">
         <v>-0.5</v>
@@ -3232,10 +3232,10 @@
         <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>-15.20873673126377</v>
+        <v>-15.7222577936834</v>
       </c>
       <c r="E140" t="n">
-        <v>31.732509173805</v>
+        <v>20.8</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -3252,10 +3252,10 @@
         <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>-16.79355730615741</v>
+        <v>-18.80056717765801</v>
       </c>
       <c r="E141" t="n">
-        <v>18.30778945184333</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F141" t="n">
         <v>5.5</v>
@@ -3272,10 +3272,10 @@
         <v>-3</v>
       </c>
       <c r="D142" t="n">
-        <v>-12.21306998753178</v>
+        <v>-12.75547358832381</v>
       </c>
       <c r="E142" t="n">
-        <v>16.62850476556433</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="F142" t="n">
         <v>-2</v>
@@ -3292,10 +3292,10 @@
         <v>15</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.767030642841792</v>
+        <v>-13.05017477055378</v>
       </c>
       <c r="E143" t="n">
-        <v>8.633436083936999</v>
+        <v>2.8</v>
       </c>
       <c r="F143" t="n">
         <v>2.5</v>
@@ -3312,10 +3312,10 @@
         <v>-7</v>
       </c>
       <c r="D144" t="n">
-        <v>-5.164855388770684</v>
+        <v>-9.492785338822857</v>
       </c>
       <c r="E144" t="n">
-        <v>28.00458841207667</v>
+        <v>17</v>
       </c>
       <c r="F144" t="n">
         <v>5.5</v>
@@ -3332,10 +3332,10 @@
         <v>-11</v>
       </c>
       <c r="D145" t="n">
-        <v>-10.19931759671269</v>
+        <v>-12.82451007415136</v>
       </c>
       <c r="E145" t="n">
-        <v>20.09880342042533</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="F145" t="n">
         <v>-2</v>
@@ -3352,10 +3352,10 @@
         <v>-1</v>
       </c>
       <c r="D146" t="n">
-        <v>-16.00754139206434</v>
+        <v>-15.2583426766281</v>
       </c>
       <c r="E146" t="n">
-        <v>26.86724354657867</v>
+        <v>13.5</v>
       </c>
       <c r="F146" t="n">
         <v>-5</v>
@@ -3372,10 +3372,10 @@
         <v>5</v>
       </c>
       <c r="D147" t="n">
-        <v>-8.697261722354209</v>
+        <v>-8.936160793676258</v>
       </c>
       <c r="E147" t="n">
-        <v>20.97517241276866</v>
+        <v>4.4</v>
       </c>
       <c r="F147" t="n">
         <v>-5</v>
@@ -3392,10 +3392,10 @@
         <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>-4.625505687276267</v>
+        <v>-12.01544842174979</v>
       </c>
       <c r="E148" t="n">
-        <v>15.60436133093634</v>
+        <v>12.8</v>
       </c>
       <c r="F148" t="n">
         <v>-3.5</v>
@@ -3412,10 +3412,10 @@
         <v>-7</v>
       </c>
       <c r="D149" t="n">
-        <v>-9.987090316597991</v>
+        <v>-9.976100682743448</v>
       </c>
       <c r="E149" t="n">
-        <v>25.82896928185666</v>
+        <v>13.9</v>
       </c>
       <c r="F149" t="n">
         <v>2.5</v>
@@ -3432,10 +3432,10 @@
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>-9.136143835154144</v>
+        <v>-9.072845539237004</v>
       </c>
       <c r="E150" t="n">
-        <v>23.20629342042901</v>
+        <v>18.8</v>
       </c>
       <c r="F150" t="n">
         <v>-0.5</v>
@@ -3452,10 +3452,10 @@
         <v>15</v>
       </c>
       <c r="D151" t="n">
-        <v>-2.935237410363597</v>
+        <v>-9.050443784764134</v>
       </c>
       <c r="E151" t="n">
-        <v>14.15145170397967</v>
+        <v>20.6</v>
       </c>
       <c r="F151" t="n">
         <v>2.5</v>
@@ -3472,10 +3472,10 @@
         <v>-9</v>
       </c>
       <c r="D152" t="n">
-        <v>-9.895374177165435</v>
+        <v>-9.19299135802768</v>
       </c>
       <c r="E152" t="n">
-        <v>19.06194686759967</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F152" t="n">
         <v>-6.5</v>
@@ -3492,10 +3492,10 @@
         <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>-11.69239026870757</v>
+        <v>-11.48622657143187</v>
       </c>
       <c r="E153" t="n">
-        <v>14.92383750166467</v>
+        <v>5</v>
       </c>
       <c r="F153" t="n">
         <v>-5</v>
@@ -3512,10 +3512,10 @@
         <v>-7</v>
       </c>
       <c r="D154" t="n">
-        <v>-9.64569820174272</v>
+        <v>-12.33292625264692</v>
       </c>
       <c r="E154" t="n">
-        <v>22.47874814732634</v>
+        <v>10.8</v>
       </c>
       <c r="F154" t="n">
         <v>-5</v>
@@ -3532,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>-7.355745514850387</v>
+        <v>-8.749082119178086</v>
       </c>
       <c r="E155" t="n">
-        <v>22.47854612296866</v>
+        <v>9.9</v>
       </c>
       <c r="F155" t="n">
         <v>-6.5</v>
@@ -3552,10 +3552,10 @@
         <v>5</v>
       </c>
       <c r="D156" t="n">
-        <v>-9.195461721183083</v>
+        <v>-8.914449436079753</v>
       </c>
       <c r="E156" t="n">
-        <v>26.93283295857934</v>
+        <v>15.9</v>
       </c>
       <c r="F156" t="n">
         <v>-3.5</v>
@@ -3572,10 +3572,10 @@
         <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>-2.314928062750954</v>
+        <v>-3.178563438316917</v>
       </c>
       <c r="E157" t="n">
-        <v>20.46276671191</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F157" t="n">
         <v>2.5</v>
@@ -3592,10 +3592,10 @@
         <v>5</v>
       </c>
       <c r="D158" t="n">
-        <v>-11.30843776054484</v>
+        <v>-11.29514140666748</v>
       </c>
       <c r="E158" t="n">
-        <v>22.47228152539667</v>
+        <v>12.8</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -3612,10 +3612,10 @@
         <v>17</v>
       </c>
       <c r="D159" t="n">
-        <v>-11.9536445975417</v>
+        <v>-16.68234331642212</v>
       </c>
       <c r="E159" t="n">
-        <v>10.22300687087733</v>
+        <v>3.9</v>
       </c>
       <c r="F159" t="n">
         <v>5.5</v>
@@ -3635,7 +3635,7 @@
         <v>-17.327950736185</v>
       </c>
       <c r="E160" t="n">
-        <v>17.82948377477</v>
+        <v>17.9</v>
       </c>
       <c r="F160" t="n">
         <v>2.5</v>
@@ -3652,10 +3652,10 @@
         <v>5</v>
       </c>
       <c r="D161" t="n">
-        <v>-12.01083644464037</v>
+        <v>-11.49020960393287</v>
       </c>
       <c r="E161" t="n">
-        <v>18.057206418751</v>
+        <v>4.8</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -3672,10 +3672,10 @@
         <v>5</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.001198661039376339</v>
+        <v>-1.895934786610538</v>
       </c>
       <c r="E162" t="n">
-        <v>17.75788471176367</v>
+        <v>5.7</v>
       </c>
       <c r="F162" t="n">
         <v>-5</v>
@@ -3692,10 +3692,10 @@
         <v>-3</v>
       </c>
       <c r="D163" t="n">
-        <v>-8.387432706540702</v>
+        <v>-11.60328510091501</v>
       </c>
       <c r="E163" t="n">
-        <v>20.637077874338</v>
+        <v>5.9</v>
       </c>
       <c r="F163" t="n">
         <v>-9.5</v>
@@ -3712,10 +3712,10 @@
         <v>-1</v>
       </c>
       <c r="D164" t="n">
-        <v>-4.45411317932637</v>
+        <v>-4.872661986196267</v>
       </c>
       <c r="E164" t="n">
-        <v>21.45676954754367</v>
+        <v>13.7</v>
       </c>
       <c r="F164" t="n">
         <v>-6.5</v>
@@ -3732,10 +3732,10 @@
         <v>-1</v>
       </c>
       <c r="D165" t="n">
-        <v>-16.95431334119047</v>
+        <v>-16.53562999078624</v>
       </c>
       <c r="E165" t="n">
-        <v>17.02841818978666</v>
+        <v>23.9</v>
       </c>
       <c r="F165" t="n">
         <v>-0.5</v>
@@ -3755,7 +3755,7 @@
         <v>-10.779735566366</v>
       </c>
       <c r="E166" t="n">
-        <v>11.33198944358734</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -3772,10 +3772,10 @@
         <v>-5</v>
       </c>
       <c r="D167" t="n">
-        <v>-7.500132549605216</v>
+        <v>-7.441839040123449</v>
       </c>
       <c r="E167" t="n">
-        <v>18.537220113453</v>
+        <v>11.9</v>
       </c>
       <c r="F167" t="n">
         <v>2.5</v>
@@ -3792,10 +3792,10 @@
         <v>-1</v>
       </c>
       <c r="D168" t="n">
-        <v>-6.412622299039871</v>
+        <v>-8.540216823457699</v>
       </c>
       <c r="E168" t="n">
-        <v>25.16845822731134</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -3812,10 +3812,10 @@
         <v>-21</v>
       </c>
       <c r="D169" t="n">
-        <v>-11.50274668382925</v>
+        <v>-13.36124095935507</v>
       </c>
       <c r="E169" t="n">
-        <v>22.70551643426333</v>
+        <v>13</v>
       </c>
       <c r="F169" t="n">
         <v>-6.5</v>
@@ -3832,10 +3832,10 @@
         <v>5</v>
       </c>
       <c r="D170" t="n">
-        <v>-7.810157270555934</v>
+        <v>-7.941572000257956</v>
       </c>
       <c r="E170" t="n">
-        <v>26.35695956398466</v>
+        <v>13.9</v>
       </c>
       <c r="F170" t="n">
         <v>7</v>
@@ -3852,10 +3852,10 @@
         <v>-5</v>
       </c>
       <c r="D171" t="n">
-        <v>-13.18262270426717</v>
+        <v>-12.24259454888164</v>
       </c>
       <c r="E171" t="n">
-        <v>30.94725486091966</v>
+        <v>20.8</v>
       </c>
       <c r="F171" t="n">
         <v>2.5</v>
@@ -3875,7 +3875,7 @@
         <v>-9.577734981138333</v>
       </c>
       <c r="E172" t="n">
-        <v>15.71925304690433</v>
+        <v>13.7</v>
       </c>
       <c r="F172" t="n">
         <v>2.5</v>
@@ -3895,7 +3895,7 @@
         <v>-16.95493489049333</v>
       </c>
       <c r="E173" t="n">
-        <v>13.68718597351133</v>
+        <v>16.8</v>
       </c>
       <c r="F173" t="n">
         <v>-6.5</v>
@@ -3912,10 +3912,10 @@
         <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>-3.453453144980233</v>
+        <v>-7.956608854497154</v>
       </c>
       <c r="E174" t="n">
-        <v>19.12854591657266</v>
+        <v>21.5</v>
       </c>
       <c r="F174" t="n">
         <v>-3.5</v>
@@ -3932,10 +3932,10 @@
         <v>-7</v>
       </c>
       <c r="D175" t="n">
-        <v>-3.133346715671992</v>
+        <v>-6.940769548170551</v>
       </c>
       <c r="E175" t="n">
-        <v>26.12097972206333</v>
+        <v>13</v>
       </c>
       <c r="F175" t="n">
         <v>4</v>
@@ -3952,10 +3952,10 @@
         <v>-5</v>
       </c>
       <c r="D176" t="n">
-        <v>-7.757078391039805</v>
+        <v>-8.448732765702129</v>
       </c>
       <c r="E176" t="n">
-        <v>28.97672235434766</v>
+        <v>25.9</v>
       </c>
       <c r="F176" t="n">
         <v>7</v>
@@ -3972,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>-11.99323659834256</v>
+        <v>-11.73009639391955</v>
       </c>
       <c r="E177" t="n">
-        <v>19.34092084551867</v>
+        <v>15.9</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -3992,10 +3992,10 @@
         <v>13</v>
       </c>
       <c r="D178" t="n">
-        <v>-3.281831640220412</v>
+        <v>-16.77275246571654</v>
       </c>
       <c r="E178" t="n">
-        <v>10.46382605059667</v>
+        <v>9.9</v>
       </c>
       <c r="F178" t="n">
         <v>7</v>
@@ -4012,10 +4012,10 @@
         <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>-4.783695313578931</v>
+        <v>-7.272125353914878</v>
       </c>
       <c r="E179" t="n">
-        <v>25.28249126096267</v>
+        <v>15.9</v>
       </c>
       <c r="F179" t="n">
         <v>-0.5</v>
@@ -4032,10 +4032,10 @@
         <v>13</v>
       </c>
       <c r="D180" t="n">
-        <v>-16.31700225795535</v>
+        <v>-16.31510018076369</v>
       </c>
       <c r="E180" t="n">
-        <v>13.339337913493</v>
+        <v>11.9</v>
       </c>
       <c r="F180" t="n">
         <v>-2</v>
@@ -4052,10 +4052,10 @@
         <v>5</v>
       </c>
       <c r="D181" t="n">
-        <v>-13.07420854253809</v>
+        <v>-12.74747409402433</v>
       </c>
       <c r="E181" t="n">
-        <v>23.46429158656334</v>
+        <v>21</v>
       </c>
       <c r="F181" t="n">
         <v>5.5</v>
@@ -4072,10 +4072,10 @@
         <v>-3</v>
       </c>
       <c r="D182" t="n">
-        <v>-12.26930154271389</v>
+        <v>-13.55980417347203</v>
       </c>
       <c r="E182" t="n">
-        <v>25.163753473195</v>
+        <v>21</v>
       </c>
       <c r="F182" t="n">
         <v>8.5</v>
@@ -4092,10 +4092,10 @@
         <v>13</v>
       </c>
       <c r="D183" t="n">
-        <v>-13.36095364636664</v>
+        <v>-13.27490502800834</v>
       </c>
       <c r="E183" t="n">
-        <v>18.63266167389033</v>
+        <v>21.9</v>
       </c>
       <c r="F183" t="n">
         <v>7</v>
@@ -4112,10 +4112,10 @@
         <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>-12.74505890342086</v>
+        <v>-12.74484715468625</v>
       </c>
       <c r="E184" t="n">
-        <v>17.43275153446533</v>
+        <v>13.7</v>
       </c>
       <c r="F184" t="n">
         <v>7</v>
@@ -4132,10 +4132,10 @@
         <v>13</v>
       </c>
       <c r="D185" t="n">
-        <v>-9.99029182676494</v>
+        <v>-12.34849872044505</v>
       </c>
       <c r="E185" t="n">
-        <v>25.48877856881533</v>
+        <v>23</v>
       </c>
       <c r="F185" t="n">
         <v>-0.5</v>
@@ -4152,10 +4152,10 @@
         <v>-5</v>
       </c>
       <c r="D186" t="n">
-        <v>-7.040391776766211</v>
+        <v>-8.532723933054008</v>
       </c>
       <c r="E186" t="n">
-        <v>28.553573697286</v>
+        <v>21</v>
       </c>
       <c r="F186" t="n">
         <v>-0.5</v>
@@ -4172,10 +4172,10 @@
         <v>21</v>
       </c>
       <c r="D187" t="n">
-        <v>-7.607262825086485</v>
+        <v>-7.575287710323443</v>
       </c>
       <c r="E187" t="n">
-        <v>24.174324009251</v>
+        <v>12.2</v>
       </c>
       <c r="F187" t="n">
         <v>-8</v>
@@ -4195,7 +4195,7 @@
         <v>-11.86378417977766</v>
       </c>
       <c r="E188" t="n">
-        <v>14.002953535748</v>
+        <v>17</v>
       </c>
       <c r="F188" t="n">
         <v>5.5</v>
@@ -4212,10 +4212,10 @@
         <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>-11.61450749548561</v>
+        <v>-12.69125732972837</v>
       </c>
       <c r="E189" t="n">
-        <v>17.61299862964867</v>
+        <v>3</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -4232,10 +4232,10 @@
         <v>-7</v>
       </c>
       <c r="D190" t="n">
-        <v>-5.586624153264797</v>
+        <v>-7.146291150027026</v>
       </c>
       <c r="E190" t="n">
-        <v>31.335100257453</v>
+        <v>18.8</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -4252,10 +4252,10 @@
         <v>-7</v>
       </c>
       <c r="D191" t="n">
-        <v>-10.84890134982812</v>
+        <v>-10.73034245970168</v>
       </c>
       <c r="E191" t="n">
-        <v>21.452662093845</v>
+        <v>23</v>
       </c>
       <c r="F191" t="n">
         <v>-8</v>
@@ -4275,7 +4275,7 @@
         <v>-18.78829949929933</v>
       </c>
       <c r="E192" t="n">
-        <v>18.28904623895233</v>
+        <v>16.6</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -4292,10 +4292,10 @@
         <v>3</v>
       </c>
       <c r="D193" t="n">
-        <v>-2.887815954352151</v>
+        <v>-19.06989102055279</v>
       </c>
       <c r="E193" t="n">
-        <v>13.99128529932267</v>
+        <v>19.9</v>
       </c>
       <c r="F193" t="n">
         <v>8.5</v>
@@ -4312,10 +4312,10 @@
         <v>5</v>
       </c>
       <c r="D194" t="n">
-        <v>-5.20965717136976</v>
+        <v>-5.042595232131265</v>
       </c>
       <c r="E194" t="n">
-        <v>18.59254263076967</v>
+        <v>10.8</v>
       </c>
       <c r="F194" t="n">
         <v>-0.5</v>
@@ -4332,10 +4332,10 @@
         <v>-13</v>
       </c>
       <c r="D195" t="n">
-        <v>-7.473069277722995</v>
+        <v>-7.306725776447404</v>
       </c>
       <c r="E195" t="n">
-        <v>22.99189291802334</v>
+        <v>7.700000000000001</v>
       </c>
       <c r="F195" t="n">
         <v>-2</v>
@@ -4352,10 +4352,10 @@
         <v>5</v>
       </c>
       <c r="D196" t="n">
-        <v>-10.56592264519868</v>
+        <v>-11.2969328754405</v>
       </c>
       <c r="E196" t="n">
-        <v>15.20908951235</v>
+        <v>-3</v>
       </c>
       <c r="F196" t="n">
         <v>-0.5</v>
@@ -4372,10 +4372,10 @@
         <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>-11.1555516960386</v>
+        <v>-10.80408612837662</v>
       </c>
       <c r="E197" t="n">
-        <v>19.61551045871334</v>
+        <v>17.5</v>
       </c>
       <c r="F197" t="n">
         <v>-5</v>
@@ -4392,10 +4392,10 @@
         <v>11</v>
       </c>
       <c r="D198" t="n">
-        <v>-10.11911174143711</v>
+        <v>-10.88759817733926</v>
       </c>
       <c r="E198" t="n">
-        <v>25.48474490742166</v>
+        <v>17.9</v>
       </c>
       <c r="F198" t="n">
         <v>-0.5</v>
@@ -4412,10 +4412,10 @@
         <v>3</v>
       </c>
       <c r="D199" t="n">
-        <v>-13.15556335049672</v>
+        <v>-13.59431403174799</v>
       </c>
       <c r="E199" t="n">
-        <v>28.47303429922833</v>
+        <v>18.8</v>
       </c>
       <c r="F199" t="n">
         <v>8.5</v>
@@ -4432,10 +4432,10 @@
         <v>-5</v>
       </c>
       <c r="D200" t="n">
-        <v>-15.3980377477137</v>
+        <v>-16.73414753036879</v>
       </c>
       <c r="E200" t="n">
-        <v>31.68169414592333</v>
+        <v>25</v>
       </c>
       <c r="F200" t="n">
         <v>2.5</v>
@@ -4452,10 +4452,10 @@
         <v>15</v>
       </c>
       <c r="D201" t="n">
-        <v>-10.95326540722233</v>
+        <v>-12.17065885528252</v>
       </c>
       <c r="E201" t="n">
-        <v>19.06595943233867</v>
+        <v>13.9</v>
       </c>
       <c r="F201" t="n">
         <v>-0.5</v>
@@ -4472,10 +4472,10 @@
         <v>19</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.9158068485034693</v>
+        <v>-9.682425408507925</v>
       </c>
       <c r="E202" t="n">
-        <v>9.865613089515332</v>
+        <v>18.8</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -4492,10 +4492,10 @@
         <v>13</v>
       </c>
       <c r="D203" t="n">
-        <v>-4.378498004536794</v>
+        <v>-14.42541224847953</v>
       </c>
       <c r="E203" t="n">
-        <v>11.12159972784833</v>
+        <v>12.6</v>
       </c>
       <c r="F203" t="n">
         <v>7</v>
@@ -4512,10 +4512,10 @@
         <v>19</v>
       </c>
       <c r="D204" t="n">
-        <v>-10.03057398948505</v>
+        <v>-11.55982853942983</v>
       </c>
       <c r="E204" t="n">
-        <v>11.16513381193067</v>
+        <v>17</v>
       </c>
       <c r="F204" t="n">
         <v>2.5</v>
@@ -4532,10 +4532,10 @@
         <v>9</v>
       </c>
       <c r="D205" t="n">
-        <v>-4.789024205734929</v>
+        <v>-11.76448565489094</v>
       </c>
       <c r="E205" t="n">
-        <v>17.10392160109267</v>
+        <v>17.7</v>
       </c>
       <c r="F205" t="n">
         <v>4</v>
@@ -4552,10 +4552,10 @@
         <v>-3</v>
       </c>
       <c r="D206" t="n">
-        <v>-9.505837577766298</v>
+        <v>-8.468822193825609</v>
       </c>
       <c r="E206" t="n">
-        <v>21.57241372909534</v>
+        <v>12.8</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -4572,10 +4572,10 @@
         <v>-9</v>
       </c>
       <c r="D207" t="n">
-        <v>-7.413306100942973</v>
+        <v>-8.670738161587693</v>
       </c>
       <c r="E207" t="n">
-        <v>24.71799673401033</v>
+        <v>13.9</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4592,10 +4592,10 @@
         <v>7</v>
       </c>
       <c r="D208" t="n">
-        <v>-7.923954211901318</v>
+        <v>-7.822106310077424</v>
       </c>
       <c r="E208" t="n">
-        <v>24.82732154263734</v>
+        <v>13.9</v>
       </c>
       <c r="F208" t="n">
         <v>-14</v>
@@ -4612,10 +4612,10 @@
         <v>15</v>
       </c>
       <c r="D209" t="n">
-        <v>-12.1424300083945</v>
+        <v>-12.1449725681243</v>
       </c>
       <c r="E209" t="n">
-        <v>17.11165073963334</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F209" t="n">
         <v>-6.5</v>
@@ -4632,10 +4632,10 @@
         <v>19</v>
       </c>
       <c r="D210" t="n">
-        <v>0.189771052249965</v>
+        <v>-7.434250898971669</v>
       </c>
       <c r="E210" t="n">
-        <v>13.65322195203833</v>
+        <v>25</v>
       </c>
       <c r="F210" t="n">
         <v>4</v>
@@ -4652,10 +4652,10 @@
         <v>-1</v>
       </c>
       <c r="D211" t="n">
-        <v>-11.50232656995644</v>
+        <v>-10.35522160269771</v>
       </c>
       <c r="E211" t="n">
-        <v>21.42460350685733</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F211" t="n">
         <v>2.5</v>
@@ -4672,10 +4672,10 @@
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>-13.08023348561031</v>
+        <v>-12.97258588476429</v>
       </c>
       <c r="E212" t="n">
-        <v>17.751082392331</v>
+        <v>19</v>
       </c>
       <c r="F212" t="n">
         <v>5.5</v>
@@ -4692,10 +4692,10 @@
         <v>-5</v>
       </c>
       <c r="D213" t="n">
-        <v>-3.684155610634129</v>
+        <v>-7.268733793080433</v>
       </c>
       <c r="E213" t="n">
-        <v>30.22945989533867</v>
+        <v>23</v>
       </c>
       <c r="F213" t="n">
         <v>8.5</v>
@@ -4712,10 +4712,10 @@
         <v>1</v>
       </c>
       <c r="D214" t="n">
-        <v>-15.2702255243308</v>
+        <v>-14.64730992827486</v>
       </c>
       <c r="E214" t="n">
-        <v>35.23022079921367</v>
+        <v>29.9</v>
       </c>
       <c r="F214" t="n">
         <v>11.5</v>
@@ -4732,10 +4732,10 @@
         <v>-5</v>
       </c>
       <c r="D215" t="n">
-        <v>-6.543054640999251</v>
+        <v>-6.230069394523568</v>
       </c>
       <c r="E215" t="n">
-        <v>21.56557792666967</v>
+        <v>15.9</v>
       </c>
       <c r="F215" t="n">
         <v>-6.5</v>
@@ -4752,10 +4752,10 @@
         <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>-4.847741667883357</v>
+        <v>-5.029168024832028</v>
       </c>
       <c r="E216" t="n">
-        <v>26.38727666993267</v>
+        <v>21.9</v>
       </c>
       <c r="F216" t="n">
         <v>4</v>
@@ -4772,10 +4772,10 @@
         <v>-5</v>
       </c>
       <c r="D217" t="n">
-        <v>-17.28872639390702</v>
+        <v>-17.20137440692926</v>
       </c>
       <c r="E217" t="n">
-        <v>22.26648892708767</v>
+        <v>11</v>
       </c>
       <c r="F217" t="n">
         <v>-2</v>
@@ -4792,10 +4792,10 @@
         <v>5</v>
       </c>
       <c r="D218" t="n">
-        <v>-11.80088823287609</v>
+        <v>-11.79624044528628</v>
       </c>
       <c r="E218" t="n">
-        <v>13.82099777107867</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F218" t="n">
         <v>7</v>
@@ -4812,10 +4812,10 @@
         <v>13</v>
       </c>
       <c r="D219" t="n">
-        <v>-11.02382868130428</v>
+        <v>-16.74489113681049</v>
       </c>
       <c r="E219" t="n">
-        <v>19.53498977391067</v>
+        <v>29</v>
       </c>
       <c r="F219" t="n">
         <v>2.5</v>
@@ -4832,10 +4832,10 @@
         <v>13</v>
       </c>
       <c r="D220" t="n">
-        <v>-11.35815955113302</v>
+        <v>-11.34683513007241</v>
       </c>
       <c r="E220" t="n">
-        <v>20.26946970601567</v>
+        <v>19.7</v>
       </c>
       <c r="F220" t="n">
         <v>5.5</v>
@@ -4852,10 +4852,10 @@
         <v>11</v>
       </c>
       <c r="D221" t="n">
-        <v>-3.509281785520638</v>
+        <v>-4.672589326071132</v>
       </c>
       <c r="E221" t="n">
-        <v>28.390087495459</v>
+        <v>18.8</v>
       </c>
       <c r="F221" t="n">
         <v>4</v>
@@ -4872,10 +4872,10 @@
         <v>7</v>
       </c>
       <c r="D222" t="n">
-        <v>-5.498260117871711</v>
+        <v>-5.574994098887871</v>
       </c>
       <c r="E222" t="n">
-        <v>22.71329625519299</v>
+        <v>17.9</v>
       </c>
       <c r="F222" t="n">
         <v>-0.5</v>
@@ -4892,10 +4892,10 @@
         <v>7</v>
       </c>
       <c r="D223" t="n">
-        <v>-5.409645447224659</v>
+        <v>-7.561973782123608</v>
       </c>
       <c r="E223" t="n">
-        <v>17.41646088385834</v>
+        <v>12.8</v>
       </c>
       <c r="F223" t="n">
         <v>8.5</v>
@@ -4912,10 +4912,10 @@
         <v>-1</v>
       </c>
       <c r="D224" t="n">
-        <v>-2.839199133443187</v>
+        <v>-5.122821742112643</v>
       </c>
       <c r="E224" t="n">
-        <v>32.42604439523799</v>
+        <v>29</v>
       </c>
       <c r="F224" t="n">
         <v>2.5</v>
@@ -4932,10 +4932,10 @@
         <v>11</v>
       </c>
       <c r="D225" t="n">
-        <v>-8.04073175633431</v>
+        <v>-8.540376647193753</v>
       </c>
       <c r="E225" t="n">
-        <v>27.52415252065934</v>
+        <v>29.9</v>
       </c>
       <c r="F225" t="n">
         <v>2.5</v>
@@ -4952,10 +4952,10 @@
         <v>25</v>
       </c>
       <c r="D226" t="n">
-        <v>-14.38743398260755</v>
+        <v>-14.38422203108571</v>
       </c>
       <c r="E226" t="n">
-        <v>16.204725750983</v>
+        <v>21.9</v>
       </c>
       <c r="F226" t="n">
         <v>5.5</v>
@@ -4972,10 +4972,10 @@
         <v>19</v>
       </c>
       <c r="D227" t="n">
-        <v>-8.950023140363616</v>
+        <v>-12.3222490983983</v>
       </c>
       <c r="E227" t="n">
-        <v>16.43184094287233</v>
+        <v>25</v>
       </c>
       <c r="F227" t="n">
         <v>7</v>
@@ -4992,10 +4992,10 @@
         <v>-1</v>
       </c>
       <c r="D228" t="n">
-        <v>-8.714633246427132</v>
+        <v>-8.624119528586101</v>
       </c>
       <c r="E228" t="n">
-        <v>26.04001030107467</v>
+        <v>23</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -5012,10 +5012,10 @@
         <v>-7</v>
       </c>
       <c r="D229" t="n">
-        <v>-7.289469087245616</v>
+        <v>-7.642849585159722</v>
       </c>
       <c r="E229" t="n">
-        <v>25.87346509125967</v>
+        <v>15</v>
       </c>
       <c r="F229" t="n">
         <v>-6.5</v>
@@ -5032,10 +5032,10 @@
         <v>-7</v>
       </c>
       <c r="D230" t="n">
-        <v>-17.39220683906492</v>
+        <v>-19.21652899798538</v>
       </c>
       <c r="E230" t="n">
-        <v>33.84868293348767</v>
+        <v>24.8</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5055,7 +5055,7 @@
         <v>-7.446396844456115</v>
       </c>
       <c r="E231" t="n">
-        <v>16.976755776525</v>
+        <v>23.9</v>
       </c>
       <c r="F231" t="n">
         <v>11.5</v>
@@ -5072,10 +5072,10 @@
         <v>7</v>
       </c>
       <c r="D232" t="n">
-        <v>-5.14195479053839</v>
+        <v>-6.816178332842622</v>
       </c>
       <c r="E232" t="n">
-        <v>21.573612012491</v>
+        <v>19.9</v>
       </c>
       <c r="F232" t="n">
         <v>-3.5</v>
@@ -5092,10 +5092,10 @@
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>-4.679252717928261</v>
+        <v>-4.111224791603618</v>
       </c>
       <c r="E233" t="n">
-        <v>27.21703215587667</v>
+        <v>17.5</v>
       </c>
       <c r="F233" t="n">
         <v>2.5</v>
@@ -5112,10 +5112,10 @@
         <v>-9</v>
       </c>
       <c r="D234" t="n">
-        <v>-6.261242596952424</v>
+        <v>-7.431045844935011</v>
       </c>
       <c r="E234" t="n">
-        <v>28.251376989257</v>
+        <v>19.9</v>
       </c>
       <c r="F234" t="n">
         <v>7</v>
@@ -5132,10 +5132,10 @@
         <v>9</v>
       </c>
       <c r="D235" t="n">
-        <v>-2.357281889896629</v>
+        <v>-3.793921272312653</v>
       </c>
       <c r="E235" t="n">
-        <v>23.37783476154333</v>
+        <v>23.7</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -5152,10 +5152,10 @@
         <v>19</v>
       </c>
       <c r="D236" t="n">
-        <v>-7.866436034572412</v>
+        <v>-9.390426779972653</v>
       </c>
       <c r="E236" t="n">
-        <v>16.105030277009</v>
+        <v>14.6</v>
       </c>
       <c r="F236" t="n">
         <v>5.5</v>
@@ -5172,10 +5172,10 @@
         <v>19</v>
       </c>
       <c r="D237" t="n">
-        <v>-7.297282176305285</v>
+        <v>-6.645359241779041</v>
       </c>
       <c r="E237" t="n">
-        <v>32.42955292828499</v>
+        <v>34.8</v>
       </c>
       <c r="F237" t="n">
         <v>2.5</v>
@@ -5192,10 +5192,10 @@
         <v>17</v>
       </c>
       <c r="D238" t="n">
-        <v>-5.88992739227129</v>
+        <v>-6.659235330907647</v>
       </c>
       <c r="E238" t="n">
-        <v>20.94909571258101</v>
+        <v>17</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -5212,10 +5212,10 @@
         <v>3</v>
       </c>
       <c r="D239" t="n">
-        <v>-2.765562499404163</v>
+        <v>-7.389250931299761</v>
       </c>
       <c r="E239" t="n">
-        <v>32.48805640845934</v>
+        <v>27</v>
       </c>
       <c r="F239" t="n">
         <v>5.5</v>
@@ -5232,10 +5232,10 @@
         <v>15</v>
       </c>
       <c r="D240" t="n">
-        <v>-6.404833479266584</v>
+        <v>-6.601754772706715</v>
       </c>
       <c r="E240" t="n">
-        <v>23.42037800483533</v>
+        <v>21.9</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -5252,10 +5252,10 @@
         <v>17</v>
       </c>
       <c r="D241" t="n">
-        <v>0.02947461488847832</v>
+        <v>-10.54182006098494</v>
       </c>
       <c r="E241" t="n">
-        <v>16.20531318421867</v>
+        <v>23.9</v>
       </c>
       <c r="F241" t="n">
         <v>5.5</v>
@@ -5272,10 +5272,10 @@
         <v>19</v>
       </c>
       <c r="D242" t="n">
-        <v>-15.04747468156861</v>
+        <v>-15.04528412633056</v>
       </c>
       <c r="E242" t="n">
-        <v>15.456509011046</v>
+        <v>23.9</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
         <v>3</v>
       </c>
       <c r="D243" t="n">
-        <v>-4.556342360611381</v>
+        <v>-4.485149225985528</v>
       </c>
       <c r="E243" t="n">
-        <v>22.13254510000834</v>
+        <v>14.8</v>
       </c>
       <c r="F243" t="n">
         <v>7</v>
@@ -5312,10 +5312,10 @@
         <v>25</v>
       </c>
       <c r="D244" t="n">
-        <v>-7.737251243699927</v>
+        <v>-12.90464160657133</v>
       </c>
       <c r="E244" t="n">
-        <v>12.981032523332</v>
+        <v>15.7</v>
       </c>
       <c r="F244" t="n">
         <v>5.5</v>
@@ -5332,10 +5332,10 @@
         <v>11</v>
       </c>
       <c r="D245" t="n">
-        <v>-10.71621285077394</v>
+        <v>-10.64541686645118</v>
       </c>
       <c r="E245" t="n">
-        <v>29.22104037742233</v>
+        <v>23.9</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -5352,10 +5352,10 @@
         <v>9</v>
       </c>
       <c r="D246" t="n">
-        <v>-9.217409586010584</v>
+        <v>-10.34030639977348</v>
       </c>
       <c r="E246" t="n">
-        <v>25.454684983631</v>
+        <v>12.8</v>
       </c>
       <c r="F246" t="n">
         <v>4</v>
@@ -5375,7 +5375,7 @@
         <v>-10.19854567178833</v>
       </c>
       <c r="E247" t="n">
-        <v>21.395799113317</v>
+        <v>30.8</v>
       </c>
       <c r="F247" t="n">
         <v>8.5</v>
@@ -5392,10 +5392,10 @@
         <v>5</v>
       </c>
       <c r="D248" t="n">
-        <v>-4.775087633464747</v>
+        <v>-5.854820405046824</v>
       </c>
       <c r="E248" t="n">
-        <v>22.32425190993</v>
+        <v>18.8</v>
       </c>
       <c r="F248" t="n">
         <v>11.5</v>
@@ -5412,10 +5412,10 @@
         <v>19</v>
       </c>
       <c r="D249" t="n">
-        <v>-8.75473345732919</v>
+        <v>-8.740162907611163</v>
       </c>
       <c r="E249" t="n">
-        <v>19.29419368578666</v>
+        <v>22.8</v>
       </c>
       <c r="F249" t="n">
         <v>5.5</v>
@@ -5432,10 +5432,10 @@
         <v>-3</v>
       </c>
       <c r="D250" t="n">
-        <v>-7.678872355341176</v>
+        <v>-8.67301888488873</v>
       </c>
       <c r="E250" t="n">
-        <v>36.13987861262334</v>
+        <v>33</v>
       </c>
       <c r="F250" t="n">
         <v>4</v>
@@ -5452,10 +5452,10 @@
         <v>19</v>
       </c>
       <c r="D251" t="n">
-        <v>-15.24016999915097</v>
+        <v>-15.23558737691753</v>
       </c>
       <c r="E251" t="n">
-        <v>17.563518357887</v>
+        <v>24.8</v>
       </c>
       <c r="F251" t="n">
         <v>4</v>
@@ -5472,10 +5472,10 @@
         <v>11</v>
       </c>
       <c r="D252" t="n">
-        <v>-3.43980164710207</v>
+        <v>-9.342347585650238</v>
       </c>
       <c r="E252" t="n">
-        <v>18.24590804573333</v>
+        <v>25.7</v>
       </c>
       <c r="F252" t="n">
         <v>7</v>
@@ -5492,10 +5492,10 @@
         <v>7</v>
       </c>
       <c r="D253" t="n">
-        <v>-3.435231778414145</v>
+        <v>-4.00963828005715</v>
       </c>
       <c r="E253" t="n">
-        <v>27.708739370666</v>
+        <v>18.6</v>
       </c>
       <c r="F253" t="n">
         <v>11.5</v>
@@ -5512,10 +5512,10 @@
         <v>5</v>
       </c>
       <c r="D254" t="n">
-        <v>-4.889402727811387</v>
+        <v>-7.006825558338786</v>
       </c>
       <c r="E254" t="n">
-        <v>32.228989727148</v>
+        <v>21.9</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -5532,10 +5532,10 @@
         <v>5</v>
       </c>
       <c r="D255" t="n">
-        <v>-5.797566463404084</v>
+        <v>-9.100522115540389</v>
       </c>
       <c r="E255" t="n">
-        <v>30.83070522954</v>
+        <v>21.7</v>
       </c>
       <c r="F255" t="n">
         <v>7</v>
@@ -5552,10 +5552,10 @@
         <v>13</v>
       </c>
       <c r="D256" t="n">
-        <v>-4.973310721303375</v>
+        <v>-6.682488486241348</v>
       </c>
       <c r="E256" t="n">
-        <v>28.09674955151267</v>
+        <v>20.8</v>
       </c>
       <c r="F256" t="n">
         <v>8.5</v>
@@ -5572,10 +5572,10 @@
         <v>9</v>
       </c>
       <c r="D257" t="n">
-        <v>-6.209864742948916</v>
+        <v>-7.919839588373449</v>
       </c>
       <c r="E257" t="n">
-        <v>29.087873329436</v>
+        <v>22.8</v>
       </c>
       <c r="F257" t="n">
         <v>7</v>
@@ -5595,7 +5595,7 @@
         <v>-15.12649928222833</v>
       </c>
       <c r="E258" t="n">
-        <v>17.99642714603367</v>
+        <v>29</v>
       </c>
       <c r="F258" t="n">
         <v>13</v>
@@ -5612,10 +5612,10 @@
         <v>-1</v>
       </c>
       <c r="D259" t="n">
-        <v>-3.254303440564581</v>
+        <v>-4.38164053542964</v>
       </c>
       <c r="E259" t="n">
-        <v>26.25449518810233</v>
+        <v>16.8</v>
       </c>
       <c r="F259" t="n">
         <v>5.5</v>
@@ -5632,10 +5632,10 @@
         <v>3</v>
       </c>
       <c r="D260" t="n">
-        <v>-6.418861208992664</v>
+        <v>-9.879498904697027</v>
       </c>
       <c r="E260" t="n">
-        <v>17.993852194035</v>
+        <v>5.9</v>
       </c>
       <c r="F260" t="n">
         <v>7</v>
@@ -5652,10 +5652,10 @@
         <v>9</v>
       </c>
       <c r="D261" t="n">
-        <v>-4.813618164751131</v>
+        <v>-4.631422886825721</v>
       </c>
       <c r="E261" t="n">
-        <v>23.923594521896</v>
+        <v>14.6</v>
       </c>
       <c r="F261" t="n">
         <v>5.5</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="D262" t="n">
-        <v>-3.438170616582992</v>
+        <v>-12.30271398733113</v>
       </c>
       <c r="E262" t="n">
-        <v>15.53788465374367</v>
+        <v>21.7</v>
       </c>
       <c r="F262" t="n">
         <v>11.5</v>
@@ -5692,10 +5692,10 @@
         <v>15</v>
       </c>
       <c r="D263" t="n">
-        <v>-7.987289696632329</v>
+        <v>-7.837332993512454</v>
       </c>
       <c r="E263" t="n">
-        <v>25.64714583248534</v>
+        <v>24.6</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -5712,10 +5712,10 @@
         <v>15</v>
       </c>
       <c r="D264" t="n">
-        <v>-11.3589091729931</v>
+        <v>-11.30272089467063</v>
       </c>
       <c r="E264" t="n">
-        <v>16.224871216335</v>
+        <v>19.9</v>
       </c>
       <c r="F264" t="n">
         <v>-2</v>
@@ -5732,10 +5732,10 @@
         <v>5</v>
       </c>
       <c r="D265" t="n">
-        <v>-3.228280842997202</v>
+        <v>-2.232287562273741</v>
       </c>
       <c r="E265" t="n">
-        <v>28.06439939444967</v>
+        <v>31</v>
       </c>
       <c r="F265" t="n">
         <v>-0.5</v>
@@ -5752,10 +5752,10 @@
         <v>-1</v>
       </c>
       <c r="D266" t="n">
-        <v>-3.570683763884075</v>
+        <v>-8.845822814643235</v>
       </c>
       <c r="E266" t="n">
-        <v>25.73179738448</v>
+        <v>15.9</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
         <v>-17.40506405164033</v>
       </c>
       <c r="E267" t="n">
-        <v>17.16322721217467</v>
+        <v>17.9</v>
       </c>
       <c r="F267" t="n">
         <v>5.5</v>
@@ -5792,10 +5792,10 @@
         <v>7</v>
       </c>
       <c r="D268" t="n">
-        <v>-2.203720293217899</v>
+        <v>-7.497009722041158</v>
       </c>
       <c r="E268" t="n">
-        <v>19.20422328912067</v>
+        <v>26.8</v>
       </c>
       <c r="F268" t="n">
         <v>-8</v>
@@ -5812,10 +5812,10 @@
         <v>13</v>
       </c>
       <c r="D269" t="n">
-        <v>-6.415505613575615</v>
+        <v>-6.347089668468085</v>
       </c>
       <c r="E269" t="n">
-        <v>30.58630210081234</v>
+        <v>31.7</v>
       </c>
       <c r="F269" t="n">
         <v>5.5</v>
@@ -5832,10 +5832,10 @@
         <v>5</v>
       </c>
       <c r="D270" t="n">
-        <v>-2.911341647235053</v>
+        <v>-6.612981808812417</v>
       </c>
       <c r="E270" t="n">
-        <v>39.53597110189867</v>
+        <v>37</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -5852,10 +5852,10 @@
         <v>-1</v>
       </c>
       <c r="D271" t="n">
-        <v>-9.817911485894307</v>
+        <v>-11.06939687601137</v>
       </c>
       <c r="E271" t="n">
-        <v>26.83814809165667</v>
+        <v>13.9</v>
       </c>
       <c r="F271" t="n">
         <v>-5</v>
@@ -5872,10 +5872,10 @@
         <v>7</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.712513940075583</v>
+        <v>-3.758817514648497</v>
       </c>
       <c r="E272" t="n">
-        <v>28.53403028644767</v>
+        <v>29</v>
       </c>
       <c r="F272" t="n">
         <v>5.5</v>
@@ -5892,10 +5892,10 @@
         <v>27</v>
       </c>
       <c r="D273" t="n">
-        <v>-3.75514312000405</v>
+        <v>-4.051877556375617</v>
       </c>
       <c r="E273" t="n">
-        <v>24.36746685517334</v>
+        <v>22.8</v>
       </c>
       <c r="F273" t="n">
         <v>7</v>
@@ -5912,10 +5912,10 @@
         <v>27</v>
       </c>
       <c r="D274" t="n">
-        <v>-4.828637626402563</v>
+        <v>-10.52242670855952</v>
       </c>
       <c r="E274" t="n">
-        <v>20.391150467994</v>
+        <v>33.7</v>
       </c>
       <c r="F274" t="n">
         <v>8.5</v>
@@ -5935,7 +5935,7 @@
         <v>-15.126689506234</v>
       </c>
       <c r="E275" t="n">
-        <v>17.83556713642366</v>
+        <v>19.7</v>
       </c>
       <c r="F275" t="n">
         <v>14.5</v>
@@ -5952,10 +5952,10 @@
         <v>25</v>
       </c>
       <c r="D276" t="n">
-        <v>-7.08467258032735</v>
+        <v>-9.283689005874132</v>
       </c>
       <c r="E276" t="n">
-        <v>18.26141224587667</v>
+        <v>16.6</v>
       </c>
       <c r="F276" t="n">
         <v>8.5</v>
@@ -5972,10 +5972,10 @@
         <v>5</v>
       </c>
       <c r="D277" t="n">
-        <v>-8.136605569068719</v>
+        <v>-7.94424447213977</v>
       </c>
       <c r="E277" t="n">
-        <v>25.69596200162434</v>
+        <v>21</v>
       </c>
       <c r="F277" t="n">
         <v>8.5</v>
@@ -5992,10 +5992,10 @@
         <v>13</v>
       </c>
       <c r="D278" t="n">
-        <v>-3.811482240081952</v>
+        <v>-6.180337229755344</v>
       </c>
       <c r="E278" t="n">
-        <v>23.26743760899233</v>
+        <v>25</v>
       </c>
       <c r="F278" t="n">
         <v>5.5</v>
@@ -6012,10 +6012,10 @@
         <v>5</v>
       </c>
       <c r="D279" t="n">
-        <v>-6.227060881978123</v>
+        <v>-8.982461384875723</v>
       </c>
       <c r="E279" t="n">
-        <v>42.18608308836133</v>
+        <v>39</v>
       </c>
       <c r="F279" t="n">
         <v>5.5</v>
@@ -6032,10 +6032,10 @@
         <v>25</v>
       </c>
       <c r="D280" t="n">
-        <v>-8.143085559341998</v>
+        <v>-11.02713454495316</v>
       </c>
       <c r="E280" t="n">
-        <v>14.66575551978933</v>
+        <v>29</v>
       </c>
       <c r="F280" t="n">
         <v>13</v>
@@ -6052,10 +6052,10 @@
         <v>27</v>
       </c>
       <c r="D281" t="n">
-        <v>-14.26112285748353</v>
+        <v>-14.250355621725</v>
       </c>
       <c r="E281" t="n">
-        <v>19.65916067952233</v>
+        <v>25</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -6072,10 +6072,10 @@
         <v>11</v>
       </c>
       <c r="D282" t="n">
-        <v>-7.400224399640316</v>
+        <v>-7.381656604173806</v>
       </c>
       <c r="E282" t="n">
-        <v>27.00150338084534</v>
+        <v>25</v>
       </c>
       <c r="F282" t="n">
         <v>-2</v>
@@ -6092,10 +6092,10 @@
         <v>5</v>
       </c>
       <c r="D283" t="n">
-        <v>-0.4993645215905126</v>
+        <v>-1.583944458459632</v>
       </c>
       <c r="E283" t="n">
-        <v>35.272581929953</v>
+        <v>30.8</v>
       </c>
       <c r="F283" t="n">
         <v>8.5</v>
@@ -6112,10 +6112,10 @@
         <v>1</v>
       </c>
       <c r="D284" t="n">
-        <v>-4.725694631669865</v>
+        <v>-4.982880829079921</v>
       </c>
       <c r="E284" t="n">
-        <v>32.80021287712233</v>
+        <v>27</v>
       </c>
       <c r="F284" t="n">
         <v>7</v>
@@ -6132,10 +6132,10 @@
         <v>17</v>
       </c>
       <c r="D285" t="n">
-        <v>-2.117666316879573</v>
+        <v>-1.993944866098499</v>
       </c>
       <c r="E285" t="n">
-        <v>25.40815925761467</v>
+        <v>27.7</v>
       </c>
       <c r="F285" t="n">
         <v>10</v>
@@ -6152,10 +6152,10 @@
         <v>7</v>
       </c>
       <c r="D286" t="n">
-        <v>-7.985037150999328</v>
+        <v>-7.962965242945846</v>
       </c>
       <c r="E286" t="n">
-        <v>23.020538020452</v>
+        <v>28.8</v>
       </c>
       <c r="F286" t="n">
         <v>10</v>
@@ -6172,10 +6172,10 @@
         <v>13</v>
       </c>
       <c r="D287" t="n">
-        <v>-11.16683457530609</v>
+        <v>-11.165277873491</v>
       </c>
       <c r="E287" t="n">
-        <v>19.053231705786</v>
+        <v>21</v>
       </c>
       <c r="F287" t="n">
         <v>5.5</v>
@@ -6192,10 +6192,10 @@
         <v>19</v>
       </c>
       <c r="D288" t="n">
-        <v>-0.3918433483818384</v>
+        <v>-7.873822197284354</v>
       </c>
       <c r="E288" t="n">
-        <v>18.17724978411134</v>
+        <v>21.7</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -6212,10 +6212,10 @@
         <v>5</v>
       </c>
       <c r="D289" t="n">
-        <v>-5.533513439118139</v>
+        <v>-5.515009419003278</v>
       </c>
       <c r="E289" t="n">
-        <v>37.38019685279166</v>
+        <v>33.9</v>
       </c>
       <c r="F289" t="n">
         <v>10</v>
@@ -6232,10 +6232,10 @@
         <v>11</v>
       </c>
       <c r="D290" t="n">
-        <v>-4.514119109139783</v>
+        <v>-10.62394376937941</v>
       </c>
       <c r="E290" t="n">
-        <v>16.949235796886</v>
+        <v>30.8</v>
       </c>
       <c r="F290" t="n">
         <v>7</v>
@@ -6252,10 +6252,10 @@
         <v>5</v>
       </c>
       <c r="D291" t="n">
-        <v>-3.794936301388081</v>
+        <v>-4.861284849882093</v>
       </c>
       <c r="E291" t="n">
-        <v>36.05425615430333</v>
+        <v>29.9</v>
       </c>
       <c r="F291" t="n">
         <v>14.5</v>
@@ -6272,10 +6272,10 @@
         <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>-1.868006461205785</v>
+        <v>-5.133218124018798</v>
       </c>
       <c r="E292" t="n">
-        <v>41.61911645181066</v>
+        <v>41</v>
       </c>
       <c r="F292" t="n">
         <v>7</v>
@@ -6292,10 +6292,10 @@
         <v>3</v>
       </c>
       <c r="D293" t="n">
-        <v>-8.487256424324148</v>
+        <v>-8.421038212394912</v>
       </c>
       <c r="E293" t="n">
-        <v>35.86580219495001</v>
+        <v>31</v>
       </c>
       <c r="F293" t="n">
         <v>5.5</v>
@@ -6312,10 +6312,10 @@
         <v>27</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.4615949314952559</v>
+        <v>-7.958357982669678</v>
       </c>
       <c r="E294" t="n">
-        <v>12.49681531707133</v>
+        <v>31.9</v>
       </c>
       <c r="F294" t="n">
         <v>11.5</v>
@@ -6332,10 +6332,10 @@
         <v>11</v>
       </c>
       <c r="D295" t="n">
-        <v>-6.726785208849133</v>
+        <v>-7.403946284003434</v>
       </c>
       <c r="E295" t="n">
-        <v>22.74857809105333</v>
+        <v>23.9</v>
       </c>
       <c r="F295" t="n">
         <v>5.5</v>
@@ -6352,10 +6352,10 @@
         <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>0.7903124297893147</v>
+        <v>-1.924384022657788</v>
       </c>
       <c r="E296" t="n">
-        <v>19.74179834709667</v>
+        <v>16.8</v>
       </c>
       <c r="F296" t="n">
         <v>5.5</v>
@@ -6372,10 +6372,10 @@
         <v>13</v>
       </c>
       <c r="D297" t="n">
-        <v>1.259150034847251</v>
+        <v>-9.63065438938828</v>
       </c>
       <c r="E297" t="n">
-        <v>14.37639750065033</v>
+        <v>28.59999999999999</v>
       </c>
       <c r="F297" t="n">
         <v>7</v>
@@ -6392,10 +6392,10 @@
         <v>7</v>
       </c>
       <c r="D298" t="n">
-        <v>0.2660589705621955</v>
+        <v>-3.802405797042502</v>
       </c>
       <c r="E298" t="n">
-        <v>33.55122035597433</v>
+        <v>25.9</v>
       </c>
       <c r="F298" t="n">
         <v>10</v>
@@ -6412,10 +6412,10 @@
         <v>7</v>
       </c>
       <c r="D299" t="n">
-        <v>0.7226658532507435</v>
+        <v>-2.270559716689897</v>
       </c>
       <c r="E299" t="n">
-        <v>31.60772156443067</v>
+        <v>20.8</v>
       </c>
       <c r="F299" t="n">
         <v>10</v>
@@ -6432,10 +6432,10 @@
         <v>21</v>
       </c>
       <c r="D300" t="n">
-        <v>0.2576734642221194</v>
+        <v>-5.067145124015414</v>
       </c>
       <c r="E300" t="n">
-        <v>24.78750841856567</v>
+        <v>31.9</v>
       </c>
       <c r="F300" t="n">
         <v>13</v>
@@ -6452,10 +6452,10 @@
         <v>5</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.4662251834461429</v>
+        <v>-3.739643154692642</v>
       </c>
       <c r="E301" t="n">
-        <v>35.58509701633299</v>
+        <v>31.9</v>
       </c>
       <c r="F301" t="n">
         <v>5.5</v>
@@ -6472,10 +6472,10 @@
         <v>7</v>
       </c>
       <c r="D302" t="n">
-        <v>0.9643306499368702</v>
+        <v>-3.418293055915066</v>
       </c>
       <c r="E302" t="n">
-        <v>35.33580163024466</v>
+        <v>30.8</v>
       </c>
       <c r="F302" t="n">
         <v>13</v>
@@ -6492,10 +6492,10 @@
         <v>5</v>
       </c>
       <c r="D303" t="n">
-        <v>-3.573300883436743</v>
+        <v>-4.344905760267247</v>
       </c>
       <c r="E303" t="n">
-        <v>28.23806951724033</v>
+        <v>24.8</v>
       </c>
       <c r="F303" t="n">
         <v>7</v>
@@ -6512,10 +6512,10 @@
         <v>19</v>
       </c>
       <c r="D304" t="n">
-        <v>-14.32837067802312</v>
+        <v>-15.2933712096641</v>
       </c>
       <c r="E304" t="n">
-        <v>19.35845911684167</v>
+        <v>29</v>
       </c>
       <c r="F304" t="n">
         <v>11.5</v>
@@ -6532,10 +6532,10 @@
         <v>7</v>
       </c>
       <c r="D305" t="n">
-        <v>0.03621433748967851</v>
+        <v>-2.833311277806506</v>
       </c>
       <c r="E305" t="n">
-        <v>16.43695601097667</v>
+        <v>21.9</v>
       </c>
       <c r="F305" t="n">
         <v>11.5</v>
@@ -6552,10 +6552,10 @@
         <v>19</v>
       </c>
       <c r="D306" t="n">
-        <v>3.373230767943563</v>
+        <v>-6.487566266327902</v>
       </c>
       <c r="E306" t="n">
-        <v>15.987016121719</v>
+        <v>35.5</v>
       </c>
       <c r="F306" t="n">
         <v>11.5</v>
@@ -6572,10 +6572,10 @@
         <v>13</v>
       </c>
       <c r="D307" t="n">
-        <v>0.2170615272184949</v>
+        <v>-0.597558805795496</v>
       </c>
       <c r="E307" t="n">
-        <v>30.16622610562433</v>
+        <v>27.9</v>
       </c>
       <c r="F307" t="n">
         <v>16</v>
@@ -6592,10 +6592,10 @@
         <v>17</v>
       </c>
       <c r="D308" t="n">
-        <v>-5.276239570111677</v>
+        <v>-7.007631493657506</v>
       </c>
       <c r="E308" t="n">
-        <v>24.536525404359</v>
+        <v>30.6</v>
       </c>
       <c r="F308" t="n">
         <v>4</v>
@@ -6615,7 +6615,7 @@
         <v>-6.356009385510418</v>
       </c>
       <c r="E309" t="n">
-        <v>17.393679033814</v>
+        <v>15.9</v>
       </c>
       <c r="F309" t="n">
         <v>14.5</v>
@@ -6632,10 +6632,10 @@
         <v>25</v>
       </c>
       <c r="D310" t="n">
-        <v>0.7959461517822991</v>
+        <v>-12.60793338696019</v>
       </c>
       <c r="E310" t="n">
-        <v>16.71627742160167</v>
+        <v>32.8</v>
       </c>
       <c r="F310" t="n">
         <v>11.5</v>
@@ -6652,10 +6652,10 @@
         <v>13</v>
       </c>
       <c r="D311" t="n">
-        <v>-10.64483123800845</v>
+        <v>-10.55619850873314</v>
       </c>
       <c r="E311" t="n">
-        <v>24.72526196041867</v>
+        <v>20.6</v>
       </c>
       <c r="F311" t="n">
         <v>8.5</v>
@@ -6672,10 +6672,10 @@
         <v>3</v>
       </c>
       <c r="D312" t="n">
-        <v>-5.075990451452213</v>
+        <v>-8.036085399538264</v>
       </c>
       <c r="E312" t="n">
-        <v>39.15008529334899</v>
+        <v>32.8</v>
       </c>
       <c r="F312" t="n">
         <v>11.5</v>
@@ -6692,10 +6692,10 @@
         <v>3</v>
       </c>
       <c r="D313" t="n">
-        <v>-6.393016264495411</v>
+        <v>-7.133811441293342</v>
       </c>
       <c r="E313" t="n">
-        <v>36.89547147959767</v>
+        <v>35</v>
       </c>
       <c r="F313" t="n">
         <v>5.5</v>
@@ -6712,10 +6712,10 @@
         <v>-1</v>
       </c>
       <c r="D314" t="n">
-        <v>-0.8691770631292888</v>
+        <v>-1.537075693521595</v>
       </c>
       <c r="E314" t="n">
-        <v>35.58164163221534</v>
+        <v>29</v>
       </c>
       <c r="F314" t="n">
         <v>11.5</v>
@@ -6732,10 +6732,10 @@
         <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>-3.879029007766664</v>
+        <v>-4.000693130585137</v>
       </c>
       <c r="E315" t="n">
-        <v>30.50833854118434</v>
+        <v>23.9</v>
       </c>
       <c r="F315" t="n">
         <v>17.5</v>
@@ -6752,10 +6752,10 @@
         <v>7</v>
       </c>
       <c r="D316" t="n">
-        <v>-6.473163733607032</v>
+        <v>-7.442802803480682</v>
       </c>
       <c r="E316" t="n">
-        <v>31.05376583514734</v>
+        <v>30.6</v>
       </c>
       <c r="F316" t="n">
         <v>-2</v>
@@ -6772,10 +6772,10 @@
         <v>15</v>
       </c>
       <c r="D317" t="n">
-        <v>0.710262111033396</v>
+        <v>0.321256182415646</v>
       </c>
       <c r="E317" t="n">
-        <v>34.20186135780467</v>
+        <v>33.5</v>
       </c>
       <c r="F317" t="n">
         <v>13</v>
@@ -6792,10 +6792,10 @@
         <v>5</v>
       </c>
       <c r="D318" t="n">
-        <v>-5.691941688903588</v>
+        <v>-6.598016050430667</v>
       </c>
       <c r="E318" t="n">
-        <v>27.613971588049</v>
+        <v>16.8</v>
       </c>
       <c r="F318" t="n">
         <v>10</v>
@@ -6812,10 +6812,10 @@
         <v>5</v>
       </c>
       <c r="D319" t="n">
-        <v>-4.193271692025409</v>
+        <v>-6.205783364635726</v>
       </c>
       <c r="E319" t="n">
-        <v>32.71598843919433</v>
+        <v>25.7</v>
       </c>
       <c r="F319" t="n">
         <v>8.5</v>
@@ -6832,10 +6832,10 @@
         <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>-2.268129434403098</v>
+        <v>-4.879434422761875</v>
       </c>
       <c r="E320" t="n">
-        <v>32.381576241671</v>
+        <v>25.7</v>
       </c>
       <c r="F320" t="n">
         <v>14.5</v>
@@ -6852,10 +6852,10 @@
         <v>1</v>
       </c>
       <c r="D321" t="n">
-        <v>-7.36555270706697</v>
+        <v>-8.815660834151867</v>
       </c>
       <c r="E321" t="n">
-        <v>34.23616506206334</v>
+        <v>27</v>
       </c>
       <c r="F321" t="n">
         <v>5.5</v>
@@ -6872,10 +6872,10 @@
         <v>3</v>
       </c>
       <c r="D322" t="n">
-        <v>-4.42749644768507</v>
+        <v>-4.880041842271443</v>
       </c>
       <c r="E322" t="n">
-        <v>35.92608430005633</v>
+        <v>29</v>
       </c>
       <c r="F322" t="n">
         <v>16</v>
@@ -6892,10 +6892,10 @@
         <v>5</v>
       </c>
       <c r="D323" t="n">
-        <v>2.039334867911757</v>
+        <v>1.3390683303161</v>
       </c>
       <c r="E323" t="n">
-        <v>34.97966505330734</v>
+        <v>33.7</v>
       </c>
       <c r="F323" t="n">
         <v>16</v>
@@ -6912,10 +6912,10 @@
         <v>21</v>
       </c>
       <c r="D324" t="n">
-        <v>-5.740553170649887</v>
+        <v>-7.534882036620827</v>
       </c>
       <c r="E324" t="n">
-        <v>23.418515655483</v>
+        <v>29.9</v>
       </c>
       <c r="F324" t="n">
         <v>13</v>
@@ -6932,10 +6932,10 @@
         <v>9</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.4069133416162241</v>
+        <v>-1.437938527968541</v>
       </c>
       <c r="E325" t="n">
-        <v>29.28475414767667</v>
+        <v>37</v>
       </c>
       <c r="F325" t="n">
         <v>8.5</v>
@@ -6952,10 +6952,10 @@
         <v>9</v>
       </c>
       <c r="D326" t="n">
-        <v>0.1003360646751157</v>
+        <v>-3.084487384043165</v>
       </c>
       <c r="E326" t="n">
-        <v>36.18201474752634</v>
+        <v>31.9</v>
       </c>
       <c r="F326" t="n">
         <v>11.5</v>
@@ -6972,10 +6972,10 @@
         <v>7</v>
       </c>
       <c r="D327" t="n">
-        <v>-3.779729640919812</v>
+        <v>-4.984577567865049</v>
       </c>
       <c r="E327" t="n">
-        <v>33.735462231131</v>
+        <v>33.9</v>
       </c>
       <c r="F327" t="n">
         <v>14.5</v>
@@ -6992,10 +6992,10 @@
         <v>23</v>
       </c>
       <c r="D328" t="n">
-        <v>-8.123311735309098</v>
+        <v>-12.47954626896995</v>
       </c>
       <c r="E328" t="n">
-        <v>21.45077111327133</v>
+        <v>30.8</v>
       </c>
       <c r="F328" t="n">
         <v>14.5</v>
@@ -7012,10 +7012,10 @@
         <v>29</v>
       </c>
       <c r="D329" t="n">
-        <v>-10.77593762845453</v>
+        <v>-10.71310955210427</v>
       </c>
       <c r="E329" t="n">
-        <v>19.25307012132966</v>
+        <v>28.8</v>
       </c>
       <c r="F329" t="n">
         <v>16</v>
@@ -7032,10 +7032,10 @@
         <v>1</v>
       </c>
       <c r="D330" t="n">
-        <v>-1.219732981974441</v>
+        <v>-4.214159442252412</v>
       </c>
       <c r="E330" t="n">
-        <v>38.19464518045767</v>
+        <v>33.9</v>
       </c>
       <c r="F330" t="n">
         <v>10</v>
@@ -7052,10 +7052,10 @@
         <v>25</v>
       </c>
       <c r="D331" t="n">
-        <v>-10.3102685074074</v>
+        <v>-10.32175432625408</v>
       </c>
       <c r="E331" t="n">
-        <v>20.46354366657334</v>
+        <v>31</v>
       </c>
       <c r="F331" t="n">
         <v>8.5</v>
@@ -7072,10 +7072,10 @@
         <v>15</v>
       </c>
       <c r="D332" t="n">
-        <v>-2.845079860183018</v>
+        <v>-3.847451207287437</v>
       </c>
       <c r="E332" t="n">
-        <v>28.389416073422</v>
+        <v>27.9</v>
       </c>
       <c r="F332" t="n">
         <v>11.5</v>
@@ -7092,10 +7092,10 @@
         <v>29</v>
       </c>
       <c r="D333" t="n">
-        <v>3.103581785408593</v>
+        <v>-7.577111428170915</v>
       </c>
       <c r="E333" t="n">
-        <v>14.010874535891</v>
+        <v>30.8</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -7112,10 +7112,10 @@
         <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>-10.21215489948594</v>
+        <v>-12.39685699336666</v>
       </c>
       <c r="E334" t="n">
-        <v>35.77153610255134</v>
+        <v>31</v>
       </c>
       <c r="F334" t="n">
         <v>14.5</v>
@@ -7132,10 +7132,10 @@
         <v>13</v>
       </c>
       <c r="D335" t="n">
-        <v>-3.020517630693476</v>
+        <v>-4.536191961028859</v>
       </c>
       <c r="E335" t="n">
-        <v>25.60363242285267</v>
+        <v>33</v>
       </c>
       <c r="F335" t="n">
         <v>13</v>
@@ -7152,10 +7152,10 @@
         <v>17</v>
       </c>
       <c r="D336" t="n">
-        <v>-4.093351654722113</v>
+        <v>-3.793876976120675</v>
       </c>
       <c r="E336" t="n">
-        <v>21.80066737088466</v>
+        <v>20.8</v>
       </c>
       <c r="F336" t="n">
         <v>7</v>
@@ -7172,10 +7172,10 @@
         <v>3</v>
       </c>
       <c r="D337" t="n">
-        <v>6.48922230523368</v>
+        <v>1.892030835894608</v>
       </c>
       <c r="E337" t="n">
-        <v>32.889556133546</v>
+        <v>26.8</v>
       </c>
       <c r="F337" t="n">
         <v>7</v>
@@ -7192,10 +7192,10 @@
         <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>-7.095121472693053</v>
+        <v>-6.876610785137544</v>
       </c>
       <c r="E338" t="n">
-        <v>37.64260068767533</v>
+        <v>35</v>
       </c>
       <c r="F338" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
         <v>13</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.085180728999872</v>
+        <v>-1.615861001382153</v>
       </c>
       <c r="E339" t="n">
-        <v>34.76827967386233</v>
+        <v>34.8</v>
       </c>
       <c r="F339" t="n">
         <v>11.5</v>
@@ -7232,10 +7232,10 @@
         <v>13</v>
       </c>
       <c r="D340" t="n">
-        <v>-4.892061369123541</v>
+        <v>-5.341940188564537</v>
       </c>
       <c r="E340" t="n">
-        <v>28.090979323786</v>
+        <v>20.8</v>
       </c>
       <c r="F340" t="n">
         <v>10</v>
@@ -7252,10 +7252,10 @@
         <v>21</v>
       </c>
       <c r="D341" t="n">
-        <v>-5.38430257359999</v>
+        <v>-5.309355549382947</v>
       </c>
       <c r="E341" t="n">
-        <v>28.833293900146</v>
+        <v>32.59999999999999</v>
       </c>
       <c r="F341" t="n">
         <v>16</v>
@@ -7272,10 +7272,10 @@
         <v>-1</v>
       </c>
       <c r="D342" t="n">
-        <v>-2.191336261045447</v>
+        <v>-5.062973998838486</v>
       </c>
       <c r="E342" t="n">
-        <v>33.65344252135233</v>
+        <v>29.9</v>
       </c>
       <c r="F342" t="n">
         <v>13</v>
@@ -7292,10 +7292,10 @@
         <v>5</v>
       </c>
       <c r="D343" t="n">
-        <v>-4.695256128500358</v>
+        <v>-3.868067795346402</v>
       </c>
       <c r="E343" t="n">
-        <v>32.18209724749799</v>
+        <v>25.9</v>
       </c>
       <c r="F343" t="n">
         <v>13</v>
@@ -7312,10 +7312,10 @@
         <v>21</v>
       </c>
       <c r="D344" t="n">
-        <v>0.6316923717922339</v>
+        <v>-1.295206924452152</v>
       </c>
       <c r="E344" t="n">
-        <v>17.529346523967</v>
+        <v>25.7</v>
       </c>
       <c r="F344" t="n">
         <v>11.5</v>
@@ -7332,10 +7332,10 @@
         <v>9</v>
       </c>
       <c r="D345" t="n">
-        <v>-5.700567998329567</v>
+        <v>-4.563509516184059</v>
       </c>
       <c r="E345" t="n">
-        <v>36.201077976308</v>
+        <v>31.9</v>
       </c>
       <c r="F345" t="n">
         <v>11.5</v>
@@ -7352,10 +7352,10 @@
         <v>21</v>
       </c>
       <c r="D346" t="n">
-        <v>-1.585876603322819</v>
+        <v>-4.52968578496577</v>
       </c>
       <c r="E346" t="n">
-        <v>20.23228265075233</v>
+        <v>31</v>
       </c>
       <c r="F346" t="n">
         <v>14.5</v>
@@ -7372,10 +7372,10 @@
         <v>7</v>
       </c>
       <c r="D347" t="n">
-        <v>5.676346595035784</v>
+        <v>0.5616403015032345</v>
       </c>
       <c r="E347" t="n">
-        <v>35.08550185927834</v>
+        <v>32.8</v>
       </c>
       <c r="F347" t="n">
         <v>8.5</v>
@@ -7392,10 +7392,10 @@
         <v>9</v>
       </c>
       <c r="D348" t="n">
-        <v>-2.472756979682732</v>
+        <v>-1.932480718018562</v>
       </c>
       <c r="E348" t="n">
-        <v>34.27007098076233</v>
+        <v>33.9</v>
       </c>
       <c r="F348" t="n">
         <v>16</v>
@@ -7412,10 +7412,10 @@
         <v>7</v>
       </c>
       <c r="D349" t="n">
-        <v>-0.4439779108983282</v>
+        <v>-2.492076983508796</v>
       </c>
       <c r="E349" t="n">
-        <v>26.69688394226766</v>
+        <v>19.9</v>
       </c>
       <c r="F349" t="n">
         <v>13</v>
@@ -7432,10 +7432,10 @@
         <v>11</v>
       </c>
       <c r="D350" t="n">
-        <v>-6.448584665110273</v>
+        <v>-6.866377835308298</v>
       </c>
       <c r="E350" t="n">
-        <v>32.634323181295</v>
+        <v>41.7</v>
       </c>
       <c r="F350" t="n">
         <v>5.5</v>
@@ -7452,10 +7452,10 @@
         <v>5</v>
       </c>
       <c r="D351" t="n">
-        <v>-7.566577488104839</v>
+        <v>-8.46601744993502</v>
       </c>
       <c r="E351" t="n">
-        <v>36.11525426202067</v>
+        <v>31</v>
       </c>
       <c r="F351" t="n">
         <v>5.5</v>
@@ -7472,10 +7472,10 @@
         <v>11</v>
       </c>
       <c r="D352" t="n">
-        <v>-8.880892049281185</v>
+        <v>-8.503358770040659</v>
       </c>
       <c r="E352" t="n">
-        <v>20.591105222063</v>
+        <v>31</v>
       </c>
       <c r="F352" t="n">
         <v>8.5</v>
@@ -7492,10 +7492,10 @@
         <v>11</v>
       </c>
       <c r="D353" t="n">
-        <v>-1.660955974942209</v>
+        <v>-3.401522239735685</v>
       </c>
       <c r="E353" t="n">
-        <v>26.18851510371233</v>
+        <v>29.7</v>
       </c>
       <c r="F353" t="n">
         <v>5.5</v>
@@ -7512,10 +7512,10 @@
         <v>15</v>
       </c>
       <c r="D354" t="n">
-        <v>-2.658110135207915</v>
+        <v>-4.889302168656975</v>
       </c>
       <c r="E354" t="n">
-        <v>30.478425528297</v>
+        <v>39.9</v>
       </c>
       <c r="F354" t="n">
         <v>5.5</v>
@@ -7532,10 +7532,10 @@
         <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>-5.490078633711773</v>
+        <v>-5.45993309037005</v>
       </c>
       <c r="E355" t="n">
-        <v>35.032852630346</v>
+        <v>33</v>
       </c>
       <c r="F355" t="n">
         <v>14.5</v>
@@ -7552,10 +7552,10 @@
         <v>11</v>
       </c>
       <c r="D356" t="n">
-        <v>1.341187226662368</v>
+        <v>-2.72317301315674</v>
       </c>
       <c r="E356" t="n">
-        <v>22.099711201738</v>
+        <v>31.7</v>
       </c>
       <c r="F356" t="n">
         <v>14.5</v>
@@ -7572,10 +7572,10 @@
         <v>25</v>
       </c>
       <c r="D357" t="n">
-        <v>-6.596765238905945</v>
+        <v>-7.169360862597371</v>
       </c>
       <c r="E357" t="n">
-        <v>27.40018586449366</v>
+        <v>26.6</v>
       </c>
       <c r="F357" t="n">
         <v>13</v>
@@ -7592,10 +7592,10 @@
         <v>29</v>
       </c>
       <c r="D358" t="n">
-        <v>2.199237128919542</v>
+        <v>-10.81470985813223</v>
       </c>
       <c r="E358" t="n">
-        <v>19.02130073629234</v>
+        <v>39.7</v>
       </c>
       <c r="F358" t="n">
         <v>14.5</v>
@@ -7612,10 +7612,10 @@
         <v>27</v>
       </c>
       <c r="D359" t="n">
-        <v>-3.860796005515194</v>
+        <v>-8.107163803570021</v>
       </c>
       <c r="E359" t="n">
-        <v>22.37551146365533</v>
+        <v>29.9</v>
       </c>
       <c r="F359" t="n">
         <v>11.5</v>
@@ -7632,10 +7632,10 @@
         <v>17</v>
       </c>
       <c r="D360" t="n">
-        <v>-6.518297690789714</v>
+        <v>-6.220465292608457</v>
       </c>
       <c r="E360" t="n">
-        <v>33.24279725825234</v>
+        <v>41</v>
       </c>
       <c r="F360" t="n">
         <v>19</v>
@@ -7652,10 +7652,10 @@
         <v>33</v>
       </c>
       <c r="D361" t="n">
-        <v>-2.99605861540775</v>
+        <v>-5.504144096772184</v>
       </c>
       <c r="E361" t="n">
-        <v>25.85842943965367</v>
+        <v>32.4</v>
       </c>
       <c r="F361" t="n">
         <v>8.5</v>
@@ -7672,10 +7672,10 @@
         <v>13</v>
       </c>
       <c r="D362" t="n">
-        <v>-1.299638438191886</v>
+        <v>-2.475755123102916</v>
       </c>
       <c r="E362" t="n">
-        <v>25.29045606798767</v>
+        <v>24.8</v>
       </c>
       <c r="F362" t="n">
         <v>17.5</v>
@@ -7695,7 +7695,7 @@
         <v>-7.444069608672705</v>
       </c>
       <c r="E363" t="n">
-        <v>23.96082461255967</v>
+        <v>37.7</v>
       </c>
       <c r="F363" t="n">
         <v>14.5</v>
@@ -7712,10 +7712,10 @@
         <v>11</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.2255787347643977</v>
+        <v>-2.021784772990322</v>
       </c>
       <c r="E364" t="n">
-        <v>24.81168865968366</v>
+        <v>31</v>
       </c>
       <c r="F364" t="n">
         <v>14.5</v>
@@ -7732,10 +7732,10 @@
         <v>21</v>
       </c>
       <c r="D365" t="n">
-        <v>-2.364832621538956</v>
+        <v>-2.354104958383093</v>
       </c>
       <c r="E365" t="n">
-        <v>25.16079115020634</v>
+        <v>32.59999999999999</v>
       </c>
       <c r="F365" t="n">
         <v>19</v>
@@ -7752,10 +7752,10 @@
         <v>7</v>
       </c>
       <c r="D366" t="n">
-        <v>-2.932505382581877</v>
+        <v>-6.192040211684938</v>
       </c>
       <c r="E366" t="n">
-        <v>40.860692478919</v>
+        <v>39.9</v>
       </c>
       <c r="F366" t="n">
         <v>20.5</v>
@@ -7772,10 +7772,10 @@
         <v>15</v>
       </c>
       <c r="D367" t="n">
-        <v>-0.289597097934231</v>
+        <v>-5.675692005440896</v>
       </c>
       <c r="E367" t="n">
-        <v>29.82541817221967</v>
+        <v>42.8</v>
       </c>
       <c r="F367" t="n">
         <v>16</v>
@@ -7792,10 +7792,10 @@
         <v>23</v>
       </c>
       <c r="D368" t="n">
-        <v>-3.176979056667888</v>
+        <v>-6.218050842224281</v>
       </c>
       <c r="E368" t="n">
-        <v>25.63051650984567</v>
+        <v>39.9</v>
       </c>
       <c r="F368" t="n">
         <v>19</v>
@@ -7812,10 +7812,10 @@
         <v>9</v>
       </c>
       <c r="D369" t="n">
-        <v>-1.441045686318673</v>
+        <v>-3.07883011643317</v>
       </c>
       <c r="E369" t="n">
-        <v>33.61730786690067</v>
+        <v>25</v>
       </c>
       <c r="F369" t="n">
         <v>16</v>
@@ -7832,10 +7832,10 @@
         <v>15</v>
       </c>
       <c r="D370" t="n">
-        <v>1.923915978731449</v>
+        <v>0.4454353742164699</v>
       </c>
       <c r="E370" t="n">
-        <v>28.60542934657133</v>
+        <v>15.7</v>
       </c>
       <c r="F370" t="n">
         <v>19</v>
@@ -7852,10 +7852,10 @@
         <v>27</v>
       </c>
       <c r="D371" t="n">
-        <v>-5.277033262075838</v>
+        <v>-5.299662112462816</v>
       </c>
       <c r="E371" t="n">
-        <v>24.41624499099566</v>
+        <v>31.7</v>
       </c>
       <c r="F371" t="n">
         <v>20.5</v>
@@ -7872,10 +7872,10 @@
         <v>13</v>
       </c>
       <c r="D372" t="n">
-        <v>-2.417042113722116</v>
+        <v>-4.275349160139813</v>
       </c>
       <c r="E372" t="n">
-        <v>35.73038911119001</v>
+        <v>37.9</v>
       </c>
       <c r="F372" t="n">
         <v>20.5</v>
@@ -7892,10 +7892,10 @@
         <v>15</v>
       </c>
       <c r="D373" t="n">
-        <v>2.630601550761655</v>
+        <v>2.760114520882845</v>
       </c>
       <c r="E373" t="n">
-        <v>36.87268093071734</v>
+        <v>38.8</v>
       </c>
       <c r="F373" t="n">
         <v>11.5</v>
@@ -7912,10 +7912,10 @@
         <v>15</v>
       </c>
       <c r="D374" t="n">
-        <v>-0.8591835097729176</v>
+        <v>-2.233175560934974</v>
       </c>
       <c r="E374" t="n">
-        <v>26.870624501853</v>
+        <v>41</v>
       </c>
       <c r="F374" t="n">
         <v>11.5</v>
@@ -7932,10 +7932,10 @@
         <v>19</v>
       </c>
       <c r="D375" t="n">
-        <v>0.7189471127830031</v>
+        <v>-3.849263004804139</v>
       </c>
       <c r="E375" t="n">
-        <v>22.09762563955299</v>
+        <v>33.9</v>
       </c>
       <c r="F375" t="n">
         <v>13</v>
@@ -7952,10 +7952,10 @@
         <v>29</v>
       </c>
       <c r="D376" t="n">
-        <v>-7.417481373822811</v>
+        <v>-7.439318426871877</v>
       </c>
       <c r="E376" t="n">
-        <v>24.73418224488267</v>
+        <v>35.9</v>
       </c>
       <c r="F376" t="n">
         <v>16</v>
@@ -7972,10 +7972,10 @@
         <v>17</v>
       </c>
       <c r="D377" t="n">
-        <v>1.466218296418507</v>
+        <v>0.3988126622416603</v>
       </c>
       <c r="E377" t="n">
-        <v>33.621677874653</v>
+        <v>33.9</v>
       </c>
       <c r="F377" t="n">
         <v>17.5</v>
@@ -7992,10 +7992,10 @@
         <v>27</v>
       </c>
       <c r="D378" t="n">
-        <v>-5.344057382187115</v>
+        <v>-5.219605923776177</v>
       </c>
       <c r="E378" t="n">
-        <v>26.17443254696633</v>
+        <v>33</v>
       </c>
       <c r="F378" t="n">
         <v>10</v>
@@ -8012,10 +8012,10 @@
         <v>11</v>
       </c>
       <c r="D379" t="n">
-        <v>3.637790766022789</v>
+        <v>1.436115308975747</v>
       </c>
       <c r="E379" t="n">
-        <v>32.20459665391867</v>
+        <v>28.8</v>
       </c>
       <c r="F379" t="n">
         <v>20.5</v>
@@ -8032,10 +8032,10 @@
         <v>25</v>
       </c>
       <c r="D380" t="n">
-        <v>-2.456548758654752</v>
+        <v>-2.555545674890773</v>
       </c>
       <c r="E380" t="n">
-        <v>29.74079030107633</v>
+        <v>35.9</v>
       </c>
       <c r="F380" t="n">
         <v>16</v>
@@ -8052,10 +8052,10 @@
         <v>11</v>
       </c>
       <c r="D381" t="n">
-        <v>-4.917669059561872</v>
+        <v>-5.898584918723315</v>
       </c>
       <c r="E381" t="n">
-        <v>40.62008646653733</v>
+        <v>37</v>
       </c>
       <c r="F381" t="n">
         <v>14.5</v>
@@ -8072,10 +8072,10 @@
         <v>27</v>
       </c>
       <c r="D382" t="n">
-        <v>-1.378897340693517</v>
+        <v>-7.073209898845452</v>
       </c>
       <c r="E382" t="n">
-        <v>15.144833762076</v>
+        <v>31</v>
       </c>
       <c r="F382" t="n">
         <v>7</v>
@@ -8092,10 +8092,10 @@
         <v>29</v>
       </c>
       <c r="D383" t="n">
-        <v>-3.622122906877287</v>
+        <v>-3.622977285184998</v>
       </c>
       <c r="E383" t="n">
-        <v>23.53328144033433</v>
+        <v>40.8</v>
       </c>
       <c r="F383" t="n">
         <v>19</v>
@@ -8112,10 +8112,10 @@
         <v>33</v>
       </c>
       <c r="D384" t="n">
-        <v>-4.967068946429541</v>
+        <v>-9.917287036815873</v>
       </c>
       <c r="E384" t="n">
-        <v>21.49495391579</v>
+        <v>30.8</v>
       </c>
       <c r="F384" t="n">
         <v>13</v>
@@ -8132,10 +8132,10 @@
         <v>21</v>
       </c>
       <c r="D385" t="n">
-        <v>1.098811012321692</v>
+        <v>0.5373091015979023</v>
       </c>
       <c r="E385" t="n">
-        <v>34.37082512607066</v>
+        <v>25.5</v>
       </c>
       <c r="F385" t="n">
         <v>17.5</v>
@@ -8152,10 +8152,10 @@
         <v>15</v>
       </c>
       <c r="D386" t="n">
-        <v>3.264312784562697</v>
+        <v>-0.9602138229564685</v>
       </c>
       <c r="E386" t="n">
-        <v>18.585521226919</v>
+        <v>29.7</v>
       </c>
       <c r="F386" t="n">
         <v>14.5</v>
@@ -8175,7 +8175,7 @@
         <v>-2.535567183211558</v>
       </c>
       <c r="E387" t="n">
-        <v>26.819625825818</v>
+        <v>39.7</v>
       </c>
       <c r="F387" t="n">
         <v>10</v>
@@ -8192,10 +8192,10 @@
         <v>9</v>
       </c>
       <c r="D388" t="n">
-        <v>2.425108822759964</v>
+        <v>2.200141246463018</v>
       </c>
       <c r="E388" t="n">
-        <v>31.77986514060966</v>
+        <v>33.5</v>
       </c>
       <c r="F388" t="n">
         <v>11.5</v>
@@ -8212,10 +8212,10 @@
         <v>17</v>
       </c>
       <c r="D389" t="n">
-        <v>4.990178792278731</v>
+        <v>1.811103417675227</v>
       </c>
       <c r="E389" t="n">
-        <v>36.624215830046</v>
+        <v>34.8</v>
       </c>
       <c r="F389" t="n">
         <v>17.5</v>
@@ -8232,10 +8232,10 @@
         <v>43</v>
       </c>
       <c r="D390" t="n">
-        <v>-7.954697059217708</v>
+        <v>-9.225704108485532</v>
       </c>
       <c r="E390" t="n">
-        <v>21.641720642562</v>
+        <v>38.8</v>
       </c>
       <c r="F390" t="n">
         <v>14.5</v>
@@ -8252,10 +8252,10 @@
         <v>27</v>
       </c>
       <c r="D391" t="n">
-        <v>0.9694091165904808</v>
+        <v>-4.416245606870039</v>
       </c>
       <c r="E391" t="n">
-        <v>20.54766002710933</v>
+        <v>43</v>
       </c>
       <c r="F391" t="n">
         <v>14.5</v>
@@ -8272,10 +8272,10 @@
         <v>37</v>
       </c>
       <c r="D392" t="n">
-        <v>-1.049640475123921</v>
+        <v>-1.257155408909161</v>
       </c>
       <c r="E392" t="n">
-        <v>23.15425838396067</v>
+        <v>33.7</v>
       </c>
       <c r="F392" t="n">
         <v>16</v>
@@ -8292,10 +8292,10 @@
         <v>27</v>
       </c>
       <c r="D393" t="n">
-        <v>-3.722498394667944</v>
+        <v>-4.429092056794652</v>
       </c>
       <c r="E393" t="n">
-        <v>28.553135360503</v>
+        <v>38.59999999999999</v>
       </c>
       <c r="F393" t="n">
         <v>14.5</v>
@@ -8312,10 +8312,10 @@
         <v>9</v>
       </c>
       <c r="D394" t="n">
-        <v>-2.571000796427819</v>
+        <v>-2.148827803887845</v>
       </c>
       <c r="E394" t="n">
-        <v>36.80057756394567</v>
+        <v>33.9</v>
       </c>
       <c r="F394" t="n">
         <v>14.5</v>
@@ -8332,10 +8332,10 @@
         <v>31</v>
       </c>
       <c r="D395" t="n">
-        <v>-4.32795813513934</v>
+        <v>-6.628430276399285</v>
       </c>
       <c r="E395" t="n">
-        <v>19.77444007921467</v>
+        <v>37.9</v>
       </c>
       <c r="F395" t="n">
         <v>17.5</v>
@@ -8352,10 +8352,10 @@
         <v>25</v>
       </c>
       <c r="D396" t="n">
-        <v>-2.964252783687482</v>
+        <v>-2.811622576116387</v>
       </c>
       <c r="E396" t="n">
-        <v>26.56407210864267</v>
+        <v>34.8</v>
       </c>
       <c r="F396" t="n">
         <v>11.5</v>
@@ -8372,10 +8372,10 @@
         <v>3</v>
       </c>
       <c r="D397" t="n">
-        <v>3.176066527789172</v>
+        <v>1.516348024524294</v>
       </c>
       <c r="E397" t="n">
-        <v>44.959822960102</v>
+        <v>43.9</v>
       </c>
       <c r="F397" t="n">
         <v>19</v>
@@ -8392,10 +8392,10 @@
         <v>13</v>
       </c>
       <c r="D398" t="n">
-        <v>1.623641147792353</v>
+        <v>0.7759562547179837</v>
       </c>
       <c r="E398" t="n">
-        <v>34.47608441059567</v>
+        <v>34.8</v>
       </c>
       <c r="F398" t="n">
         <v>20.5</v>
@@ -8412,10 +8412,10 @@
         <v>37</v>
       </c>
       <c r="D399" t="n">
-        <v>-7.530559144770747</v>
+        <v>-7.521513945763667</v>
       </c>
       <c r="E399" t="n">
-        <v>22.73792292463867</v>
+        <v>37</v>
       </c>
       <c r="F399" t="n">
         <v>19</v>
@@ -8432,10 +8432,10 @@
         <v>21</v>
       </c>
       <c r="D400" t="n">
-        <v>6.433175689727761</v>
+        <v>5.906920073781943</v>
       </c>
       <c r="E400" t="n">
-        <v>32.99748448549066</v>
+        <v>28.8</v>
       </c>
       <c r="F400" t="n">
         <v>14.5</v>
@@ -8452,10 +8452,10 @@
         <v>7</v>
       </c>
       <c r="D401" t="n">
-        <v>-1.280516202048094</v>
+        <v>-1.152800133799763</v>
       </c>
       <c r="E401" t="n">
-        <v>38.605500882596</v>
+        <v>33.9</v>
       </c>
       <c r="F401" t="n">
         <v>17.5</v>
@@ -8472,10 +8472,10 @@
         <v>17</v>
       </c>
       <c r="D402" t="n">
-        <v>4.493101092526079</v>
+        <v>1.92235435186735</v>
       </c>
       <c r="E402" t="n">
-        <v>40.14588921125133</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F402" t="n">
         <v>13</v>
@@ -8492,10 +8492,10 @@
         <v>29</v>
       </c>
       <c r="D403" t="n">
-        <v>-2.432721101855826</v>
+        <v>-1.324647806147128</v>
       </c>
       <c r="E403" t="n">
-        <v>22.112958802467</v>
+        <v>28.8</v>
       </c>
       <c r="F403" t="n">
         <v>13</v>
@@ -8512,10 +8512,10 @@
         <v>7</v>
       </c>
       <c r="D404" t="n">
-        <v>1.877364424857602</v>
+        <v>-1.675220191202326</v>
       </c>
       <c r="E404" t="n">
-        <v>37.38664306346133</v>
+        <v>33.9</v>
       </c>
       <c r="F404" t="n">
         <v>17.5</v>
@@ -8532,10 +8532,10 @@
         <v>23</v>
       </c>
       <c r="D405" t="n">
-        <v>5.120590272830606</v>
+        <v>3.285523000699553</v>
       </c>
       <c r="E405" t="n">
-        <v>26.65768336713</v>
+        <v>33.5</v>
       </c>
       <c r="F405" t="n">
         <v>11.5</v>
@@ -8552,10 +8552,10 @@
         <v>13</v>
       </c>
       <c r="D406" t="n">
-        <v>3.241803186618125</v>
+        <v>1.498901900880139</v>
       </c>
       <c r="E406" t="n">
-        <v>32.117903060986</v>
+        <v>30.8</v>
       </c>
       <c r="F406" t="n">
         <v>16</v>
@@ -8575,7 +8575,7 @@
         <v>0.3891414475957227</v>
       </c>
       <c r="E407" t="n">
-        <v>26.85302717791667</v>
+        <v>35.7</v>
       </c>
       <c r="F407" t="n">
         <v>20.5</v>
@@ -8592,10 +8592,10 @@
         <v>21</v>
       </c>
       <c r="D408" t="n">
-        <v>-5.652963659332277</v>
+        <v>-5.627019008818197</v>
       </c>
       <c r="E408" t="n">
-        <v>29.04188806331533</v>
+        <v>36.8</v>
       </c>
       <c r="F408" t="n">
         <v>14.5</v>
@@ -8612,10 +8612,10 @@
         <v>35</v>
       </c>
       <c r="D409" t="n">
-        <v>-6.990062327078939</v>
+        <v>-7.430110984826372</v>
       </c>
       <c r="E409" t="n">
-        <v>23.38832109304567</v>
+        <v>39</v>
       </c>
       <c r="F409" t="n">
         <v>22</v>
@@ -8632,10 +8632,10 @@
         <v>13</v>
       </c>
       <c r="D410" t="n">
-        <v>1.955844981307868</v>
+        <v>0.1256179464703751</v>
       </c>
       <c r="E410" t="n">
-        <v>39.37992364423</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F410" t="n">
         <v>20.5</v>
@@ -8652,10 +8652,10 @@
         <v>29</v>
       </c>
       <c r="D411" t="n">
-        <v>-1.320152140318466</v>
+        <v>-5.092614484938498</v>
       </c>
       <c r="E411" t="n">
-        <v>22.83308003753633</v>
+        <v>38.8</v>
       </c>
       <c r="F411" t="n">
         <v>10</v>
@@ -8672,10 +8672,10 @@
         <v>29</v>
       </c>
       <c r="D412" t="n">
-        <v>-1.034970884928048</v>
+        <v>-4.108693146142889</v>
       </c>
       <c r="E412" t="n">
-        <v>22.728473418299</v>
+        <v>35.7</v>
       </c>
       <c r="F412" t="n">
         <v>13</v>
@@ -8692,10 +8692,10 @@
         <v>31</v>
       </c>
       <c r="D413" t="n">
-        <v>-6.506686879596511</v>
+        <v>-7.463804828800212</v>
       </c>
       <c r="E413" t="n">
-        <v>18.80164746082233</v>
+        <v>31.9</v>
       </c>
       <c r="F413" t="n">
         <v>17.5</v>
@@ -8712,10 +8712,10 @@
         <v>15</v>
       </c>
       <c r="D414" t="n">
-        <v>-0.8081940470902812</v>
+        <v>-1.055122844270363</v>
       </c>
       <c r="E414" t="n">
-        <v>33.84679247218434</v>
+        <v>31.5</v>
       </c>
       <c r="F414" t="n">
         <v>16</v>
@@ -8732,10 +8732,10 @@
         <v>11</v>
       </c>
       <c r="D415" t="n">
-        <v>-1.247453980613392</v>
+        <v>-1.215686709645218</v>
       </c>
       <c r="E415" t="n">
-        <v>37.79537297392832</v>
+        <v>33.9</v>
       </c>
       <c r="F415" t="n">
         <v>17.5</v>
@@ -8752,10 +8752,10 @@
         <v>27</v>
       </c>
       <c r="D416" t="n">
-        <v>-3.097635384737931</v>
+        <v>-4.396800403551372</v>
       </c>
       <c r="E416" t="n">
-        <v>28.47088445798333</v>
+        <v>38.8</v>
       </c>
       <c r="F416" t="n">
         <v>22</v>
@@ -8772,10 +8772,10 @@
         <v>9</v>
       </c>
       <c r="D417" t="n">
-        <v>1.589212068424359</v>
+        <v>-2.291263596076391</v>
       </c>
       <c r="E417" t="n">
-        <v>39.48348082439767</v>
+        <v>37</v>
       </c>
       <c r="F417" t="n">
         <v>22</v>
@@ -8792,10 +8792,10 @@
         <v>11</v>
       </c>
       <c r="D418" t="n">
-        <v>-0.9527170534632587</v>
+        <v>-1.338984177475091</v>
       </c>
       <c r="E418" t="n">
-        <v>41.41657256395333</v>
+        <v>39.9</v>
       </c>
       <c r="F418" t="n">
         <v>19</v>
@@ -8812,10 +8812,10 @@
         <v>31</v>
       </c>
       <c r="D419" t="n">
-        <v>1.749140368897689</v>
+        <v>-2.378608825728114</v>
       </c>
       <c r="E419" t="n">
-        <v>29.43201933441733</v>
+        <v>37.9</v>
       </c>
       <c r="F419" t="n">
         <v>20.5</v>
@@ -8832,10 +8832,10 @@
         <v>29</v>
       </c>
       <c r="D420" t="n">
-        <v>-4.466506986272396</v>
+        <v>-4.478171664319876</v>
       </c>
       <c r="E420" t="n">
-        <v>27.36827708866499</v>
+        <v>38.8</v>
       </c>
       <c r="F420" t="n">
         <v>19</v>
@@ -8852,10 +8852,10 @@
         <v>19</v>
       </c>
       <c r="D421" t="n">
-        <v>3.349463780859484</v>
+        <v>3.493919627918584</v>
       </c>
       <c r="E421" t="n">
-        <v>34.04588666410334</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F421" t="n">
         <v>20.5</v>
@@ -8872,10 +8872,10 @@
         <v>13</v>
       </c>
       <c r="D422" t="n">
-        <v>1.89536486302844</v>
+        <v>-0.4493073074287441</v>
       </c>
       <c r="E422" t="n">
-        <v>37.74736907150101</v>
+        <v>37.9</v>
       </c>
       <c r="F422" t="n">
         <v>19</v>
@@ -8892,10 +8892,10 @@
         <v>13</v>
       </c>
       <c r="D423" t="n">
-        <v>-2.153566372956333</v>
+        <v>-3.529479282034087</v>
       </c>
       <c r="E423" t="n">
-        <v>37.68185162446066</v>
+        <v>32.8</v>
       </c>
       <c r="F423" t="n">
         <v>20.5</v>
@@ -8912,10 +8912,10 @@
         <v>21</v>
       </c>
       <c r="D424" t="n">
-        <v>6.566300075481858</v>
+        <v>5.505363169646428</v>
       </c>
       <c r="E424" t="n">
-        <v>35.89190225965633</v>
+        <v>37.5</v>
       </c>
       <c r="F424" t="n">
         <v>16</v>
@@ -8932,10 +8932,10 @@
         <v>25</v>
       </c>
       <c r="D425" t="n">
-        <v>-2.240985015828472</v>
+        <v>-1.289749166080068</v>
       </c>
       <c r="E425" t="n">
-        <v>31.65561222249967</v>
+        <v>35.9</v>
       </c>
       <c r="F425" t="n">
         <v>17.5</v>
@@ -8952,10 +8952,10 @@
         <v>31</v>
       </c>
       <c r="D426" t="n">
-        <v>-6.334908006338511</v>
+        <v>-6.328346785914285</v>
       </c>
       <c r="E426" t="n">
-        <v>26.16624435053633</v>
+        <v>41.9</v>
       </c>
       <c r="F426" t="n">
         <v>19</v>
@@ -8975,7 +8975,7 @@
         <v>-2.245770890171666</v>
       </c>
       <c r="E427" t="n">
-        <v>26.341456402351</v>
+        <v>39.7</v>
       </c>
       <c r="F427" t="n">
         <v>20.5</v>
@@ -8992,10 +8992,10 @@
         <v>17</v>
       </c>
       <c r="D428" t="n">
-        <v>2.393039001757681</v>
+        <v>0.8586256083960975</v>
       </c>
       <c r="E428" t="n">
-        <v>38.794313148877</v>
+        <v>39.9</v>
       </c>
       <c r="F428" t="n">
         <v>20.5</v>
@@ -9012,10 +9012,10 @@
         <v>15</v>
       </c>
       <c r="D429" t="n">
-        <v>3.099026868778368</v>
+        <v>-1.440130905972663</v>
       </c>
       <c r="E429" t="n">
-        <v>39.89631697305434</v>
+        <v>33.9</v>
       </c>
       <c r="F429" t="n">
         <v>17.5</v>
@@ -9032,10 +9032,10 @@
         <v>43</v>
       </c>
       <c r="D430" t="n">
-        <v>-2.815439710802257</v>
+        <v>-6.031533531499718</v>
       </c>
       <c r="E430" t="n">
-        <v>23.08316423836266</v>
+        <v>38.59999999999999</v>
       </c>
       <c r="F430" t="n">
         <v>17.5</v>
@@ -9052,10 +9052,10 @@
         <v>41</v>
       </c>
       <c r="D431" t="n">
-        <v>-1.770205774874493</v>
+        <v>-6.483394036182426</v>
       </c>
       <c r="E431" t="n">
-        <v>17.71409776070367</v>
+        <v>39.7</v>
       </c>
       <c r="F431" t="n">
         <v>22</v>
@@ -9072,10 +9072,10 @@
         <v>35</v>
       </c>
       <c r="D432" t="n">
-        <v>2.783702214198911</v>
+        <v>-4.129181923723293</v>
       </c>
       <c r="E432" t="n">
-        <v>19.27533395865733</v>
+        <v>36.8</v>
       </c>
       <c r="F432" t="n">
         <v>14.5</v>
@@ -9092,10 +9092,10 @@
         <v>13</v>
       </c>
       <c r="D433" t="n">
-        <v>1.314292561826795</v>
+        <v>-0.5394951999804173</v>
       </c>
       <c r="E433" t="n">
-        <v>38.14835785045533</v>
+        <v>38.8</v>
       </c>
       <c r="F433" t="n">
         <v>19</v>
@@ -9112,10 +9112,10 @@
         <v>33</v>
       </c>
       <c r="D434" t="n">
-        <v>-4.917844974478849</v>
+        <v>-4.91737737000209</v>
       </c>
       <c r="E434" t="n">
-        <v>23.683605085458</v>
+        <v>37</v>
       </c>
       <c r="F434" t="n">
         <v>22</v>
@@ -9132,10 +9132,10 @@
         <v>11</v>
       </c>
       <c r="D435" t="n">
-        <v>-1.497531277696717</v>
+        <v>-1.629499795376638</v>
       </c>
       <c r="E435" t="n">
-        <v>36.07793882725733</v>
+        <v>33.9</v>
       </c>
       <c r="F435" t="n">
         <v>19</v>
@@ -9152,10 +9152,10 @@
         <v>17</v>
       </c>
       <c r="D436" t="n">
-        <v>-1.769214395192785</v>
+        <v>-2.000851078070042</v>
       </c>
       <c r="E436" t="n">
-        <v>30.256203043173</v>
+        <v>39</v>
       </c>
       <c r="F436" t="n">
         <v>23.5</v>
@@ -9172,10 +9172,10 @@
         <v>15</v>
       </c>
       <c r="D437" t="n">
-        <v>3.824111608488553</v>
+        <v>-0.6395139177057325</v>
       </c>
       <c r="E437" t="n">
-        <v>40.05386608388667</v>
+        <v>33.7</v>
       </c>
       <c r="F437" t="n">
         <v>16</v>
@@ -9192,10 +9192,10 @@
         <v>23</v>
       </c>
       <c r="D438" t="n">
-        <v>-3.806465006120005</v>
+        <v>-3.783377107596139</v>
       </c>
       <c r="E438" t="n">
-        <v>31.469218204187</v>
+        <v>39.7</v>
       </c>
       <c r="F438" t="n">
         <v>19</v>
@@ -9212,10 +9212,10 @@
         <v>13</v>
       </c>
       <c r="D439" t="n">
-        <v>1.819915568686496</v>
+        <v>-0.1908777370631428</v>
       </c>
       <c r="E439" t="n">
-        <v>40.96587991473233</v>
+        <v>39.9</v>
       </c>
       <c r="F439" t="n">
         <v>17.5</v>
@@ -9232,10 +9232,10 @@
         <v>31</v>
       </c>
       <c r="D440" t="n">
-        <v>6.749578445428652</v>
+        <v>4.759227350410999</v>
       </c>
       <c r="E440" t="n">
-        <v>24.14722187545367</v>
+        <v>33.09999999999999</v>
       </c>
       <c r="F440" t="n">
         <v>17.5</v>
@@ -9252,10 +9252,10 @@
         <v>11</v>
       </c>
       <c r="D441" t="n">
-        <v>0.4912947732289329</v>
+        <v>0.677884067585573</v>
       </c>
       <c r="E441" t="n">
-        <v>40.39307555039267</v>
+        <v>36.8</v>
       </c>
       <c r="F441" t="n">
         <v>17.5</v>
@@ -9272,10 +9272,10 @@
         <v>19</v>
       </c>
       <c r="D442" t="n">
-        <v>-0.1355764835746383</v>
+        <v>-0.07175836499018579</v>
       </c>
       <c r="E442" t="n">
-        <v>35.68884871921399</v>
+        <v>41.9</v>
       </c>
       <c r="F442" t="n">
         <v>19</v>
@@ -9292,10 +9292,10 @@
         <v>7</v>
       </c>
       <c r="D443" t="n">
-        <v>1.42974244017267</v>
+        <v>-1.541966372324565</v>
       </c>
       <c r="E443" t="n">
-        <v>41.035525947503</v>
+        <v>41</v>
       </c>
       <c r="F443" t="n">
         <v>19</v>
@@ -9312,10 +9312,10 @@
         <v>11</v>
       </c>
       <c r="D444" t="n">
-        <v>0.5372660068202321</v>
+        <v>-1.084744409189314</v>
       </c>
       <c r="E444" t="n">
-        <v>41.90722546470133</v>
+        <v>43.9</v>
       </c>
       <c r="F444" t="n">
         <v>22</v>
@@ -9332,10 +9332,10 @@
         <v>9</v>
       </c>
       <c r="D445" t="n">
-        <v>6.181210281492905</v>
+        <v>2.477458202909179</v>
       </c>
       <c r="E445" t="n">
-        <v>39.15068272080433</v>
+        <v>33.7</v>
       </c>
       <c r="F445" t="n">
         <v>16</v>
@@ -9352,10 +9352,10 @@
         <v>17</v>
       </c>
       <c r="D446" t="n">
-        <v>1.853072887577438</v>
+        <v>-0.888641577089203</v>
       </c>
       <c r="E446" t="n">
-        <v>39.23559710324433</v>
+        <v>35.9</v>
       </c>
       <c r="F446" t="n">
         <v>17.5</v>
@@ -9372,10 +9372,10 @@
         <v>35</v>
       </c>
       <c r="D447" t="n">
-        <v>-4.160090280859792</v>
+        <v>-4.142588259792474</v>
       </c>
       <c r="E447" t="n">
-        <v>27.09306057523033</v>
+        <v>40.8</v>
       </c>
       <c r="F447" t="n">
         <v>19</v>
@@ -9392,13 +9392,13 @@
         <v>29</v>
       </c>
       <c r="D448" t="n">
-        <v>-7.502528390003762</v>
+        <v>-7.494413186848452</v>
       </c>
       <c r="E448" t="n">
-        <v>23.81207637390834</v>
+        <v>35</v>
       </c>
       <c r="F448" t="n">
-        <v>17.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="449">
@@ -9412,10 +9412,10 @@
         <v>29</v>
       </c>
       <c r="D449" t="n">
-        <v>1.080054641161189</v>
+        <v>-0.5810422459860057</v>
       </c>
       <c r="E449" t="n">
-        <v>26.05140038474167</v>
+        <v>37.9</v>
       </c>
       <c r="F449" t="n">
         <v>19</v>
@@ -9432,10 +9432,10 @@
         <v>15</v>
       </c>
       <c r="D450" t="n">
-        <v>1.237526711192292</v>
+        <v>-0.4650566229847108</v>
       </c>
       <c r="E450" t="n">
-        <v>37.37693358431233</v>
+        <v>34.8</v>
       </c>
       <c r="F450" t="n">
         <v>22</v>
@@ -9452,10 +9452,10 @@
         <v>17</v>
       </c>
       <c r="D451" t="n">
-        <v>2.183723829680334</v>
+        <v>-0.1039621030240891</v>
       </c>
       <c r="E451" t="n">
-        <v>43.819378769632</v>
+        <v>43.9</v>
       </c>
       <c r="F451" t="n">
         <v>19</v>
@@ -9472,10 +9472,10 @@
         <v>23</v>
       </c>
       <c r="D452" t="n">
-        <v>1.814181042559888</v>
+        <v>0.5667753408456071</v>
       </c>
       <c r="E452" t="n">
-        <v>30.57702677904933</v>
+        <v>41.7</v>
       </c>
       <c r="F452" t="n">
         <v>19</v>
@@ -9492,10 +9492,10 @@
         <v>15</v>
       </c>
       <c r="D453" t="n">
-        <v>1.29772611650654</v>
+        <v>0.8474447506843528</v>
       </c>
       <c r="E453" t="n">
-        <v>45.19064181901467</v>
+        <v>45.9</v>
       </c>
       <c r="F453" t="n">
         <v>17.5</v>
@@ -9512,10 +9512,10 @@
         <v>29</v>
       </c>
       <c r="D454" t="n">
-        <v>1.254730827179698</v>
+        <v>1.22605619357334</v>
       </c>
       <c r="E454" t="n">
-        <v>26.55697316213434</v>
+        <v>34.6</v>
       </c>
       <c r="F454" t="n">
         <v>16</v>
@@ -9532,10 +9532,10 @@
         <v>19</v>
       </c>
       <c r="D455" t="n">
-        <v>1.077247458260286</v>
+        <v>-1.449163043556349</v>
       </c>
       <c r="E455" t="n">
-        <v>27.24500649805167</v>
+        <v>36.8</v>
       </c>
       <c r="F455" t="n">
         <v>19</v>
@@ -9552,10 +9552,10 @@
         <v>43</v>
       </c>
       <c r="D456" t="n">
-        <v>-1.530720009055517</v>
+        <v>-7.063041762791196</v>
       </c>
       <c r="E456" t="n">
-        <v>18.82474588440067</v>
+        <v>43</v>
       </c>
       <c r="F456" t="n">
         <v>19</v>
@@ -9572,10 +9572,10 @@
         <v>39</v>
       </c>
       <c r="D457" t="n">
-        <v>-3.22157903794493</v>
+        <v>-3.258944684774359</v>
       </c>
       <c r="E457" t="n">
-        <v>26.11042629982567</v>
+        <v>39.9</v>
       </c>
       <c r="F457" t="n">
         <v>19</v>
@@ -9592,10 +9592,10 @@
         <v>11</v>
       </c>
       <c r="D458" t="n">
-        <v>0.5880676398045616</v>
+        <v>0.3038155417847883</v>
       </c>
       <c r="E458" t="n">
-        <v>40.31305153967166</v>
+        <v>41</v>
       </c>
       <c r="F458" t="n">
         <v>20.5</v>
@@ -9612,10 +9612,10 @@
         <v>11</v>
       </c>
       <c r="D459" t="n">
-        <v>2.9172792906478</v>
+        <v>2.925567382898334</v>
       </c>
       <c r="E459" t="n">
-        <v>42.17982387472433</v>
+        <v>37.7</v>
       </c>
       <c r="F459" t="n">
         <v>20.5</v>
@@ -9632,10 +9632,10 @@
         <v>17</v>
       </c>
       <c r="D460" t="n">
-        <v>0.405910447225811</v>
+        <v>1.227335378612259</v>
       </c>
       <c r="E460" t="n">
-        <v>39.83203960440633</v>
+        <v>37.7</v>
       </c>
       <c r="F460" t="n">
         <v>22</v>
@@ -9652,10 +9652,10 @@
         <v>13</v>
       </c>
       <c r="D461" t="n">
-        <v>0.3736442069623271</v>
+        <v>0.3567135355337989</v>
       </c>
       <c r="E461" t="n">
-        <v>41.96897014369067</v>
+        <v>37.7</v>
       </c>
       <c r="F461" t="n">
         <v>20.5</v>
@@ -9672,10 +9672,10 @@
         <v>33</v>
       </c>
       <c r="D462" t="n">
-        <v>-1.677054882970716</v>
+        <v>-5.230389973549588</v>
       </c>
       <c r="E462" t="n">
-        <v>20.453565169756</v>
+        <v>41.9</v>
       </c>
       <c r="F462" t="n">
         <v>16</v>
@@ -9692,13 +9692,13 @@
         <v>39</v>
       </c>
       <c r="D463" t="n">
-        <v>0.115534978325541</v>
+        <v>-4.468962519235911</v>
       </c>
       <c r="E463" t="n">
-        <v>20.81605397782966</v>
+        <v>36.6</v>
       </c>
       <c r="F463" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="464">
@@ -9712,10 +9712,10 @@
         <v>15</v>
       </c>
       <c r="D464" t="n">
-        <v>3.654000955365812</v>
+        <v>3.142223358714665</v>
       </c>
       <c r="E464" t="n">
-        <v>40.91984933314933</v>
+        <v>42.8</v>
       </c>
       <c r="F464" t="n">
         <v>20.5</v>
@@ -9732,10 +9732,10 @@
         <v>15</v>
       </c>
       <c r="D465" t="n">
-        <v>0.9344606982955969</v>
+        <v>1.02510534400717</v>
       </c>
       <c r="E465" t="n">
-        <v>43.53050758867533</v>
+        <v>43.9</v>
       </c>
       <c r="F465" t="n">
         <v>22</v>
@@ -9752,10 +9752,10 @@
         <v>15</v>
       </c>
       <c r="D466" t="n">
-        <v>-0.06379010554774121</v>
+        <v>-0.6141674555601673</v>
       </c>
       <c r="E466" t="n">
-        <v>43.00745006794899</v>
+        <v>41.9</v>
       </c>
       <c r="F466" t="n">
         <v>20.5</v>
@@ -9772,10 +9772,10 @@
         <v>25</v>
       </c>
       <c r="D467" t="n">
-        <v>-1.068208858495589</v>
+        <v>-0.8160733879181367</v>
       </c>
       <c r="E467" t="n">
-        <v>30.51566324493666</v>
+        <v>42.8</v>
       </c>
       <c r="F467" t="n">
         <v>20.5</v>
@@ -9792,10 +9792,10 @@
         <v>15</v>
       </c>
       <c r="D468" t="n">
-        <v>0.1414990514666193</v>
+        <v>1.137338576071934</v>
       </c>
       <c r="E468" t="n">
-        <v>32.51929965733066</v>
+        <v>47</v>
       </c>
       <c r="F468" t="n">
         <v>23.5</v>
@@ -9812,10 +9812,10 @@
         <v>21</v>
       </c>
       <c r="D469" t="n">
-        <v>0.747153771685686</v>
+        <v>0.6915120900000564</v>
       </c>
       <c r="E469" t="n">
-        <v>35.80186939609467</v>
+        <v>44.8</v>
       </c>
       <c r="F469" t="n">
         <v>22</v>
@@ -9832,10 +9832,10 @@
         <v>15</v>
       </c>
       <c r="D470" t="n">
-        <v>3.370856387879552</v>
+        <v>2.250366219827656</v>
       </c>
       <c r="E470" t="n">
-        <v>28.632707969252</v>
+        <v>34.8</v>
       </c>
       <c r="F470" t="n">
         <v>20.5</v>
@@ -9852,10 +9852,10 @@
         <v>15</v>
       </c>
       <c r="D471" t="n">
-        <v>1.103872232072785</v>
+        <v>0.02060750638746916</v>
       </c>
       <c r="E471" t="n">
-        <v>41.44302837382566</v>
+        <v>43</v>
       </c>
       <c r="F471" t="n">
         <v>20.5</v>
@@ -9872,10 +9872,10 @@
         <v>11</v>
       </c>
       <c r="D472" t="n">
-        <v>-1.069260771200562</v>
+        <v>-1.059969664252619</v>
       </c>
       <c r="E472" t="n">
-        <v>42.949900156172</v>
+        <v>43</v>
       </c>
       <c r="F472" t="n">
         <v>19</v>
@@ -9892,10 +9892,10 @@
         <v>15</v>
       </c>
       <c r="D473" t="n">
-        <v>-1.66808423150432</v>
+        <v>-1.707842522936838</v>
       </c>
       <c r="E473" t="n">
-        <v>41.52861381864967</v>
+        <v>41</v>
       </c>
       <c r="F473" t="n">
         <v>23.5</v>
@@ -9912,10 +9912,10 @@
         <v>21</v>
       </c>
       <c r="D474" t="n">
-        <v>5.930382220371998</v>
+        <v>5.089236637678793</v>
       </c>
       <c r="E474" t="n">
-        <v>34.11682665778099</v>
+        <v>44.8</v>
       </c>
       <c r="F474" t="n">
         <v>19</v>
@@ -9932,10 +9932,10 @@
         <v>13</v>
       </c>
       <c r="D475" t="n">
-        <v>4.283264006550239</v>
+        <v>1.098682892356061</v>
       </c>
       <c r="E475" t="n">
-        <v>39.00393966459099</v>
+        <v>35.9</v>
       </c>
       <c r="F475" t="n">
         <v>23.5</v>
@@ -9952,10 +9952,10 @@
         <v>17</v>
       </c>
       <c r="D476" t="n">
-        <v>1.537558212154845</v>
+        <v>2.123629903505583</v>
       </c>
       <c r="E476" t="n">
-        <v>38.42323441427267</v>
+        <v>42.8</v>
       </c>
       <c r="F476" t="n">
         <v>23.5</v>
@@ -9972,13 +9972,13 @@
         <v>31</v>
       </c>
       <c r="D477" t="n">
-        <v>2.646193479793757</v>
+        <v>2.587962081711049</v>
       </c>
       <c r="E477" t="n">
-        <v>30.47319614031033</v>
+        <v>40.6</v>
       </c>
       <c r="F477" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="478">
@@ -9992,13 +9992,13 @@
         <v>27</v>
       </c>
       <c r="D478" t="n">
-        <v>0.9861539129384234</v>
+        <v>1.46521177615566</v>
       </c>
       <c r="E478" t="n">
-        <v>36.398826638623</v>
+        <v>43.7</v>
       </c>
       <c r="F478" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="479">
@@ -10012,10 +10012,10 @@
         <v>15</v>
       </c>
       <c r="D479" t="n">
-        <v>2.116326748681817</v>
+        <v>2.227730912077593</v>
       </c>
       <c r="E479" t="n">
-        <v>43.92810634346966</v>
+        <v>42.8</v>
       </c>
       <c r="F479" t="n">
         <v>23.5</v>
@@ -10032,10 +10032,10 @@
         <v>39</v>
       </c>
       <c r="D480" t="n">
-        <v>1.670865877650102</v>
+        <v>-2.852511499325471</v>
       </c>
       <c r="E480" t="n">
-        <v>22.636619552558</v>
+        <v>38.8</v>
       </c>
       <c r="F480" t="n">
         <v>20.5</v>
@@ -10052,10 +10052,10 @@
         <v>15</v>
       </c>
       <c r="D481" t="n">
-        <v>1.887036497254344</v>
+        <v>1.656101105496402</v>
       </c>
       <c r="E481" t="n">
-        <v>44.25260862349034</v>
+        <v>43.9</v>
       </c>
       <c r="F481" t="n">
         <v>23.5</v>
@@ -10072,10 +10072,10 @@
         <v>33</v>
       </c>
       <c r="D482" t="n">
-        <v>-0.5519348464709929</v>
+        <v>-2.181595041450903</v>
       </c>
       <c r="E482" t="n">
-        <v>34.60862857127633</v>
+        <v>41.9</v>
       </c>
       <c r="F482" t="n">
         <v>22</v>
@@ -10092,10 +10092,10 @@
         <v>35</v>
       </c>
       <c r="D483" t="n">
-        <v>5.534193079421418</v>
+        <v>2.309738472745105</v>
       </c>
       <c r="E483" t="n">
-        <v>20.00843942851434</v>
+        <v>37.5</v>
       </c>
       <c r="F483" t="n">
         <v>22</v>
@@ -10112,10 +10112,10 @@
         <v>27</v>
       </c>
       <c r="D484" t="n">
-        <v>3.490536006550041</v>
+        <v>2.92055749528471</v>
       </c>
       <c r="E484" t="n">
-        <v>31.25134625719233</v>
+        <v>43.7</v>
       </c>
       <c r="F484" t="n">
         <v>23.5</v>
@@ -10132,10 +10132,10 @@
         <v>11</v>
       </c>
       <c r="D485" t="n">
-        <v>7.359402690456197</v>
+        <v>1.26214717618925</v>
       </c>
       <c r="E485" t="n">
-        <v>45.33605578810433</v>
+        <v>47</v>
       </c>
       <c r="F485" t="n">
         <v>23.5</v>
@@ -10152,10 +10152,10 @@
         <v>15</v>
       </c>
       <c r="D486" t="n">
-        <v>6.104788669292432</v>
+        <v>1.558160184887974</v>
       </c>
       <c r="E486" t="n">
-        <v>45.361732144264</v>
+        <v>45.9</v>
       </c>
       <c r="F486" t="n">
         <v>22</v>
@@ -10172,10 +10172,10 @@
         <v>33</v>
       </c>
       <c r="D487" t="n">
-        <v>-7.009829047119147</v>
+        <v>-7.521761006827451</v>
       </c>
       <c r="E487" t="n">
-        <v>24.417718650888</v>
+        <v>45</v>
       </c>
       <c r="F487" t="n">
         <v>23.5</v>
@@ -10192,10 +10192,10 @@
         <v>43</v>
       </c>
       <c r="D488" t="n">
-        <v>0.9017332412194039</v>
+        <v>-6.425254374315139</v>
       </c>
       <c r="E488" t="n">
-        <v>13.66374145747267</v>
+        <v>41</v>
       </c>
       <c r="F488" t="n">
         <v>22</v>
@@ -10212,10 +10212,10 @@
         <v>17</v>
       </c>
       <c r="D489" t="n">
-        <v>2.697693598389759</v>
+        <v>-0.2984252876331439</v>
       </c>
       <c r="E489" t="n">
-        <v>45.27212561287367</v>
+        <v>45.9</v>
       </c>
       <c r="F489" t="n">
         <v>22</v>
@@ -10232,10 +10232,10 @@
         <v>15</v>
       </c>
       <c r="D490" t="n">
-        <v>3.107723364500595</v>
+        <v>1.906705737190377</v>
       </c>
       <c r="E490" t="n">
-        <v>38.123865848425</v>
+        <v>41.9</v>
       </c>
       <c r="F490" t="n">
         <v>20.5</v>
@@ -10252,10 +10252,10 @@
         <v>45</v>
       </c>
       <c r="D491" t="n">
-        <v>4.600427641391479</v>
+        <v>-1.825583128419374</v>
       </c>
       <c r="E491" t="n">
-        <v>16.407147994561</v>
+        <v>43.7</v>
       </c>
       <c r="F491" t="n">
         <v>22</v>
@@ -10272,10 +10272,10 @@
         <v>33</v>
       </c>
       <c r="D492" t="n">
-        <v>-0.5379247174150048</v>
+        <v>-0.5532374137363099</v>
       </c>
       <c r="E492" t="n">
-        <v>30.82407910213</v>
+        <v>40.6</v>
       </c>
       <c r="F492" t="n">
         <v>20.5</v>
@@ -10292,10 +10292,10 @@
         <v>15</v>
       </c>
       <c r="D493" t="n">
-        <v>1.832998777836163</v>
+        <v>-0.5918792189979392</v>
       </c>
       <c r="E493" t="n">
-        <v>42.806347163342</v>
+        <v>45</v>
       </c>
       <c r="F493" t="n">
         <v>23.5</v>
@@ -10312,10 +10312,10 @@
         <v>17</v>
       </c>
       <c r="D494" t="n">
-        <v>3.170702592496574</v>
+        <v>2.792917539201678</v>
       </c>
       <c r="E494" t="n">
-        <v>38.44818413968233</v>
+        <v>43.9</v>
       </c>
       <c r="F494" t="n">
         <v>23.5</v>
@@ -10332,10 +10332,10 @@
         <v>23</v>
       </c>
       <c r="D495" t="n">
-        <v>1.567292728118034</v>
+        <v>-0.1398359058776345</v>
       </c>
       <c r="E495" t="n">
-        <v>29.68385201340433</v>
+        <v>47</v>
       </c>
       <c r="F495" t="n">
         <v>22</v>
@@ -10352,13 +10352,13 @@
         <v>43</v>
       </c>
       <c r="D496" t="n">
-        <v>-2.120594495835002</v>
+        <v>-2.120665427487619</v>
       </c>
       <c r="E496" t="n">
-        <v>28.67775297772467</v>
+        <v>42.59999999999999</v>
       </c>
       <c r="F496" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="497">
@@ -10372,10 +10372,10 @@
         <v>23</v>
       </c>
       <c r="D497" t="n">
-        <v>3.173256215559968</v>
+        <v>1.224652498852347</v>
       </c>
       <c r="E497" t="n">
-        <v>31.400645578128</v>
+        <v>42.8</v>
       </c>
       <c r="F497" t="n">
         <v>23.5</v>
@@ -10392,10 +10392,10 @@
         <v>25</v>
       </c>
       <c r="D498" t="n">
-        <v>3.931589581895683</v>
+        <v>2.687541208121736</v>
       </c>
       <c r="E498" t="n">
-        <v>29.404805636438</v>
+        <v>40.8</v>
       </c>
       <c r="F498" t="n">
         <v>20.5</v>
@@ -10412,10 +10412,10 @@
         <v>17</v>
       </c>
       <c r="D499" t="n">
-        <v>4.226717026870005</v>
+        <v>0.8240832438619535</v>
       </c>
       <c r="E499" t="n">
-        <v>42.03187860316634</v>
+        <v>43.9</v>
       </c>
       <c r="F499" t="n">
         <v>23.5</v>
@@ -10432,10 +10432,10 @@
         <v>17</v>
       </c>
       <c r="D500" t="n">
-        <v>7.617096489903453</v>
+        <v>2.630254364117565</v>
       </c>
       <c r="E500" t="n">
-        <v>44.14385043833533</v>
+        <v>44.8</v>
       </c>
       <c r="F500" t="n">
         <v>23.5</v>
@@ -10452,10 +10452,10 @@
         <v>23</v>
       </c>
       <c r="D501" t="n">
-        <v>5.294372608326582</v>
+        <v>4.989565238231685</v>
       </c>
       <c r="E501" t="n">
-        <v>34.11682665778099</v>
+        <v>44.8</v>
       </c>
       <c r="F501" t="n">
         <v>23.5</v>
@@ -10537,13 +10537,13 @@
         <v>8.728</v>
       </c>
       <c r="D3" t="n">
-        <v>-6.233754801053133</v>
+        <v>-8.085577424066329</v>
       </c>
       <c r="E3" t="n">
-        <v>24.29771875540524</v>
+        <v>21.9624</v>
       </c>
       <c r="F3" t="n">
-        <v>5.737</v>
+        <v>5.764</v>
       </c>
     </row>
     <row r="4">
@@ -10559,13 +10559,13 @@
         <v>13.65558369063234</v>
       </c>
       <c r="D4" t="n">
-        <v>6.535820885318892</v>
+        <v>6.17377840023794</v>
       </c>
       <c r="E4" t="n">
-        <v>9.163647066367529</v>
+        <v>14.46110623108943</v>
       </c>
       <c r="F4" t="n">
-        <v>10.99577852134996</v>
+        <v>11.03221298955444</v>
       </c>
     </row>
     <row r="5">
@@ -10584,7 +10584,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E5" t="n">
-        <v>3.018313872154333</v>
+        <v>-13.2</v>
       </c>
       <c r="F5" t="n">
         <v>-21.5</v>
@@ -10603,10 +10603,10 @@
         <v>-1</v>
       </c>
       <c r="D6" t="n">
-        <v>-11.32086820819188</v>
+        <v>-12.62876437265224</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55602607842341</v>
+        <v>9.9</v>
       </c>
       <c r="F6" t="n">
         <v>-2.375</v>
@@ -10625,10 +10625,10 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.622755329347932</v>
+        <v>-7.930705794315703</v>
       </c>
       <c r="E7" t="n">
-        <v>23.18027590219484</v>
+        <v>22.8</v>
       </c>
       <c r="F7" t="n">
         <v>5.5</v>
@@ -10647,10 +10647,10 @@
         <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.231147027169736</v>
+        <v>-3.501682725504332</v>
       </c>
       <c r="E8" t="n">
-        <v>30.64574635114175</v>
+        <v>33.9</v>
       </c>
       <c r="F8" t="n">
         <v>14.5</v>
@@ -10669,10 +10669,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>7.617096489903453</v>
+        <v>5.906920073781943</v>
       </c>
       <c r="E9" t="n">
-        <v>45.361732144264</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
         <v>23.5</v>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -475,7 +475,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.3</v>
+        <v>-3</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -495,7 +495,7 @@
         <v>-15.08041566639237</v>
       </c>
       <c r="E3" t="n">
-        <v>-10.1</v>
+        <v>-13</v>
       </c>
       <c r="F3" t="n">
         <v>-18.5</v>
@@ -515,7 +515,7 @@
         <v>-16.24192719111304</v>
       </c>
       <c r="E4" t="n">
-        <v>-13.2</v>
+        <v>-3</v>
       </c>
       <c r="F4" t="n">
         <v>-18.5</v>
@@ -535,7 +535,7 @@
         <v>-18.76282389482354</v>
       </c>
       <c r="E5" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>-3.5</v>
@@ -555,7 +555,7 @@
         <v>-9.011605956684511</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>-12.5</v>
@@ -575,7 +575,7 @@
         <v>-16.88493498782972</v>
       </c>
       <c r="E7" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="F7" t="n">
         <v>-12.5</v>
@@ -595,7 +595,7 @@
         <v>-22.1585517447926</v>
       </c>
       <c r="E8" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F8" t="n">
         <v>-8</v>
@@ -615,7 +615,7 @@
         <v>-14.86028872807583</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="F9" t="n">
         <v>-11</v>
@@ -635,7 +635,7 @@
         <v>-16.66542535497044</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>-2</v>
@@ -655,7 +655,7 @@
         <v>-16.50768248317392</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
@@ -675,7 +675,7 @@
         <v>-22.1585747570583</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9</v>
+        <v>-11</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5</v>
@@ -695,7 +695,7 @@
         <v>-16.07701479937518</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1</v>
+        <v>-9</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5</v>
@@ -715,7 +715,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
         <v>-5</v>
@@ -735,7 +735,7 @@
         <v>-14.49481384471911</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>-18.5</v>
@@ -755,7 +755,7 @@
         <v>-19.39923887184475</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.299999999999999</v>
+        <v>-13</v>
       </c>
       <c r="F16" t="n">
         <v>-12.5</v>
@@ -775,7 +775,7 @@
         <v>-15.21056902635355</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7999999999999999</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>-12.5</v>
@@ -795,7 +795,7 @@
         <v>-18.66489425226396</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3000000000000003</v>
+        <v>-11</v>
       </c>
       <c r="F18" t="n">
         <v>-11</v>
@@ -815,7 +815,7 @@
         <v>-9.011666353277461</v>
       </c>
       <c r="E19" t="n">
-        <v>13.9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>-12.5</v>
@@ -835,7 +835,7 @@
         <v>-12.42194598309683</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>-8</v>
@@ -855,7 +855,7 @@
         <v>-8.344026407773633</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.5</v>
+        <v>-3</v>
       </c>
       <c r="F21" t="n">
         <v>-17</v>
@@ -875,7 +875,7 @@
         <v>-10.61191573078219</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.1</v>
+        <v>-11</v>
       </c>
       <c r="F22" t="n">
         <v>-5</v>
@@ -895,7 +895,7 @@
         <v>-13.76809791504057</v>
       </c>
       <c r="E23" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
         <v>-21.5</v>
@@ -915,7 +915,7 @@
         <v>-13.61382958064067</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1000000000000001</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>-9.5</v>
@@ -935,7 +935,7 @@
         <v>-17.04709742089801</v>
       </c>
       <c r="E25" t="n">
-        <v>4.8</v>
+        <v>-5</v>
       </c>
       <c r="F25" t="n">
         <v>-5</v>
@@ -955,7 +955,7 @@
         <v>-11.45515617083332</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
         <v>-9.5</v>
@@ -975,7 +975,7 @@
         <v>-22.65071637595969</v>
       </c>
       <c r="E27" t="n">
-        <v>2.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>-12.5</v>
@@ -995,7 +995,7 @@
         <v>-18.723853564575</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>-6.5</v>
@@ -1015,7 +1015,7 @@
         <v>-19.58043031028957</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.1</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
         <v>-11</v>
@@ -1035,7 +1035,7 @@
         <v>-21.81599222693938</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7999999999999998</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1055,7 +1055,7 @@
         <v>-12.33207495069766</v>
       </c>
       <c r="E31" t="n">
-        <v>12.8</v>
+        <v>-3</v>
       </c>
       <c r="F31" t="n">
         <v>-9.5</v>
@@ -1075,7 +1075,7 @@
         <v>-12.07550353950178</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1095,7 +1095,7 @@
         <v>-13.9055061383892</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7</v>
+        <v>-7</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -1115,7 +1115,7 @@
         <v>-20.68298851778319</v>
       </c>
       <c r="E34" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5</v>
@@ -1135,7 +1135,7 @@
         <v>-13.67390778367567</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F35" t="n">
         <v>-9.5</v>
@@ -1155,7 +1155,7 @@
         <v>-9.665718240118361</v>
       </c>
       <c r="E36" t="n">
-        <v>4.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
         <v>-20</v>
@@ -1175,7 +1175,7 @@
         <v>-15.36778170122901</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F37" t="n">
         <v>-12.5</v>
@@ -1195,7 +1195,7 @@
         <v>-12.35413898216171</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
         <v>-21.5</v>
@@ -1215,7 +1215,7 @@
         <v>-16.22217341588913</v>
       </c>
       <c r="E39" t="n">
-        <v>6.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
@@ -1235,7 +1235,7 @@
         <v>-10.00948967549725</v>
       </c>
       <c r="E40" t="n">
-        <v>18.8</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
         <v>-17</v>
@@ -1255,7 +1255,7 @@
         <v>-15.10350776269546</v>
       </c>
       <c r="E41" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F41" t="n">
         <v>-17</v>
@@ -1275,7 +1275,7 @@
         <v>-13.62641184742081</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.199999999999999</v>
+        <v>-11</v>
       </c>
       <c r="F42" t="n">
         <v>-12.5</v>
@@ -1295,7 +1295,7 @@
         <v>-14.71610395027719</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.3000000000000003</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
         <v>-11</v>
@@ -1315,7 +1315,7 @@
         <v>-17.32238709223246</v>
       </c>
       <c r="E44" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>-6.5</v>
@@ -1335,7 +1335,7 @@
         <v>-18.3985178425561</v>
       </c>
       <c r="E45" t="n">
-        <v>3.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>2.5</v>
@@ -1355,7 +1355,7 @@
         <v>-13.92117656900311</v>
       </c>
       <c r="E46" t="n">
-        <v>3.9</v>
+        <v>-7</v>
       </c>
       <c r="F46" t="n">
         <v>-11</v>
@@ -1375,7 +1375,7 @@
         <v>-11.07952799310252</v>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
         <v>-8</v>
@@ -1395,7 +1395,7 @@
         <v>-17.00931480520146</v>
       </c>
       <c r="E48" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
         <v>-18.5</v>
@@ -1415,7 +1415,7 @@
         <v>-12.51496523440635</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>-12.56933176486039</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
         <v>-2</v>
@@ -1455,7 +1455,7 @@
         <v>-18.61042700136766</v>
       </c>
       <c r="E51" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
         <v>-9.5</v>
@@ -1475,7 +1475,7 @@
         <v>-19.98298420591642</v>
       </c>
       <c r="E52" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
         <v>-18.5</v>
@@ -1495,7 +1495,7 @@
         <v>-6.672983718717866</v>
       </c>
       <c r="E53" t="n">
-        <v>-2.3</v>
+        <v>11</v>
       </c>
       <c r="F53" t="n">
         <v>-8</v>
@@ -1515,7 +1515,7 @@
         <v>-15.35638027898899</v>
       </c>
       <c r="E54" t="n">
-        <v>-4.1</v>
+        <v>7</v>
       </c>
       <c r="F54" t="n">
         <v>-11</v>
@@ -1535,7 +1535,7 @@
         <v>-15.19729180569158</v>
       </c>
       <c r="E55" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="F55" t="n">
         <v>-5</v>
@@ -1555,7 +1555,7 @@
         <v>-14.51951403443939</v>
       </c>
       <c r="E56" t="n">
-        <v>1.9</v>
+        <v>-1</v>
       </c>
       <c r="F56" t="n">
         <v>-14</v>
@@ -1595,7 +1595,7 @@
         <v>-16.72760094092684</v>
       </c>
       <c r="E58" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F58" t="n">
         <v>-9.5</v>
@@ -1615,7 +1615,7 @@
         <v>-11.78050191422369</v>
       </c>
       <c r="E59" t="n">
-        <v>17.9</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
         <v>-9.5</v>
@@ -1635,7 +1635,7 @@
         <v>-13.16902826441466</v>
       </c>
       <c r="E60" t="n">
-        <v>13.7</v>
+        <v>-9</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5</v>
@@ -1655,7 +1655,7 @@
         <v>-18.54419594854977</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7999999999999998</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>-11</v>
@@ -1675,7 +1675,7 @@
         <v>-8.807644726031004</v>
       </c>
       <c r="E62" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>-11</v>
@@ -1715,7 +1715,7 @@
         <v>-15.86301331944633</v>
       </c>
       <c r="E64" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>-9.5</v>
@@ -1735,7 +1735,7 @@
         <v>-16.55071283344781</v>
       </c>
       <c r="E65" t="n">
-        <v>9.9</v>
+        <v>-3</v>
       </c>
       <c r="F65" t="n">
         <v>-0.5</v>
@@ -1755,7 +1755,7 @@
         <v>-17.9336097374753</v>
       </c>
       <c r="E66" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
         <v>-17</v>
@@ -1775,7 +1775,7 @@
         <v>-11.96824934592622</v>
       </c>
       <c r="E67" t="n">
-        <v>9.9</v>
+        <v>-5</v>
       </c>
       <c r="F67" t="n">
         <v>-3.5</v>
@@ -1795,7 +1795,7 @@
         <v>-11.58305819485098</v>
       </c>
       <c r="E68" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
         <v>-6.5</v>
@@ -1815,7 +1815,7 @@
         <v>-16.96770942927208</v>
       </c>
       <c r="E69" t="n">
-        <v>2.8</v>
+        <v>-11</v>
       </c>
       <c r="F69" t="n">
         <v>-5</v>
@@ -1835,7 +1835,7 @@
         <v>-13.70594101887073</v>
       </c>
       <c r="E70" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
         <v>-11</v>
@@ -1855,7 +1855,7 @@
         <v>-13.35983540697217</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F71" t="n">
         <v>-11</v>
@@ -1875,7 +1875,7 @@
         <v>-13.73945420010882</v>
       </c>
       <c r="E72" t="n">
-        <v>6.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F72" t="n">
         <v>-9.5</v>
@@ -1895,7 +1895,7 @@
         <v>-21.43215273472283</v>
       </c>
       <c r="E73" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>-14</v>
@@ -1915,7 +1915,7 @@
         <v>-19.93026650520378</v>
       </c>
       <c r="E74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
         <v>-6.5</v>
@@ -1935,7 +1935,7 @@
         <v>-13.63373489971633</v>
       </c>
       <c r="E75" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F75" t="n">
         <v>-9.5</v>
@@ -1955,7 +1955,7 @@
         <v>-14.70893704404678</v>
       </c>
       <c r="E76" t="n">
-        <v>3.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="F76" t="n">
         <v>2.5</v>
@@ -1975,7 +1975,7 @@
         <v>-20.41126671783134</v>
       </c>
       <c r="E77" t="n">
-        <v>-6.1</v>
+        <v>-5</v>
       </c>
       <c r="F77" t="n">
         <v>-2</v>
@@ -1995,7 +1995,7 @@
         <v>-8.298668334372483</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.5</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
         <v>-9.5</v>
@@ -2015,7 +2015,7 @@
         <v>-11.09414578630654</v>
       </c>
       <c r="E79" t="n">
-        <v>7.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
         <v>-3.5</v>
@@ -2035,7 +2035,7 @@
         <v>-14.76956546226694</v>
       </c>
       <c r="E80" t="n">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="F80" t="n">
         <v>-5</v>
@@ -2055,7 +2055,7 @@
         <v>-14.11114333061668</v>
       </c>
       <c r="E81" t="n">
-        <v>6.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
         <v>-11</v>
@@ -2075,7 +2075,7 @@
         <v>-17.36533220259155</v>
       </c>
       <c r="E82" t="n">
-        <v>7.9</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
         <v>-9.5</v>
@@ -2095,7 +2095,7 @@
         <v>-14.29537266647307</v>
       </c>
       <c r="E83" t="n">
-        <v>9.500000000000002</v>
+        <v>7</v>
       </c>
       <c r="F83" t="n">
         <v>-11</v>
@@ -2115,7 +2115,7 @@
         <v>-15.52673225528131</v>
       </c>
       <c r="E84" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="F84" t="n">
         <v>-2</v>
@@ -2135,7 +2135,7 @@
         <v>-10.61618120478381</v>
       </c>
       <c r="E85" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
         <v>-6.5</v>
@@ -2155,7 +2155,7 @@
         <v>-9.558453099269794</v>
       </c>
       <c r="E86" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
         <v>-3.5</v>
@@ -2175,7 +2175,7 @@
         <v>-11.95578259847385</v>
       </c>
       <c r="E87" t="n">
-        <v>-6.3</v>
+        <v>7</v>
       </c>
       <c r="F87" t="n">
         <v>-2</v>
@@ -2195,7 +2195,7 @@
         <v>-14.53892114818133</v>
       </c>
       <c r="E88" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
         <v>-0.5</v>
@@ -2235,7 +2235,7 @@
         <v>-8.626986066168405</v>
       </c>
       <c r="E90" t="n">
-        <v>17.7</v>
+        <v>9</v>
       </c>
       <c r="F90" t="n">
         <v>-9.5</v>
@@ -2255,7 +2255,7 @@
         <v>-14.42115485021459</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.1</v>
+        <v>3</v>
       </c>
       <c r="F91" t="n">
         <v>-2</v>
@@ -2275,7 +2275,7 @@
         <v>-14.81963907250334</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.1000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="F92" t="n">
         <v>-8</v>
@@ -2295,7 +2295,7 @@
         <v>-18.27445887317804</v>
       </c>
       <c r="E93" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
         <v>-0.5</v>
@@ -2315,7 +2315,7 @@
         <v>-14.01149006572236</v>
       </c>
       <c r="E94" t="n">
-        <v>3.299999999999999</v>
+        <v>7</v>
       </c>
       <c r="F94" t="n">
         <v>-2</v>
@@ -2335,7 +2335,7 @@
         <v>-11.76638385536769</v>
       </c>
       <c r="E95" t="n">
-        <v>15.9</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
         <v>-5</v>
@@ -2355,7 +2355,7 @@
         <v>-9.413356115683376</v>
       </c>
       <c r="E96" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>-5</v>
@@ -2395,7 +2395,7 @@
         <v>-11.85349409751063</v>
       </c>
       <c r="E98" t="n">
-        <v>6.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="F98" t="n">
         <v>-3.5</v>
@@ -2415,7 +2415,7 @@
         <v>-15.24029031651793</v>
       </c>
       <c r="E99" t="n">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
         <v>-5</v>
@@ -2435,7 +2435,7 @@
         <v>-16.01872556029471</v>
       </c>
       <c r="E100" t="n">
-        <v>11.9</v>
+        <v>7</v>
       </c>
       <c r="F100" t="n">
         <v>-2</v>
@@ -2455,7 +2455,7 @@
         <v>-11.30979160160691</v>
       </c>
       <c r="E101" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>-15.21465658295874</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F102" t="n">
         <v>-9.5</v>
@@ -2495,7 +2495,7 @@
         <v>-11.91209159844877</v>
       </c>
       <c r="E103" t="n">
-        <v>15.7</v>
+        <v>13</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>-18.47233524338426</v>
       </c>
       <c r="E104" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
         <v>-11</v>
@@ -2535,7 +2535,7 @@
         <v>-15.99683898329127</v>
       </c>
       <c r="E105" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="F105" t="n">
         <v>4</v>
@@ -2555,7 +2555,7 @@
         <v>-11.78397827839792</v>
       </c>
       <c r="E106" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
         <v>-12.5</v>
@@ -2575,7 +2575,7 @@
         <v>-14.09994806721748</v>
       </c>
       <c r="E107" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F107" t="n">
         <v>-14</v>
@@ -2595,7 +2595,7 @@
         <v>-13.11527797743044</v>
       </c>
       <c r="E108" t="n">
-        <v>-13.2</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
         <v>-9.5</v>
@@ -2615,7 +2615,7 @@
         <v>-10.20573754684604</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6000000000000005</v>
+        <v>13</v>
       </c>
       <c r="F109" t="n">
         <v>-11</v>
@@ -2635,7 +2635,7 @@
         <v>-12.319581041081</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F110" t="n">
         <v>-5</v>
@@ -2655,7 +2655,7 @@
         <v>-6.059953702883841</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.2999999999999998</v>
+        <v>11</v>
       </c>
       <c r="F111" t="n">
         <v>-0.5</v>
@@ -2675,7 +2675,7 @@
         <v>-13.07604183385386</v>
       </c>
       <c r="E112" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>-12.00565567818595</v>
       </c>
       <c r="E113" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F113" t="n">
         <v>-6.5</v>
@@ -2715,7 +2715,7 @@
         <v>-18.23586872181258</v>
       </c>
       <c r="E114" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="F114" t="n">
         <v>-2</v>
@@ -2735,7 +2735,7 @@
         <v>-16.23673636012176</v>
       </c>
       <c r="E115" t="n">
-        <v>-4.1</v>
+        <v>13</v>
       </c>
       <c r="F115" t="n">
         <v>-0.5</v>
@@ -2755,7 +2755,7 @@
         <v>-9.138045441859136</v>
       </c>
       <c r="E116" t="n">
-        <v>4.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="F116" t="n">
         <v>-6.5</v>
@@ -2775,7 +2775,7 @@
         <v>-8.735620769461221</v>
       </c>
       <c r="E117" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>-3.275988466822424</v>
       </c>
       <c r="E118" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="F118" t="n">
         <v>-2</v>
@@ -2815,7 +2815,7 @@
         <v>-21.46730196390546</v>
       </c>
       <c r="E119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F119" t="n">
         <v>-8</v>
@@ -2835,7 +2835,7 @@
         <v>-9.30602509382889</v>
       </c>
       <c r="E120" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F120" t="n">
         <v>-2</v>
@@ -2855,7 +2855,7 @@
         <v>-15.45651431364378</v>
       </c>
       <c r="E121" t="n">
-        <v>9.9</v>
+        <v>19</v>
       </c>
       <c r="F121" t="n">
         <v>-2</v>
@@ -2875,7 +2875,7 @@
         <v>-6.65815148548338</v>
       </c>
       <c r="E122" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F122" t="n">
         <v>-8</v>
@@ -2895,7 +2895,7 @@
         <v>-6.936543698335337</v>
       </c>
       <c r="E123" t="n">
-        <v>17.9</v>
+        <v>-1</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         <v>-11.38242419822538</v>
       </c>
       <c r="E124" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F124" t="n">
         <v>-6.5</v>
@@ -2935,7 +2935,7 @@
         <v>-15.10018684775595</v>
       </c>
       <c r="E125" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F125" t="n">
         <v>-3.5</v>
@@ -2955,7 +2955,7 @@
         <v>-14.27988774904433</v>
       </c>
       <c r="E126" t="n">
-        <v>21.7</v>
+        <v>9</v>
       </c>
       <c r="F126" t="n">
         <v>-5</v>
@@ -2975,7 +2975,7 @@
         <v>-6.334648954400722</v>
       </c>
       <c r="E127" t="n">
-        <v>2.6</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
         <v>-12.5</v>
@@ -2995,7 +2995,7 @@
         <v>-13.5475756767352</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" t="n">
         <v>-6.5</v>
@@ -3015,7 +3015,7 @@
         <v>-11.66477267457763</v>
       </c>
       <c r="E129" t="n">
-        <v>11.9</v>
+        <v>-1</v>
       </c>
       <c r="F129" t="n">
         <v>-3.5</v>
@@ -3035,7 +3035,7 @@
         <v>-14.70454073338186</v>
       </c>
       <c r="E130" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3055,7 +3055,7 @@
         <v>-11.29764528453063</v>
       </c>
       <c r="E131" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="F131" t="n">
         <v>-5</v>
@@ -3075,7 +3075,7 @@
         <v>-9.092734146744514</v>
       </c>
       <c r="E132" t="n">
-        <v>1.9</v>
+        <v>23</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
         <v>-7.953307220522068</v>
       </c>
       <c r="E133" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
         <v>-5</v>
@@ -3115,7 +3115,7 @@
         <v>-8.629619074258962</v>
       </c>
       <c r="E134" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="F134" t="n">
         <v>-6.5</v>
@@ -3135,7 +3135,7 @@
         <v>-12.45493151160171</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
         <v>5.5</v>
@@ -3155,7 +3155,7 @@
         <v>-15.35178539224633</v>
       </c>
       <c r="E136" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="F136" t="n">
         <v>-3.5</v>
@@ -3175,7 +3175,7 @@
         <v>-14.42757650544786</v>
       </c>
       <c r="E137" t="n">
-        <v>18.6</v>
+        <v>23</v>
       </c>
       <c r="F137" t="n">
         <v>-11</v>
@@ -3195,7 +3195,7 @@
         <v>-13.78355315746163</v>
       </c>
       <c r="E138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F138" t="n">
         <v>-5</v>
@@ -3215,7 +3215,7 @@
         <v>-11.16316554267884</v>
       </c>
       <c r="E139" t="n">
-        <v>14.8</v>
+        <v>5</v>
       </c>
       <c r="F139" t="n">
         <v>-0.5</v>
@@ -3235,7 +3235,7 @@
         <v>-15.7222577936834</v>
       </c>
       <c r="E140" t="n">
-        <v>20.8</v>
+        <v>9</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -3255,7 +3255,7 @@
         <v>-18.80056717765801</v>
       </c>
       <c r="E141" t="n">
-        <v>6.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F141" t="n">
         <v>5.5</v>
@@ -3275,7 +3275,7 @@
         <v>-12.75547358832381</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.1000000000000001</v>
+        <v>23</v>
       </c>
       <c r="F142" t="n">
         <v>-2</v>
@@ -3295,7 +3295,7 @@
         <v>-13.05017477055378</v>
       </c>
       <c r="E143" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F143" t="n">
         <v>2.5</v>
@@ -3315,7 +3315,7 @@
         <v>-9.492785338822857</v>
       </c>
       <c r="E144" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F144" t="n">
         <v>5.5</v>
@@ -3335,7 +3335,7 @@
         <v>-12.82451007415136</v>
       </c>
       <c r="E145" t="n">
-        <v>4.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="F145" t="n">
         <v>-2</v>
@@ -3355,7 +3355,7 @@
         <v>-15.2583426766281</v>
       </c>
       <c r="E146" t="n">
-        <v>13.5</v>
+        <v>-1</v>
       </c>
       <c r="F146" t="n">
         <v>-5</v>
@@ -3375,7 +3375,7 @@
         <v>-8.936160793676258</v>
       </c>
       <c r="E147" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="F147" t="n">
         <v>-5</v>
@@ -3395,7 +3395,7 @@
         <v>-12.01544842174979</v>
       </c>
       <c r="E148" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
         <v>-3.5</v>
@@ -3415,7 +3415,7 @@
         <v>-9.976100682743448</v>
       </c>
       <c r="E149" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
         <v>2.5</v>
@@ -3435,7 +3435,7 @@
         <v>-9.072845539237004</v>
       </c>
       <c r="E150" t="n">
-        <v>18.8</v>
+        <v>11</v>
       </c>
       <c r="F150" t="n">
         <v>-0.5</v>
@@ -3455,7 +3455,7 @@
         <v>-9.050443784764134</v>
       </c>
       <c r="E151" t="n">
-        <v>20.6</v>
+        <v>29</v>
       </c>
       <c r="F151" t="n">
         <v>2.5</v>
@@ -3475,7 +3475,7 @@
         <v>-9.19299135802768</v>
       </c>
       <c r="E152" t="n">
-        <v>6.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F152" t="n">
         <v>-6.5</v>
@@ -3495,7 +3495,7 @@
         <v>-11.48622657143187</v>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F153" t="n">
         <v>-5</v>
@@ -3515,7 +3515,7 @@
         <v>-12.33292625264692</v>
       </c>
       <c r="E154" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="F154" t="n">
         <v>-5</v>
@@ -3535,7 +3535,7 @@
         <v>-8.749082119178086</v>
       </c>
       <c r="E155" t="n">
-        <v>9.9</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
         <v>-6.5</v>
@@ -3555,7 +3555,7 @@
         <v>-8.914449436079753</v>
       </c>
       <c r="E156" t="n">
-        <v>15.9</v>
+        <v>25</v>
       </c>
       <c r="F156" t="n">
         <v>-3.5</v>
@@ -3575,7 +3575,7 @@
         <v>-3.178563438316917</v>
       </c>
       <c r="E157" t="n">
-        <v>9.699999999999999</v>
+        <v>29</v>
       </c>
       <c r="F157" t="n">
         <v>2.5</v>
@@ -3595,7 +3595,7 @@
         <v>-11.29514140666748</v>
       </c>
       <c r="E158" t="n">
-        <v>12.8</v>
+        <v>21</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -3615,7 +3615,7 @@
         <v>-16.68234331642212</v>
       </c>
       <c r="E159" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>5.5</v>
@@ -3635,7 +3635,7 @@
         <v>-17.327950736185</v>
       </c>
       <c r="E160" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="F160" t="n">
         <v>2.5</v>
@@ -3655,7 +3655,7 @@
         <v>-11.49020960393287</v>
       </c>
       <c r="E161" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -3675,7 +3675,7 @@
         <v>-1.895934786610538</v>
       </c>
       <c r="E162" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="F162" t="n">
         <v>-5</v>
@@ -3695,7 +3695,7 @@
         <v>-11.60328510091501</v>
       </c>
       <c r="E163" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="F163" t="n">
         <v>-9.5</v>
@@ -3715,7 +3715,7 @@
         <v>-4.872661986196267</v>
       </c>
       <c r="E164" t="n">
-        <v>13.7</v>
+        <v>23</v>
       </c>
       <c r="F164" t="n">
         <v>-6.5</v>
@@ -3735,7 +3735,7 @@
         <v>-16.53562999078624</v>
       </c>
       <c r="E165" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F165" t="n">
         <v>-0.5</v>
@@ -3755,7 +3755,7 @@
         <v>-10.779735566366</v>
       </c>
       <c r="E166" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>-7.441839040123449</v>
       </c>
       <c r="E167" t="n">
-        <v>11.9</v>
+        <v>27</v>
       </c>
       <c r="F167" t="n">
         <v>2.5</v>
@@ -3795,7 +3795,7 @@
         <v>-8.540216823457699</v>
       </c>
       <c r="E168" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -3815,7 +3815,7 @@
         <v>-13.36124095935507</v>
       </c>
       <c r="E169" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F169" t="n">
         <v>-6.5</v>
@@ -3835,7 +3835,7 @@
         <v>-7.941572000257956</v>
       </c>
       <c r="E170" t="n">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="F170" t="n">
         <v>7</v>
@@ -3855,7 +3855,7 @@
         <v>-12.24259454888164</v>
       </c>
       <c r="E171" t="n">
-        <v>20.8</v>
+        <v>7</v>
       </c>
       <c r="F171" t="n">
         <v>2.5</v>
@@ -3875,7 +3875,7 @@
         <v>-9.577734981138333</v>
       </c>
       <c r="E172" t="n">
-        <v>13.7</v>
+        <v>21</v>
       </c>
       <c r="F172" t="n">
         <v>2.5</v>
@@ -3895,7 +3895,7 @@
         <v>-16.95493489049333</v>
       </c>
       <c r="E173" t="n">
-        <v>16.8</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
         <v>-6.5</v>
@@ -3915,7 +3915,7 @@
         <v>-7.956608854497154</v>
       </c>
       <c r="E174" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="F174" t="n">
         <v>-3.5</v>
@@ -3955,7 +3955,7 @@
         <v>-8.448732765702129</v>
       </c>
       <c r="E176" t="n">
-        <v>25.9</v>
+        <v>13</v>
       </c>
       <c r="F176" t="n">
         <v>7</v>
@@ -3975,7 +3975,7 @@
         <v>-11.73009639391955</v>
       </c>
       <c r="E177" t="n">
-        <v>15.9</v>
+        <v>31</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -3995,7 +3995,7 @@
         <v>-16.77275246571654</v>
       </c>
       <c r="E178" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="F178" t="n">
         <v>7</v>
@@ -4015,7 +4015,7 @@
         <v>-7.272125353914878</v>
       </c>
       <c r="E179" t="n">
-        <v>15.9</v>
+        <v>11</v>
       </c>
       <c r="F179" t="n">
         <v>-0.5</v>
@@ -4035,7 +4035,7 @@
         <v>-16.31510018076369</v>
       </c>
       <c r="E180" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F180" t="n">
         <v>-2</v>
@@ -4055,7 +4055,7 @@
         <v>-12.74747409402433</v>
       </c>
       <c r="E181" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F181" t="n">
         <v>5.5</v>
@@ -4075,7 +4075,7 @@
         <v>-13.55980417347203</v>
       </c>
       <c r="E182" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F182" t="n">
         <v>8.5</v>
@@ -4095,7 +4095,7 @@
         <v>-13.27490502800834</v>
       </c>
       <c r="E183" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="F183" t="n">
         <v>7</v>
@@ -4115,7 +4115,7 @@
         <v>-12.74484715468625</v>
       </c>
       <c r="E184" t="n">
-        <v>13.7</v>
+        <v>17</v>
       </c>
       <c r="F184" t="n">
         <v>7</v>
@@ -4135,7 +4135,7 @@
         <v>-12.34849872044505</v>
       </c>
       <c r="E185" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F185" t="n">
         <v>-0.5</v>
@@ -4155,7 +4155,7 @@
         <v>-8.532723933054008</v>
       </c>
       <c r="E186" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F186" t="n">
         <v>-0.5</v>
@@ -4175,7 +4175,7 @@
         <v>-7.575287710323443</v>
       </c>
       <c r="E187" t="n">
-        <v>12.2</v>
+        <v>21</v>
       </c>
       <c r="F187" t="n">
         <v>-8</v>
@@ -4195,7 +4195,7 @@
         <v>-11.86378417977766</v>
       </c>
       <c r="E188" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
         <v>5.5</v>
@@ -4215,7 +4215,7 @@
         <v>-12.69125732972837</v>
       </c>
       <c r="E189" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -4235,7 +4235,7 @@
         <v>-7.146291150027026</v>
       </c>
       <c r="E190" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -4255,7 +4255,7 @@
         <v>-10.73034245970168</v>
       </c>
       <c r="E191" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F191" t="n">
         <v>-8</v>
@@ -4275,7 +4275,7 @@
         <v>-18.78829949929933</v>
       </c>
       <c r="E192" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -4295,7 +4295,7 @@
         <v>-19.06989102055279</v>
       </c>
       <c r="E193" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="F193" t="n">
         <v>8.5</v>
@@ -4315,7 +4315,7 @@
         <v>-5.042595232131265</v>
       </c>
       <c r="E194" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F194" t="n">
         <v>-0.5</v>
@@ -4335,7 +4335,7 @@
         <v>-7.306725776447404</v>
       </c>
       <c r="E195" t="n">
-        <v>7.700000000000001</v>
+        <v>7</v>
       </c>
       <c r="F195" t="n">
         <v>-2</v>
@@ -4355,7 +4355,7 @@
         <v>-11.2969328754405</v>
       </c>
       <c r="E196" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="F196" t="n">
         <v>-0.5</v>
@@ -4375,7 +4375,7 @@
         <v>-10.80408612837662</v>
       </c>
       <c r="E197" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
         <v>-5</v>
@@ -4395,7 +4395,7 @@
         <v>-10.88759817733926</v>
       </c>
       <c r="E198" t="n">
-        <v>17.9</v>
+        <v>23</v>
       </c>
       <c r="F198" t="n">
         <v>-0.5</v>
@@ -4415,7 +4415,7 @@
         <v>-13.59431403174799</v>
       </c>
       <c r="E199" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
       <c r="F199" t="n">
         <v>8.5</v>
@@ -4435,7 +4435,7 @@
         <v>-16.73414753036879</v>
       </c>
       <c r="E200" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
         <v>2.5</v>
@@ -4455,7 +4455,7 @@
         <v>-12.17065885528252</v>
       </c>
       <c r="E201" t="n">
-        <v>13.9</v>
+        <v>7</v>
       </c>
       <c r="F201" t="n">
         <v>-0.5</v>
@@ -4475,7 +4475,7 @@
         <v>-9.682425408507925</v>
       </c>
       <c r="E202" t="n">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -4495,7 +4495,7 @@
         <v>-14.42541224847953</v>
       </c>
       <c r="E203" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="F203" t="n">
         <v>7</v>
@@ -4535,7 +4535,7 @@
         <v>-11.76448565489094</v>
       </c>
       <c r="E205" t="n">
-        <v>17.7</v>
+        <v>25</v>
       </c>
       <c r="F205" t="n">
         <v>4</v>
@@ -4555,7 +4555,7 @@
         <v>-8.468822193825609</v>
       </c>
       <c r="E206" t="n">
-        <v>12.8</v>
+        <v>17</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -4575,7 +4575,7 @@
         <v>-8.670738161587693</v>
       </c>
       <c r="E207" t="n">
-        <v>13.9</v>
+        <v>17</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>-7.822106310077424</v>
       </c>
       <c r="E208" t="n">
-        <v>13.9</v>
+        <v>9</v>
       </c>
       <c r="F208" t="n">
         <v>-14</v>
@@ -4615,7 +4615,7 @@
         <v>-12.1449725681243</v>
       </c>
       <c r="E209" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="F209" t="n">
         <v>-6.5</v>
@@ -4635,7 +4635,7 @@
         <v>-7.434250898971669</v>
       </c>
       <c r="E210" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F210" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         <v>-10.35522160269771</v>
       </c>
       <c r="E211" t="n">
-        <v>6.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="F211" t="n">
         <v>2.5</v>
@@ -4675,7 +4675,7 @@
         <v>-12.97258588476429</v>
       </c>
       <c r="E212" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F212" t="n">
         <v>5.5</v>
@@ -4695,7 +4695,7 @@
         <v>-7.268733793080433</v>
       </c>
       <c r="E213" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F213" t="n">
         <v>8.5</v>
@@ -4715,7 +4715,7 @@
         <v>-14.64730992827486</v>
       </c>
       <c r="E214" t="n">
-        <v>29.9</v>
+        <v>21</v>
       </c>
       <c r="F214" t="n">
         <v>11.5</v>
@@ -4735,7 +4735,7 @@
         <v>-6.230069394523568</v>
       </c>
       <c r="E215" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F215" t="n">
         <v>-6.5</v>
@@ -4755,7 +4755,7 @@
         <v>-5.029168024832028</v>
       </c>
       <c r="E216" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="F216" t="n">
         <v>4</v>
@@ -4775,7 +4775,7 @@
         <v>-17.20137440692926</v>
       </c>
       <c r="E217" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F217" t="n">
         <v>-2</v>
@@ -4795,7 +4795,7 @@
         <v>-11.79624044528628</v>
       </c>
       <c r="E218" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="F218" t="n">
         <v>7</v>
@@ -4815,7 +4815,7 @@
         <v>-16.74489113681049</v>
       </c>
       <c r="E219" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F219" t="n">
         <v>2.5</v>
@@ -4835,7 +4835,7 @@
         <v>-11.34683513007241</v>
       </c>
       <c r="E220" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="F220" t="n">
         <v>5.5</v>
@@ -4855,7 +4855,7 @@
         <v>-4.672589326071132</v>
       </c>
       <c r="E221" t="n">
-        <v>18.8</v>
+        <v>17</v>
       </c>
       <c r="F221" t="n">
         <v>4</v>
@@ -4875,7 +4875,7 @@
         <v>-5.574994098887871</v>
       </c>
       <c r="E222" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="F222" t="n">
         <v>-0.5</v>
@@ -4895,7 +4895,7 @@
         <v>-7.561973782123608</v>
       </c>
       <c r="E223" t="n">
-        <v>12.8</v>
+        <v>17</v>
       </c>
       <c r="F223" t="n">
         <v>8.5</v>
@@ -4915,7 +4915,7 @@
         <v>-5.122821742112643</v>
       </c>
       <c r="E224" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F224" t="n">
         <v>2.5</v>
@@ -4935,7 +4935,7 @@
         <v>-8.540376647193753</v>
       </c>
       <c r="E225" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="F225" t="n">
         <v>2.5</v>
@@ -4955,7 +4955,7 @@
         <v>-14.38422203108571</v>
       </c>
       <c r="E226" t="n">
-        <v>21.9</v>
+        <v>21</v>
       </c>
       <c r="F226" t="n">
         <v>5.5</v>
@@ -4995,7 +4995,7 @@
         <v>-8.624119528586101</v>
       </c>
       <c r="E228" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -5015,7 +5015,7 @@
         <v>-7.642849585159722</v>
       </c>
       <c r="E229" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F229" t="n">
         <v>-6.5</v>
@@ -5035,7 +5035,7 @@
         <v>-19.21652899798538</v>
       </c>
       <c r="E230" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5055,7 +5055,7 @@
         <v>-7.446396844456115</v>
       </c>
       <c r="E231" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F231" t="n">
         <v>11.5</v>
@@ -5075,7 +5075,7 @@
         <v>-6.816178332842622</v>
       </c>
       <c r="E232" t="n">
-        <v>19.9</v>
+        <v>27</v>
       </c>
       <c r="F232" t="n">
         <v>-3.5</v>
@@ -5095,7 +5095,7 @@
         <v>-4.111224791603618</v>
       </c>
       <c r="E233" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="F233" t="n">
         <v>2.5</v>
@@ -5115,7 +5115,7 @@
         <v>-7.431045844935011</v>
       </c>
       <c r="E234" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
       <c r="F234" t="n">
         <v>7</v>
@@ -5135,7 +5135,7 @@
         <v>-3.793921272312653</v>
       </c>
       <c r="E235" t="n">
-        <v>23.7</v>
+        <v>21</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
         <v>-9.390426779972653</v>
       </c>
       <c r="E236" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="F236" t="n">
         <v>5.5</v>
@@ -5175,7 +5175,7 @@
         <v>-6.645359241779041</v>
       </c>
       <c r="E237" t="n">
-        <v>34.8</v>
+        <v>23</v>
       </c>
       <c r="F237" t="n">
         <v>2.5</v>
@@ -5195,7 +5195,7 @@
         <v>-6.659235330907647</v>
       </c>
       <c r="E238" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -5215,7 +5215,7 @@
         <v>-7.389250931299761</v>
       </c>
       <c r="E239" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F239" t="n">
         <v>5.5</v>
@@ -5235,7 +5235,7 @@
         <v>-6.601754772706715</v>
       </c>
       <c r="E240" t="n">
-        <v>21.9</v>
+        <v>27</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -5255,7 +5255,7 @@
         <v>-10.54182006098494</v>
       </c>
       <c r="E241" t="n">
-        <v>23.9</v>
+        <v>19</v>
       </c>
       <c r="F241" t="n">
         <v>5.5</v>
@@ -5275,7 +5275,7 @@
         <v>-15.04528412633056</v>
       </c>
       <c r="E242" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>-4.485149225985528</v>
       </c>
       <c r="E243" t="n">
-        <v>14.8</v>
+        <v>21</v>
       </c>
       <c r="F243" t="n">
         <v>7</v>
@@ -5315,7 +5315,7 @@
         <v>-12.90464160657133</v>
       </c>
       <c r="E244" t="n">
-        <v>15.7</v>
+        <v>21</v>
       </c>
       <c r="F244" t="n">
         <v>5.5</v>
@@ -5335,7 +5335,7 @@
         <v>-10.64541686645118</v>
       </c>
       <c r="E245" t="n">
-        <v>23.9</v>
+        <v>15</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -5355,7 +5355,7 @@
         <v>-10.34030639977348</v>
       </c>
       <c r="E246" t="n">
-        <v>12.8</v>
+        <v>21</v>
       </c>
       <c r="F246" t="n">
         <v>4</v>
@@ -5375,7 +5375,7 @@
         <v>-10.19854567178833</v>
       </c>
       <c r="E247" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F247" t="n">
         <v>8.5</v>
@@ -5395,7 +5395,7 @@
         <v>-5.854820405046824</v>
       </c>
       <c r="E248" t="n">
-        <v>18.8</v>
+        <v>33</v>
       </c>
       <c r="F248" t="n">
         <v>11.5</v>
@@ -5415,7 +5415,7 @@
         <v>-8.740162907611163</v>
       </c>
       <c r="E249" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F249" t="n">
         <v>5.5</v>
@@ -5435,7 +5435,7 @@
         <v>-8.67301888488873</v>
       </c>
       <c r="E250" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F250" t="n">
         <v>4</v>
@@ -5455,7 +5455,7 @@
         <v>-15.23558737691753</v>
       </c>
       <c r="E251" t="n">
-        <v>24.8</v>
+        <v>29</v>
       </c>
       <c r="F251" t="n">
         <v>4</v>
@@ -5475,7 +5475,7 @@
         <v>-9.342347585650238</v>
       </c>
       <c r="E252" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="F252" t="n">
         <v>7</v>
@@ -5495,7 +5495,7 @@
         <v>-4.00963828005715</v>
       </c>
       <c r="E253" t="n">
-        <v>18.6</v>
+        <v>35</v>
       </c>
       <c r="F253" t="n">
         <v>11.5</v>
@@ -5515,7 +5515,7 @@
         <v>-7.006825558338786</v>
       </c>
       <c r="E254" t="n">
-        <v>21.9</v>
+        <v>29</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -5535,7 +5535,7 @@
         <v>-9.100522115540389</v>
       </c>
       <c r="E255" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="F255" t="n">
         <v>7</v>
@@ -5555,7 +5555,7 @@
         <v>-6.682488486241348</v>
       </c>
       <c r="E256" t="n">
-        <v>20.8</v>
+        <v>19</v>
       </c>
       <c r="F256" t="n">
         <v>8.5</v>
@@ -5575,7 +5575,7 @@
         <v>-7.919839588373449</v>
       </c>
       <c r="E257" t="n">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="F257" t="n">
         <v>7</v>
@@ -5615,7 +5615,7 @@
         <v>-4.38164053542964</v>
       </c>
       <c r="E259" t="n">
-        <v>16.8</v>
+        <v>27</v>
       </c>
       <c r="F259" t="n">
         <v>5.5</v>
@@ -5635,7 +5635,7 @@
         <v>-9.879498904697027</v>
       </c>
       <c r="E260" t="n">
-        <v>5.9</v>
+        <v>33</v>
       </c>
       <c r="F260" t="n">
         <v>7</v>
@@ -5655,7 +5655,7 @@
         <v>-4.631422886825721</v>
       </c>
       <c r="E261" t="n">
-        <v>14.6</v>
+        <v>21</v>
       </c>
       <c r="F261" t="n">
         <v>5.5</v>
@@ -5675,7 +5675,7 @@
         <v>-12.30271398733113</v>
       </c>
       <c r="E262" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="F262" t="n">
         <v>11.5</v>
@@ -5695,7 +5695,7 @@
         <v>-7.837332993512454</v>
       </c>
       <c r="E263" t="n">
-        <v>24.6</v>
+        <v>21</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
         <v>-11.30272089467063</v>
       </c>
       <c r="E264" t="n">
-        <v>19.9</v>
+        <v>25</v>
       </c>
       <c r="F264" t="n">
         <v>-2</v>
@@ -5735,7 +5735,7 @@
         <v>-2.232287562273741</v>
       </c>
       <c r="E265" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F265" t="n">
         <v>-0.5</v>
@@ -5755,7 +5755,7 @@
         <v>-8.845822814643235</v>
       </c>
       <c r="E266" t="n">
-        <v>15.9</v>
+        <v>7</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
         <v>-17.40506405164033</v>
       </c>
       <c r="E267" t="n">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="F267" t="n">
         <v>5.5</v>
@@ -5795,7 +5795,7 @@
         <v>-7.497009722041158</v>
       </c>
       <c r="E268" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="F268" t="n">
         <v>-8</v>
@@ -5815,7 +5815,7 @@
         <v>-6.347089668468085</v>
       </c>
       <c r="E269" t="n">
-        <v>31.7</v>
+        <v>27</v>
       </c>
       <c r="F269" t="n">
         <v>5.5</v>
@@ -5835,7 +5835,7 @@
         <v>-6.612981808812417</v>
       </c>
       <c r="E270" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -5855,7 +5855,7 @@
         <v>-11.06939687601137</v>
       </c>
       <c r="E271" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="F271" t="n">
         <v>-5</v>
@@ -5875,7 +5875,7 @@
         <v>-3.758817514648497</v>
       </c>
       <c r="E272" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F272" t="n">
         <v>5.5</v>
@@ -5895,7 +5895,7 @@
         <v>-4.051877556375617</v>
       </c>
       <c r="E273" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="F273" t="n">
         <v>7</v>
@@ -5915,7 +5915,7 @@
         <v>-10.52242670855952</v>
       </c>
       <c r="E274" t="n">
-        <v>33.7</v>
+        <v>35</v>
       </c>
       <c r="F274" t="n">
         <v>8.5</v>
@@ -5935,7 +5935,7 @@
         <v>-15.126689506234</v>
       </c>
       <c r="E275" t="n">
-        <v>19.7</v>
+        <v>23</v>
       </c>
       <c r="F275" t="n">
         <v>14.5</v>
@@ -5955,7 +5955,7 @@
         <v>-9.283689005874132</v>
       </c>
       <c r="E276" t="n">
-        <v>16.6</v>
+        <v>13</v>
       </c>
       <c r="F276" t="n">
         <v>8.5</v>
@@ -5975,7 +5975,7 @@
         <v>-7.94424447213977</v>
       </c>
       <c r="E277" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F277" t="n">
         <v>8.5</v>
@@ -5995,7 +5995,7 @@
         <v>-6.180337229755344</v>
       </c>
       <c r="E278" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F278" t="n">
         <v>5.5</v>
@@ -6015,7 +6015,7 @@
         <v>-8.982461384875723</v>
       </c>
       <c r="E279" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F279" t="n">
         <v>5.5</v>
@@ -6035,7 +6035,7 @@
         <v>-11.02713454495316</v>
       </c>
       <c r="E280" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F280" t="n">
         <v>13</v>
@@ -6055,7 +6055,7 @@
         <v>-14.250355621725</v>
       </c>
       <c r="E281" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -6095,7 +6095,7 @@
         <v>-1.583944458459632</v>
       </c>
       <c r="E283" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="F283" t="n">
         <v>8.5</v>
@@ -6135,7 +6135,7 @@
         <v>-1.993944866098499</v>
       </c>
       <c r="E285" t="n">
-        <v>27.7</v>
+        <v>25</v>
       </c>
       <c r="F285" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
         <v>-7.962965242945846</v>
       </c>
       <c r="E286" t="n">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="F286" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
         <v>-7.873822197284354</v>
       </c>
       <c r="E288" t="n">
-        <v>21.7</v>
+        <v>27</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -6215,7 +6215,7 @@
         <v>-5.515009419003278</v>
       </c>
       <c r="E289" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="F289" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
         <v>-10.62394376937941</v>
       </c>
       <c r="E290" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F290" t="n">
         <v>7</v>
@@ -6255,7 +6255,7 @@
         <v>-4.861284849882093</v>
       </c>
       <c r="E291" t="n">
-        <v>29.9</v>
+        <v>21</v>
       </c>
       <c r="F291" t="n">
         <v>14.5</v>
@@ -6275,7 +6275,7 @@
         <v>-5.133218124018798</v>
       </c>
       <c r="E292" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F292" t="n">
         <v>7</v>
@@ -6295,7 +6295,7 @@
         <v>-8.421038212394912</v>
       </c>
       <c r="E293" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F293" t="n">
         <v>5.5</v>
@@ -6315,7 +6315,7 @@
         <v>-7.958357982669678</v>
       </c>
       <c r="E294" t="n">
-        <v>31.9</v>
+        <v>31</v>
       </c>
       <c r="F294" t="n">
         <v>11.5</v>
@@ -6335,7 +6335,7 @@
         <v>-7.403946284003434</v>
       </c>
       <c r="E295" t="n">
-        <v>23.9</v>
+        <v>29</v>
       </c>
       <c r="F295" t="n">
         <v>5.5</v>
@@ -6355,7 +6355,7 @@
         <v>-1.924384022657788</v>
       </c>
       <c r="E296" t="n">
-        <v>16.8</v>
+        <v>21</v>
       </c>
       <c r="F296" t="n">
         <v>5.5</v>
@@ -6375,7 +6375,7 @@
         <v>-9.63065438938828</v>
       </c>
       <c r="E297" t="n">
-        <v>28.59999999999999</v>
+        <v>29</v>
       </c>
       <c r="F297" t="n">
         <v>7</v>
@@ -6395,7 +6395,7 @@
         <v>-3.802405797042502</v>
       </c>
       <c r="E298" t="n">
-        <v>25.9</v>
+        <v>27</v>
       </c>
       <c r="F298" t="n">
         <v>10</v>
@@ -6415,7 +6415,7 @@
         <v>-2.270559716689897</v>
       </c>
       <c r="E299" t="n">
-        <v>20.8</v>
+        <v>29</v>
       </c>
       <c r="F299" t="n">
         <v>10</v>
@@ -6435,7 +6435,7 @@
         <v>-5.067145124015414</v>
       </c>
       <c r="E300" t="n">
-        <v>31.9</v>
+        <v>29</v>
       </c>
       <c r="F300" t="n">
         <v>13</v>
@@ -6455,7 +6455,7 @@
         <v>-3.739643154692642</v>
       </c>
       <c r="E301" t="n">
-        <v>31.9</v>
+        <v>27</v>
       </c>
       <c r="F301" t="n">
         <v>5.5</v>
@@ -6475,7 +6475,7 @@
         <v>-3.418293055915066</v>
       </c>
       <c r="E302" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="F302" t="n">
         <v>13</v>
@@ -6495,7 +6495,7 @@
         <v>-4.344905760267247</v>
       </c>
       <c r="E303" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="F303" t="n">
         <v>7</v>
@@ -6515,7 +6515,7 @@
         <v>-15.2933712096641</v>
       </c>
       <c r="E304" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F304" t="n">
         <v>11.5</v>
@@ -6535,7 +6535,7 @@
         <v>-2.833311277806506</v>
       </c>
       <c r="E305" t="n">
-        <v>21.9</v>
+        <v>33</v>
       </c>
       <c r="F305" t="n">
         <v>11.5</v>
@@ -6555,7 +6555,7 @@
         <v>-6.487566266327902</v>
       </c>
       <c r="E306" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="F306" t="n">
         <v>11.5</v>
@@ -6575,7 +6575,7 @@
         <v>-0.597558805795496</v>
       </c>
       <c r="E307" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="F307" t="n">
         <v>16</v>
@@ -6595,7 +6595,7 @@
         <v>-7.007631493657506</v>
       </c>
       <c r="E308" t="n">
-        <v>30.6</v>
+        <v>29</v>
       </c>
       <c r="F308" t="n">
         <v>4</v>
@@ -6615,7 +6615,7 @@
         <v>-6.356009385510418</v>
       </c>
       <c r="E309" t="n">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="F309" t="n">
         <v>14.5</v>
@@ -6635,7 +6635,7 @@
         <v>-12.60793338696019</v>
       </c>
       <c r="E310" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="F310" t="n">
         <v>11.5</v>
@@ -6655,7 +6655,7 @@
         <v>-10.55619850873314</v>
       </c>
       <c r="E311" t="n">
-        <v>20.6</v>
+        <v>19</v>
       </c>
       <c r="F311" t="n">
         <v>8.5</v>
@@ -6675,7 +6675,7 @@
         <v>-8.036085399538264</v>
       </c>
       <c r="E312" t="n">
-        <v>32.8</v>
+        <v>35</v>
       </c>
       <c r="F312" t="n">
         <v>11.5</v>
@@ -6695,7 +6695,7 @@
         <v>-7.133811441293342</v>
       </c>
       <c r="E313" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F313" t="n">
         <v>5.5</v>
@@ -6715,7 +6715,7 @@
         <v>-1.537075693521595</v>
       </c>
       <c r="E314" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F314" t="n">
         <v>11.5</v>
@@ -6735,7 +6735,7 @@
         <v>-4.000693130585137</v>
       </c>
       <c r="E315" t="n">
-        <v>23.9</v>
+        <v>37</v>
       </c>
       <c r="F315" t="n">
         <v>17.5</v>
@@ -6755,7 +6755,7 @@
         <v>-7.442802803480682</v>
       </c>
       <c r="E316" t="n">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="F316" t="n">
         <v>-2</v>
@@ -6775,7 +6775,7 @@
         <v>0.321256182415646</v>
       </c>
       <c r="E317" t="n">
-        <v>33.5</v>
+        <v>25</v>
       </c>
       <c r="F317" t="n">
         <v>13</v>
@@ -6795,7 +6795,7 @@
         <v>-6.598016050430667</v>
       </c>
       <c r="E318" t="n">
-        <v>16.8</v>
+        <v>33</v>
       </c>
       <c r="F318" t="n">
         <v>10</v>
@@ -6815,7 +6815,7 @@
         <v>-6.205783364635726</v>
       </c>
       <c r="E319" t="n">
-        <v>25.7</v>
+        <v>21</v>
       </c>
       <c r="F319" t="n">
         <v>8.5</v>
@@ -6835,7 +6835,7 @@
         <v>-4.879434422761875</v>
       </c>
       <c r="E320" t="n">
-        <v>25.7</v>
+        <v>37</v>
       </c>
       <c r="F320" t="n">
         <v>14.5</v>
@@ -6855,7 +6855,7 @@
         <v>-8.815660834151867</v>
       </c>
       <c r="E321" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F321" t="n">
         <v>5.5</v>
@@ -6875,7 +6875,7 @@
         <v>-4.880041842271443</v>
       </c>
       <c r="E322" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F322" t="n">
         <v>16</v>
@@ -6895,7 +6895,7 @@
         <v>1.3390683303161</v>
       </c>
       <c r="E323" t="n">
-        <v>33.7</v>
+        <v>25</v>
       </c>
       <c r="F323" t="n">
         <v>16</v>
@@ -6915,7 +6915,7 @@
         <v>-7.534882036620827</v>
       </c>
       <c r="E324" t="n">
-        <v>29.9</v>
+        <v>37</v>
       </c>
       <c r="F324" t="n">
         <v>13</v>
@@ -6935,7 +6935,7 @@
         <v>-1.437938527968541</v>
       </c>
       <c r="E325" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F325" t="n">
         <v>8.5</v>
@@ -6955,7 +6955,7 @@
         <v>-3.084487384043165</v>
       </c>
       <c r="E326" t="n">
-        <v>31.9</v>
+        <v>25</v>
       </c>
       <c r="F326" t="n">
         <v>11.5</v>
@@ -6975,7 +6975,7 @@
         <v>-4.984577567865049</v>
       </c>
       <c r="E327" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F327" t="n">
         <v>14.5</v>
@@ -6995,7 +6995,7 @@
         <v>-12.47954626896995</v>
       </c>
       <c r="E328" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F328" t="n">
         <v>14.5</v>
@@ -7015,7 +7015,7 @@
         <v>-10.71310955210427</v>
       </c>
       <c r="E329" t="n">
-        <v>28.8</v>
+        <v>31</v>
       </c>
       <c r="F329" t="n">
         <v>16</v>
@@ -7035,7 +7035,7 @@
         <v>-4.214159442252412</v>
       </c>
       <c r="E330" t="n">
-        <v>33.9</v>
+        <v>27</v>
       </c>
       <c r="F330" t="n">
         <v>10</v>
@@ -7055,7 +7055,7 @@
         <v>-10.32175432625408</v>
       </c>
       <c r="E331" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F331" t="n">
         <v>8.5</v>
@@ -7075,7 +7075,7 @@
         <v>-3.847451207287437</v>
       </c>
       <c r="E332" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="F332" t="n">
         <v>11.5</v>
@@ -7095,7 +7095,7 @@
         <v>-7.577111428170915</v>
       </c>
       <c r="E333" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -7115,7 +7115,7 @@
         <v>-12.39685699336666</v>
       </c>
       <c r="E334" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F334" t="n">
         <v>14.5</v>
@@ -7135,7 +7135,7 @@
         <v>-4.536191961028859</v>
       </c>
       <c r="E335" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F335" t="n">
         <v>13</v>
@@ -7155,7 +7155,7 @@
         <v>-3.793876976120675</v>
       </c>
       <c r="E336" t="n">
-        <v>20.8</v>
+        <v>31</v>
       </c>
       <c r="F336" t="n">
         <v>7</v>
@@ -7175,7 +7175,7 @@
         <v>1.892030835894608</v>
       </c>
       <c r="E337" t="n">
-        <v>26.8</v>
+        <v>31</v>
       </c>
       <c r="F337" t="n">
         <v>7</v>
@@ -7215,7 +7215,7 @@
         <v>-1.615861001382153</v>
       </c>
       <c r="E339" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F339" t="n">
         <v>11.5</v>
@@ -7235,7 +7235,7 @@
         <v>-5.341940188564537</v>
       </c>
       <c r="E340" t="n">
-        <v>20.8</v>
+        <v>27</v>
       </c>
       <c r="F340" t="n">
         <v>10</v>
@@ -7255,7 +7255,7 @@
         <v>-5.309355549382947</v>
       </c>
       <c r="E341" t="n">
-        <v>32.59999999999999</v>
+        <v>37</v>
       </c>
       <c r="F341" t="n">
         <v>16</v>
@@ -7275,7 +7275,7 @@
         <v>-5.062973998838486</v>
       </c>
       <c r="E342" t="n">
-        <v>29.9</v>
+        <v>33</v>
       </c>
       <c r="F342" t="n">
         <v>13</v>
@@ -7295,7 +7295,7 @@
         <v>-3.868067795346402</v>
       </c>
       <c r="E343" t="n">
-        <v>25.9</v>
+        <v>31</v>
       </c>
       <c r="F343" t="n">
         <v>13</v>
@@ -7315,7 +7315,7 @@
         <v>-1.295206924452152</v>
       </c>
       <c r="E344" t="n">
-        <v>25.7</v>
+        <v>31</v>
       </c>
       <c r="F344" t="n">
         <v>11.5</v>
@@ -7335,7 +7335,7 @@
         <v>-4.563509516184059</v>
       </c>
       <c r="E345" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="F345" t="n">
         <v>11.5</v>
@@ -7355,7 +7355,7 @@
         <v>-4.52968578496577</v>
       </c>
       <c r="E346" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F346" t="n">
         <v>14.5</v>
@@ -7375,7 +7375,7 @@
         <v>0.5616403015032345</v>
       </c>
       <c r="E347" t="n">
-        <v>32.8</v>
+        <v>31</v>
       </c>
       <c r="F347" t="n">
         <v>8.5</v>
@@ -7395,7 +7395,7 @@
         <v>-1.932480718018562</v>
       </c>
       <c r="E348" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F348" t="n">
         <v>16</v>
@@ -7415,7 +7415,7 @@
         <v>-2.492076983508796</v>
       </c>
       <c r="E349" t="n">
-        <v>19.9</v>
+        <v>27</v>
       </c>
       <c r="F349" t="n">
         <v>13</v>
@@ -7435,7 +7435,7 @@
         <v>-6.866377835308298</v>
       </c>
       <c r="E350" t="n">
-        <v>41.7</v>
+        <v>43</v>
       </c>
       <c r="F350" t="n">
         <v>5.5</v>
@@ -7455,7 +7455,7 @@
         <v>-8.46601744993502</v>
       </c>
       <c r="E351" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F351" t="n">
         <v>5.5</v>
@@ -7475,7 +7475,7 @@
         <v>-8.503358770040659</v>
       </c>
       <c r="E352" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F352" t="n">
         <v>8.5</v>
@@ -7495,7 +7495,7 @@
         <v>-3.401522239735685</v>
       </c>
       <c r="E353" t="n">
-        <v>29.7</v>
+        <v>31</v>
       </c>
       <c r="F353" t="n">
         <v>5.5</v>
@@ -7515,7 +7515,7 @@
         <v>-4.889302168656975</v>
       </c>
       <c r="E354" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
       <c r="F354" t="n">
         <v>5.5</v>
@@ -7535,7 +7535,7 @@
         <v>-5.45993309037005</v>
       </c>
       <c r="E355" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F355" t="n">
         <v>14.5</v>
@@ -7555,7 +7555,7 @@
         <v>-2.72317301315674</v>
       </c>
       <c r="E356" t="n">
-        <v>31.7</v>
+        <v>31</v>
       </c>
       <c r="F356" t="n">
         <v>14.5</v>
@@ -7575,7 +7575,7 @@
         <v>-7.169360862597371</v>
       </c>
       <c r="E357" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="F357" t="n">
         <v>13</v>
@@ -7595,7 +7595,7 @@
         <v>-10.81470985813223</v>
       </c>
       <c r="E358" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F358" t="n">
         <v>14.5</v>
@@ -7615,7 +7615,7 @@
         <v>-8.107163803570021</v>
       </c>
       <c r="E359" t="n">
-        <v>29.9</v>
+        <v>27</v>
       </c>
       <c r="F359" t="n">
         <v>11.5</v>
@@ -7635,7 +7635,7 @@
         <v>-6.220465292608457</v>
       </c>
       <c r="E360" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F360" t="n">
         <v>19</v>
@@ -7655,7 +7655,7 @@
         <v>-5.504144096772184</v>
       </c>
       <c r="E361" t="n">
-        <v>32.4</v>
+        <v>39</v>
       </c>
       <c r="F361" t="n">
         <v>8.5</v>
@@ -7675,7 +7675,7 @@
         <v>-2.475755123102916</v>
       </c>
       <c r="E362" t="n">
-        <v>24.8</v>
+        <v>31</v>
       </c>
       <c r="F362" t="n">
         <v>17.5</v>
@@ -7695,7 +7695,7 @@
         <v>-7.444069608672705</v>
       </c>
       <c r="E363" t="n">
-        <v>37.7</v>
+        <v>41</v>
       </c>
       <c r="F363" t="n">
         <v>14.5</v>
@@ -7715,7 +7715,7 @@
         <v>-2.021784772990322</v>
       </c>
       <c r="E364" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F364" t="n">
         <v>14.5</v>
@@ -7735,7 +7735,7 @@
         <v>-2.354104958383093</v>
       </c>
       <c r="E365" t="n">
-        <v>32.59999999999999</v>
+        <v>37</v>
       </c>
       <c r="F365" t="n">
         <v>19</v>
@@ -7755,7 +7755,7 @@
         <v>-6.192040211684938</v>
       </c>
       <c r="E366" t="n">
-        <v>39.9</v>
+        <v>31</v>
       </c>
       <c r="F366" t="n">
         <v>20.5</v>
@@ -7775,7 +7775,7 @@
         <v>-5.675692005440896</v>
       </c>
       <c r="E367" t="n">
-        <v>42.8</v>
+        <v>39</v>
       </c>
       <c r="F367" t="n">
         <v>16</v>
@@ -7795,7 +7795,7 @@
         <v>-6.218050842224281</v>
       </c>
       <c r="E368" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F368" t="n">
         <v>19</v>
@@ -7815,7 +7815,7 @@
         <v>-3.07883011643317</v>
       </c>
       <c r="E369" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F369" t="n">
         <v>16</v>
@@ -7835,7 +7835,7 @@
         <v>0.4454353742164699</v>
       </c>
       <c r="E370" t="n">
-        <v>15.7</v>
+        <v>35</v>
       </c>
       <c r="F370" t="n">
         <v>19</v>
@@ -7855,7 +7855,7 @@
         <v>-5.299662112462816</v>
       </c>
       <c r="E371" t="n">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="F371" t="n">
         <v>20.5</v>
@@ -7875,7 +7875,7 @@
         <v>-4.275349160139813</v>
       </c>
       <c r="E372" t="n">
-        <v>37.9</v>
+        <v>41</v>
       </c>
       <c r="F372" t="n">
         <v>20.5</v>
@@ -7895,7 +7895,7 @@
         <v>2.760114520882845</v>
       </c>
       <c r="E373" t="n">
-        <v>38.8</v>
+        <v>35</v>
       </c>
       <c r="F373" t="n">
         <v>11.5</v>
@@ -7915,7 +7915,7 @@
         <v>-2.233175560934974</v>
       </c>
       <c r="E374" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F374" t="n">
         <v>11.5</v>
@@ -7935,7 +7935,7 @@
         <v>-3.849263004804139</v>
       </c>
       <c r="E375" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="F375" t="n">
         <v>13</v>
@@ -7955,7 +7955,7 @@
         <v>-7.439318426871877</v>
       </c>
       <c r="E376" t="n">
-        <v>35.9</v>
+        <v>37</v>
       </c>
       <c r="F376" t="n">
         <v>16</v>
@@ -7975,7 +7975,7 @@
         <v>0.3988126622416603</v>
       </c>
       <c r="E377" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="F377" t="n">
         <v>17.5</v>
@@ -7995,7 +7995,7 @@
         <v>-5.219605923776177</v>
       </c>
       <c r="E378" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F378" t="n">
         <v>10</v>
@@ -8015,7 +8015,7 @@
         <v>1.436115308975747</v>
       </c>
       <c r="E379" t="n">
-        <v>28.8</v>
+        <v>33</v>
       </c>
       <c r="F379" t="n">
         <v>20.5</v>
@@ -8035,7 +8035,7 @@
         <v>-2.555545674890773</v>
       </c>
       <c r="E380" t="n">
-        <v>35.9</v>
+        <v>43</v>
       </c>
       <c r="F380" t="n">
         <v>16</v>
@@ -8055,7 +8055,7 @@
         <v>-5.898584918723315</v>
       </c>
       <c r="E381" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F381" t="n">
         <v>14.5</v>
@@ -8075,7 +8075,7 @@
         <v>-7.073209898845452</v>
       </c>
       <c r="E382" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F382" t="n">
         <v>7</v>
@@ -8095,7 +8095,7 @@
         <v>-3.622977285184998</v>
       </c>
       <c r="E383" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="F383" t="n">
         <v>19</v>
@@ -8115,7 +8115,7 @@
         <v>-9.917287036815873</v>
       </c>
       <c r="E384" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="F384" t="n">
         <v>13</v>
@@ -8135,7 +8135,7 @@
         <v>0.5373091015979023</v>
       </c>
       <c r="E385" t="n">
-        <v>25.5</v>
+        <v>41</v>
       </c>
       <c r="F385" t="n">
         <v>17.5</v>
@@ -8155,7 +8155,7 @@
         <v>-0.9602138229564685</v>
       </c>
       <c r="E386" t="n">
-        <v>29.7</v>
+        <v>37</v>
       </c>
       <c r="F386" t="n">
         <v>14.5</v>
@@ -8175,7 +8175,7 @@
         <v>-2.535567183211558</v>
       </c>
       <c r="E387" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="F387" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>2.200141246463018</v>
       </c>
       <c r="E388" t="n">
-        <v>33.5</v>
+        <v>31</v>
       </c>
       <c r="F388" t="n">
         <v>11.5</v>
@@ -8215,7 +8215,7 @@
         <v>1.811103417675227</v>
       </c>
       <c r="E389" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F389" t="n">
         <v>17.5</v>
@@ -8235,7 +8235,7 @@
         <v>-9.225704108485532</v>
       </c>
       <c r="E390" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="F390" t="n">
         <v>14.5</v>
@@ -8275,7 +8275,7 @@
         <v>-1.257155408909161</v>
       </c>
       <c r="E392" t="n">
-        <v>33.7</v>
+        <v>33</v>
       </c>
       <c r="F392" t="n">
         <v>16</v>
@@ -8295,7 +8295,7 @@
         <v>-4.429092056794652</v>
       </c>
       <c r="E393" t="n">
-        <v>38.59999999999999</v>
+        <v>43</v>
       </c>
       <c r="F393" t="n">
         <v>14.5</v>
@@ -8315,7 +8315,7 @@
         <v>-2.148827803887845</v>
       </c>
       <c r="E394" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="F394" t="n">
         <v>14.5</v>
@@ -8335,7 +8335,7 @@
         <v>-6.628430276399285</v>
       </c>
       <c r="E395" t="n">
-        <v>37.9</v>
+        <v>39</v>
       </c>
       <c r="F395" t="n">
         <v>17.5</v>
@@ -8355,7 +8355,7 @@
         <v>-2.811622576116387</v>
       </c>
       <c r="E396" t="n">
-        <v>34.8</v>
+        <v>37</v>
       </c>
       <c r="F396" t="n">
         <v>11.5</v>
@@ -8375,7 +8375,7 @@
         <v>1.516348024524294</v>
       </c>
       <c r="E397" t="n">
-        <v>43.9</v>
+        <v>31</v>
       </c>
       <c r="F397" t="n">
         <v>19</v>
@@ -8395,7 +8395,7 @@
         <v>0.7759562547179837</v>
       </c>
       <c r="E398" t="n">
-        <v>34.8</v>
+        <v>39</v>
       </c>
       <c r="F398" t="n">
         <v>20.5</v>
@@ -8435,7 +8435,7 @@
         <v>5.906920073781943</v>
       </c>
       <c r="E400" t="n">
-        <v>28.8</v>
+        <v>37</v>
       </c>
       <c r="F400" t="n">
         <v>14.5</v>
@@ -8455,7 +8455,7 @@
         <v>-1.152800133799763</v>
       </c>
       <c r="E401" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="F401" t="n">
         <v>17.5</v>
@@ -8475,7 +8475,7 @@
         <v>1.92235435186735</v>
       </c>
       <c r="E402" t="n">
-        <v>34.59999999999999</v>
+        <v>41</v>
       </c>
       <c r="F402" t="n">
         <v>13</v>
@@ -8495,7 +8495,7 @@
         <v>-1.324647806147128</v>
       </c>
       <c r="E403" t="n">
-        <v>28.8</v>
+        <v>41</v>
       </c>
       <c r="F403" t="n">
         <v>13</v>
@@ -8515,7 +8515,7 @@
         <v>-1.675220191202326</v>
       </c>
       <c r="E404" t="n">
-        <v>33.9</v>
+        <v>31</v>
       </c>
       <c r="F404" t="n">
         <v>17.5</v>
@@ -8535,7 +8535,7 @@
         <v>3.285523000699553</v>
       </c>
       <c r="E405" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="F405" t="n">
         <v>11.5</v>
@@ -8555,7 +8555,7 @@
         <v>1.498901900880139</v>
       </c>
       <c r="E406" t="n">
-        <v>30.8</v>
+        <v>29</v>
       </c>
       <c r="F406" t="n">
         <v>16</v>
@@ -8575,7 +8575,7 @@
         <v>0.3891414475957227</v>
       </c>
       <c r="E407" t="n">
-        <v>35.7</v>
+        <v>37</v>
       </c>
       <c r="F407" t="n">
         <v>20.5</v>
@@ -8595,7 +8595,7 @@
         <v>-5.627019008818197</v>
       </c>
       <c r="E408" t="n">
-        <v>36.8</v>
+        <v>41</v>
       </c>
       <c r="F408" t="n">
         <v>14.5</v>
@@ -8635,7 +8635,7 @@
         <v>0.1256179464703751</v>
       </c>
       <c r="E410" t="n">
-        <v>34.59999999999999</v>
+        <v>35</v>
       </c>
       <c r="F410" t="n">
         <v>20.5</v>
@@ -8655,7 +8655,7 @@
         <v>-5.092614484938498</v>
       </c>
       <c r="E411" t="n">
-        <v>38.8</v>
+        <v>43</v>
       </c>
       <c r="F411" t="n">
         <v>10</v>
@@ -8675,7 +8675,7 @@
         <v>-4.108693146142889</v>
       </c>
       <c r="E412" t="n">
-        <v>35.7</v>
+        <v>37</v>
       </c>
       <c r="F412" t="n">
         <v>13</v>
@@ -8695,7 +8695,7 @@
         <v>-7.463804828800212</v>
       </c>
       <c r="E413" t="n">
-        <v>31.9</v>
+        <v>35</v>
       </c>
       <c r="F413" t="n">
         <v>17.5</v>
@@ -8715,7 +8715,7 @@
         <v>-1.055122844270363</v>
       </c>
       <c r="E414" t="n">
-        <v>31.5</v>
+        <v>37</v>
       </c>
       <c r="F414" t="n">
         <v>16</v>
@@ -8735,7 +8735,7 @@
         <v>-1.215686709645218</v>
       </c>
       <c r="E415" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="F415" t="n">
         <v>17.5</v>
@@ -8755,7 +8755,7 @@
         <v>-4.396800403551372</v>
       </c>
       <c r="E416" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F416" t="n">
         <v>22</v>
@@ -8775,7 +8775,7 @@
         <v>-2.291263596076391</v>
       </c>
       <c r="E417" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F417" t="n">
         <v>22</v>
@@ -8795,7 +8795,7 @@
         <v>-1.338984177475091</v>
       </c>
       <c r="E418" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F418" t="n">
         <v>19</v>
@@ -8815,7 +8815,7 @@
         <v>-2.378608825728114</v>
       </c>
       <c r="E419" t="n">
-        <v>37.9</v>
+        <v>37</v>
       </c>
       <c r="F419" t="n">
         <v>20.5</v>
@@ -8835,7 +8835,7 @@
         <v>-4.478171664319876</v>
       </c>
       <c r="E420" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F420" t="n">
         <v>19</v>
@@ -8855,7 +8855,7 @@
         <v>3.493919627918584</v>
       </c>
       <c r="E421" t="n">
-        <v>34.59999999999999</v>
+        <v>33</v>
       </c>
       <c r="F421" t="n">
         <v>20.5</v>
@@ -8875,7 +8875,7 @@
         <v>-0.4493073074287441</v>
       </c>
       <c r="E422" t="n">
-        <v>37.9</v>
+        <v>39</v>
       </c>
       <c r="F422" t="n">
         <v>19</v>
@@ -8895,7 +8895,7 @@
         <v>-3.529479282034087</v>
       </c>
       <c r="E423" t="n">
-        <v>32.8</v>
+        <v>43</v>
       </c>
       <c r="F423" t="n">
         <v>20.5</v>
@@ -8915,7 +8915,7 @@
         <v>5.505363169646428</v>
       </c>
       <c r="E424" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="F424" t="n">
         <v>16</v>
@@ -8935,7 +8935,7 @@
         <v>-1.289749166080068</v>
       </c>
       <c r="E425" t="n">
-        <v>35.9</v>
+        <v>37</v>
       </c>
       <c r="F425" t="n">
         <v>17.5</v>
@@ -8955,7 +8955,7 @@
         <v>-6.328346785914285</v>
       </c>
       <c r="E426" t="n">
-        <v>41.9</v>
+        <v>45</v>
       </c>
       <c r="F426" t="n">
         <v>19</v>
@@ -8975,7 +8975,7 @@
         <v>-2.245770890171666</v>
       </c>
       <c r="E427" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F427" t="n">
         <v>20.5</v>
@@ -8995,7 +8995,7 @@
         <v>0.8586256083960975</v>
       </c>
       <c r="E428" t="n">
-        <v>39.9</v>
+        <v>35</v>
       </c>
       <c r="F428" t="n">
         <v>20.5</v>
@@ -9015,7 +9015,7 @@
         <v>-1.440130905972663</v>
       </c>
       <c r="E429" t="n">
-        <v>33.9</v>
+        <v>41</v>
       </c>
       <c r="F429" t="n">
         <v>17.5</v>
@@ -9035,7 +9035,7 @@
         <v>-6.031533531499718</v>
       </c>
       <c r="E430" t="n">
-        <v>38.59999999999999</v>
+        <v>43</v>
       </c>
       <c r="F430" t="n">
         <v>17.5</v>
@@ -9055,7 +9055,7 @@
         <v>-6.483394036182426</v>
       </c>
       <c r="E431" t="n">
-        <v>39.7</v>
+        <v>43</v>
       </c>
       <c r="F431" t="n">
         <v>22</v>
@@ -9075,7 +9075,7 @@
         <v>-4.129181923723293</v>
       </c>
       <c r="E432" t="n">
-        <v>36.8</v>
+        <v>39</v>
       </c>
       <c r="F432" t="n">
         <v>14.5</v>
@@ -9095,7 +9095,7 @@
         <v>-0.5394951999804173</v>
       </c>
       <c r="E433" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="F433" t="n">
         <v>19</v>
@@ -9115,7 +9115,7 @@
         <v>-4.91737737000209</v>
       </c>
       <c r="E434" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F434" t="n">
         <v>22</v>
@@ -9135,7 +9135,7 @@
         <v>-1.629499795376638</v>
       </c>
       <c r="E435" t="n">
-        <v>33.9</v>
+        <v>41</v>
       </c>
       <c r="F435" t="n">
         <v>19</v>
@@ -9155,7 +9155,7 @@
         <v>-2.000851078070042</v>
       </c>
       <c r="E436" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F436" t="n">
         <v>23.5</v>
@@ -9175,7 +9175,7 @@
         <v>-0.6395139177057325</v>
       </c>
       <c r="E437" t="n">
-        <v>33.7</v>
+        <v>45</v>
       </c>
       <c r="F437" t="n">
         <v>16</v>
@@ -9195,7 +9195,7 @@
         <v>-3.783377107596139</v>
       </c>
       <c r="E438" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="F438" t="n">
         <v>19</v>
@@ -9215,7 +9215,7 @@
         <v>-0.1908777370631428</v>
       </c>
       <c r="E439" t="n">
-        <v>39.9</v>
+        <v>43</v>
       </c>
       <c r="F439" t="n">
         <v>17.5</v>
@@ -9235,7 +9235,7 @@
         <v>4.759227350410999</v>
       </c>
       <c r="E440" t="n">
-        <v>33.09999999999999</v>
+        <v>39</v>
       </c>
       <c r="F440" t="n">
         <v>17.5</v>
@@ -9255,7 +9255,7 @@
         <v>0.677884067585573</v>
       </c>
       <c r="E441" t="n">
-        <v>36.8</v>
+        <v>41</v>
       </c>
       <c r="F441" t="n">
         <v>17.5</v>
@@ -9275,7 +9275,7 @@
         <v>-0.07175836499018579</v>
       </c>
       <c r="E442" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="F442" t="n">
         <v>19</v>
@@ -9295,7 +9295,7 @@
         <v>-1.541966372324565</v>
       </c>
       <c r="E443" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F443" t="n">
         <v>19</v>
@@ -9315,7 +9315,7 @@
         <v>-1.084744409189314</v>
       </c>
       <c r="E444" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F444" t="n">
         <v>22</v>
@@ -9335,7 +9335,7 @@
         <v>2.477458202909179</v>
       </c>
       <c r="E445" t="n">
-        <v>33.7</v>
+        <v>41</v>
       </c>
       <c r="F445" t="n">
         <v>16</v>
@@ -9355,7 +9355,7 @@
         <v>-0.888641577089203</v>
       </c>
       <c r="E446" t="n">
-        <v>35.9</v>
+        <v>41</v>
       </c>
       <c r="F446" t="n">
         <v>17.5</v>
@@ -9375,7 +9375,7 @@
         <v>-4.142588259792474</v>
       </c>
       <c r="E447" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
       <c r="F447" t="n">
         <v>19</v>
@@ -9395,7 +9395,7 @@
         <v>-7.494413186848452</v>
       </c>
       <c r="E448" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F448" t="n">
         <v>23.5</v>
@@ -9415,7 +9415,7 @@
         <v>-0.5810422459860057</v>
       </c>
       <c r="E449" t="n">
-        <v>37.9</v>
+        <v>35</v>
       </c>
       <c r="F449" t="n">
         <v>19</v>
@@ -9435,7 +9435,7 @@
         <v>-0.4650566229847108</v>
       </c>
       <c r="E450" t="n">
-        <v>34.8</v>
+        <v>39</v>
       </c>
       <c r="F450" t="n">
         <v>22</v>
@@ -9455,7 +9455,7 @@
         <v>-0.1039621030240891</v>
       </c>
       <c r="E451" t="n">
-        <v>43.9</v>
+        <v>35</v>
       </c>
       <c r="F451" t="n">
         <v>19</v>
@@ -9475,7 +9475,7 @@
         <v>0.5667753408456071</v>
       </c>
       <c r="E452" t="n">
-        <v>41.7</v>
+        <v>39</v>
       </c>
       <c r="F452" t="n">
         <v>19</v>
@@ -9495,7 +9495,7 @@
         <v>0.8474447506843528</v>
       </c>
       <c r="E453" t="n">
-        <v>45.9</v>
+        <v>37</v>
       </c>
       <c r="F453" t="n">
         <v>17.5</v>
@@ -9515,7 +9515,7 @@
         <v>1.22605619357334</v>
       </c>
       <c r="E454" t="n">
-        <v>34.6</v>
+        <v>39</v>
       </c>
       <c r="F454" t="n">
         <v>16</v>
@@ -9535,7 +9535,7 @@
         <v>-1.449163043556349</v>
       </c>
       <c r="E455" t="n">
-        <v>36.8</v>
+        <v>39</v>
       </c>
       <c r="F455" t="n">
         <v>19</v>
@@ -9575,7 +9575,7 @@
         <v>-3.258944684774359</v>
       </c>
       <c r="E457" t="n">
-        <v>39.9</v>
+        <v>45</v>
       </c>
       <c r="F457" t="n">
         <v>19</v>
@@ -9595,7 +9595,7 @@
         <v>0.3038155417847883</v>
       </c>
       <c r="E458" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F458" t="n">
         <v>20.5</v>
@@ -9615,7 +9615,7 @@
         <v>2.925567382898334</v>
       </c>
       <c r="E459" t="n">
-        <v>37.7</v>
+        <v>45</v>
       </c>
       <c r="F459" t="n">
         <v>20.5</v>
@@ -9635,7 +9635,7 @@
         <v>1.227335378612259</v>
       </c>
       <c r="E460" t="n">
-        <v>37.7</v>
+        <v>35</v>
       </c>
       <c r="F460" t="n">
         <v>22</v>
@@ -9655,7 +9655,7 @@
         <v>0.3567135355337989</v>
       </c>
       <c r="E461" t="n">
-        <v>37.7</v>
+        <v>47</v>
       </c>
       <c r="F461" t="n">
         <v>20.5</v>
@@ -9675,7 +9675,7 @@
         <v>-5.230389973549588</v>
       </c>
       <c r="E462" t="n">
-        <v>41.9</v>
+        <v>39</v>
       </c>
       <c r="F462" t="n">
         <v>16</v>
@@ -9695,7 +9695,7 @@
         <v>-4.468962519235911</v>
       </c>
       <c r="E463" t="n">
-        <v>36.6</v>
+        <v>41</v>
       </c>
       <c r="F463" t="n">
         <v>22</v>
@@ -9715,7 +9715,7 @@
         <v>3.142223358714665</v>
       </c>
       <c r="E464" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F464" t="n">
         <v>20.5</v>
@@ -9735,7 +9735,7 @@
         <v>1.02510534400717</v>
       </c>
       <c r="E465" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F465" t="n">
         <v>22</v>
@@ -9755,7 +9755,7 @@
         <v>-0.6141674555601673</v>
       </c>
       <c r="E466" t="n">
-        <v>41.9</v>
+        <v>47</v>
       </c>
       <c r="F466" t="n">
         <v>20.5</v>
@@ -9775,7 +9775,7 @@
         <v>-0.8160733879181367</v>
       </c>
       <c r="E467" t="n">
-        <v>42.8</v>
+        <v>41</v>
       </c>
       <c r="F467" t="n">
         <v>20.5</v>
@@ -9795,7 +9795,7 @@
         <v>1.137338576071934</v>
       </c>
       <c r="E468" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F468" t="n">
         <v>23.5</v>
@@ -9815,7 +9815,7 @@
         <v>0.6915120900000564</v>
       </c>
       <c r="E469" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F469" t="n">
         <v>22</v>
@@ -9835,7 +9835,7 @@
         <v>2.250366219827656</v>
       </c>
       <c r="E470" t="n">
-        <v>34.8</v>
+        <v>41</v>
       </c>
       <c r="F470" t="n">
         <v>20.5</v>
@@ -9855,7 +9855,7 @@
         <v>0.02060750638746916</v>
       </c>
       <c r="E471" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F471" t="n">
         <v>20.5</v>
@@ -9895,7 +9895,7 @@
         <v>-1.707842522936838</v>
       </c>
       <c r="E473" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F473" t="n">
         <v>23.5</v>
@@ -9915,7 +9915,7 @@
         <v>5.089236637678793</v>
       </c>
       <c r="E474" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="F474" t="n">
         <v>19</v>
@@ -9935,7 +9935,7 @@
         <v>1.098682892356061</v>
       </c>
       <c r="E475" t="n">
-        <v>35.9</v>
+        <v>45</v>
       </c>
       <c r="F475" t="n">
         <v>23.5</v>
@@ -9955,7 +9955,7 @@
         <v>2.123629903505583</v>
       </c>
       <c r="E476" t="n">
-        <v>42.8</v>
+        <v>45</v>
       </c>
       <c r="F476" t="n">
         <v>23.5</v>
@@ -9975,7 +9975,7 @@
         <v>2.587962081711049</v>
       </c>
       <c r="E477" t="n">
-        <v>40.6</v>
+        <v>45</v>
       </c>
       <c r="F477" t="n">
         <v>22</v>
@@ -9995,7 +9995,7 @@
         <v>1.46521177615566</v>
       </c>
       <c r="E478" t="n">
-        <v>43.7</v>
+        <v>45</v>
       </c>
       <c r="F478" t="n">
         <v>20.5</v>
@@ -10015,7 +10015,7 @@
         <v>2.227730912077593</v>
       </c>
       <c r="E479" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F479" t="n">
         <v>23.5</v>
@@ -10035,7 +10035,7 @@
         <v>-2.852511499325471</v>
       </c>
       <c r="E480" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="F480" t="n">
         <v>20.5</v>
@@ -10055,7 +10055,7 @@
         <v>1.656101105496402</v>
       </c>
       <c r="E481" t="n">
-        <v>43.9</v>
+        <v>47</v>
       </c>
       <c r="F481" t="n">
         <v>23.5</v>
@@ -10075,7 +10075,7 @@
         <v>-2.181595041450903</v>
       </c>
       <c r="E482" t="n">
-        <v>41.9</v>
+        <v>43</v>
       </c>
       <c r="F482" t="n">
         <v>22</v>
@@ -10095,7 +10095,7 @@
         <v>2.309738472745105</v>
       </c>
       <c r="E483" t="n">
-        <v>37.5</v>
+        <v>43</v>
       </c>
       <c r="F483" t="n">
         <v>22</v>
@@ -10115,7 +10115,7 @@
         <v>2.92055749528471</v>
       </c>
       <c r="E484" t="n">
-        <v>43.7</v>
+        <v>45</v>
       </c>
       <c r="F484" t="n">
         <v>23.5</v>
@@ -10155,7 +10155,7 @@
         <v>1.558160184887974</v>
       </c>
       <c r="E486" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="F486" t="n">
         <v>22</v>
@@ -10195,7 +10195,7 @@
         <v>-6.425254374315139</v>
       </c>
       <c r="E488" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F488" t="n">
         <v>22</v>
@@ -10215,7 +10215,7 @@
         <v>-0.2984252876331439</v>
       </c>
       <c r="E489" t="n">
-        <v>45.9</v>
+        <v>47</v>
       </c>
       <c r="F489" t="n">
         <v>22</v>
@@ -10235,7 +10235,7 @@
         <v>1.906705737190377</v>
       </c>
       <c r="E490" t="n">
-        <v>41.9</v>
+        <v>47</v>
       </c>
       <c r="F490" t="n">
         <v>20.5</v>
@@ -10255,7 +10255,7 @@
         <v>-1.825583128419374</v>
       </c>
       <c r="E491" t="n">
-        <v>43.7</v>
+        <v>47</v>
       </c>
       <c r="F491" t="n">
         <v>22</v>
@@ -10275,7 +10275,7 @@
         <v>-0.5532374137363099</v>
       </c>
       <c r="E492" t="n">
-        <v>40.6</v>
+        <v>45</v>
       </c>
       <c r="F492" t="n">
         <v>20.5</v>
@@ -10315,7 +10315,7 @@
         <v>2.792917539201678</v>
       </c>
       <c r="E494" t="n">
-        <v>43.9</v>
+        <v>47</v>
       </c>
       <c r="F494" t="n">
         <v>23.5</v>
@@ -10355,7 +10355,7 @@
         <v>-2.120665427487619</v>
       </c>
       <c r="E496" t="n">
-        <v>42.59999999999999</v>
+        <v>47</v>
       </c>
       <c r="F496" t="n">
         <v>23.5</v>
@@ -10375,7 +10375,7 @@
         <v>1.224652498852347</v>
       </c>
       <c r="E497" t="n">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="F497" t="n">
         <v>23.5</v>
@@ -10395,7 +10395,7 @@
         <v>2.687541208121736</v>
       </c>
       <c r="E498" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
       <c r="F498" t="n">
         <v>20.5</v>
@@ -10415,7 +10415,7 @@
         <v>0.8240832438619535</v>
       </c>
       <c r="E499" t="n">
-        <v>43.9</v>
+        <v>43</v>
       </c>
       <c r="F499" t="n">
         <v>23.5</v>
@@ -10435,7 +10435,7 @@
         <v>2.630254364117565</v>
       </c>
       <c r="E500" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F500" t="n">
         <v>23.5</v>
@@ -10455,7 +10455,7 @@
         <v>4.989565238231685</v>
       </c>
       <c r="E501" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="F501" t="n">
         <v>23.5</v>
@@ -10540,7 +10540,7 @@
         <v>-8.085577424066329</v>
       </c>
       <c r="E3" t="n">
-        <v>21.9624</v>
+        <v>23.052</v>
       </c>
       <c r="F3" t="n">
         <v>5.764</v>
@@ -10562,7 +10562,7 @@
         <v>6.17377840023794</v>
       </c>
       <c r="E4" t="n">
-        <v>14.46110623108943</v>
+        <v>15.03893730522674</v>
       </c>
       <c r="F4" t="n">
         <v>11.03221298955444</v>
@@ -10584,7 +10584,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.2</v>
+        <v>-13</v>
       </c>
       <c r="F5" t="n">
         <v>-21.5</v>
@@ -10606,7 +10606,7 @@
         <v>-12.62876437265224</v>
       </c>
       <c r="E6" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>-2.375</v>
@@ -10628,7 +10628,7 @@
         <v>-7.930705794315703</v>
       </c>
       <c r="E7" t="n">
-        <v>22.8</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
         <v>5.5</v>
@@ -10650,7 +10650,7 @@
         <v>-3.501682725504332</v>
       </c>
       <c r="E8" t="n">
-        <v>33.9</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>14.5</v>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -475,7 +475,7 @@
         <v>-20.88028902850273</v>
       </c>
       <c r="E2" t="n">
-        <v>-3</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>-0.5</v>
@@ -495,7 +495,7 @@
         <v>-15.08041566639237</v>
       </c>
       <c r="E3" t="n">
-        <v>-13</v>
+        <v>-29</v>
       </c>
       <c r="F3" t="n">
         <v>-18.5</v>
@@ -515,7 +515,7 @@
         <v>-16.24192719111304</v>
       </c>
       <c r="E4" t="n">
-        <v>-3</v>
+        <v>-16</v>
       </c>
       <c r="F4" t="n">
         <v>-18.5</v>
@@ -535,7 +535,7 @@
         <v>-18.76282389482354</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>-3.5</v>
@@ -555,7 +555,7 @@
         <v>-9.011605956684511</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>-21</v>
       </c>
       <c r="F6" t="n">
         <v>-12.5</v>
@@ -575,7 +575,7 @@
         <v>-16.88493498782972</v>
       </c>
       <c r="E7" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="F7" t="n">
         <v>-12.5</v>
@@ -595,7 +595,7 @@
         <v>-22.1585517447926</v>
       </c>
       <c r="E8" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="F8" t="n">
         <v>-8</v>
@@ -615,7 +615,7 @@
         <v>-14.86028872807583</v>
       </c>
       <c r="E9" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="F9" t="n">
         <v>-11</v>
@@ -635,7 +635,7 @@
         <v>-16.66542535497044</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>-2</v>
@@ -655,7 +655,7 @@
         <v>-16.50768248317392</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
@@ -675,7 +675,7 @@
         <v>-22.1585747570583</v>
       </c>
       <c r="E12" t="n">
-        <v>-11</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>-12.5</v>
@@ -695,7 +695,7 @@
         <v>-16.07701479937518</v>
       </c>
       <c r="E13" t="n">
-        <v>-9</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5</v>
@@ -715,7 +715,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>-5</v>
@@ -735,7 +735,7 @@
         <v>-14.49481384471911</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F15" t="n">
         <v>-18.5</v>
@@ -755,7 +755,7 @@
         <v>-19.39923887184475</v>
       </c>
       <c r="E16" t="n">
-        <v>-13</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>-12.5</v>
@@ -775,7 +775,7 @@
         <v>-15.21056902635355</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>-12.5</v>
@@ -795,7 +795,7 @@
         <v>-18.66489425226396</v>
       </c>
       <c r="E18" t="n">
-        <v>-11</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>-11</v>
@@ -815,7 +815,7 @@
         <v>-9.011666353277461</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>-12.5</v>
@@ -835,7 +835,7 @@
         <v>-12.42194598309683</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="F20" t="n">
         <v>-8</v>
@@ -855,7 +855,7 @@
         <v>-8.344026407773633</v>
       </c>
       <c r="E21" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>-17</v>
@@ -875,7 +875,7 @@
         <v>-10.61191573078219</v>
       </c>
       <c r="E22" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="F22" t="n">
         <v>-5</v>
@@ -895,7 +895,7 @@
         <v>-13.76809791504057</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
         <v>-21.5</v>
@@ -915,7 +915,7 @@
         <v>-13.61382958064067</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>-9.5</v>
@@ -935,7 +935,7 @@
         <v>-17.04709742089801</v>
       </c>
       <c r="E25" t="n">
-        <v>-5</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
         <v>-5</v>
@@ -955,7 +955,7 @@
         <v>-11.45515617083332</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>-9.5</v>
@@ -975,7 +975,7 @@
         <v>-22.65071637595969</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F27" t="n">
         <v>-12.5</v>
@@ -995,7 +995,7 @@
         <v>-18.723853564575</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
         <v>-6.5</v>
@@ -1015,7 +1015,7 @@
         <v>-19.58043031028957</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
         <v>-11</v>
@@ -1035,7 +1035,7 @@
         <v>-21.81599222693938</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1055,7 +1055,7 @@
         <v>-12.33207495069766</v>
       </c>
       <c r="E31" t="n">
-        <v>-3</v>
+        <v>65</v>
       </c>
       <c r="F31" t="n">
         <v>-9.5</v>
@@ -1075,7 +1075,7 @@
         <v>-12.07550353950178</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -1095,7 +1095,7 @@
         <v>-13.9055061383892</v>
       </c>
       <c r="E33" t="n">
-        <v>-7</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -1115,7 +1115,7 @@
         <v>-20.68298851778319</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5</v>
@@ -1135,7 +1135,7 @@
         <v>-13.67390778367567</v>
       </c>
       <c r="E35" t="n">
-        <v>-1</v>
+        <v>41</v>
       </c>
       <c r="F35" t="n">
         <v>-9.5</v>
@@ -1155,7 +1155,7 @@
         <v>-9.665718240118361</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
         <v>-20</v>
@@ -1175,7 +1175,7 @@
         <v>-15.36778170122901</v>
       </c>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F37" t="n">
         <v>-12.5</v>
@@ -1195,7 +1195,7 @@
         <v>-12.35413898216171</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F38" t="n">
         <v>-21.5</v>
@@ -1215,7 +1215,7 @@
         <v>-16.22217341588913</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
         <v>2.5</v>
@@ -1235,7 +1235,7 @@
         <v>-10.00948967549725</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="F40" t="n">
         <v>-17</v>
@@ -1255,7 +1255,7 @@
         <v>-15.10350776269546</v>
       </c>
       <c r="E41" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
         <v>-17</v>
@@ -1275,7 +1275,7 @@
         <v>-13.62641184742081</v>
       </c>
       <c r="E42" t="n">
-        <v>-11</v>
+        <v>16</v>
       </c>
       <c r="F42" t="n">
         <v>-12.5</v>
@@ -1295,7 +1295,7 @@
         <v>-14.71610395027719</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
         <v>-11</v>
@@ -1315,7 +1315,7 @@
         <v>-17.32238709223246</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F44" t="n">
         <v>-6.5</v>
@@ -1335,7 +1335,7 @@
         <v>-18.3985178425561</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F45" t="n">
         <v>2.5</v>
@@ -1355,7 +1355,7 @@
         <v>-13.92117656900311</v>
       </c>
       <c r="E46" t="n">
-        <v>-7</v>
+        <v>39</v>
       </c>
       <c r="F46" t="n">
         <v>-11</v>
@@ -1375,7 +1375,7 @@
         <v>-11.07952799310252</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F47" t="n">
         <v>-8</v>
@@ -1395,7 +1395,7 @@
         <v>-17.00931480520146</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F48" t="n">
         <v>-18.5</v>
@@ -1415,7 +1415,7 @@
         <v>-12.51496523440635</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -1435,7 +1435,7 @@
         <v>-12.56933176486039</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n">
         <v>-2</v>
@@ -1455,7 +1455,7 @@
         <v>-18.61042700136766</v>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F51" t="n">
         <v>-9.5</v>
@@ -1475,7 +1475,7 @@
         <v>-19.98298420591642</v>
       </c>
       <c r="E52" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F52" t="n">
         <v>-18.5</v>
@@ -1495,7 +1495,7 @@
         <v>-6.672983718717866</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
         <v>-8</v>
@@ -1515,7 +1515,7 @@
         <v>-15.35638027898899</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>-11</v>
@@ -1535,7 +1535,7 @@
         <v>-15.19729180569158</v>
       </c>
       <c r="E55" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F55" t="n">
         <v>-5</v>
@@ -1555,7 +1555,7 @@
         <v>-14.51951403443939</v>
       </c>
       <c r="E56" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
         <v>-14</v>
@@ -1575,7 +1575,7 @@
         <v>-16.3915095915476</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
         <v>-9.5</v>
@@ -1595,7 +1595,7 @@
         <v>-16.72760094092684</v>
       </c>
       <c r="E58" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="F58" t="n">
         <v>-9.5</v>
@@ -1615,7 +1615,7 @@
         <v>-11.78050191422369</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="F59" t="n">
         <v>-9.5</v>
@@ -1635,7 +1635,7 @@
         <v>-13.16902826441466</v>
       </c>
       <c r="E60" t="n">
-        <v>-9</v>
+        <v>82</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5</v>
@@ -1655,7 +1655,7 @@
         <v>-18.54419594854977</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n">
         <v>-11</v>
@@ -1675,7 +1675,7 @@
         <v>-8.807644726031004</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
         <v>-11</v>
@@ -1695,7 +1695,7 @@
         <v>-14.28909157388709</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="F63" t="n">
         <v>-8</v>
@@ -1715,7 +1715,7 @@
         <v>-15.86301331944633</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
         <v>-9.5</v>
@@ -1735,7 +1735,7 @@
         <v>-16.55071283344781</v>
       </c>
       <c r="E65" t="n">
-        <v>-3</v>
+        <v>60</v>
       </c>
       <c r="F65" t="n">
         <v>-0.5</v>
@@ -1755,7 +1755,7 @@
         <v>-17.9336097374753</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
         <v>-17</v>
@@ -1775,7 +1775,7 @@
         <v>-11.96824934592622</v>
       </c>
       <c r="E67" t="n">
-        <v>-5</v>
+        <v>63</v>
       </c>
       <c r="F67" t="n">
         <v>-3.5</v>
@@ -1795,7 +1795,7 @@
         <v>-11.58305819485098</v>
       </c>
       <c r="E68" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F68" t="n">
         <v>-6.5</v>
@@ -1815,7 +1815,7 @@
         <v>-16.96770942927208</v>
       </c>
       <c r="E69" t="n">
-        <v>-11</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>-5</v>
@@ -1835,7 +1835,7 @@
         <v>-13.70594101887073</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
         <v>-11</v>
@@ -1855,7 +1855,7 @@
         <v>-13.35983540697217</v>
       </c>
       <c r="E71" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>-11</v>
@@ -1875,7 +1875,7 @@
         <v>-13.73945420010882</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F72" t="n">
         <v>-9.5</v>
@@ -1895,7 +1895,7 @@
         <v>-21.43215273472283</v>
       </c>
       <c r="E73" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
         <v>-14</v>
@@ -1915,7 +1915,7 @@
         <v>-19.93026650520378</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F74" t="n">
         <v>-6.5</v>
@@ -1935,7 +1935,7 @@
         <v>-13.63373489971633</v>
       </c>
       <c r="E75" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
         <v>-9.5</v>
@@ -1955,7 +1955,7 @@
         <v>-14.70893704404678</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
         <v>2.5</v>
@@ -1975,7 +1975,7 @@
         <v>-20.41126671783134</v>
       </c>
       <c r="E77" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="F77" t="n">
         <v>-2</v>
@@ -1995,7 +1995,7 @@
         <v>-8.298668334372483</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F78" t="n">
         <v>-9.5</v>
@@ -2015,7 +2015,7 @@
         <v>-11.09414578630654</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F79" t="n">
         <v>-3.5</v>
@@ -2035,7 +2035,7 @@
         <v>-14.76956546226694</v>
       </c>
       <c r="E80" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>-5</v>
@@ -2055,7 +2055,7 @@
         <v>-14.11114333061668</v>
       </c>
       <c r="E81" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F81" t="n">
         <v>-11</v>
@@ -2075,7 +2075,7 @@
         <v>-17.36533220259155</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F82" t="n">
         <v>-9.5</v>
@@ -2095,7 +2095,7 @@
         <v>-14.29537266647307</v>
       </c>
       <c r="E83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
         <v>-11</v>
@@ -2115,7 +2115,7 @@
         <v>-15.52673225528131</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n">
         <v>-2</v>
@@ -2135,7 +2135,7 @@
         <v>-10.61618120478381</v>
       </c>
       <c r="E85" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
         <v>-6.5</v>
@@ -2155,7 +2155,7 @@
         <v>-9.558453099269794</v>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F86" t="n">
         <v>-3.5</v>
@@ -2175,7 +2175,7 @@
         <v>-11.95578259847385</v>
       </c>
       <c r="E87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F87" t="n">
         <v>-2</v>
@@ -2195,7 +2195,7 @@
         <v>-14.53892114818133</v>
       </c>
       <c r="E88" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F88" t="n">
         <v>-0.5</v>
@@ -2215,7 +2215,7 @@
         <v>-14.98567711898332</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
         <v>-2</v>
@@ -2235,7 +2235,7 @@
         <v>-8.626986066168405</v>
       </c>
       <c r="E90" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F90" t="n">
         <v>-9.5</v>
@@ -2255,7 +2255,7 @@
         <v>-14.42115485021459</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>-2</v>
@@ -2275,7 +2275,7 @@
         <v>-14.81963907250334</v>
       </c>
       <c r="E92" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
         <v>-8</v>
@@ -2295,7 +2295,7 @@
         <v>-18.27445887317804</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F93" t="n">
         <v>-0.5</v>
@@ -2315,7 +2315,7 @@
         <v>-14.01149006572236</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F94" t="n">
         <v>-2</v>
@@ -2335,7 +2335,7 @@
         <v>-11.76638385536769</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="F95" t="n">
         <v>-5</v>
@@ -2355,7 +2355,7 @@
         <v>-9.413356115683376</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="F96" t="n">
         <v>-5</v>
@@ -2375,7 +2375,7 @@
         <v>-14.28585576463446</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
         <v>2.5</v>
@@ -2395,7 +2395,7 @@
         <v>-11.85349409751063</v>
       </c>
       <c r="E98" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F98" t="n">
         <v>-3.5</v>
@@ -2415,7 +2415,7 @@
         <v>-15.24029031651793</v>
       </c>
       <c r="E99" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
         <v>-5</v>
@@ -2435,7 +2435,7 @@
         <v>-16.01872556029471</v>
       </c>
       <c r="E100" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="F100" t="n">
         <v>-2</v>
@@ -2455,7 +2455,7 @@
         <v>-11.30979160160691</v>
       </c>
       <c r="E101" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>-15.21465658295874</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
         <v>-9.5</v>
@@ -2495,7 +2495,7 @@
         <v>-11.91209159844877</v>
       </c>
       <c r="E103" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>-18.47233524338426</v>
       </c>
       <c r="E104" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F104" t="n">
         <v>-11</v>
@@ -2535,7 +2535,7 @@
         <v>-15.99683898329127</v>
       </c>
       <c r="E105" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F105" t="n">
         <v>4</v>
@@ -2555,7 +2555,7 @@
         <v>-11.78397827839792</v>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="F106" t="n">
         <v>-12.5</v>
@@ -2575,7 +2575,7 @@
         <v>-14.09994806721748</v>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F107" t="n">
         <v>-14</v>
@@ -2595,7 +2595,7 @@
         <v>-13.11527797743044</v>
       </c>
       <c r="E108" t="n">
-        <v>21</v>
+        <v>-14</v>
       </c>
       <c r="F108" t="n">
         <v>-9.5</v>
@@ -2615,7 +2615,7 @@
         <v>-10.20573754684604</v>
       </c>
       <c r="E109" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F109" t="n">
         <v>-11</v>
@@ -2635,7 +2635,7 @@
         <v>-12.319581041081</v>
       </c>
       <c r="E110" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F110" t="n">
         <v>-5</v>
@@ -2655,7 +2655,7 @@
         <v>-6.059953702883841</v>
       </c>
       <c r="E111" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F111" t="n">
         <v>-0.5</v>
@@ -2675,7 +2675,7 @@
         <v>-13.07604183385386</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>-12.00565567818595</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="F113" t="n">
         <v>-6.5</v>
@@ -2715,7 +2715,7 @@
         <v>-18.23586872181258</v>
       </c>
       <c r="E114" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F114" t="n">
         <v>-2</v>
@@ -2735,7 +2735,7 @@
         <v>-16.23673636012176</v>
       </c>
       <c r="E115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F115" t="n">
         <v>-0.5</v>
@@ -2755,7 +2755,7 @@
         <v>-9.138045441859136</v>
       </c>
       <c r="E116" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F116" t="n">
         <v>-6.5</v>
@@ -2775,7 +2775,7 @@
         <v>-8.735620769461221</v>
       </c>
       <c r="E117" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
         <v>-3.275988466822424</v>
       </c>
       <c r="E118" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F118" t="n">
         <v>-2</v>
@@ -2815,7 +2815,7 @@
         <v>-21.46730196390546</v>
       </c>
       <c r="E119" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F119" t="n">
         <v>-8</v>
@@ -2835,7 +2835,7 @@
         <v>-9.30602509382889</v>
       </c>
       <c r="E120" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F120" t="n">
         <v>-2</v>
@@ -2855,7 +2855,7 @@
         <v>-15.45651431364378</v>
       </c>
       <c r="E121" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F121" t="n">
         <v>-2</v>
@@ -2875,7 +2875,7 @@
         <v>-6.65815148548338</v>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="F122" t="n">
         <v>-8</v>
@@ -2895,7 +2895,7 @@
         <v>-6.936543698335337</v>
       </c>
       <c r="E123" t="n">
-        <v>-1</v>
+        <v>82</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         <v>-11.38242419822538</v>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="F124" t="n">
         <v>-6.5</v>
@@ -2935,7 +2935,7 @@
         <v>-15.10018684775595</v>
       </c>
       <c r="E125" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="F125" t="n">
         <v>-3.5</v>
@@ -2955,7 +2955,7 @@
         <v>-14.27988774904433</v>
       </c>
       <c r="E126" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="F126" t="n">
         <v>-5</v>
@@ -2975,7 +2975,7 @@
         <v>-6.334648954400722</v>
       </c>
       <c r="E127" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F127" t="n">
         <v>-12.5</v>
@@ -2995,7 +2995,7 @@
         <v>-13.5475756767352</v>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F128" t="n">
         <v>-6.5</v>
@@ -3015,7 +3015,7 @@
         <v>-11.66477267457763</v>
       </c>
       <c r="E129" t="n">
-        <v>-1</v>
+        <v>70</v>
       </c>
       <c r="F129" t="n">
         <v>-3.5</v>
@@ -3035,7 +3035,7 @@
         <v>-14.70454073338186</v>
       </c>
       <c r="E130" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -3055,7 +3055,7 @@
         <v>-11.29764528453063</v>
       </c>
       <c r="E131" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="F131" t="n">
         <v>-5</v>
@@ -3075,7 +3075,7 @@
         <v>-9.092734146744514</v>
       </c>
       <c r="E132" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -3095,7 +3095,7 @@
         <v>-7.953307220522068</v>
       </c>
       <c r="E133" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="F133" t="n">
         <v>-5</v>
@@ -3115,7 +3115,7 @@
         <v>-8.629619074258962</v>
       </c>
       <c r="E134" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F134" t="n">
         <v>-6.5</v>
@@ -3135,7 +3135,7 @@
         <v>-12.45493151160171</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F135" t="n">
         <v>5.5</v>
@@ -3155,7 +3155,7 @@
         <v>-15.35178539224633</v>
       </c>
       <c r="E136" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F136" t="n">
         <v>-3.5</v>
@@ -3175,7 +3175,7 @@
         <v>-14.42757650544786</v>
       </c>
       <c r="E137" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F137" t="n">
         <v>-11</v>
@@ -3195,7 +3195,7 @@
         <v>-13.78355315746163</v>
       </c>
       <c r="E138" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F138" t="n">
         <v>-5</v>
@@ -3215,7 +3215,7 @@
         <v>-11.16316554267884</v>
       </c>
       <c r="E139" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="F139" t="n">
         <v>-0.5</v>
@@ -3235,7 +3235,7 @@
         <v>-15.7222577936834</v>
       </c>
       <c r="E140" t="n">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -3255,7 +3255,7 @@
         <v>-18.80056717765801</v>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F141" t="n">
         <v>5.5</v>
@@ -3275,7 +3275,7 @@
         <v>-12.75547358832381</v>
       </c>
       <c r="E142" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F142" t="n">
         <v>-2</v>
@@ -3295,7 +3295,7 @@
         <v>-13.05017477055378</v>
       </c>
       <c r="E143" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F143" t="n">
         <v>2.5</v>
@@ -3315,7 +3315,7 @@
         <v>-9.492785338822857</v>
       </c>
       <c r="E144" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="F144" t="n">
         <v>5.5</v>
@@ -3335,7 +3335,7 @@
         <v>-12.82451007415136</v>
       </c>
       <c r="E145" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F145" t="n">
         <v>-2</v>
@@ -3355,7 +3355,7 @@
         <v>-15.2583426766281</v>
       </c>
       <c r="E146" t="n">
-        <v>-1</v>
+        <v>91</v>
       </c>
       <c r="F146" t="n">
         <v>-5</v>
@@ -3375,7 +3375,7 @@
         <v>-8.936160793676258</v>
       </c>
       <c r="E147" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F147" t="n">
         <v>-5</v>
@@ -3395,7 +3395,7 @@
         <v>-12.01544842174979</v>
       </c>
       <c r="E148" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F148" t="n">
         <v>-3.5</v>
@@ -3415,7 +3415,7 @@
         <v>-9.976100682743448</v>
       </c>
       <c r="E149" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="F149" t="n">
         <v>2.5</v>
@@ -3435,7 +3435,7 @@
         <v>-9.072845539237004</v>
       </c>
       <c r="E150" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="F150" t="n">
         <v>-0.5</v>
@@ -3455,7 +3455,7 @@
         <v>-9.050443784764134</v>
       </c>
       <c r="E151" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F151" t="n">
         <v>2.5</v>
@@ -3475,7 +3475,7 @@
         <v>-9.19299135802768</v>
       </c>
       <c r="E152" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="F152" t="n">
         <v>-6.5</v>
@@ -3495,7 +3495,7 @@
         <v>-11.48622657143187</v>
       </c>
       <c r="E153" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F153" t="n">
         <v>-5</v>
@@ -3515,7 +3515,7 @@
         <v>-12.33292625264692</v>
       </c>
       <c r="E154" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="F154" t="n">
         <v>-5</v>
@@ -3535,7 +3535,7 @@
         <v>-8.749082119178086</v>
       </c>
       <c r="E155" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F155" t="n">
         <v>-6.5</v>
@@ -3555,7 +3555,7 @@
         <v>-8.914449436079753</v>
       </c>
       <c r="E156" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="F156" t="n">
         <v>-3.5</v>
@@ -3575,7 +3575,7 @@
         <v>-3.178563438316917</v>
       </c>
       <c r="E157" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F157" t="n">
         <v>2.5</v>
@@ -3595,7 +3595,7 @@
         <v>-11.29514140666748</v>
       </c>
       <c r="E158" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -3615,7 +3615,7 @@
         <v>-16.68234331642212</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F159" t="n">
         <v>5.5</v>
@@ -3635,7 +3635,7 @@
         <v>-17.327950736185</v>
       </c>
       <c r="E160" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F160" t="n">
         <v>2.5</v>
@@ -3655,7 +3655,7 @@
         <v>-11.49020960393287</v>
       </c>
       <c r="E161" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -3675,7 +3675,7 @@
         <v>-1.895934786610538</v>
       </c>
       <c r="E162" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F162" t="n">
         <v>-5</v>
@@ -3695,7 +3695,7 @@
         <v>-11.60328510091501</v>
       </c>
       <c r="E163" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="F163" t="n">
         <v>-9.5</v>
@@ -3715,7 +3715,7 @@
         <v>-4.872661986196267</v>
       </c>
       <c r="E164" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F164" t="n">
         <v>-6.5</v>
@@ -3735,7 +3735,7 @@
         <v>-16.53562999078624</v>
       </c>
       <c r="E165" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F165" t="n">
         <v>-0.5</v>
@@ -3755,7 +3755,7 @@
         <v>-10.779735566366</v>
       </c>
       <c r="E166" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>-7.441839040123449</v>
       </c>
       <c r="E167" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F167" t="n">
         <v>2.5</v>
@@ -3795,7 +3795,7 @@
         <v>-8.540216823457699</v>
       </c>
       <c r="E168" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -3815,7 +3815,7 @@
         <v>-13.36124095935507</v>
       </c>
       <c r="E169" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F169" t="n">
         <v>-6.5</v>
@@ -3835,7 +3835,7 @@
         <v>-7.941572000257956</v>
       </c>
       <c r="E170" t="n">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F170" t="n">
         <v>7</v>
@@ -3855,7 +3855,7 @@
         <v>-12.24259454888164</v>
       </c>
       <c r="E171" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F171" t="n">
         <v>2.5</v>
@@ -3875,7 +3875,7 @@
         <v>-9.577734981138333</v>
       </c>
       <c r="E172" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="F172" t="n">
         <v>2.5</v>
@@ -3895,7 +3895,7 @@
         <v>-16.95493489049333</v>
       </c>
       <c r="E173" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F173" t="n">
         <v>-6.5</v>
@@ -3915,7 +3915,7 @@
         <v>-7.956608854497154</v>
       </c>
       <c r="E174" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="F174" t="n">
         <v>-3.5</v>
@@ -3935,7 +3935,7 @@
         <v>-6.940769548170551</v>
       </c>
       <c r="E175" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F175" t="n">
         <v>4</v>
@@ -3955,7 +3955,7 @@
         <v>-8.448732765702129</v>
       </c>
       <c r="E176" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="F176" t="n">
         <v>7</v>
@@ -3975,7 +3975,7 @@
         <v>-11.73009639391955</v>
       </c>
       <c r="E177" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="F177" t="n">
         <v>4</v>
@@ -3995,7 +3995,7 @@
         <v>-16.77275246571654</v>
       </c>
       <c r="E178" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F178" t="n">
         <v>7</v>
@@ -4015,7 +4015,7 @@
         <v>-7.272125353914878</v>
       </c>
       <c r="E179" t="n">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="F179" t="n">
         <v>-0.5</v>
@@ -4035,7 +4035,7 @@
         <v>-16.31510018076369</v>
       </c>
       <c r="E180" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F180" t="n">
         <v>-2</v>
@@ -4055,7 +4055,7 @@
         <v>-12.74747409402433</v>
       </c>
       <c r="E181" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="F181" t="n">
         <v>5.5</v>
@@ -4075,7 +4075,7 @@
         <v>-13.55980417347203</v>
       </c>
       <c r="E182" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="F182" t="n">
         <v>8.5</v>
@@ -4095,7 +4095,7 @@
         <v>-13.27490502800834</v>
       </c>
       <c r="E183" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F183" t="n">
         <v>7</v>
@@ -4115,7 +4115,7 @@
         <v>-12.74484715468625</v>
       </c>
       <c r="E184" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F184" t="n">
         <v>7</v>
@@ -4135,7 +4135,7 @@
         <v>-12.34849872044505</v>
       </c>
       <c r="E185" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F185" t="n">
         <v>-0.5</v>
@@ -4155,7 +4155,7 @@
         <v>-8.532723933054008</v>
       </c>
       <c r="E186" t="n">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="F186" t="n">
         <v>-0.5</v>
@@ -4175,7 +4175,7 @@
         <v>-7.575287710323443</v>
       </c>
       <c r="E187" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="F187" t="n">
         <v>-8</v>
@@ -4195,7 +4195,7 @@
         <v>-11.86378417977766</v>
       </c>
       <c r="E188" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F188" t="n">
         <v>5.5</v>
@@ -4215,7 +4215,7 @@
         <v>-12.69125732972837</v>
       </c>
       <c r="E189" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F189" t="n">
         <v>4</v>
@@ -4235,7 +4235,7 @@
         <v>-7.146291150027026</v>
       </c>
       <c r="E190" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F190" t="n">
         <v>4</v>
@@ -4255,7 +4255,7 @@
         <v>-10.73034245970168</v>
       </c>
       <c r="E191" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F191" t="n">
         <v>-8</v>
@@ -4275,7 +4275,7 @@
         <v>-18.78829949929933</v>
       </c>
       <c r="E192" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F192" t="n">
         <v>4</v>
@@ -4295,7 +4295,7 @@
         <v>-19.06989102055279</v>
       </c>
       <c r="E193" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F193" t="n">
         <v>8.5</v>
@@ -4315,7 +4315,7 @@
         <v>-5.042595232131265</v>
       </c>
       <c r="E194" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="F194" t="n">
         <v>-0.5</v>
@@ -4335,7 +4335,7 @@
         <v>-7.306725776447404</v>
       </c>
       <c r="E195" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="F195" t="n">
         <v>-2</v>
@@ -4355,7 +4355,7 @@
         <v>-11.2969328754405</v>
       </c>
       <c r="E196" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
         <v>-0.5</v>
@@ -4375,7 +4375,7 @@
         <v>-10.80408612837662</v>
       </c>
       <c r="E197" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="F197" t="n">
         <v>-5</v>
@@ -4395,7 +4395,7 @@
         <v>-10.88759817733926</v>
       </c>
       <c r="E198" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F198" t="n">
         <v>-0.5</v>
@@ -4415,7 +4415,7 @@
         <v>-13.59431403174799</v>
       </c>
       <c r="E199" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="F199" t="n">
         <v>8.5</v>
@@ -4435,7 +4435,7 @@
         <v>-16.73414753036879</v>
       </c>
       <c r="E200" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="F200" t="n">
         <v>2.5</v>
@@ -4455,7 +4455,7 @@
         <v>-12.17065885528252</v>
       </c>
       <c r="E201" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="F201" t="n">
         <v>-0.5</v>
@@ -4475,7 +4475,7 @@
         <v>-9.682425408507925</v>
       </c>
       <c r="E202" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -4495,7 +4495,7 @@
         <v>-14.42541224847953</v>
       </c>
       <c r="E203" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F203" t="n">
         <v>7</v>
@@ -4515,7 +4515,7 @@
         <v>-11.55982853942983</v>
       </c>
       <c r="E204" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F204" t="n">
         <v>2.5</v>
@@ -4535,7 +4535,7 @@
         <v>-11.76448565489094</v>
       </c>
       <c r="E205" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F205" t="n">
         <v>4</v>
@@ -4555,7 +4555,7 @@
         <v>-8.468822193825609</v>
       </c>
       <c r="E206" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
@@ -4575,7 +4575,7 @@
         <v>-8.670738161587693</v>
       </c>
       <c r="E207" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>-7.822106310077424</v>
       </c>
       <c r="E208" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="F208" t="n">
         <v>-14</v>
@@ -4615,7 +4615,7 @@
         <v>-12.1449725681243</v>
       </c>
       <c r="E209" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F209" t="n">
         <v>-6.5</v>
@@ -4635,7 +4635,7 @@
         <v>-7.434250898971669</v>
       </c>
       <c r="E210" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F210" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         <v>-10.35522160269771</v>
       </c>
       <c r="E211" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F211" t="n">
         <v>2.5</v>
@@ -4675,7 +4675,7 @@
         <v>-12.97258588476429</v>
       </c>
       <c r="E212" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F212" t="n">
         <v>5.5</v>
@@ -4695,7 +4695,7 @@
         <v>-7.268733793080433</v>
       </c>
       <c r="E213" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F213" t="n">
         <v>8.5</v>
@@ -4715,7 +4715,7 @@
         <v>-14.64730992827486</v>
       </c>
       <c r="E214" t="n">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="F214" t="n">
         <v>11.5</v>
@@ -4735,7 +4735,7 @@
         <v>-6.230069394523568</v>
       </c>
       <c r="E215" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="F215" t="n">
         <v>-6.5</v>
@@ -4755,7 +4755,7 @@
         <v>-5.029168024832028</v>
       </c>
       <c r="E216" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="F216" t="n">
         <v>4</v>
@@ -4775,7 +4775,7 @@
         <v>-17.20137440692926</v>
       </c>
       <c r="E217" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F217" t="n">
         <v>-2</v>
@@ -4795,7 +4795,7 @@
         <v>-11.79624044528628</v>
       </c>
       <c r="E218" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F218" t="n">
         <v>7</v>
@@ -4815,7 +4815,7 @@
         <v>-16.74489113681049</v>
       </c>
       <c r="E219" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="F219" t="n">
         <v>2.5</v>
@@ -4835,7 +4835,7 @@
         <v>-11.34683513007241</v>
       </c>
       <c r="E220" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F220" t="n">
         <v>5.5</v>
@@ -4855,7 +4855,7 @@
         <v>-4.672589326071132</v>
       </c>
       <c r="E221" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="F221" t="n">
         <v>4</v>
@@ -4875,7 +4875,7 @@
         <v>-5.574994098887871</v>
       </c>
       <c r="E222" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F222" t="n">
         <v>-0.5</v>
@@ -4895,7 +4895,7 @@
         <v>-7.561973782123608</v>
       </c>
       <c r="E223" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F223" t="n">
         <v>8.5</v>
@@ -4915,7 +4915,7 @@
         <v>-5.122821742112643</v>
       </c>
       <c r="E224" t="n">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="F224" t="n">
         <v>2.5</v>
@@ -4935,7 +4935,7 @@
         <v>-8.540376647193753</v>
       </c>
       <c r="E225" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="F225" t="n">
         <v>2.5</v>
@@ -4955,7 +4955,7 @@
         <v>-14.38422203108571</v>
       </c>
       <c r="E226" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F226" t="n">
         <v>5.5</v>
@@ -4975,7 +4975,7 @@
         <v>-12.3222490983983</v>
       </c>
       <c r="E227" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F227" t="n">
         <v>7</v>
@@ -4995,7 +4995,7 @@
         <v>-8.624119528586101</v>
       </c>
       <c r="E228" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
@@ -5015,7 +5015,7 @@
         <v>-7.642849585159722</v>
       </c>
       <c r="E229" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="F229" t="n">
         <v>-6.5</v>
@@ -5035,7 +5035,7 @@
         <v>-19.21652899798538</v>
       </c>
       <c r="E230" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="F230" t="n">
         <v>2.5</v>
@@ -5055,7 +5055,7 @@
         <v>-7.446396844456115</v>
       </c>
       <c r="E231" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F231" t="n">
         <v>11.5</v>
@@ -5075,7 +5075,7 @@
         <v>-6.816178332842622</v>
       </c>
       <c r="E232" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="F232" t="n">
         <v>-3.5</v>
@@ -5095,7 +5095,7 @@
         <v>-4.111224791603618</v>
       </c>
       <c r="E233" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="F233" t="n">
         <v>2.5</v>
@@ -5115,7 +5115,7 @@
         <v>-7.431045844935011</v>
       </c>
       <c r="E234" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="F234" t="n">
         <v>7</v>
@@ -5135,7 +5135,7 @@
         <v>-3.793921272312653</v>
       </c>
       <c r="E235" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="F235" t="n">
         <v>10</v>
@@ -5155,7 +5155,7 @@
         <v>-9.390426779972653</v>
       </c>
       <c r="E236" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F236" t="n">
         <v>5.5</v>
@@ -5175,7 +5175,7 @@
         <v>-6.645359241779041</v>
       </c>
       <c r="E237" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="F237" t="n">
         <v>2.5</v>
@@ -5195,7 +5195,7 @@
         <v>-6.659235330907647</v>
       </c>
       <c r="E238" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F238" t="n">
         <v>10</v>
@@ -5215,7 +5215,7 @@
         <v>-7.389250931299761</v>
       </c>
       <c r="E239" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="F239" t="n">
         <v>5.5</v>
@@ -5235,7 +5235,7 @@
         <v>-6.601754772706715</v>
       </c>
       <c r="E240" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="F240" t="n">
         <v>10</v>
@@ -5255,7 +5255,7 @@
         <v>-10.54182006098494</v>
       </c>
       <c r="E241" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F241" t="n">
         <v>5.5</v>
@@ -5275,7 +5275,7 @@
         <v>-15.04528412633056</v>
       </c>
       <c r="E242" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F242" t="n">
         <v>10</v>
@@ -5295,7 +5295,7 @@
         <v>-4.485149225985528</v>
       </c>
       <c r="E243" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="F243" t="n">
         <v>7</v>
@@ -5315,7 +5315,7 @@
         <v>-12.90464160657133</v>
       </c>
       <c r="E244" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F244" t="n">
         <v>5.5</v>
@@ -5335,7 +5335,7 @@
         <v>-10.64541686645118</v>
       </c>
       <c r="E245" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F245" t="n">
         <v>2.5</v>
@@ -5355,7 +5355,7 @@
         <v>-10.34030639977348</v>
       </c>
       <c r="E246" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="F246" t="n">
         <v>4</v>
@@ -5375,7 +5375,7 @@
         <v>-10.19854567178833</v>
       </c>
       <c r="E247" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F247" t="n">
         <v>8.5</v>
@@ -5395,7 +5395,7 @@
         <v>-5.854820405046824</v>
       </c>
       <c r="E248" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F248" t="n">
         <v>11.5</v>
@@ -5415,7 +5415,7 @@
         <v>-8.740162907611163</v>
       </c>
       <c r="E249" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F249" t="n">
         <v>5.5</v>
@@ -5435,7 +5435,7 @@
         <v>-8.67301888488873</v>
       </c>
       <c r="E250" t="n">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="F250" t="n">
         <v>4</v>
@@ -5455,7 +5455,7 @@
         <v>-15.23558737691753</v>
       </c>
       <c r="E251" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="F251" t="n">
         <v>4</v>
@@ -5475,7 +5475,7 @@
         <v>-9.342347585650238</v>
       </c>
       <c r="E252" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F252" t="n">
         <v>7</v>
@@ -5495,7 +5495,7 @@
         <v>-4.00963828005715</v>
       </c>
       <c r="E253" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="F253" t="n">
         <v>11.5</v>
@@ -5515,7 +5515,7 @@
         <v>-7.006825558338786</v>
       </c>
       <c r="E254" t="n">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F254" t="n">
         <v>4</v>
@@ -5535,7 +5535,7 @@
         <v>-9.100522115540389</v>
       </c>
       <c r="E255" t="n">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="F255" t="n">
         <v>7</v>
@@ -5555,7 +5555,7 @@
         <v>-6.682488486241348</v>
       </c>
       <c r="E256" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F256" t="n">
         <v>8.5</v>
@@ -5575,7 +5575,7 @@
         <v>-7.919839588373449</v>
       </c>
       <c r="E257" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="F257" t="n">
         <v>7</v>
@@ -5595,7 +5595,7 @@
         <v>-15.12649928222833</v>
       </c>
       <c r="E258" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F258" t="n">
         <v>13</v>
@@ -5615,7 +5615,7 @@
         <v>-4.38164053542964</v>
       </c>
       <c r="E259" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F259" t="n">
         <v>5.5</v>
@@ -5635,7 +5635,7 @@
         <v>-9.879498904697027</v>
       </c>
       <c r="E260" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F260" t="n">
         <v>7</v>
@@ -5655,7 +5655,7 @@
         <v>-4.631422886825721</v>
       </c>
       <c r="E261" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="F261" t="n">
         <v>5.5</v>
@@ -5675,7 +5675,7 @@
         <v>-12.30271398733113</v>
       </c>
       <c r="E262" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F262" t="n">
         <v>11.5</v>
@@ -5695,7 +5695,7 @@
         <v>-7.837332993512454</v>
       </c>
       <c r="E263" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -5715,7 +5715,7 @@
         <v>-11.30272089467063</v>
       </c>
       <c r="E264" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F264" t="n">
         <v>-2</v>
@@ -5735,7 +5735,7 @@
         <v>-2.232287562273741</v>
       </c>
       <c r="E265" t="n">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="F265" t="n">
         <v>-0.5</v>
@@ -5755,7 +5755,7 @@
         <v>-8.845822814643235</v>
       </c>
       <c r="E266" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
         <v>-17.40506405164033</v>
       </c>
       <c r="E267" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F267" t="n">
         <v>5.5</v>
@@ -5795,7 +5795,7 @@
         <v>-7.497009722041158</v>
       </c>
       <c r="E268" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F268" t="n">
         <v>-8</v>
@@ -5815,7 +5815,7 @@
         <v>-6.347089668468085</v>
       </c>
       <c r="E269" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="F269" t="n">
         <v>5.5</v>
@@ -5835,7 +5835,7 @@
         <v>-6.612981808812417</v>
       </c>
       <c r="E270" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="F270" t="n">
         <v>4</v>
@@ -5855,7 +5855,7 @@
         <v>-11.06939687601137</v>
       </c>
       <c r="E271" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F271" t="n">
         <v>-5</v>
@@ -5875,7 +5875,7 @@
         <v>-3.758817514648497</v>
       </c>
       <c r="E272" t="n">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="F272" t="n">
         <v>5.5</v>
@@ -5895,7 +5895,7 @@
         <v>-4.051877556375617</v>
       </c>
       <c r="E273" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F273" t="n">
         <v>7</v>
@@ -5915,7 +5915,7 @@
         <v>-10.52242670855952</v>
       </c>
       <c r="E274" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="F274" t="n">
         <v>8.5</v>
@@ -5935,7 +5935,7 @@
         <v>-15.126689506234</v>
       </c>
       <c r="E275" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F275" t="n">
         <v>14.5</v>
@@ -5955,7 +5955,7 @@
         <v>-9.283689005874132</v>
       </c>
       <c r="E276" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F276" t="n">
         <v>8.5</v>
@@ -5975,7 +5975,7 @@
         <v>-7.94424447213977</v>
       </c>
       <c r="E277" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="F277" t="n">
         <v>8.5</v>
@@ -5995,7 +5995,7 @@
         <v>-6.180337229755344</v>
       </c>
       <c r="E278" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="F278" t="n">
         <v>5.5</v>
@@ -6015,7 +6015,7 @@
         <v>-8.982461384875723</v>
       </c>
       <c r="E279" t="n">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="F279" t="n">
         <v>5.5</v>
@@ -6035,7 +6035,7 @@
         <v>-11.02713454495316</v>
       </c>
       <c r="E280" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="F280" t="n">
         <v>13</v>
@@ -6055,7 +6055,7 @@
         <v>-14.250355621725</v>
       </c>
       <c r="E281" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F281" t="n">
         <v>4</v>
@@ -6075,7 +6075,7 @@
         <v>-7.381656604173806</v>
       </c>
       <c r="E282" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F282" t="n">
         <v>-2</v>
@@ -6095,7 +6095,7 @@
         <v>-1.583944458459632</v>
       </c>
       <c r="E283" t="n">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="F283" t="n">
         <v>8.5</v>
@@ -6115,7 +6115,7 @@
         <v>-4.982880829079921</v>
       </c>
       <c r="E284" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F284" t="n">
         <v>7</v>
@@ -6135,7 +6135,7 @@
         <v>-1.993944866098499</v>
       </c>
       <c r="E285" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="F285" t="n">
         <v>10</v>
@@ -6155,7 +6155,7 @@
         <v>-7.962965242945846</v>
       </c>
       <c r="E286" t="n">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="F286" t="n">
         <v>10</v>
@@ -6175,7 +6175,7 @@
         <v>-11.165277873491</v>
       </c>
       <c r="E287" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="F287" t="n">
         <v>5.5</v>
@@ -6195,7 +6195,7 @@
         <v>-7.873822197284354</v>
       </c>
       <c r="E288" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F288" t="n">
         <v>4</v>
@@ -6215,7 +6215,7 @@
         <v>-5.515009419003278</v>
       </c>
       <c r="E289" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="F289" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
         <v>-10.62394376937941</v>
       </c>
       <c r="E290" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F290" t="n">
         <v>7</v>
@@ -6255,7 +6255,7 @@
         <v>-4.861284849882093</v>
       </c>
       <c r="E291" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="F291" t="n">
         <v>14.5</v>
@@ -6275,7 +6275,7 @@
         <v>-5.133218124018798</v>
       </c>
       <c r="E292" t="n">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="F292" t="n">
         <v>7</v>
@@ -6295,7 +6295,7 @@
         <v>-8.421038212394912</v>
       </c>
       <c r="E293" t="n">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="F293" t="n">
         <v>5.5</v>
@@ -6315,7 +6315,7 @@
         <v>-7.958357982669678</v>
       </c>
       <c r="E294" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F294" t="n">
         <v>11.5</v>
@@ -6335,7 +6335,7 @@
         <v>-7.403946284003434</v>
       </c>
       <c r="E295" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F295" t="n">
         <v>5.5</v>
@@ -6355,7 +6355,7 @@
         <v>-1.924384022657788</v>
       </c>
       <c r="E296" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F296" t="n">
         <v>5.5</v>
@@ -6375,7 +6375,7 @@
         <v>-9.63065438938828</v>
       </c>
       <c r="E297" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="F297" t="n">
         <v>7</v>
@@ -6395,7 +6395,7 @@
         <v>-3.802405797042502</v>
       </c>
       <c r="E298" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="F298" t="n">
         <v>10</v>
@@ -6415,7 +6415,7 @@
         <v>-2.270559716689897</v>
       </c>
       <c r="E299" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="F299" t="n">
         <v>10</v>
@@ -6435,7 +6435,7 @@
         <v>-5.067145124015414</v>
       </c>
       <c r="E300" t="n">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="F300" t="n">
         <v>13</v>
@@ -6455,7 +6455,7 @@
         <v>-3.739643154692642</v>
       </c>
       <c r="E301" t="n">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="F301" t="n">
         <v>5.5</v>
@@ -6475,7 +6475,7 @@
         <v>-3.418293055915066</v>
       </c>
       <c r="E302" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F302" t="n">
         <v>13</v>
@@ -6495,7 +6495,7 @@
         <v>-4.344905760267247</v>
       </c>
       <c r="E303" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F303" t="n">
         <v>7</v>
@@ -6515,7 +6515,7 @@
         <v>-15.2933712096641</v>
       </c>
       <c r="E304" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F304" t="n">
         <v>11.5</v>
@@ -6535,7 +6535,7 @@
         <v>-2.833311277806506</v>
       </c>
       <c r="E305" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F305" t="n">
         <v>11.5</v>
@@ -6555,7 +6555,7 @@
         <v>-6.487566266327902</v>
       </c>
       <c r="E306" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F306" t="n">
         <v>11.5</v>
@@ -6575,7 +6575,7 @@
         <v>-0.597558805795496</v>
       </c>
       <c r="E307" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F307" t="n">
         <v>16</v>
@@ -6595,7 +6595,7 @@
         <v>-7.007631493657506</v>
       </c>
       <c r="E308" t="n">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="F308" t="n">
         <v>4</v>
@@ -6615,7 +6615,7 @@
         <v>-6.356009385510418</v>
       </c>
       <c r="E309" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F309" t="n">
         <v>14.5</v>
@@ -6635,7 +6635,7 @@
         <v>-12.60793338696019</v>
       </c>
       <c r="E310" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F310" t="n">
         <v>11.5</v>
@@ -6655,7 +6655,7 @@
         <v>-10.55619850873314</v>
       </c>
       <c r="E311" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="F311" t="n">
         <v>8.5</v>
@@ -6675,7 +6675,7 @@
         <v>-8.036085399538264</v>
       </c>
       <c r="E312" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F312" t="n">
         <v>11.5</v>
@@ -6695,7 +6695,7 @@
         <v>-7.133811441293342</v>
       </c>
       <c r="E313" t="n">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="F313" t="n">
         <v>5.5</v>
@@ -6715,7 +6715,7 @@
         <v>-1.537075693521595</v>
       </c>
       <c r="E314" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="F314" t="n">
         <v>11.5</v>
@@ -6735,7 +6735,7 @@
         <v>-4.000693130585137</v>
       </c>
       <c r="E315" t="n">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F315" t="n">
         <v>17.5</v>
@@ -6755,7 +6755,7 @@
         <v>-7.442802803480682</v>
       </c>
       <c r="E316" t="n">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="F316" t="n">
         <v>-2</v>
@@ -6775,7 +6775,7 @@
         <v>0.321256182415646</v>
       </c>
       <c r="E317" t="n">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="F317" t="n">
         <v>13</v>
@@ -6795,7 +6795,7 @@
         <v>-6.598016050430667</v>
       </c>
       <c r="E318" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="F318" t="n">
         <v>10</v>
@@ -6815,7 +6815,7 @@
         <v>-6.205783364635726</v>
       </c>
       <c r="E319" t="n">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="F319" t="n">
         <v>8.5</v>
@@ -6835,7 +6835,7 @@
         <v>-4.879434422761875</v>
       </c>
       <c r="E320" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="F320" t="n">
         <v>14.5</v>
@@ -6855,7 +6855,7 @@
         <v>-8.815660834151867</v>
       </c>
       <c r="E321" t="n">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="F321" t="n">
         <v>5.5</v>
@@ -6875,7 +6875,7 @@
         <v>-4.880041842271443</v>
       </c>
       <c r="E322" t="n">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="F322" t="n">
         <v>16</v>
@@ -6895,7 +6895,7 @@
         <v>1.3390683303161</v>
       </c>
       <c r="E323" t="n">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="F323" t="n">
         <v>16</v>
@@ -6915,7 +6915,7 @@
         <v>-7.534882036620827</v>
       </c>
       <c r="E324" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F324" t="n">
         <v>13</v>
@@ -6935,7 +6935,7 @@
         <v>-1.437938527968541</v>
       </c>
       <c r="E325" t="n">
-        <v>33</v>
+        <v>123</v>
       </c>
       <c r="F325" t="n">
         <v>8.5</v>
@@ -6955,7 +6955,7 @@
         <v>-3.084487384043165</v>
       </c>
       <c r="E326" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="F326" t="n">
         <v>11.5</v>
@@ -6975,7 +6975,7 @@
         <v>-4.984577567865049</v>
       </c>
       <c r="E327" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F327" t="n">
         <v>14.5</v>
@@ -6995,7 +6995,7 @@
         <v>-12.47954626896995</v>
       </c>
       <c r="E328" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="F328" t="n">
         <v>14.5</v>
@@ -7015,7 +7015,7 @@
         <v>-10.71310955210427</v>
       </c>
       <c r="E329" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F329" t="n">
         <v>16</v>
@@ -7035,7 +7035,7 @@
         <v>-4.214159442252412</v>
       </c>
       <c r="E330" t="n">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="F330" t="n">
         <v>10</v>
@@ -7055,7 +7055,7 @@
         <v>-10.32175432625408</v>
       </c>
       <c r="E331" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="F331" t="n">
         <v>8.5</v>
@@ -7075,7 +7075,7 @@
         <v>-3.847451207287437</v>
       </c>
       <c r="E332" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="F332" t="n">
         <v>11.5</v>
@@ -7095,7 +7095,7 @@
         <v>-7.577111428170915</v>
       </c>
       <c r="E333" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="F333" t="n">
         <v>4</v>
@@ -7115,7 +7115,7 @@
         <v>-12.39685699336666</v>
       </c>
       <c r="E334" t="n">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="F334" t="n">
         <v>14.5</v>
@@ -7135,7 +7135,7 @@
         <v>-4.536191961028859</v>
       </c>
       <c r="E335" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="F335" t="n">
         <v>13</v>
@@ -7155,7 +7155,7 @@
         <v>-3.793876976120675</v>
       </c>
       <c r="E336" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F336" t="n">
         <v>7</v>
@@ -7175,7 +7175,7 @@
         <v>1.892030835894608</v>
       </c>
       <c r="E337" t="n">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F337" t="n">
         <v>7</v>
@@ -7195,7 +7195,7 @@
         <v>-6.876610785137544</v>
       </c>
       <c r="E338" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="F338" t="n">
         <v>10</v>
@@ -7215,7 +7215,7 @@
         <v>-1.615861001382153</v>
       </c>
       <c r="E339" t="n">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="F339" t="n">
         <v>11.5</v>
@@ -7235,7 +7235,7 @@
         <v>-5.341940188564537</v>
       </c>
       <c r="E340" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F340" t="n">
         <v>10</v>
@@ -7255,7 +7255,7 @@
         <v>-5.309355549382947</v>
       </c>
       <c r="E341" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F341" t="n">
         <v>16</v>
@@ -7275,7 +7275,7 @@
         <v>-5.062973998838486</v>
       </c>
       <c r="E342" t="n">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F342" t="n">
         <v>13</v>
@@ -7295,7 +7295,7 @@
         <v>-3.868067795346402</v>
       </c>
       <c r="E343" t="n">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="F343" t="n">
         <v>13</v>
@@ -7315,7 +7315,7 @@
         <v>-1.295206924452152</v>
       </c>
       <c r="E344" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="F344" t="n">
         <v>11.5</v>
@@ -7335,7 +7335,7 @@
         <v>-4.563509516184059</v>
       </c>
       <c r="E345" t="n">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="F345" t="n">
         <v>11.5</v>
@@ -7355,7 +7355,7 @@
         <v>-4.52968578496577</v>
       </c>
       <c r="E346" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="F346" t="n">
         <v>14.5</v>
@@ -7375,7 +7375,7 @@
         <v>0.5616403015032345</v>
       </c>
       <c r="E347" t="n">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F347" t="n">
         <v>8.5</v>
@@ -7395,7 +7395,7 @@
         <v>-1.932480718018562</v>
       </c>
       <c r="E348" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="F348" t="n">
         <v>16</v>
@@ -7415,7 +7415,7 @@
         <v>-2.492076983508796</v>
       </c>
       <c r="E349" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="F349" t="n">
         <v>13</v>
@@ -7435,7 +7435,7 @@
         <v>-6.866377835308298</v>
       </c>
       <c r="E350" t="n">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="F350" t="n">
         <v>5.5</v>
@@ -7455,7 +7455,7 @@
         <v>-8.46601744993502</v>
       </c>
       <c r="E351" t="n">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="F351" t="n">
         <v>5.5</v>
@@ -7475,7 +7475,7 @@
         <v>-8.503358770040659</v>
       </c>
       <c r="E352" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F352" t="n">
         <v>8.5</v>
@@ -7495,7 +7495,7 @@
         <v>-3.401522239735685</v>
       </c>
       <c r="E353" t="n">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="F353" t="n">
         <v>5.5</v>
@@ -7515,7 +7515,7 @@
         <v>-4.889302168656975</v>
       </c>
       <c r="E354" t="n">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="F354" t="n">
         <v>5.5</v>
@@ -7535,7 +7535,7 @@
         <v>-5.45993309037005</v>
       </c>
       <c r="E355" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="F355" t="n">
         <v>14.5</v>
@@ -7555,7 +7555,7 @@
         <v>-2.72317301315674</v>
       </c>
       <c r="E356" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="F356" t="n">
         <v>14.5</v>
@@ -7575,7 +7575,7 @@
         <v>-7.169360862597371</v>
       </c>
       <c r="E357" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F357" t="n">
         <v>13</v>
@@ -7595,7 +7595,7 @@
         <v>-10.81470985813223</v>
       </c>
       <c r="E358" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F358" t="n">
         <v>14.5</v>
@@ -7615,7 +7615,7 @@
         <v>-8.107163803570021</v>
       </c>
       <c r="E359" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="F359" t="n">
         <v>11.5</v>
@@ -7635,7 +7635,7 @@
         <v>-6.220465292608457</v>
       </c>
       <c r="E360" t="n">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="F360" t="n">
         <v>19</v>
@@ -7655,7 +7655,7 @@
         <v>-5.504144096772184</v>
       </c>
       <c r="E361" t="n">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="F361" t="n">
         <v>8.5</v>
@@ -7675,7 +7675,7 @@
         <v>-2.475755123102916</v>
       </c>
       <c r="E362" t="n">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="F362" t="n">
         <v>17.5</v>
@@ -7695,7 +7695,7 @@
         <v>-7.444069608672705</v>
       </c>
       <c r="E363" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="F363" t="n">
         <v>14.5</v>
@@ -7715,7 +7715,7 @@
         <v>-2.021784772990322</v>
       </c>
       <c r="E364" t="n">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="F364" t="n">
         <v>14.5</v>
@@ -7735,7 +7735,7 @@
         <v>-2.354104958383093</v>
       </c>
       <c r="E365" t="n">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F365" t="n">
         <v>19</v>
@@ -7755,7 +7755,7 @@
         <v>-6.192040211684938</v>
       </c>
       <c r="E366" t="n">
-        <v>31</v>
+        <v>161</v>
       </c>
       <c r="F366" t="n">
         <v>20.5</v>
@@ -7775,7 +7775,7 @@
         <v>-5.675692005440896</v>
       </c>
       <c r="E367" t="n">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="F367" t="n">
         <v>16</v>
@@ -7795,7 +7795,7 @@
         <v>-6.218050842224281</v>
       </c>
       <c r="E368" t="n">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="F368" t="n">
         <v>19</v>
@@ -7815,7 +7815,7 @@
         <v>-3.07883011643317</v>
       </c>
       <c r="E369" t="n">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="F369" t="n">
         <v>16</v>
@@ -7835,7 +7835,7 @@
         <v>0.4454353742164699</v>
       </c>
       <c r="E370" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F370" t="n">
         <v>19</v>
@@ -7855,7 +7855,7 @@
         <v>-5.299662112462816</v>
       </c>
       <c r="E371" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="F371" t="n">
         <v>20.5</v>
@@ -7875,7 +7875,7 @@
         <v>-4.275349160139813</v>
       </c>
       <c r="E372" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="F372" t="n">
         <v>20.5</v>
@@ -7895,7 +7895,7 @@
         <v>2.760114520882845</v>
       </c>
       <c r="E373" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F373" t="n">
         <v>11.5</v>
@@ -7915,7 +7915,7 @@
         <v>-2.233175560934974</v>
       </c>
       <c r="E374" t="n">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="F374" t="n">
         <v>11.5</v>
@@ -7935,7 +7935,7 @@
         <v>-3.849263004804139</v>
       </c>
       <c r="E375" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F375" t="n">
         <v>13</v>
@@ -7955,7 +7955,7 @@
         <v>-7.439318426871877</v>
       </c>
       <c r="E376" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="F376" t="n">
         <v>16</v>
@@ -7975,7 +7975,7 @@
         <v>0.3988126622416603</v>
       </c>
       <c r="E377" t="n">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="F377" t="n">
         <v>17.5</v>
@@ -7995,7 +7995,7 @@
         <v>-5.219605923776177</v>
       </c>
       <c r="E378" t="n">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="F378" t="n">
         <v>10</v>
@@ -8015,7 +8015,7 @@
         <v>1.436115308975747</v>
       </c>
       <c r="E379" t="n">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="F379" t="n">
         <v>20.5</v>
@@ -8035,7 +8035,7 @@
         <v>-2.555545674890773</v>
       </c>
       <c r="E380" t="n">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F380" t="n">
         <v>16</v>
@@ -8055,7 +8055,7 @@
         <v>-5.898584918723315</v>
       </c>
       <c r="E381" t="n">
-        <v>39</v>
+        <v>154</v>
       </c>
       <c r="F381" t="n">
         <v>14.5</v>
@@ -8075,7 +8075,7 @@
         <v>-7.073209898845452</v>
       </c>
       <c r="E382" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="F382" t="n">
         <v>7</v>
@@ -8095,7 +8095,7 @@
         <v>-3.622977285184998</v>
       </c>
       <c r="E383" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="F383" t="n">
         <v>19</v>
@@ -8115,7 +8115,7 @@
         <v>-9.917287036815873</v>
       </c>
       <c r="E384" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="F384" t="n">
         <v>13</v>
@@ -8135,7 +8135,7 @@
         <v>0.5373091015979023</v>
       </c>
       <c r="E385" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="F385" t="n">
         <v>17.5</v>
@@ -8155,7 +8155,7 @@
         <v>-0.9602138229564685</v>
       </c>
       <c r="E386" t="n">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="F386" t="n">
         <v>14.5</v>
@@ -8175,7 +8175,7 @@
         <v>-2.535567183211558</v>
       </c>
       <c r="E387" t="n">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="F387" t="n">
         <v>10</v>
@@ -8195,7 +8195,7 @@
         <v>2.200141246463018</v>
       </c>
       <c r="E388" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="F388" t="n">
         <v>11.5</v>
@@ -8215,7 +8215,7 @@
         <v>1.811103417675227</v>
       </c>
       <c r="E389" t="n">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="F389" t="n">
         <v>17.5</v>
@@ -8235,7 +8235,7 @@
         <v>-9.225704108485532</v>
       </c>
       <c r="E390" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="F390" t="n">
         <v>14.5</v>
@@ -8255,7 +8255,7 @@
         <v>-4.416245606870039</v>
       </c>
       <c r="E391" t="n">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="F391" t="n">
         <v>14.5</v>
@@ -8275,7 +8275,7 @@
         <v>-1.257155408909161</v>
       </c>
       <c r="E392" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="F392" t="n">
         <v>16</v>
@@ -8295,7 +8295,7 @@
         <v>-4.429092056794652</v>
       </c>
       <c r="E393" t="n">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="F393" t="n">
         <v>14.5</v>
@@ -8315,7 +8315,7 @@
         <v>-2.148827803887845</v>
       </c>
       <c r="E394" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="F394" t="n">
         <v>14.5</v>
@@ -8335,7 +8335,7 @@
         <v>-6.628430276399285</v>
       </c>
       <c r="E395" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F395" t="n">
         <v>17.5</v>
@@ -8355,7 +8355,7 @@
         <v>-2.811622576116387</v>
       </c>
       <c r="E396" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="F396" t="n">
         <v>11.5</v>
@@ -8375,7 +8375,7 @@
         <v>1.516348024524294</v>
       </c>
       <c r="E397" t="n">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="F397" t="n">
         <v>19</v>
@@ -8395,7 +8395,7 @@
         <v>0.7759562547179837</v>
       </c>
       <c r="E398" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="F398" t="n">
         <v>20.5</v>
@@ -8415,7 +8415,7 @@
         <v>-7.521513945763667</v>
       </c>
       <c r="E399" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F399" t="n">
         <v>19</v>
@@ -8435,7 +8435,7 @@
         <v>5.906920073781943</v>
       </c>
       <c r="E400" t="n">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="F400" t="n">
         <v>14.5</v>
@@ -8455,7 +8455,7 @@
         <v>-1.152800133799763</v>
       </c>
       <c r="E401" t="n">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F401" t="n">
         <v>17.5</v>
@@ -8475,7 +8475,7 @@
         <v>1.92235435186735</v>
       </c>
       <c r="E402" t="n">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="F402" t="n">
         <v>13</v>
@@ -8495,7 +8495,7 @@
         <v>-1.324647806147128</v>
       </c>
       <c r="E403" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="F403" t="n">
         <v>13</v>
@@ -8515,7 +8515,7 @@
         <v>-1.675220191202326</v>
       </c>
       <c r="E404" t="n">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F404" t="n">
         <v>17.5</v>
@@ -8535,7 +8535,7 @@
         <v>3.285523000699553</v>
       </c>
       <c r="E405" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F405" t="n">
         <v>11.5</v>
@@ -8555,7 +8555,7 @@
         <v>1.498901900880139</v>
       </c>
       <c r="E406" t="n">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c r="F406" t="n">
         <v>16</v>
@@ -8575,7 +8575,7 @@
         <v>0.3891414475957227</v>
       </c>
       <c r="E407" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="F407" t="n">
         <v>20.5</v>
@@ -8595,7 +8595,7 @@
         <v>-5.627019008818197</v>
       </c>
       <c r="E408" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F408" t="n">
         <v>14.5</v>
@@ -8615,7 +8615,7 @@
         <v>-7.430110984826372</v>
       </c>
       <c r="E409" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="F409" t="n">
         <v>22</v>
@@ -8635,7 +8635,7 @@
         <v>0.1256179464703751</v>
       </c>
       <c r="E410" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="F410" t="n">
         <v>20.5</v>
@@ -8655,7 +8655,7 @@
         <v>-5.092614484938498</v>
       </c>
       <c r="E411" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="F411" t="n">
         <v>10</v>
@@ -8675,7 +8675,7 @@
         <v>-4.108693146142889</v>
       </c>
       <c r="E412" t="n">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="F412" t="n">
         <v>13</v>
@@ -8695,7 +8695,7 @@
         <v>-7.463804828800212</v>
       </c>
       <c r="E413" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="F413" t="n">
         <v>17.5</v>
@@ -8715,7 +8715,7 @@
         <v>-1.055122844270363</v>
       </c>
       <c r="E414" t="n">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="F414" t="n">
         <v>16</v>
@@ -8735,7 +8735,7 @@
         <v>-1.215686709645218</v>
       </c>
       <c r="E415" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="F415" t="n">
         <v>17.5</v>
@@ -8755,7 +8755,7 @@
         <v>-4.396800403551372</v>
       </c>
       <c r="E416" t="n">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="F416" t="n">
         <v>22</v>
@@ -8775,7 +8775,7 @@
         <v>-2.291263596076391</v>
       </c>
       <c r="E417" t="n">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="F417" t="n">
         <v>22</v>
@@ -8795,7 +8795,7 @@
         <v>-1.338984177475091</v>
       </c>
       <c r="E418" t="n">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="F418" t="n">
         <v>19</v>
@@ -8815,7 +8815,7 @@
         <v>-2.378608825728114</v>
       </c>
       <c r="E419" t="n">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="F419" t="n">
         <v>20.5</v>
@@ -8835,7 +8835,7 @@
         <v>-4.478171664319876</v>
       </c>
       <c r="E420" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="F420" t="n">
         <v>19</v>
@@ -8855,7 +8855,7 @@
         <v>3.493919627918584</v>
       </c>
       <c r="E421" t="n">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="F421" t="n">
         <v>20.5</v>
@@ -8875,7 +8875,7 @@
         <v>-0.4493073074287441</v>
       </c>
       <c r="E422" t="n">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="F422" t="n">
         <v>19</v>
@@ -8895,7 +8895,7 @@
         <v>-3.529479282034087</v>
       </c>
       <c r="E423" t="n">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="F423" t="n">
         <v>20.5</v>
@@ -8915,7 +8915,7 @@
         <v>5.505363169646428</v>
       </c>
       <c r="E424" t="n">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="F424" t="n">
         <v>16</v>
@@ -8935,7 +8935,7 @@
         <v>-1.289749166080068</v>
       </c>
       <c r="E425" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="F425" t="n">
         <v>17.5</v>
@@ -8955,7 +8955,7 @@
         <v>-6.328346785914285</v>
       </c>
       <c r="E426" t="n">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="F426" t="n">
         <v>19</v>
@@ -8975,7 +8975,7 @@
         <v>-2.245770890171666</v>
       </c>
       <c r="E427" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="F427" t="n">
         <v>20.5</v>
@@ -8995,7 +8995,7 @@
         <v>0.8586256083960975</v>
       </c>
       <c r="E428" t="n">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="F428" t="n">
         <v>20.5</v>
@@ -9015,7 +9015,7 @@
         <v>-1.440130905972663</v>
       </c>
       <c r="E429" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F429" t="n">
         <v>17.5</v>
@@ -9035,7 +9035,7 @@
         <v>-6.031533531499718</v>
       </c>
       <c r="E430" t="n">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F430" t="n">
         <v>17.5</v>
@@ -9055,7 +9055,7 @@
         <v>-6.483394036182426</v>
       </c>
       <c r="E431" t="n">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="F431" t="n">
         <v>22</v>
@@ -9075,7 +9075,7 @@
         <v>-4.129181923723293</v>
       </c>
       <c r="E432" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F432" t="n">
         <v>14.5</v>
@@ -9095,7 +9095,7 @@
         <v>-0.5394951999804173</v>
       </c>
       <c r="E433" t="n">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="F433" t="n">
         <v>19</v>
@@ -9115,7 +9115,7 @@
         <v>-4.91737737000209</v>
       </c>
       <c r="E434" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="F434" t="n">
         <v>22</v>
@@ -9135,7 +9135,7 @@
         <v>-1.629499795376638</v>
       </c>
       <c r="E435" t="n">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="F435" t="n">
         <v>19</v>
@@ -9155,7 +9155,7 @@
         <v>-2.000851078070042</v>
       </c>
       <c r="E436" t="n">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F436" t="n">
         <v>23.5</v>
@@ -9175,7 +9175,7 @@
         <v>-0.6395139177057325</v>
       </c>
       <c r="E437" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="F437" t="n">
         <v>16</v>
@@ -9195,7 +9195,7 @@
         <v>-3.783377107596139</v>
       </c>
       <c r="E438" t="n">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="F438" t="n">
         <v>19</v>
@@ -9215,7 +9215,7 @@
         <v>-0.1908777370631428</v>
       </c>
       <c r="E439" t="n">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="F439" t="n">
         <v>17.5</v>
@@ -9235,7 +9235,7 @@
         <v>4.759227350410999</v>
       </c>
       <c r="E440" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="F440" t="n">
         <v>17.5</v>
@@ -9255,7 +9255,7 @@
         <v>0.677884067585573</v>
       </c>
       <c r="E441" t="n">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="F441" t="n">
         <v>17.5</v>
@@ -9275,7 +9275,7 @@
         <v>-0.07175836499018579</v>
       </c>
       <c r="E442" t="n">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="F442" t="n">
         <v>19</v>
@@ -9295,7 +9295,7 @@
         <v>-1.541966372324565</v>
       </c>
       <c r="E443" t="n">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="F443" t="n">
         <v>19</v>
@@ -9315,7 +9315,7 @@
         <v>-1.084744409189314</v>
       </c>
       <c r="E444" t="n">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="F444" t="n">
         <v>22</v>
@@ -9335,7 +9335,7 @@
         <v>2.477458202909179</v>
       </c>
       <c r="E445" t="n">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="F445" t="n">
         <v>16</v>
@@ -9355,7 +9355,7 @@
         <v>-0.888641577089203</v>
       </c>
       <c r="E446" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="F446" t="n">
         <v>17.5</v>
@@ -9375,7 +9375,7 @@
         <v>-4.142588259792474</v>
       </c>
       <c r="E447" t="n">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="F447" t="n">
         <v>19</v>
@@ -9395,7 +9395,7 @@
         <v>-7.494413186848452</v>
       </c>
       <c r="E448" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="F448" t="n">
         <v>23.5</v>
@@ -9415,7 +9415,7 @@
         <v>-0.5810422459860057</v>
       </c>
       <c r="E449" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="F449" t="n">
         <v>19</v>
@@ -9435,7 +9435,7 @@
         <v>-0.4650566229847108</v>
       </c>
       <c r="E450" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="F450" t="n">
         <v>22</v>
@@ -9455,7 +9455,7 @@
         <v>-0.1039621030240891</v>
       </c>
       <c r="E451" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="F451" t="n">
         <v>19</v>
@@ -9475,7 +9475,7 @@
         <v>0.5667753408456071</v>
       </c>
       <c r="E452" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="F452" t="n">
         <v>19</v>
@@ -9495,7 +9495,7 @@
         <v>0.8474447506843528</v>
       </c>
       <c r="E453" t="n">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="F453" t="n">
         <v>17.5</v>
@@ -9515,7 +9515,7 @@
         <v>1.22605619357334</v>
       </c>
       <c r="E454" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="F454" t="n">
         <v>16</v>
@@ -9535,7 +9535,7 @@
         <v>-1.449163043556349</v>
       </c>
       <c r="E455" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="F455" t="n">
         <v>19</v>
@@ -9555,7 +9555,7 @@
         <v>-7.063041762791196</v>
       </c>
       <c r="E456" t="n">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="F456" t="n">
         <v>19</v>
@@ -9575,7 +9575,7 @@
         <v>-3.258944684774359</v>
       </c>
       <c r="E457" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="F457" t="n">
         <v>19</v>
@@ -9595,7 +9595,7 @@
         <v>0.3038155417847883</v>
       </c>
       <c r="E458" t="n">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="F458" t="n">
         <v>20.5</v>
@@ -9615,7 +9615,7 @@
         <v>2.925567382898334</v>
       </c>
       <c r="E459" t="n">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="F459" t="n">
         <v>20.5</v>
@@ -9635,7 +9635,7 @@
         <v>1.227335378612259</v>
       </c>
       <c r="E460" t="n">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="F460" t="n">
         <v>22</v>
@@ -9655,7 +9655,7 @@
         <v>0.3567135355337989</v>
       </c>
       <c r="E461" t="n">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="F461" t="n">
         <v>20.5</v>
@@ -9675,7 +9675,7 @@
         <v>-5.230389973549588</v>
       </c>
       <c r="E462" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F462" t="n">
         <v>16</v>
@@ -9695,7 +9695,7 @@
         <v>-4.468962519235911</v>
       </c>
       <c r="E463" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="F463" t="n">
         <v>22</v>
@@ -9715,7 +9715,7 @@
         <v>3.142223358714665</v>
       </c>
       <c r="E464" t="n">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="F464" t="n">
         <v>20.5</v>
@@ -9735,7 +9735,7 @@
         <v>1.02510534400717</v>
       </c>
       <c r="E465" t="n">
-        <v>43</v>
+        <v>175</v>
       </c>
       <c r="F465" t="n">
         <v>22</v>
@@ -9755,7 +9755,7 @@
         <v>-0.6141674555601673</v>
       </c>
       <c r="E466" t="n">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="F466" t="n">
         <v>20.5</v>
@@ -9775,7 +9775,7 @@
         <v>-0.8160733879181367</v>
       </c>
       <c r="E467" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="F467" t="n">
         <v>20.5</v>
@@ -9795,7 +9795,7 @@
         <v>1.137338576071934</v>
       </c>
       <c r="E468" t="n">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="F468" t="n">
         <v>23.5</v>
@@ -9815,7 +9815,7 @@
         <v>0.6915120900000564</v>
       </c>
       <c r="E469" t="n">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="F469" t="n">
         <v>22</v>
@@ -9835,7 +9835,7 @@
         <v>2.250366219827656</v>
       </c>
       <c r="E470" t="n">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F470" t="n">
         <v>20.5</v>
@@ -9855,7 +9855,7 @@
         <v>0.02060750638746916</v>
       </c>
       <c r="E471" t="n">
-        <v>47</v>
+        <v>165</v>
       </c>
       <c r="F471" t="n">
         <v>20.5</v>
@@ -9875,7 +9875,7 @@
         <v>-1.059969664252619</v>
       </c>
       <c r="E472" t="n">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="F472" t="n">
         <v>19</v>
@@ -9895,7 +9895,7 @@
         <v>-1.707842522936838</v>
       </c>
       <c r="E473" t="n">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="F473" t="n">
         <v>23.5</v>
@@ -9915,7 +9915,7 @@
         <v>5.089236637678793</v>
       </c>
       <c r="E474" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F474" t="n">
         <v>19</v>
@@ -9935,7 +9935,7 @@
         <v>1.098682892356061</v>
       </c>
       <c r="E475" t="n">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="F475" t="n">
         <v>23.5</v>
@@ -9955,7 +9955,7 @@
         <v>2.123629903505583</v>
       </c>
       <c r="E476" t="n">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F476" t="n">
         <v>23.5</v>
@@ -9975,7 +9975,7 @@
         <v>2.587962081711049</v>
       </c>
       <c r="E477" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="F477" t="n">
         <v>22</v>
@@ -9995,7 +9995,7 @@
         <v>1.46521177615566</v>
       </c>
       <c r="E478" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="F478" t="n">
         <v>20.5</v>
@@ -10015,7 +10015,7 @@
         <v>2.227730912077593</v>
       </c>
       <c r="E479" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="F479" t="n">
         <v>23.5</v>
@@ -10035,7 +10035,7 @@
         <v>-2.852511499325471</v>
       </c>
       <c r="E480" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="F480" t="n">
         <v>20.5</v>
@@ -10055,7 +10055,7 @@
         <v>1.656101105496402</v>
       </c>
       <c r="E481" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="F481" t="n">
         <v>23.5</v>
@@ -10075,7 +10075,7 @@
         <v>-2.181595041450903</v>
       </c>
       <c r="E482" t="n">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="F482" t="n">
         <v>22</v>
@@ -10095,7 +10095,7 @@
         <v>2.309738472745105</v>
       </c>
       <c r="E483" t="n">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="F483" t="n">
         <v>22</v>
@@ -10115,7 +10115,7 @@
         <v>2.92055749528471</v>
       </c>
       <c r="E484" t="n">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="F484" t="n">
         <v>23.5</v>
@@ -10135,7 +10135,7 @@
         <v>1.26214717618925</v>
       </c>
       <c r="E485" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F485" t="n">
         <v>23.5</v>
@@ -10155,7 +10155,7 @@
         <v>1.558160184887974</v>
       </c>
       <c r="E486" t="n">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="F486" t="n">
         <v>22</v>
@@ -10175,7 +10175,7 @@
         <v>-7.521761006827451</v>
       </c>
       <c r="E487" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="F487" t="n">
         <v>23.5</v>
@@ -10195,7 +10195,7 @@
         <v>-6.425254374315139</v>
       </c>
       <c r="E488" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="F488" t="n">
         <v>22</v>
@@ -10215,7 +10215,7 @@
         <v>-0.2984252876331439</v>
       </c>
       <c r="E489" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F489" t="n">
         <v>22</v>
@@ -10235,7 +10235,7 @@
         <v>1.906705737190377</v>
       </c>
       <c r="E490" t="n">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="F490" t="n">
         <v>20.5</v>
@@ -10255,7 +10255,7 @@
         <v>-1.825583128419374</v>
       </c>
       <c r="E491" t="n">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="F491" t="n">
         <v>22</v>
@@ -10275,7 +10275,7 @@
         <v>-0.5532374137363099</v>
       </c>
       <c r="E492" t="n">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="F492" t="n">
         <v>20.5</v>
@@ -10295,7 +10295,7 @@
         <v>-0.5918792189979392</v>
       </c>
       <c r="E493" t="n">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="F493" t="n">
         <v>23.5</v>
@@ -10315,7 +10315,7 @@
         <v>2.792917539201678</v>
       </c>
       <c r="E494" t="n">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="F494" t="n">
         <v>23.5</v>
@@ -10335,7 +10335,7 @@
         <v>-0.1398359058776345</v>
       </c>
       <c r="E495" t="n">
-        <v>47</v>
+        <v>143</v>
       </c>
       <c r="F495" t="n">
         <v>22</v>
@@ -10355,7 +10355,7 @@
         <v>-2.120665427487619</v>
       </c>
       <c r="E496" t="n">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="F496" t="n">
         <v>23.5</v>
@@ -10375,7 +10375,7 @@
         <v>1.224652498852347</v>
       </c>
       <c r="E497" t="n">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="F497" t="n">
         <v>23.5</v>
@@ -10395,7 +10395,7 @@
         <v>2.687541208121736</v>
       </c>
       <c r="E498" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="F498" t="n">
         <v>20.5</v>
@@ -10415,7 +10415,7 @@
         <v>0.8240832438619535</v>
       </c>
       <c r="E499" t="n">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="F499" t="n">
         <v>23.5</v>
@@ -10435,7 +10435,7 @@
         <v>2.630254364117565</v>
       </c>
       <c r="E500" t="n">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="F500" t="n">
         <v>23.5</v>
@@ -10455,7 +10455,7 @@
         <v>4.989565238231685</v>
       </c>
       <c r="E501" t="n">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="F501" t="n">
         <v>23.5</v>
@@ -10540,7 +10540,7 @@
         <v>-8.085577424066329</v>
       </c>
       <c r="E3" t="n">
-        <v>23.052</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>5.764</v>
@@ -10562,7 +10562,7 @@
         <v>6.17377840023794</v>
       </c>
       <c r="E4" t="n">
-        <v>15.03893730522674</v>
+        <v>46.17505572864084</v>
       </c>
       <c r="F4" t="n">
         <v>11.03221298955444</v>
@@ -10584,7 +10584,7 @@
         <v>-25.44342248327767</v>
       </c>
       <c r="E5" t="n">
-        <v>-13</v>
+        <v>-29</v>
       </c>
       <c r="F5" t="n">
         <v>-21.5</v>
@@ -10606,7 +10606,7 @@
         <v>-12.62876437265224</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>-2.375</v>
@@ -10628,7 +10628,7 @@
         <v>-7.930705794315703</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="F7" t="n">
         <v>5.5</v>
@@ -10650,7 +10650,7 @@
         <v>-3.501682725504332</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>119.25</v>
       </c>
       <c r="F8" t="n">
         <v>14.5</v>
@@ -10672,7 +10672,7 @@
         <v>5.906920073781943</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="F9" t="n">
         <v>23.5</v>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -9358,7 +9358,7 @@
         <v>11.5</v>
       </c>
       <c r="F446" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="447">
@@ -9838,7 +9838,7 @@
         <v>24.5</v>
       </c>
       <c r="F470" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="471">
@@ -10058,7 +10058,7 @@
         <v>32.5</v>
       </c>
       <c r="F481" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="482">
@@ -11118,7 +11118,7 @@
         <v>-12</v>
       </c>
       <c r="F534" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="535">
@@ -12398,7 +12398,7 @@
         <v>13.75</v>
       </c>
       <c r="F598" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="599">
@@ -12498,7 +12498,7 @@
         <v>26.5</v>
       </c>
       <c r="F603" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="604">
@@ -14058,7 +14058,7 @@
         <v>11</v>
       </c>
       <c r="F681" t="n">
-        <v>13</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="682">
@@ -14078,7 +14078,7 @@
         <v>22</v>
       </c>
       <c r="F682" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="683">
@@ -14098,7 +14098,7 @@
         <v>11.25</v>
       </c>
       <c r="F683" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="684">
@@ -14278,7 +14278,7 @@
         <v>37.75</v>
       </c>
       <c r="F692" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="693">
@@ -14458,7 +14458,7 @@
         <v>37</v>
       </c>
       <c r="F701" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="702">
@@ -14478,7 +14478,7 @@
         <v>13</v>
       </c>
       <c r="F702" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="703">
@@ -15038,7 +15038,7 @@
         <v>6</v>
       </c>
       <c r="F730" t="n">
-        <v>5.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="731">
@@ -15618,7 +15618,7 @@
         <v>-4</v>
       </c>
       <c r="F759" t="n">
-        <v>16</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="760">
@@ -15638,7 +15638,7 @@
         <v>-4.75</v>
       </c>
       <c r="F760" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="761">
@@ -15678,7 +15678,7 @@
         <v>33</v>
       </c>
       <c r="F762" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="763">
@@ -16298,7 +16298,7 @@
         <v>36</v>
       </c>
       <c r="F793" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="794">
@@ -16978,7 +16978,7 @@
         <v>-7.5</v>
       </c>
       <c r="F827" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="828">
@@ -16998,7 +16998,7 @@
         <v>31.25</v>
       </c>
       <c r="F828" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="829">
@@ -17358,7 +17358,7 @@
         <v>-1.25</v>
       </c>
       <c r="F846" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="847">
@@ -17398,7 +17398,7 @@
         <v>25</v>
       </c>
       <c r="F848" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="849">
@@ -17418,7 +17418,7 @@
         <v>35.75</v>
       </c>
       <c r="F849" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="850">
@@ -17458,7 +17458,7 @@
         <v>27.5</v>
       </c>
       <c r="F851" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="852">
@@ -17478,7 +17478,7 @@
         <v>33.25</v>
       </c>
       <c r="F852" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="853">
@@ -17498,7 +17498,7 @@
         <v>26.5</v>
       </c>
       <c r="F853" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="854">
@@ -17538,7 +17538,7 @@
         <v>-1.5</v>
       </c>
       <c r="F855" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="856">
@@ -18178,7 +18178,7 @@
         <v>3.25</v>
       </c>
       <c r="F887" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="888">
@@ -18258,7 +18258,7 @@
         <v>17.5</v>
       </c>
       <c r="F891" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="892">
@@ -18278,7 +18278,7 @@
         <v>20.5</v>
       </c>
       <c r="F892" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="893">
@@ -18318,7 +18318,7 @@
         <v>37.75</v>
       </c>
       <c r="F894" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="895">
@@ -18338,7 +18338,7 @@
         <v>35.75</v>
       </c>
       <c r="F895" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="896">
@@ -18378,7 +18378,7 @@
         <v>35.25</v>
       </c>
       <c r="F897" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="898">
@@ -18438,7 +18438,7 @@
         <v>35.25</v>
       </c>
       <c r="F900" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="901">
@@ -18938,7 +18938,7 @@
         <v>25.75</v>
       </c>
       <c r="F925" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="926">
@@ -19018,7 +19018,7 @@
         <v>35.75</v>
       </c>
       <c r="F929" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="930">
@@ -19598,7 +19598,7 @@
         <v>39.75</v>
       </c>
       <c r="F958" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="959">
@@ -20658,7 +20658,7 @@
         <v>11.25</v>
       </c>
       <c r="F1011" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1012">
@@ -20678,7 +20678,7 @@
         <v>35.25</v>
       </c>
       <c r="F1012" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="1013">
@@ -20738,7 +20738,7 @@
         <v>37.25</v>
       </c>
       <c r="F1015" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1016">
@@ -21478,7 +21478,7 @@
         <v>34</v>
       </c>
       <c r="F1052" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1053">
@@ -21518,7 +21518,7 @@
         <v>36.5</v>
       </c>
       <c r="F1054" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1055">
@@ -21538,7 +21538,7 @@
         <v>41.25</v>
       </c>
       <c r="F1055" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1056">
@@ -26798,7 +26798,7 @@
         <v>25.25</v>
       </c>
       <c r="F1318" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1319">
@@ -26818,7 +26818,7 @@
         <v>28</v>
       </c>
       <c r="F1319" t="n">
-        <v>23.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1320">
@@ -26838,7 +26838,7 @@
         <v>31.5</v>
       </c>
       <c r="F1320" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1321">
@@ -26878,7 +26878,7 @@
         <v>3.5</v>
       </c>
       <c r="F1322" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1323">
@@ -26898,7 +26898,7 @@
         <v>24.75</v>
       </c>
       <c r="F1323" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="1324">
@@ -27298,7 +27298,7 @@
         <v>34.5</v>
       </c>
       <c r="F1343" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1344">
@@ -27358,7 +27358,7 @@
         <v>36</v>
       </c>
       <c r="F1346" t="n">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1347">
@@ -27478,7 +27478,7 @@
         <v>39.25</v>
       </c>
       <c r="F1352" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1353">
@@ -27818,7 +27818,7 @@
         <v>29.75</v>
       </c>
       <c r="F1369" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1370">
@@ -28898,7 +28898,7 @@
         <v>22.75</v>
       </c>
       <c r="F1423" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1424">
@@ -28918,7 +28918,7 @@
         <v>39</v>
       </c>
       <c r="F1424" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1425">
@@ -29078,7 +29078,7 @@
         <v>40.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>22</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="1433">
@@ -29098,7 +29098,7 @@
         <v>38.5</v>
       </c>
       <c r="F1433" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1434">
@@ -29118,7 +29118,7 @@
         <v>42.5</v>
       </c>
       <c r="F1434" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1435">
@@ -30178,7 +30178,7 @@
         <v>43.25</v>
       </c>
       <c r="F1487" t="n">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="1488">
@@ -30198,7 +30198,7 @@
         <v>36.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1489">
@@ -30398,7 +30398,7 @@
         <v>40.5</v>
       </c>
       <c r="F1498" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1499">
@@ -30543,7 +30543,7 @@
         <v>27.26</v>
       </c>
       <c r="F3" t="n">
-        <v>15.843</v>
+        <v>15.866</v>
       </c>
     </row>
     <row r="4">
@@ -30565,7 +30565,7 @@
         <v>14.51602424816504</v>
       </c>
       <c r="F4" t="n">
-        <v>9.101377609072214</v>
+        <v>9.110564138366042</v>
       </c>
     </row>
     <row r="5">

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,43 +442,3513 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>wind#0</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>battery#0</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>grid#0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>load#0</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37447.52125924824</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32084.48411535302</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C4" t="n">
+        <v>32707.14900149575</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>28552.39108416848</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" t="n">
+        <v>31564.34744516323</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30905.05364627173</v>
+      </c>
+      <c r="D7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>40823.72346568709</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n">
+        <v>40907.03704060733</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" t="n">
+        <v>42856.29459852685</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C11" t="n">
+        <v>38829.54115177665</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C12" t="n">
+        <v>42839.97407460878</v>
+      </c>
+      <c r="D12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="n">
+        <v>44305.69811949111</v>
+      </c>
+      <c r="D13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39893.26655567193</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>76</v>
+      </c>
+      <c r="C15" t="n">
+        <v>43187.33548977972</v>
+      </c>
+      <c r="D15" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84</v>
+      </c>
+      <c r="C16" t="n">
+        <v>49074.53013829903</v>
+      </c>
+      <c r="D16" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C17" t="n">
+        <v>46769.43092141971</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>60</v>
+      </c>
+      <c r="C18" t="n">
+        <v>47651.33068181456</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>66</v>
+      </c>
+      <c r="C19" t="n">
+        <v>42834.83442807123</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C20" t="n">
+        <v>43935.57829346989</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>88</v>
+      </c>
+      <c r="C21" t="n">
+        <v>48535.06328972657</v>
+      </c>
+      <c r="D21" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" t="n">
+        <v>45527.71669088824</v>
+      </c>
+      <c r="D22" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>88</v>
+      </c>
+      <c r="C23" t="n">
+        <v>49792.19853549719</v>
+      </c>
+      <c r="D23" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106</v>
+      </c>
+      <c r="C24" t="n">
+        <v>44482.55221744867</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>70</v>
+      </c>
+      <c r="C25" t="n">
+        <v>51730.59996321929</v>
+      </c>
+      <c r="D25" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104</v>
+      </c>
+      <c r="C26" t="n">
+        <v>43873.01270062249</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B27" t="n">
+        <v>92</v>
+      </c>
+      <c r="C27" t="n">
+        <v>51900.77145106289</v>
+      </c>
+      <c r="D27" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96</v>
+      </c>
+      <c r="C28" t="n">
+        <v>43576.43781712215</v>
+      </c>
+      <c r="D28" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>82</v>
+      </c>
+      <c r="C29" t="n">
+        <v>48738.19866300663</v>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110</v>
+      </c>
+      <c r="C30" t="n">
+        <v>49432.99437543642</v>
+      </c>
+      <c r="D30" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84</v>
+      </c>
+      <c r="C31" t="n">
+        <v>40292.64740287764</v>
+      </c>
+      <c r="D31" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54377.51103769917</v>
+      </c>
+      <c r="D32" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>122</v>
+      </c>
+      <c r="C33" t="n">
+        <v>51177.41800211072</v>
+      </c>
+      <c r="D33" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>120</v>
+      </c>
+      <c r="C34" t="n">
+        <v>49470.53995044796</v>
+      </c>
+      <c r="D34" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>130</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50087.92735596791</v>
+      </c>
+      <c r="D35" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>116</v>
+      </c>
+      <c r="C36" t="n">
+        <v>47368.12376849648</v>
+      </c>
+      <c r="D36" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102</v>
+      </c>
+      <c r="C37" t="n">
+        <v>51806.81923691716</v>
+      </c>
+      <c r="D37" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>112</v>
+      </c>
+      <c r="C38" t="n">
+        <v>48069.94627466197</v>
+      </c>
+      <c r="D38" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>128</v>
+      </c>
+      <c r="C39" t="n">
+        <v>55975.59650215632</v>
+      </c>
+      <c r="D39" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>116</v>
+      </c>
+      <c r="C40" t="n">
+        <v>46803.00287526185</v>
+      </c>
+      <c r="D40" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>136</v>
+      </c>
+      <c r="C41" t="n">
+        <v>46743.05531580098</v>
+      </c>
+      <c r="D41" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>146</v>
+      </c>
+      <c r="C42" t="n">
+        <v>50934.35990287764</v>
+      </c>
+      <c r="D42" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>150</v>
+      </c>
+      <c r="C43" t="n">
+        <v>61926.48354056172</v>
+      </c>
+      <c r="D43" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>130</v>
+      </c>
+      <c r="C44" t="n">
+        <v>47544.34871079715</v>
+      </c>
+      <c r="D44" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>114</v>
+      </c>
+      <c r="C45" t="n">
+        <v>47868.46515437337</v>
+      </c>
+      <c r="D45" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>128</v>
+      </c>
+      <c r="C46" t="n">
+        <v>59436.94876849648</v>
+      </c>
+      <c r="D46" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>130</v>
+      </c>
+      <c r="C47" t="n">
+        <v>56751.82430650708</v>
+      </c>
+      <c r="D47" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>146</v>
+      </c>
+      <c r="C48" t="n">
+        <v>63747.84251519355</v>
+      </c>
+      <c r="D48" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>132</v>
+      </c>
+      <c r="C49" t="n">
+        <v>47195.63311794976</v>
+      </c>
+      <c r="D49" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>168</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50734.17705315853</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>126</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46854.18812213348</v>
+      </c>
+      <c r="D51" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>146</v>
+      </c>
+      <c r="C52" t="n">
+        <v>52952.29597515551</v>
+      </c>
+      <c r="D52" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" t="n">
+        <v>44645.23221943042</v>
+      </c>
+      <c r="D53" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>144</v>
+      </c>
+      <c r="C54" t="n">
+        <v>47966.9082333484</v>
+      </c>
+      <c r="D54" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>166</v>
+      </c>
+      <c r="C55" t="n">
+        <v>57294.57550563385</v>
+      </c>
+      <c r="D55" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>148</v>
+      </c>
+      <c r="C56" t="n">
+        <v>56958.87561662858</v>
+      </c>
+      <c r="D56" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>148</v>
+      </c>
+      <c r="C57" t="n">
+        <v>48616.37067785105</v>
+      </c>
+      <c r="D57" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>148</v>
+      </c>
+      <c r="C58" t="n">
+        <v>46393.92924418364</v>
+      </c>
+      <c r="D58" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>150</v>
+      </c>
+      <c r="C59" t="n">
+        <v>57102.78378126786</v>
+      </c>
+      <c r="D59" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>160</v>
+      </c>
+      <c r="C60" t="n">
+        <v>50050.66281602115</v>
+      </c>
+      <c r="D60" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>152</v>
+      </c>
+      <c r="C61" t="n">
+        <v>45106.57734385713</v>
+      </c>
+      <c r="D61" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>154</v>
+      </c>
+      <c r="C62" t="n">
+        <v>50585.64907020488</v>
+      </c>
+      <c r="D62" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>152</v>
+      </c>
+      <c r="C63" t="n">
+        <v>59432.71609738024</v>
+      </c>
+      <c r="D63" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
-      <c r="F2" t="n">
-        <v>20.5</v>
+      <c r="B64" t="n">
+        <v>150</v>
+      </c>
+      <c r="C64" t="n">
+        <v>70207.53895304464</v>
+      </c>
+      <c r="D64" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>170</v>
+      </c>
+      <c r="C65" t="n">
+        <v>47596.01121079715</v>
+      </c>
+      <c r="D65" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>154</v>
+      </c>
+      <c r="C66" t="n">
+        <v>55632.38758962776</v>
+      </c>
+      <c r="D66" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>170</v>
+      </c>
+      <c r="C67" t="n">
+        <v>47326.26096348513</v>
+      </c>
+      <c r="D67" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>168</v>
+      </c>
+      <c r="C68" t="n">
+        <v>50934.66858350792</v>
+      </c>
+      <c r="D68" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>150</v>
+      </c>
+      <c r="C69" t="n">
+        <v>45514.98323555037</v>
+      </c>
+      <c r="D69" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>166</v>
+      </c>
+      <c r="C70" t="n">
+        <v>42399.19430452533</v>
+      </c>
+      <c r="D70" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>162</v>
+      </c>
+      <c r="C71" t="n">
+        <v>43715.38430826867</v>
+      </c>
+      <c r="D71" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>182</v>
+      </c>
+      <c r="C72" t="n">
+        <v>50876.56805870904</v>
+      </c>
+      <c r="D72" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>162</v>
+      </c>
+      <c r="C73" t="n">
+        <v>51017.60686883055</v>
+      </c>
+      <c r="D73" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>184</v>
+      </c>
+      <c r="C74" t="n">
+        <v>68690.60437609701</v>
+      </c>
+      <c r="D74" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>160</v>
+      </c>
+      <c r="C75" t="n">
+        <v>67254.38628280922</v>
+      </c>
+      <c r="D75" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>186</v>
+      </c>
+      <c r="C76" t="n">
+        <v>46885.21198400899</v>
+      </c>
+      <c r="D76" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>184</v>
+      </c>
+      <c r="C77" t="n">
+        <v>54490.70155633253</v>
+      </c>
+      <c r="D77" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>174</v>
+      </c>
+      <c r="C78" t="n">
+        <v>52370.9340686635</v>
+      </c>
+      <c r="D78" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>196</v>
+      </c>
+      <c r="C79" t="n">
+        <v>54303.78204633245</v>
+      </c>
+      <c r="D79" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>184</v>
+      </c>
+      <c r="C80" t="n">
+        <v>58159.61788230813</v>
+      </c>
+      <c r="D80" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>160</v>
+      </c>
+      <c r="C81" t="n">
+        <v>42295.94538384951</v>
+      </c>
+      <c r="D81" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>176</v>
+      </c>
+      <c r="C82" t="n">
+        <v>49706.13299594521</v>
+      </c>
+      <c r="D82" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>190</v>
+      </c>
+      <c r="C83" t="n">
+        <v>62504.64295211825</v>
+      </c>
+      <c r="D83" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>190</v>
+      </c>
+      <c r="C84" t="n">
+        <v>73080.10990618057</v>
+      </c>
+      <c r="D84" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>198</v>
+      </c>
+      <c r="C85" t="n">
+        <v>76921.19217670443</v>
+      </c>
+      <c r="D85" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>186</v>
+      </c>
+      <c r="C86" t="n">
+        <v>79523.23736103241</v>
+      </c>
+      <c r="D86" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>166</v>
+      </c>
+      <c r="C87" t="n">
+        <v>74520.89384513265</v>
+      </c>
+      <c r="D87" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>186</v>
+      </c>
+      <c r="C88" t="n">
+        <v>56543.11597097181</v>
+      </c>
+      <c r="D88" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>170</v>
+      </c>
+      <c r="C89" t="n">
+        <v>60264.55895876974</v>
+      </c>
+      <c r="D89" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>174</v>
+      </c>
+      <c r="C90" t="n">
+        <v>55937.07972779789</v>
+      </c>
+      <c r="D90" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>192</v>
+      </c>
+      <c r="C91" t="n">
+        <v>51290.31002488216</v>
+      </c>
+      <c r="D91" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>202</v>
+      </c>
+      <c r="C92" t="n">
+        <v>50205.15567190575</v>
+      </c>
+      <c r="D92" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>190</v>
+      </c>
+      <c r="C93" t="n">
+        <v>77995.10747555031</v>
+      </c>
+      <c r="D93" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>196</v>
+      </c>
+      <c r="C94" t="n">
+        <v>73512.69270700816</v>
+      </c>
+      <c r="D94" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>210</v>
+      </c>
+      <c r="C95" t="n">
+        <v>79586.98116212587</v>
+      </c>
+      <c r="D95" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>204</v>
+      </c>
+      <c r="C96" t="n">
+        <v>66719.35068203477</v>
+      </c>
+      <c r="D96" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>198</v>
+      </c>
+      <c r="C97" t="n">
+        <v>64925.74044287002</v>
+      </c>
+      <c r="D97" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>204</v>
+      </c>
+      <c r="C98" t="n">
+        <v>52962.33294264981</v>
+      </c>
+      <c r="D98" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>198</v>
+      </c>
+      <c r="C99" t="n">
+        <v>65064.42377950628</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>194</v>
+      </c>
+      <c r="C100" t="n">
+        <v>57846.25782064528</v>
+      </c>
+      <c r="D100" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>196</v>
+      </c>
+      <c r="C101" t="n">
+        <v>60049.58597889886</v>
+      </c>
+      <c r="D101" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>198</v>
+      </c>
+      <c r="C102" t="n">
+        <v>47541.74365111606</v>
+      </c>
+      <c r="D102" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>192</v>
+      </c>
+      <c r="C103" t="n">
+        <v>46853.91121740303</v>
+      </c>
+      <c r="D103" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>184</v>
+      </c>
+      <c r="C104" t="n">
+        <v>46835.55264556551</v>
+      </c>
+      <c r="D104" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>194</v>
+      </c>
+      <c r="C105" t="n">
+        <v>47842.19252290039</v>
+      </c>
+      <c r="D105" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>194</v>
+      </c>
+      <c r="C106" t="n">
+        <v>73428.95366388741</v>
+      </c>
+      <c r="D106" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>192</v>
+      </c>
+      <c r="C107" t="n">
+        <v>79532.40062873937</v>
+      </c>
+      <c r="D107" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>180</v>
+      </c>
+      <c r="C108" t="n">
+        <v>62865.55919066803</v>
+      </c>
+      <c r="D108" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>182</v>
+      </c>
+      <c r="C109" t="n">
+        <v>58326.0302603036</v>
+      </c>
+      <c r="D109" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>212</v>
+      </c>
+      <c r="C110" t="n">
+        <v>45179.6439506225</v>
+      </c>
+      <c r="D110" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>208</v>
+      </c>
+      <c r="C111" t="n">
+        <v>71260.023127198</v>
+      </c>
+      <c r="D111" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>210</v>
+      </c>
+      <c r="C112" t="n">
+        <v>82851.64598726628</v>
+      </c>
+      <c r="D112" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>212</v>
+      </c>
+      <c r="C113" t="n">
+        <v>72669.23205624124</v>
+      </c>
+      <c r="D113" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>218</v>
+      </c>
+      <c r="C114" t="n">
+        <v>78855.59700448724</v>
+      </c>
+      <c r="D114" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>212</v>
+      </c>
+      <c r="C115" t="n">
+        <v>82279.66104760799</v>
+      </c>
+      <c r="D115" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>214</v>
+      </c>
+      <c r="C116" t="n">
+        <v>84660.64974233083</v>
+      </c>
+      <c r="D116" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>222</v>
+      </c>
+      <c r="C117" t="n">
+        <v>79259.74312962014</v>
+      </c>
+      <c r="D117" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>196</v>
+      </c>
+      <c r="C118" t="n">
+        <v>74349.29313072115</v>
+      </c>
+      <c r="D118" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>218</v>
+      </c>
+      <c r="C119" t="n">
+        <v>72773.75759755482</v>
+      </c>
+      <c r="D119" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>216</v>
+      </c>
+      <c r="C120" t="n">
+        <v>57998.76168890648</v>
+      </c>
+      <c r="D120" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>212</v>
+      </c>
+      <c r="C121" t="n">
+        <v>51015.63746211833</v>
+      </c>
+      <c r="D121" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>214</v>
+      </c>
+      <c r="C122" t="n">
+        <v>56590.02257707659</v>
+      </c>
+      <c r="D122" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>210</v>
+      </c>
+      <c r="C123" t="n">
+        <v>53766.66270172349</v>
+      </c>
+      <c r="D123" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>202</v>
+      </c>
+      <c r="C124" t="n">
+        <v>56399.03466547443</v>
+      </c>
+      <c r="D124" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>210</v>
+      </c>
+      <c r="C125" t="n">
+        <v>86899.51842582363</v>
+      </c>
+      <c r="D125" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>216</v>
+      </c>
+      <c r="C126" t="n">
+        <v>67324.8603298935</v>
+      </c>
+      <c r="D126" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>216</v>
+      </c>
+      <c r="C127" t="n">
+        <v>44136.04864979489</v>
+      </c>
+      <c r="D127" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>226</v>
+      </c>
+      <c r="C128" t="n">
+        <v>64812.26520106288</v>
+      </c>
+      <c r="D128" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>208</v>
+      </c>
+      <c r="C129" t="n">
+        <v>79266.60854496562</v>
+      </c>
+      <c r="D129" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>212</v>
+      </c>
+      <c r="C130" t="n">
+        <v>87830.4596819891</v>
+      </c>
+      <c r="D130" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>212</v>
+      </c>
+      <c r="C131" t="n">
+        <v>84009.31408715993</v>
+      </c>
+      <c r="D131" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>83301.1801570157</v>
+      </c>
+      <c r="D132" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>218</v>
+      </c>
+      <c r="C133" t="n">
+        <v>85884.15045233841</v>
+      </c>
+      <c r="D133" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>214</v>
+      </c>
+      <c r="C134" t="n">
+        <v>83917.847535892</v>
+      </c>
+      <c r="D134" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>216</v>
+      </c>
+      <c r="C135" t="n">
+        <v>74791.813665649</v>
+      </c>
+      <c r="D135" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>214</v>
+      </c>
+      <c r="C136" t="n">
+        <v>72099.80181025041</v>
+      </c>
+      <c r="D136" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>220</v>
+      </c>
+      <c r="C137" t="n">
+        <v>65919.55633852679</v>
+      </c>
+      <c r="D137" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>212</v>
+      </c>
+      <c r="C138" t="n">
+        <v>56458.13329655265</v>
+      </c>
+      <c r="D138" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>224</v>
+      </c>
+      <c r="C139" t="n">
+        <v>63425.58288605147</v>
+      </c>
+      <c r="D139" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>218</v>
+      </c>
+      <c r="C140" t="n">
+        <v>67076.6662204858</v>
+      </c>
+      <c r="D140" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>224</v>
+      </c>
+      <c r="C141" t="n">
+        <v>48299.53776052378</v>
+      </c>
+      <c r="D141" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>220</v>
+      </c>
+      <c r="C142" t="n">
+        <v>71070.48747092615</v>
+      </c>
+      <c r="D142" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>230</v>
+      </c>
+      <c r="C143" t="n">
+        <v>57600.43472977965</v>
+      </c>
+      <c r="D143" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>212</v>
+      </c>
+      <c r="C144" t="n">
+        <v>48444.30829324971</v>
+      </c>
+      <c r="D144" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>220</v>
+      </c>
+      <c r="C145" t="n">
+        <v>70850.16068599829</v>
+      </c>
+      <c r="D145" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>230</v>
+      </c>
+      <c r="C146" t="n">
+        <v>57953.00436728916</v>
+      </c>
+      <c r="D146" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>232</v>
+      </c>
+      <c r="C147" t="n">
+        <v>69792.77109605908</v>
+      </c>
+      <c r="D147" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>228</v>
+      </c>
+      <c r="C148" t="n">
+        <v>48504.37055804848</v>
+      </c>
+      <c r="D148" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>226</v>
+      </c>
+      <c r="C149" t="n">
+        <v>64195.65247136655</v>
+      </c>
+      <c r="D149" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>228</v>
+      </c>
+      <c r="C150" t="n">
+        <v>45223.57865287762</v>
+      </c>
+      <c r="D150" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>222</v>
+      </c>
+      <c r="C151" t="n">
+        <v>73033.67413671204</v>
+      </c>
+      <c r="D151" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>224</v>
+      </c>
+      <c r="C152" t="n">
+        <v>80014.68782592997</v>
+      </c>
+      <c r="D152" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>222</v>
+      </c>
+      <c r="C153" t="n">
+        <v>87537.36795652217</v>
+      </c>
+      <c r="D153" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>220</v>
+      </c>
+      <c r="C154" t="n">
+        <v>87166.56480157151</v>
+      </c>
+      <c r="D154" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>228</v>
+      </c>
+      <c r="C155" t="n">
+        <v>86965.4524801744</v>
+      </c>
+      <c r="D155" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>226</v>
+      </c>
+      <c r="C156" t="n">
+        <v>86750.9694996429</v>
+      </c>
+      <c r="D156" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>226</v>
+      </c>
+      <c r="C157" t="n">
+        <v>84569.21914463911</v>
+      </c>
+      <c r="D157" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>220</v>
+      </c>
+      <c r="C158" t="n">
+        <v>69860.88872224733</v>
+      </c>
+      <c r="D158" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>226</v>
+      </c>
+      <c r="C159" t="n">
+        <v>58539.5012788457</v>
+      </c>
+      <c r="D159" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>220</v>
+      </c>
+      <c r="C160" t="n">
+        <v>63682.99157438862</v>
+      </c>
+      <c r="D160" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>232</v>
+      </c>
+      <c r="C161" t="n">
+        <v>50918.26692829143</v>
+      </c>
+      <c r="D161" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>230</v>
+      </c>
+      <c r="C162" t="n">
+        <v>63206.78776492771</v>
+      </c>
+      <c r="D162" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>224</v>
+      </c>
+      <c r="C163" t="n">
+        <v>49190.77353549721</v>
+      </c>
+      <c r="D163" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>232</v>
+      </c>
+      <c r="C164" t="n">
+        <v>62734.18234804084</v>
+      </c>
+      <c r="D164" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>226</v>
+      </c>
+      <c r="C165" t="n">
+        <v>73943.55366278643</v>
+      </c>
+      <c r="D165" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>226</v>
+      </c>
+      <c r="C166" t="n">
+        <v>57919.79020546682</v>
+      </c>
+      <c r="D166" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>224</v>
+      </c>
+      <c r="C167" t="n">
+        <v>60391.59472823827</v>
+      </c>
+      <c r="D167" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>234</v>
+      </c>
+      <c r="C168" t="n">
+        <v>48283.56376783589</v>
+      </c>
+      <c r="D168" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>226</v>
+      </c>
+      <c r="C169" t="n">
+        <v>53900.7628193241</v>
+      </c>
+      <c r="D169" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>230</v>
+      </c>
+      <c r="C170" t="n">
+        <v>49553.16573246764</v>
+      </c>
+      <c r="D170" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>228</v>
+      </c>
+      <c r="C171" t="n">
+        <v>61116.35353087309</v>
+      </c>
+      <c r="D171" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>226</v>
+      </c>
+      <c r="C172" t="n">
+        <v>46920.3740103036</v>
+      </c>
+      <c r="D172" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>226</v>
+      </c>
+      <c r="C173" t="n">
+        <v>52310.07758126032</v>
+      </c>
+      <c r="D173" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>232</v>
+      </c>
+      <c r="C174" t="n">
+        <v>51698.40359407732</v>
+      </c>
+      <c r="D174" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>234</v>
+      </c>
+      <c r="C175" t="n">
+        <v>83427.53979606659</v>
+      </c>
+      <c r="D175" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>230</v>
+      </c>
+      <c r="C176" t="n">
+        <v>86788.09426554265</v>
+      </c>
+      <c r="D176" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>226</v>
+      </c>
+      <c r="C177" t="n">
+        <v>86874.88009821542</v>
+      </c>
+      <c r="D177" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>230</v>
+      </c>
+      <c r="C178" t="n">
+        <v>88358.77658715997</v>
+      </c>
+      <c r="D178" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>226</v>
+      </c>
+      <c r="C179" t="n">
+        <v>85658.52283760039</v>
+      </c>
+      <c r="D179" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>236</v>
+      </c>
+      <c r="C180" t="n">
+        <v>89582.57456372793</v>
+      </c>
+      <c r="D180" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>230</v>
+      </c>
+      <c r="C181" t="n">
+        <v>87365.8115867196</v>
+      </c>
+      <c r="D181" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>230</v>
+      </c>
+      <c r="C182" t="n">
+        <v>87205.20069414556</v>
+      </c>
+      <c r="D182" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>232</v>
+      </c>
+      <c r="C183" t="n">
+        <v>86502.64581306734</v>
+      </c>
+      <c r="D183" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>228</v>
+      </c>
+      <c r="C184" t="n">
+        <v>87750.76140481375</v>
+      </c>
+      <c r="D184" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>232</v>
+      </c>
+      <c r="C185" t="n">
+        <v>89597.76230113112</v>
+      </c>
+      <c r="D185" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>230</v>
+      </c>
+      <c r="C186" t="n">
+        <v>88976.26444436572</v>
+      </c>
+      <c r="D186" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>226</v>
+      </c>
+      <c r="C187" t="n">
+        <v>87969.95480091093</v>
+      </c>
+      <c r="D187" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>236</v>
+      </c>
+      <c r="C188" t="n">
+        <v>89129.34831460874</v>
+      </c>
+      <c r="D188" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>234</v>
+      </c>
+      <c r="C189" t="n">
+        <v>88975.12069436572</v>
+      </c>
+      <c r="D189" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>232</v>
+      </c>
+      <c r="C190" t="n">
+        <v>88298.43116322687</v>
+      </c>
+      <c r="D190" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>230</v>
+      </c>
+      <c r="C191" t="n">
+        <v>89104.38783693977</v>
+      </c>
+      <c r="D191" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>228</v>
+      </c>
+      <c r="C192" t="n">
+        <v>88341.2339087773</v>
+      </c>
+      <c r="D192" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>232</v>
+      </c>
+      <c r="C193" t="n">
+        <v>88435.09265811669</v>
+      </c>
+      <c r="D193" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>224</v>
+      </c>
+      <c r="C194" t="n">
+        <v>87259.14396823818</v>
+      </c>
+      <c r="D194" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>236</v>
+      </c>
+      <c r="C195" t="n">
+        <v>82576.62009535285</v>
+      </c>
+      <c r="D195" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>230</v>
+      </c>
+      <c r="C196" t="n">
+        <v>61521.53341415325</v>
+      </c>
+      <c r="D196" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>232</v>
+      </c>
+      <c r="C197" t="n">
+        <v>83225.20194106277</v>
+      </c>
+      <c r="D197" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>236</v>
+      </c>
+      <c r="C198" t="n">
+        <v>89283.64849211059</v>
+      </c>
+      <c r="D198" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>232</v>
+      </c>
+      <c r="C199" t="n">
+        <v>79243.63479738777</v>
+      </c>
+      <c r="D199" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>230</v>
+      </c>
+      <c r="C200" t="n">
+        <v>61036.66020458602</v>
+      </c>
+      <c r="D200" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>234</v>
+      </c>
+      <c r="C201" t="n">
+        <v>65074.29193159439</v>
+      </c>
+      <c r="D201" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>230</v>
+      </c>
+      <c r="C202" t="n">
+        <v>60050.68966635523</v>
+      </c>
+      <c r="D202" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>226</v>
+      </c>
+      <c r="C203" t="n">
+        <v>60770.43330095656</v>
+      </c>
+      <c r="D203" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>230</v>
+      </c>
+      <c r="C204" t="n">
+        <v>75522.2843170765</v>
+      </c>
+      <c r="D204" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>236</v>
+      </c>
+      <c r="C205" t="n">
+        <v>82119.64771449484</v>
+      </c>
+      <c r="D205" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>236</v>
+      </c>
+      <c r="C206" t="n">
+        <v>47742.97656954431</v>
+      </c>
+      <c r="D206" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>234</v>
+      </c>
+      <c r="C207" t="n">
+        <v>64974.54103857998</v>
+      </c>
+      <c r="D207" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>228</v>
+      </c>
+      <c r="C208" t="n">
+        <v>73340.64824259664</v>
+      </c>
+      <c r="D208" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>238</v>
+      </c>
+      <c r="C209" t="n">
+        <v>57739.71812191328</v>
+      </c>
+      <c r="D209" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>234</v>
+      </c>
+      <c r="C210" t="n">
+        <v>74361.2920591038</v>
+      </c>
+      <c r="D210" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>232</v>
+      </c>
+      <c r="C211" t="n">
+        <v>88743.01176532246</v>
+      </c>
+      <c r="D211" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>236</v>
+      </c>
+      <c r="C212" t="n">
+        <v>88333.07313490481</v>
+      </c>
+      <c r="D212" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>230</v>
+      </c>
+      <c r="C213" t="n">
+        <v>88894.04134909617</v>
+      </c>
+      <c r="D213" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>234</v>
+      </c>
+      <c r="C214" t="n">
+        <v>88561.03998017438</v>
+      </c>
+      <c r="D214" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>230</v>
+      </c>
+      <c r="C215" t="n">
+        <v>88917.21801532248</v>
+      </c>
+      <c r="D215" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>234</v>
+      </c>
+      <c r="C216" t="n">
+        <v>89954.9408132875</v>
+      </c>
+      <c r="D216" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>234</v>
+      </c>
+      <c r="C217" t="n">
+        <v>87815.52456262698</v>
+      </c>
+      <c r="D217" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>236</v>
+      </c>
+      <c r="C218" t="n">
+        <v>89953.59224211064</v>
+      </c>
+      <c r="D218" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>238</v>
+      </c>
+      <c r="C219" t="n">
+        <v>87521.4766470613</v>
+      </c>
+      <c r="D219" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>230</v>
+      </c>
+      <c r="C220" t="n">
+        <v>88450.98253985551</v>
+      </c>
+      <c r="D220" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>232</v>
+      </c>
+      <c r="C221" t="n">
+        <v>65176.36258742582</v>
+      </c>
+      <c r="D221" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>236</v>
+      </c>
+      <c r="C222" t="n">
+        <v>63741.9581212527</v>
+      </c>
+      <c r="D222" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>230</v>
+      </c>
+      <c r="C223" t="n">
+        <v>64992.96479386467</v>
+      </c>
+      <c r="D223" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>238</v>
+      </c>
+      <c r="C224" t="n">
+        <v>79336.48991036431</v>
+      </c>
+      <c r="D224" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>238</v>
+      </c>
+      <c r="C225" t="n">
+        <v>88986.78361037181</v>
+      </c>
+      <c r="D225" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>230</v>
+      </c>
+      <c r="C226" t="n">
+        <v>89788.4646229686</v>
+      </c>
+      <c r="D226" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>232</v>
+      </c>
+      <c r="C227" t="n">
+        <v>88759.84426554266</v>
+      </c>
+      <c r="D227" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>234</v>
+      </c>
+      <c r="C228" t="n">
+        <v>89172.4174795138</v>
+      </c>
+      <c r="D228" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>234</v>
+      </c>
+      <c r="C229" t="n">
+        <v>88627.95104804836</v>
+      </c>
+      <c r="D229" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>234</v>
+      </c>
+      <c r="C230" t="n">
+        <v>90139.91753501115</v>
+      </c>
+      <c r="D230" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>238</v>
+      </c>
+      <c r="C231" t="n">
+        <v>89437.94509865581</v>
+      </c>
+      <c r="D231" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>228</v>
+      </c>
+      <c r="C232" t="n">
+        <v>88848.66581328752</v>
+      </c>
+      <c r="D232" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>234</v>
+      </c>
+      <c r="C233" t="n">
+        <v>89058.55670564137</v>
+      </c>
+      <c r="D233" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>234</v>
+      </c>
+      <c r="C234" t="n">
+        <v>89559.09081328753</v>
+      </c>
+      <c r="D234" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>234</v>
+      </c>
+      <c r="C235" t="n">
+        <v>89266.74253941511</v>
+      </c>
+      <c r="D235" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>238</v>
+      </c>
+      <c r="C236" t="n">
+        <v>89959.72968220933</v>
+      </c>
+      <c r="D236" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>238</v>
+      </c>
+      <c r="C237" t="n">
+        <v>89120.03158693979</v>
+      </c>
+      <c r="D237" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>232</v>
+      </c>
+      <c r="C238" t="n">
+        <v>88580.97849189043</v>
+      </c>
+      <c r="D238" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>230</v>
+      </c>
+      <c r="C239" t="n">
+        <v>88126.68253435059</v>
+      </c>
+      <c r="D239" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>236</v>
+      </c>
+      <c r="C240" t="n">
+        <v>89236.02730157152</v>
+      </c>
+      <c r="D240" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>238</v>
+      </c>
+      <c r="C241" t="n">
+        <v>88708.3030747834</v>
+      </c>
+      <c r="D241" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
+        <v>234</v>
+      </c>
+      <c r="C242" t="n">
+        <v>89959.72968220933</v>
+      </c>
+      <c r="D242" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
+        <v>238</v>
+      </c>
+      <c r="C243" t="n">
+        <v>89629.77224189037</v>
+      </c>
+      <c r="D243" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
+        <v>234</v>
+      </c>
+      <c r="C244" t="n">
+        <v>89669.18908715995</v>
+      </c>
+      <c r="D244" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
+        <v>238</v>
+      </c>
+      <c r="C245" t="n">
+        <v>89511.52170608174</v>
+      </c>
+      <c r="D245" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
+        <v>238</v>
+      </c>
+      <c r="C246" t="n">
+        <v>89720.46247973402</v>
+      </c>
+      <c r="D246" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
+        <v>232</v>
+      </c>
+      <c r="C247" t="n">
+        <v>89319.88194414556</v>
+      </c>
+      <c r="D247" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
+        <v>234</v>
+      </c>
+      <c r="C248" t="n">
+        <v>89528.44742049331</v>
+      </c>
+      <c r="D248" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
+        <v>232</v>
+      </c>
+      <c r="C249" t="n">
+        <v>89643.15992049329</v>
+      </c>
+      <c r="D249" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
+        <v>238</v>
+      </c>
+      <c r="C250" t="n">
+        <v>88335.82676576286</v>
+      </c>
+      <c r="D250" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
+        <v>234</v>
+      </c>
+      <c r="C251" t="n">
+        <v>89512.47527373556</v>
+      </c>
+      <c r="D251" t="n">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -492,7 +3962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,22 +3973,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>wind#0</t>
+          <t>battery#0</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>battery#0</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>grid#0</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>load#0</t>
         </is>
       </c>
     </row>
@@ -529,19 +3989,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
@@ -551,19 +4005,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>187.136</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>65612.33051372593</v>
       </c>
       <c r="D3" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E3" t="n">
-        <v>62</v>
-      </c>
-      <c r="F3" t="n">
-        <v>20.5</v>
+        <v>160.72</v>
       </c>
     </row>
     <row r="4">
@@ -572,11 +4020,15 @@
           <t>std</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>58.61224346787405</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17574.14601289595</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62.13156141362281</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -585,19 +4037,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>-2</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>28552.39108416848</v>
       </c>
       <c r="D5" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F5" t="n">
-        <v>20.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -607,19 +4053,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>49591.40754833703</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E6" t="n">
-        <v>62</v>
-      </c>
-      <c r="F6" t="n">
-        <v>20.5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
@@ -629,19 +4069,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>63036.17347779787</v>
       </c>
       <c r="D7" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E7" t="n">
-        <v>62</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20.5</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -651,19 +4085,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>85827.7435486539</v>
       </c>
       <c r="D8" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E8" t="n">
-        <v>62</v>
-      </c>
-      <c r="F8" t="n">
-        <v>20.5</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="9">
@@ -673,19 +4101,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>90139.91753501115</v>
       </c>
       <c r="D9" t="n">
-        <v>-15.09408024056189</v>
-      </c>
-      <c r="E9" t="n">
-        <v>62</v>
-      </c>
-      <c r="F9" t="n">
-        <v>20.5</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,13 +456,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>37447.52125924824</v>
+        <v>-144.4887406201906</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="3">
@@ -470,13 +470,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="C3" t="n">
-        <v>32084.48411535302</v>
+        <v>-143.8360173079146</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>32707.14900149575</v>
+        <v>-169.0617039009178</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>28552.39108416848</v>
+        <v>-149.4751611436395</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="6">
@@ -512,13 +512,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>-26</v>
       </c>
       <c r="C6" t="n">
-        <v>31564.34744516323</v>
+        <v>-151.0885196172343</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>30905.05364627173</v>
+        <v>-151.9468207603953</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
@@ -540,13 +540,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>-2</v>
       </c>
       <c r="C8" t="n">
-        <v>40823.72346568709</v>
+        <v>-147.886979783321</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -554,13 +554,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>40907.03704060733</v>
+        <v>-140.7398096881055</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -568,13 +568,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>42856.29459852685</v>
+        <v>-154.1991867707985</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-140.8435646157142</v>
+      </c>
+      <c r="D11" t="n">
         <v>22</v>
-      </c>
-      <c r="C11" t="n">
-        <v>38829.54115177665</v>
-      </c>
-      <c r="D11" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -596,13 +596,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
-        <v>42839.97407460878</v>
+        <v>-128.7223503596609</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -610,13 +610,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>44305.69811949111</v>
+        <v>-155.261933282822</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="14">
@@ -624,13 +624,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
-        <v>39893.26655567193</v>
+        <v>-134.2834558808708</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +638,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>43187.33548977972</v>
+        <v>-139.9252473113547</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -652,13 +652,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>49074.53013829903</v>
+        <v>-132.388209322353</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -666,13 +666,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>46769.43092141971</v>
+        <v>-157.0820288094993</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -680,13 +680,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C18" t="n">
-        <v>47651.33068181456</v>
+        <v>-122.9934654337471</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -694,10 +694,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>42834.83442807123</v>
+        <v>-146.981362776633</v>
       </c>
       <c r="D19" t="n">
         <v>34</v>
@@ -708,13 +708,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>43935.57829346989</v>
+        <v>-127.7860740032249</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -722,13 +722,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C21" t="n">
-        <v>48535.06328972657</v>
+        <v>-134.6678268854487</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="22">
@@ -736,13 +736,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>45527.71669088824</v>
+        <v>-116.2686255143823</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -750,13 +750,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>49792.19853549719</v>
+        <v>-148.0032634736457</v>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -764,13 +764,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="C24" t="n">
-        <v>44482.55221744867</v>
+        <v>-128.5135057032351</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -778,13 +778,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>51730.59996321929</v>
+        <v>-117.984779956361</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -792,13 +792,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="C26" t="n">
-        <v>43873.01270062249</v>
+        <v>-130.7559752482558</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -806,13 +806,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C27" t="n">
-        <v>51900.77145106289</v>
+        <v>-113.5643684886618</v>
       </c>
       <c r="D27" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -820,13 +820,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C28" t="n">
-        <v>43576.43781712215</v>
+        <v>-110.2856549525048</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -834,13 +834,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="C29" t="n">
-        <v>48738.19866300663</v>
+        <v>-130.9819974257329</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -848,13 +848,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C30" t="n">
-        <v>49432.99437543642</v>
+        <v>-132.3802397818083</v>
       </c>
       <c r="D30" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
@@ -862,13 +862,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C31" t="n">
-        <v>40292.64740287764</v>
+        <v>-123.8907634152485</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -876,13 +876,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>54377.51103769917</v>
+        <v>-130.1410332026821</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -890,13 +890,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="C33" t="n">
-        <v>51177.41800211072</v>
+        <v>-145.7877087079758</v>
       </c>
       <c r="D33" t="n">
-        <v>118</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -904,13 +904,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="C34" t="n">
-        <v>49470.53995044796</v>
+        <v>-118.0585131414137</v>
       </c>
       <c r="D34" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -918,13 +918,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>50087.92735596791</v>
+        <v>-123.5066427116462</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
@@ -932,13 +932,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="C36" t="n">
-        <v>47368.12376849648</v>
+        <v>-132.2344412227721</v>
       </c>
       <c r="D36" t="n">
-        <v>98</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -946,13 +946,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C37" t="n">
-        <v>51806.81923691716</v>
+        <v>-130.0142004652141</v>
       </c>
       <c r="D37" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -960,13 +960,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C38" t="n">
-        <v>48069.94627466197</v>
+        <v>-121.9664449341694</v>
       </c>
       <c r="D38" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -974,13 +974,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="C39" t="n">
-        <v>55975.59650215632</v>
+        <v>-111.3630762208333</v>
       </c>
       <c r="D39" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -988,13 +988,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>46803.00287526185</v>
+        <v>-126.2140071229041</v>
       </c>
       <c r="D40" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1002,13 +1002,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="C41" t="n">
-        <v>46743.05531580098</v>
+        <v>-123.5627700959065</v>
       </c>
       <c r="D41" t="n">
-        <v>102</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -1016,13 +1016,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="C42" t="n">
-        <v>50934.35990287764</v>
+        <v>-119.3662708297842</v>
       </c>
       <c r="D42" t="n">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -1030,13 +1030,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C43" t="n">
-        <v>61926.48354056172</v>
+        <v>-102.4986717970041</v>
       </c>
       <c r="D43" t="n">
-        <v>106</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44">
@@ -1044,13 +1044,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="C44" t="n">
-        <v>47544.34871079715</v>
+        <v>-129.9390364183476</v>
       </c>
       <c r="D44" t="n">
-        <v>92</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -1058,13 +1058,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="C45" t="n">
-        <v>47868.46515437337</v>
+        <v>-132.2871115482318</v>
       </c>
       <c r="D45" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
@@ -1072,13 +1072,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="C46" t="n">
-        <v>59436.94876849648</v>
+        <v>-110.3686778361729</v>
       </c>
       <c r="D46" t="n">
-        <v>134</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
@@ -1086,13 +1086,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C47" t="n">
-        <v>56751.82430650708</v>
+        <v>-128.5888707516186</v>
       </c>
       <c r="D47" t="n">
-        <v>128</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48">
@@ -1100,13 +1100,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="C48" t="n">
-        <v>63747.84251519355</v>
+        <v>-118.7417975259607</v>
       </c>
       <c r="D48" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
@@ -1114,13 +1114,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="C49" t="n">
-        <v>47195.63311794976</v>
+        <v>-106.8283061254453</v>
       </c>
       <c r="D49" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -1128,13 +1128,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C50" t="n">
-        <v>50734.17705315853</v>
+        <v>-92.79587758879518</v>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
@@ -1142,13 +1142,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C51" t="n">
-        <v>46854.18812213348</v>
+        <v>-131.7715415329425</v>
       </c>
       <c r="D51" t="n">
-        <v>132</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -1156,13 +1156,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="C52" t="n">
-        <v>52952.29597515551</v>
+        <v>-111.3267674688468</v>
       </c>
       <c r="D52" t="n">
-        <v>136</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
@@ -1170,13 +1170,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="C53" t="n">
-        <v>44645.23221943042</v>
+        <v>-85.63904973094461</v>
       </c>
       <c r="D53" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
@@ -1184,13 +1184,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="C54" t="n">
-        <v>47966.9082333484</v>
+        <v>-126.3199285249379</v>
       </c>
       <c r="D54" t="n">
-        <v>114</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -1198,13 +1198,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="C55" t="n">
-        <v>57294.57550563385</v>
+        <v>-104.498611560513</v>
       </c>
       <c r="D55" t="n">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56">
@@ -1212,13 +1212,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C56" t="n">
-        <v>56958.87561662858</v>
+        <v>-97.4819416310656</v>
       </c>
       <c r="D56" t="n">
-        <v>120</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -1226,13 +1226,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="C57" t="n">
-        <v>48616.37067785105</v>
+        <v>-89.31752661933143</v>
       </c>
       <c r="D57" t="n">
-        <v>144</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
@@ -1240,13 +1240,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="C58" t="n">
-        <v>46393.92924418364</v>
+        <v>-92.95656738057171</v>
       </c>
       <c r="D58" t="n">
-        <v>114</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -1254,13 +1254,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="C59" t="n">
-        <v>57102.78378126786</v>
+        <v>-111.0465284685545</v>
       </c>
       <c r="D59" t="n">
-        <v>124</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
@@ -1268,13 +1268,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="C60" t="n">
-        <v>50050.66281602115</v>
+        <v>-103.2607644636541</v>
       </c>
       <c r="D60" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61">
@@ -1282,13 +1282,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="C61" t="n">
-        <v>45106.57734385713</v>
+        <v>-109.7547552975412</v>
       </c>
       <c r="D61" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
@@ -1296,13 +1296,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="C62" t="n">
-        <v>50585.64907020488</v>
+        <v>-103.2879253029243</v>
       </c>
       <c r="D62" t="n">
-        <v>142</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -1310,13 +1310,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="C63" t="n">
-        <v>59432.71609738024</v>
+        <v>-82.63235954459348</v>
       </c>
       <c r="D63" t="n">
-        <v>134</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64">
@@ -1324,13 +1324,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="C64" t="n">
-        <v>70207.53895304464</v>
+        <v>-65.59517722784352</v>
       </c>
       <c r="D64" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65">
@@ -1338,13 +1338,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="C65" t="n">
-        <v>47596.01121079715</v>
+        <v>-99.61068979468025</v>
       </c>
       <c r="D65" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66">
@@ -1352,13 +1352,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="C66" t="n">
-        <v>55632.38758962776</v>
+        <v>-93.98135774546805</v>
       </c>
       <c r="D66" t="n">
-        <v>136</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
@@ -1366,13 +1366,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="C67" t="n">
-        <v>47326.26096348513</v>
+        <v>-76.19411994191918</v>
       </c>
       <c r="D67" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
@@ -1380,13 +1380,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="C68" t="n">
-        <v>50934.66858350792</v>
+        <v>-85.38338407608508</v>
       </c>
       <c r="D68" t="n">
-        <v>140</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
@@ -1394,13 +1394,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C69" t="n">
-        <v>45514.98323555037</v>
+        <v>-68.78934693869911</v>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70">
@@ -1408,13 +1408,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="C70" t="n">
-        <v>42399.19430452533</v>
+        <v>-93.38761294900891</v>
       </c>
       <c r="D70" t="n">
-        <v>138</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71">
@@ -1422,13 +1422,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="C71" t="n">
-        <v>43715.38430826867</v>
+        <v>-84.66459799769933</v>
       </c>
       <c r="D71" t="n">
-        <v>146</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -1436,13 +1436,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="C72" t="n">
-        <v>50876.56805870904</v>
+        <v>-99.28373888332283</v>
       </c>
       <c r="D72" t="n">
-        <v>166</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73">
@@ -1450,13 +1450,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="C73" t="n">
-        <v>51017.60686883055</v>
+        <v>-88.27635939953802</v>
       </c>
       <c r="D73" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
@@ -1464,13 +1464,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="C74" t="n">
-        <v>68690.60437609701</v>
+        <v>-76.07360633801167</v>
       </c>
       <c r="D74" t="n">
-        <v>132</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
@@ -1478,13 +1478,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C75" t="n">
-        <v>67254.38628280922</v>
+        <v>-109.1553895055336</v>
       </c>
       <c r="D75" t="n">
-        <v>144</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -1492,13 +1492,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="C76" t="n">
-        <v>46885.21198400899</v>
+        <v>-87.48498188988921</v>
       </c>
       <c r="D76" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77">
@@ -1506,13 +1506,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="C77" t="n">
-        <v>54490.70155633253</v>
+        <v>-97.58946613487916</v>
       </c>
       <c r="D77" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
@@ -1520,13 +1520,13 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="C78" t="n">
-        <v>52370.9340686635</v>
+        <v>-90.32356242259553</v>
       </c>
       <c r="D78" t="n">
-        <v>156</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79">
@@ -1534,13 +1534,13 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="C79" t="n">
-        <v>54303.78204633245</v>
+        <v>-65.08976638460263</v>
       </c>
       <c r="D79" t="n">
-        <v>150</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80">
@@ -1548,13 +1548,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="C80" t="n">
-        <v>58159.61788230813</v>
+        <v>-75.91627781483614</v>
       </c>
       <c r="D80" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81">
@@ -1562,13 +1562,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="C81" t="n">
-        <v>42295.94538384951</v>
+        <v>-72.76369395125523</v>
       </c>
       <c r="D81" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
@@ -1576,13 +1576,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="C82" t="n">
-        <v>49706.13299594521</v>
+        <v>-100.4202954542371</v>
       </c>
       <c r="D82" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83">
@@ -1590,13 +1590,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="C83" t="n">
-        <v>62504.64295211825</v>
+        <v>-78.8021347721843</v>
       </c>
       <c r="D83" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84">
@@ -1604,13 +1604,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="C84" t="n">
-        <v>73080.10990618057</v>
+        <v>-48.32021431110194</v>
       </c>
       <c r="D84" t="n">
-        <v>198</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85">
@@ -1618,13 +1618,13 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="C85" t="n">
-        <v>76921.19217670443</v>
+        <v>-70.79772051807805</v>
       </c>
       <c r="D85" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86">
@@ -1632,13 +1632,13 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="C86" t="n">
-        <v>79523.23736103241</v>
+        <v>-85.54367078195138</v>
       </c>
       <c r="D86" t="n">
-        <v>168</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87">
@@ -1646,13 +1646,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="C87" t="n">
-        <v>74520.89384513265</v>
+        <v>-67.11050286754516</v>
       </c>
       <c r="D87" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88">
@@ -1660,10 +1660,10 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>186</v>
+        <v>118</v>
       </c>
       <c r="C88" t="n">
-        <v>56543.11597097181</v>
+        <v>-60.14110712215177</v>
       </c>
       <c r="D88" t="n">
         <v>132</v>
@@ -1674,13 +1674,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="C89" t="n">
-        <v>60264.55895876974</v>
+        <v>-98.68171502190981</v>
       </c>
       <c r="D89" t="n">
-        <v>156</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90">
@@ -1688,13 +1688,13 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="C90" t="n">
-        <v>55937.07972779789</v>
+        <v>-41.45730587366263</v>
       </c>
       <c r="D90" t="n">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91">
@@ -1702,13 +1702,13 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>192</v>
+        <v>120</v>
       </c>
       <c r="C91" t="n">
-        <v>51290.31002488216</v>
+        <v>-62.12970402611055</v>
       </c>
       <c r="D91" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92">
@@ -1716,13 +1716,13 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="C92" t="n">
-        <v>50205.15567190575</v>
+        <v>-73.81079936006229</v>
       </c>
       <c r="D92" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -1730,13 +1730,13 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="C93" t="n">
-        <v>77995.10747555031</v>
+        <v>-65.05227166309606</v>
       </c>
       <c r="D93" t="n">
-        <v>168</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -1744,13 +1744,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="C94" t="n">
-        <v>73512.69270700816</v>
+        <v>-51.20819776500922</v>
       </c>
       <c r="D94" t="n">
-        <v>170</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95">
@@ -1758,13 +1758,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="C95" t="n">
-        <v>79586.98116212587</v>
+        <v>-61.64011153471738</v>
       </c>
       <c r="D95" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96">
@@ -1772,13 +1772,13 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="C96" t="n">
-        <v>66719.35068203477</v>
+        <v>-65.34678359554098</v>
       </c>
       <c r="D96" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97">
@@ -1786,13 +1786,13 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="C97" t="n">
-        <v>64925.74044287002</v>
+        <v>-73.99994506604142</v>
       </c>
       <c r="D97" t="n">
-        <v>152</v>
+        <v>104</v>
       </c>
     </row>
     <row r="98">
@@ -1800,13 +1800,13 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="C98" t="n">
-        <v>52962.33294264981</v>
+        <v>-45.33632638757614</v>
       </c>
       <c r="D98" t="n">
-        <v>140</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99">
@@ -1814,13 +1814,13 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="C99" t="n">
-        <v>65064.42377950628</v>
+        <v>-67.04218872812874</v>
       </c>
       <c r="D99" t="n">
-        <v>146</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100">
@@ -1828,13 +1828,13 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="C100" t="n">
-        <v>57846.25782064528</v>
+        <v>-70.38559946813699</v>
       </c>
       <c r="D100" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101">
@@ -1842,13 +1842,13 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="C101" t="n">
-        <v>60049.58597889886</v>
+        <v>-66.63231266671374</v>
       </c>
       <c r="D101" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102">
@@ -1856,13 +1856,13 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="C102" t="n">
-        <v>47541.74365111606</v>
+        <v>-56.52568355094975</v>
       </c>
       <c r="D102" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103">
@@ -1870,13 +1870,13 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C103" t="n">
-        <v>46853.91121740303</v>
+        <v>-43.05486093324106</v>
       </c>
       <c r="D103" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="104">
@@ -1884,13 +1884,13 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="C104" t="n">
-        <v>46835.55264556551</v>
+        <v>-41.53582781542554</v>
       </c>
       <c r="D104" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105">
@@ -1898,13 +1898,13 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="C105" t="n">
-        <v>47842.19252290039</v>
+        <v>-59.79414021192899</v>
       </c>
       <c r="D105" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106">
@@ -1912,13 +1912,13 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="C106" t="n">
-        <v>73428.95366388741</v>
+        <v>-17.08184450184913</v>
       </c>
       <c r="D106" t="n">
-        <v>172</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107">
@@ -1926,13 +1926,13 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="C107" t="n">
-        <v>79532.40062873937</v>
+        <v>-28.09809231250753</v>
       </c>
       <c r="D107" t="n">
-        <v>196</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108">
@@ -1940,13 +1940,13 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C108" t="n">
-        <v>62865.55919066803</v>
+        <v>-46.8290629647439</v>
       </c>
       <c r="D108" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109">
@@ -1954,13 +1954,13 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C109" t="n">
-        <v>58326.0302603036</v>
+        <v>-45.67746549106359</v>
       </c>
       <c r="D109" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110">
@@ -1968,13 +1968,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="C110" t="n">
-        <v>45179.6439506225</v>
+        <v>-17.29699023647482</v>
       </c>
       <c r="D110" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="111">
@@ -1982,13 +1982,13 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="C111" t="n">
-        <v>71260.023127198</v>
+        <v>-32.7949009012109</v>
       </c>
       <c r="D111" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112">
@@ -1996,13 +1996,13 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="C112" t="n">
-        <v>82851.64598726628</v>
+        <v>-12.27060680071798</v>
       </c>
       <c r="D112" t="n">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113">
@@ -2010,13 +2010,13 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C113" t="n">
-        <v>72669.23205624124</v>
+        <v>-40.27687906298079</v>
       </c>
       <c r="D113" t="n">
-        <v>186</v>
+        <v>106</v>
       </c>
     </row>
     <row r="114">
@@ -2024,13 +2024,13 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="C114" t="n">
-        <v>78855.59700448724</v>
+        <v>-32.90887288633189</v>
       </c>
       <c r="D114" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
     </row>
     <row r="115">
@@ -2038,13 +2038,13 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C115" t="n">
-        <v>82279.66104760799</v>
+        <v>-8.400076171572922</v>
       </c>
       <c r="D115" t="n">
-        <v>188</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116">
@@ -2052,13 +2052,13 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="C116" t="n">
-        <v>84660.64974233083</v>
+        <v>-16.24602825591701</v>
       </c>
       <c r="D116" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="117">
@@ -2066,13 +2066,13 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="C117" t="n">
-        <v>79259.74312962014</v>
+        <v>-21.55318642969136</v>
       </c>
       <c r="D117" t="n">
-        <v>204</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118">
@@ -2080,13 +2080,13 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C118" t="n">
-        <v>74349.29313072115</v>
+        <v>-31.14460895900196</v>
       </c>
       <c r="D118" t="n">
-        <v>180</v>
+        <v>124</v>
       </c>
     </row>
     <row r="119">
@@ -2094,13 +2094,13 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="C119" t="n">
-        <v>72773.75759755482</v>
+        <v>-41.36587199733942</v>
       </c>
       <c r="D119" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
     </row>
     <row r="120">
@@ -2108,13 +2108,13 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="C120" t="n">
-        <v>57998.76168890648</v>
+        <v>-40.11180816273945</v>
       </c>
       <c r="D120" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="121">
@@ -2122,13 +2122,13 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="C121" t="n">
-        <v>51015.63746211833</v>
+        <v>-19.22974389362965</v>
       </c>
       <c r="D121" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="122">
@@ -2136,13 +2136,13 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="C122" t="n">
-        <v>56590.02257707659</v>
+        <v>-5.309879244181739</v>
       </c>
       <c r="D122" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="123">
@@ -2150,13 +2150,13 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C123" t="n">
-        <v>53766.66270172349</v>
+        <v>3.850956793561545</v>
       </c>
       <c r="D123" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="124">
@@ -2167,10 +2167,10 @@
         <v>202</v>
       </c>
       <c r="C124" t="n">
-        <v>56399.03466547443</v>
+        <v>-37.53357047612884</v>
       </c>
       <c r="D124" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="125">
@@ -2178,13 +2178,13 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C125" t="n">
-        <v>86899.51842582363</v>
+        <v>-29.10528521087248</v>
       </c>
       <c r="D125" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126">
@@ -2192,13 +2192,13 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C126" t="n">
-        <v>67324.8603298935</v>
+        <v>-10.63349244252708</v>
       </c>
       <c r="D126" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="127">
@@ -2206,13 +2206,13 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C127" t="n">
-        <v>44136.04864979489</v>
+        <v>3.365504040481553</v>
       </c>
       <c r="D127" t="n">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="128">
@@ -2220,13 +2220,13 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="C128" t="n">
-        <v>64812.26520106288</v>
+        <v>-9.641934395119572</v>
       </c>
       <c r="D128" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129">
@@ -2234,13 +2234,13 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="C129" t="n">
-        <v>79266.60854496562</v>
+        <v>-31.78411167715448</v>
       </c>
       <c r="D129" t="n">
-        <v>208</v>
+        <v>164</v>
       </c>
     </row>
     <row r="130">
@@ -2251,10 +2251,10 @@
         <v>212</v>
       </c>
       <c r="C130" t="n">
-        <v>87830.4596819891</v>
+        <v>-37.26677776441346</v>
       </c>
       <c r="D130" t="n">
-        <v>214</v>
+        <v>138</v>
       </c>
     </row>
     <row r="131">
@@ -2262,13 +2262,13 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C131" t="n">
-        <v>84009.31408715993</v>
+        <v>-13.06310143664813</v>
       </c>
       <c r="D131" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="132">
@@ -2276,13 +2276,13 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C132" t="n">
-        <v>83301.1801570157</v>
+        <v>12.88969637955859</v>
       </c>
       <c r="D132" t="n">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C133" t="n">
-        <v>85884.15045233841</v>
+        <v>28.70291010617359</v>
       </c>
       <c r="D133" t="n">
-        <v>214</v>
+        <v>182</v>
       </c>
     </row>
     <row r="134">
@@ -2304,13 +2304,13 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C134" t="n">
-        <v>83917.847535892</v>
+        <v>-10.52575925870336</v>
       </c>
       <c r="D134" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135">
@@ -2318,13 +2318,13 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C135" t="n">
-        <v>74791.813665649</v>
+        <v>7.361106040140204</v>
       </c>
       <c r="D135" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="136">
@@ -2332,13 +2332,13 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C136" t="n">
-        <v>72099.80181025041</v>
+        <v>4.930229639681502</v>
       </c>
       <c r="D136" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="137">
@@ -2346,13 +2346,13 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C137" t="n">
-        <v>65919.55633852679</v>
+        <v>16.52391155700159</v>
       </c>
       <c r="D137" t="n">
-        <v>200</v>
+        <v>112</v>
       </c>
     </row>
     <row r="138">
@@ -2360,13 +2360,13 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C138" t="n">
-        <v>56458.13329655265</v>
+        <v>23.10963607860094</v>
       </c>
       <c r="D138" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
     </row>
     <row r="139">
@@ -2374,13 +2374,13 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C139" t="n">
-        <v>63425.58288605147</v>
+        <v>25.42295558357023</v>
       </c>
       <c r="D139" t="n">
-        <v>160</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140">
@@ -2388,13 +2388,13 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C140" t="n">
-        <v>67076.6662204858</v>
+        <v>24.55592470011661</v>
       </c>
       <c r="D140" t="n">
-        <v>198</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141">
@@ -2402,13 +2402,13 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C141" t="n">
-        <v>48299.53776052378</v>
+        <v>25.19890487750684</v>
       </c>
       <c r="D141" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142">
@@ -2416,13 +2416,13 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C142" t="n">
-        <v>71070.48747092615</v>
+        <v>23.75669924272592</v>
       </c>
       <c r="D142" t="n">
-        <v>184</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143">
@@ -2430,13 +2430,13 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C143" t="n">
-        <v>57600.43472977965</v>
+        <v>17.25948473058595</v>
       </c>
       <c r="D143" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144">
@@ -2444,13 +2444,13 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C144" t="n">
-        <v>48444.30829324971</v>
+        <v>21.32494022275203</v>
       </c>
       <c r="D144" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145">
@@ -2458,13 +2458,13 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C145" t="n">
-        <v>70850.16068599829</v>
+        <v>35.13598654425731</v>
       </c>
       <c r="D145" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146">
@@ -2472,13 +2472,13 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C146" t="n">
-        <v>57953.00436728916</v>
+        <v>30.7566538215685</v>
       </c>
       <c r="D146" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
     </row>
     <row r="147">
@@ -2486,13 +2486,13 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C147" t="n">
-        <v>69792.77109605908</v>
+        <v>24.91410829702653</v>
       </c>
       <c r="D147" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148">
@@ -2503,10 +2503,10 @@
         <v>228</v>
       </c>
       <c r="C148" t="n">
-        <v>48504.37055804848</v>
+        <v>33.75505424418945</v>
       </c>
       <c r="D148" t="n">
-        <v>140</v>
+        <v>216</v>
       </c>
     </row>
     <row r="149">
@@ -2514,13 +2514,13 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C149" t="n">
-        <v>64195.65247136655</v>
+        <v>37.87673652999906</v>
       </c>
       <c r="D149" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150">
@@ -2528,13 +2528,13 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C150" t="n">
-        <v>45223.57865287762</v>
+        <v>34.80826123350013</v>
       </c>
       <c r="D150" t="n">
-        <v>162</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151">
@@ -2542,1413 +2542,13 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C151" t="n">
-        <v>73033.67413671204</v>
+        <v>36.42563536795609</v>
       </c>
       <c r="D151" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="n">
         <v>224</v>
-      </c>
-      <c r="C152" t="n">
-        <v>80014.68782592997</v>
-      </c>
-      <c r="D152" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="n">
-        <v>222</v>
-      </c>
-      <c r="C153" t="n">
-        <v>87537.36795652217</v>
-      </c>
-      <c r="D153" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="n">
-        <v>220</v>
-      </c>
-      <c r="C154" t="n">
-        <v>87166.56480157151</v>
-      </c>
-      <c r="D154" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="n">
-        <v>228</v>
-      </c>
-      <c r="C155" t="n">
-        <v>86965.4524801744</v>
-      </c>
-      <c r="D155" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="n">
-        <v>226</v>
-      </c>
-      <c r="C156" t="n">
-        <v>86750.9694996429</v>
-      </c>
-      <c r="D156" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="n">
-        <v>226</v>
-      </c>
-      <c r="C157" t="n">
-        <v>84569.21914463911</v>
-      </c>
-      <c r="D157" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" t="n">
-        <v>220</v>
-      </c>
-      <c r="C158" t="n">
-        <v>69860.88872224733</v>
-      </c>
-      <c r="D158" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>157</v>
-      </c>
-      <c r="B159" t="n">
-        <v>226</v>
-      </c>
-      <c r="C159" t="n">
-        <v>58539.5012788457</v>
-      </c>
-      <c r="D159" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>158</v>
-      </c>
-      <c r="B160" t="n">
-        <v>220</v>
-      </c>
-      <c r="C160" t="n">
-        <v>63682.99157438862</v>
-      </c>
-      <c r="D160" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>159</v>
-      </c>
-      <c r="B161" t="n">
-        <v>232</v>
-      </c>
-      <c r="C161" t="n">
-        <v>50918.26692829143</v>
-      </c>
-      <c r="D161" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>160</v>
-      </c>
-      <c r="B162" t="n">
-        <v>230</v>
-      </c>
-      <c r="C162" t="n">
-        <v>63206.78776492771</v>
-      </c>
-      <c r="D162" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>161</v>
-      </c>
-      <c r="B163" t="n">
-        <v>224</v>
-      </c>
-      <c r="C163" t="n">
-        <v>49190.77353549721</v>
-      </c>
-      <c r="D163" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>162</v>
-      </c>
-      <c r="B164" t="n">
-        <v>232</v>
-      </c>
-      <c r="C164" t="n">
-        <v>62734.18234804084</v>
-      </c>
-      <c r="D164" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>163</v>
-      </c>
-      <c r="B165" t="n">
-        <v>226</v>
-      </c>
-      <c r="C165" t="n">
-        <v>73943.55366278643</v>
-      </c>
-      <c r="D165" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>164</v>
-      </c>
-      <c r="B166" t="n">
-        <v>226</v>
-      </c>
-      <c r="C166" t="n">
-        <v>57919.79020546682</v>
-      </c>
-      <c r="D166" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>165</v>
-      </c>
-      <c r="B167" t="n">
-        <v>224</v>
-      </c>
-      <c r="C167" t="n">
-        <v>60391.59472823827</v>
-      </c>
-      <c r="D167" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>166</v>
-      </c>
-      <c r="B168" t="n">
-        <v>234</v>
-      </c>
-      <c r="C168" t="n">
-        <v>48283.56376783589</v>
-      </c>
-      <c r="D168" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>167</v>
-      </c>
-      <c r="B169" t="n">
-        <v>226</v>
-      </c>
-      <c r="C169" t="n">
-        <v>53900.7628193241</v>
-      </c>
-      <c r="D169" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>168</v>
-      </c>
-      <c r="B170" t="n">
-        <v>230</v>
-      </c>
-      <c r="C170" t="n">
-        <v>49553.16573246764</v>
-      </c>
-      <c r="D170" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>169</v>
-      </c>
-      <c r="B171" t="n">
-        <v>228</v>
-      </c>
-      <c r="C171" t="n">
-        <v>61116.35353087309</v>
-      </c>
-      <c r="D171" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>170</v>
-      </c>
-      <c r="B172" t="n">
-        <v>226</v>
-      </c>
-      <c r="C172" t="n">
-        <v>46920.3740103036</v>
-      </c>
-      <c r="D172" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>171</v>
-      </c>
-      <c r="B173" t="n">
-        <v>226</v>
-      </c>
-      <c r="C173" t="n">
-        <v>52310.07758126032</v>
-      </c>
-      <c r="D173" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>172</v>
-      </c>
-      <c r="B174" t="n">
-        <v>232</v>
-      </c>
-      <c r="C174" t="n">
-        <v>51698.40359407732</v>
-      </c>
-      <c r="D174" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>173</v>
-      </c>
-      <c r="B175" t="n">
-        <v>234</v>
-      </c>
-      <c r="C175" t="n">
-        <v>83427.53979606659</v>
-      </c>
-      <c r="D175" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>174</v>
-      </c>
-      <c r="B176" t="n">
-        <v>230</v>
-      </c>
-      <c r="C176" t="n">
-        <v>86788.09426554265</v>
-      </c>
-      <c r="D176" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>175</v>
-      </c>
-      <c r="B177" t="n">
-        <v>226</v>
-      </c>
-      <c r="C177" t="n">
-        <v>86874.88009821542</v>
-      </c>
-      <c r="D177" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>176</v>
-      </c>
-      <c r="B178" t="n">
-        <v>230</v>
-      </c>
-      <c r="C178" t="n">
-        <v>88358.77658715997</v>
-      </c>
-      <c r="D178" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>177</v>
-      </c>
-      <c r="B179" t="n">
-        <v>226</v>
-      </c>
-      <c r="C179" t="n">
-        <v>85658.52283760039</v>
-      </c>
-      <c r="D179" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>178</v>
-      </c>
-      <c r="B180" t="n">
-        <v>236</v>
-      </c>
-      <c r="C180" t="n">
-        <v>89582.57456372793</v>
-      </c>
-      <c r="D180" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>179</v>
-      </c>
-      <c r="B181" t="n">
-        <v>230</v>
-      </c>
-      <c r="C181" t="n">
-        <v>87365.8115867196</v>
-      </c>
-      <c r="D181" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>180</v>
-      </c>
-      <c r="B182" t="n">
-        <v>230</v>
-      </c>
-      <c r="C182" t="n">
-        <v>87205.20069414556</v>
-      </c>
-      <c r="D182" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>181</v>
-      </c>
-      <c r="B183" t="n">
-        <v>232</v>
-      </c>
-      <c r="C183" t="n">
-        <v>86502.64581306734</v>
-      </c>
-      <c r="D183" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>182</v>
-      </c>
-      <c r="B184" t="n">
-        <v>228</v>
-      </c>
-      <c r="C184" t="n">
-        <v>87750.76140481375</v>
-      </c>
-      <c r="D184" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>183</v>
-      </c>
-      <c r="B185" t="n">
-        <v>232</v>
-      </c>
-      <c r="C185" t="n">
-        <v>89597.76230113112</v>
-      </c>
-      <c r="D185" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>184</v>
-      </c>
-      <c r="B186" t="n">
-        <v>230</v>
-      </c>
-      <c r="C186" t="n">
-        <v>88976.26444436572</v>
-      </c>
-      <c r="D186" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>185</v>
-      </c>
-      <c r="B187" t="n">
-        <v>226</v>
-      </c>
-      <c r="C187" t="n">
-        <v>87969.95480091093</v>
-      </c>
-      <c r="D187" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>186</v>
-      </c>
-      <c r="B188" t="n">
-        <v>236</v>
-      </c>
-      <c r="C188" t="n">
-        <v>89129.34831460874</v>
-      </c>
-      <c r="D188" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>187</v>
-      </c>
-      <c r="B189" t="n">
-        <v>234</v>
-      </c>
-      <c r="C189" t="n">
-        <v>88975.12069436572</v>
-      </c>
-      <c r="D189" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>188</v>
-      </c>
-      <c r="B190" t="n">
-        <v>232</v>
-      </c>
-      <c r="C190" t="n">
-        <v>88298.43116322687</v>
-      </c>
-      <c r="D190" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>189</v>
-      </c>
-      <c r="B191" t="n">
-        <v>230</v>
-      </c>
-      <c r="C191" t="n">
-        <v>89104.38783693977</v>
-      </c>
-      <c r="D191" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>190</v>
-      </c>
-      <c r="B192" t="n">
-        <v>228</v>
-      </c>
-      <c r="C192" t="n">
-        <v>88341.2339087773</v>
-      </c>
-      <c r="D192" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>191</v>
-      </c>
-      <c r="B193" t="n">
-        <v>232</v>
-      </c>
-      <c r="C193" t="n">
-        <v>88435.09265811669</v>
-      </c>
-      <c r="D193" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>192</v>
-      </c>
-      <c r="B194" t="n">
-        <v>224</v>
-      </c>
-      <c r="C194" t="n">
-        <v>87259.14396823818</v>
-      </c>
-      <c r="D194" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>193</v>
-      </c>
-      <c r="B195" t="n">
-        <v>236</v>
-      </c>
-      <c r="C195" t="n">
-        <v>82576.62009535285</v>
-      </c>
-      <c r="D195" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>194</v>
-      </c>
-      <c r="B196" t="n">
-        <v>230</v>
-      </c>
-      <c r="C196" t="n">
-        <v>61521.53341415325</v>
-      </c>
-      <c r="D196" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>195</v>
-      </c>
-      <c r="B197" t="n">
-        <v>232</v>
-      </c>
-      <c r="C197" t="n">
-        <v>83225.20194106277</v>
-      </c>
-      <c r="D197" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>196</v>
-      </c>
-      <c r="B198" t="n">
-        <v>236</v>
-      </c>
-      <c r="C198" t="n">
-        <v>89283.64849211059</v>
-      </c>
-      <c r="D198" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>197</v>
-      </c>
-      <c r="B199" t="n">
-        <v>232</v>
-      </c>
-      <c r="C199" t="n">
-        <v>79243.63479738777</v>
-      </c>
-      <c r="D199" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>198</v>
-      </c>
-      <c r="B200" t="n">
-        <v>230</v>
-      </c>
-      <c r="C200" t="n">
-        <v>61036.66020458602</v>
-      </c>
-      <c r="D200" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>199</v>
-      </c>
-      <c r="B201" t="n">
-        <v>234</v>
-      </c>
-      <c r="C201" t="n">
-        <v>65074.29193159439</v>
-      </c>
-      <c r="D201" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>200</v>
-      </c>
-      <c r="B202" t="n">
-        <v>230</v>
-      </c>
-      <c r="C202" t="n">
-        <v>60050.68966635523</v>
-      </c>
-      <c r="D202" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>201</v>
-      </c>
-      <c r="B203" t="n">
-        <v>226</v>
-      </c>
-      <c r="C203" t="n">
-        <v>60770.43330095656</v>
-      </c>
-      <c r="D203" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>202</v>
-      </c>
-      <c r="B204" t="n">
-        <v>230</v>
-      </c>
-      <c r="C204" t="n">
-        <v>75522.2843170765</v>
-      </c>
-      <c r="D204" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>203</v>
-      </c>
-      <c r="B205" t="n">
-        <v>236</v>
-      </c>
-      <c r="C205" t="n">
-        <v>82119.64771449484</v>
-      </c>
-      <c r="D205" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>204</v>
-      </c>
-      <c r="B206" t="n">
-        <v>236</v>
-      </c>
-      <c r="C206" t="n">
-        <v>47742.97656954431</v>
-      </c>
-      <c r="D206" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>205</v>
-      </c>
-      <c r="B207" t="n">
-        <v>234</v>
-      </c>
-      <c r="C207" t="n">
-        <v>64974.54103857998</v>
-      </c>
-      <c r="D207" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>206</v>
-      </c>
-      <c r="B208" t="n">
-        <v>228</v>
-      </c>
-      <c r="C208" t="n">
-        <v>73340.64824259664</v>
-      </c>
-      <c r="D208" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>207</v>
-      </c>
-      <c r="B209" t="n">
-        <v>238</v>
-      </c>
-      <c r="C209" t="n">
-        <v>57739.71812191328</v>
-      </c>
-      <c r="D209" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>208</v>
-      </c>
-      <c r="B210" t="n">
-        <v>234</v>
-      </c>
-      <c r="C210" t="n">
-        <v>74361.2920591038</v>
-      </c>
-      <c r="D210" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>209</v>
-      </c>
-      <c r="B211" t="n">
-        <v>232</v>
-      </c>
-      <c r="C211" t="n">
-        <v>88743.01176532246</v>
-      </c>
-      <c r="D211" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>210</v>
-      </c>
-      <c r="B212" t="n">
-        <v>236</v>
-      </c>
-      <c r="C212" t="n">
-        <v>88333.07313490481</v>
-      </c>
-      <c r="D212" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>211</v>
-      </c>
-      <c r="B213" t="n">
-        <v>230</v>
-      </c>
-      <c r="C213" t="n">
-        <v>88894.04134909617</v>
-      </c>
-      <c r="D213" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>212</v>
-      </c>
-      <c r="B214" t="n">
-        <v>234</v>
-      </c>
-      <c r="C214" t="n">
-        <v>88561.03998017438</v>
-      </c>
-      <c r="D214" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>213</v>
-      </c>
-      <c r="B215" t="n">
-        <v>230</v>
-      </c>
-      <c r="C215" t="n">
-        <v>88917.21801532248</v>
-      </c>
-      <c r="D215" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>214</v>
-      </c>
-      <c r="B216" t="n">
-        <v>234</v>
-      </c>
-      <c r="C216" t="n">
-        <v>89954.9408132875</v>
-      </c>
-      <c r="D216" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>215</v>
-      </c>
-      <c r="B217" t="n">
-        <v>234</v>
-      </c>
-      <c r="C217" t="n">
-        <v>87815.52456262698</v>
-      </c>
-      <c r="D217" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>216</v>
-      </c>
-      <c r="B218" t="n">
-        <v>236</v>
-      </c>
-      <c r="C218" t="n">
-        <v>89953.59224211064</v>
-      </c>
-      <c r="D218" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>217</v>
-      </c>
-      <c r="B219" t="n">
-        <v>238</v>
-      </c>
-      <c r="C219" t="n">
-        <v>87521.4766470613</v>
-      </c>
-      <c r="D219" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>218</v>
-      </c>
-      <c r="B220" t="n">
-        <v>230</v>
-      </c>
-      <c r="C220" t="n">
-        <v>88450.98253985551</v>
-      </c>
-      <c r="D220" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>219</v>
-      </c>
-      <c r="B221" t="n">
-        <v>232</v>
-      </c>
-      <c r="C221" t="n">
-        <v>65176.36258742582</v>
-      </c>
-      <c r="D221" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>220</v>
-      </c>
-      <c r="B222" t="n">
-        <v>236</v>
-      </c>
-      <c r="C222" t="n">
-        <v>63741.9581212527</v>
-      </c>
-      <c r="D222" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>221</v>
-      </c>
-      <c r="B223" t="n">
-        <v>230</v>
-      </c>
-      <c r="C223" t="n">
-        <v>64992.96479386467</v>
-      </c>
-      <c r="D223" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
-        <v>222</v>
-      </c>
-      <c r="B224" t="n">
-        <v>238</v>
-      </c>
-      <c r="C224" t="n">
-        <v>79336.48991036431</v>
-      </c>
-      <c r="D224" t="n">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
-        <v>223</v>
-      </c>
-      <c r="B225" t="n">
-        <v>238</v>
-      </c>
-      <c r="C225" t="n">
-        <v>88986.78361037181</v>
-      </c>
-      <c r="D225" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>224</v>
-      </c>
-      <c r="B226" t="n">
-        <v>230</v>
-      </c>
-      <c r="C226" t="n">
-        <v>89788.4646229686</v>
-      </c>
-      <c r="D226" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>225</v>
-      </c>
-      <c r="B227" t="n">
-        <v>232</v>
-      </c>
-      <c r="C227" t="n">
-        <v>88759.84426554266</v>
-      </c>
-      <c r="D227" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
-        <v>226</v>
-      </c>
-      <c r="B228" t="n">
-        <v>234</v>
-      </c>
-      <c r="C228" t="n">
-        <v>89172.4174795138</v>
-      </c>
-      <c r="D228" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
-        <v>227</v>
-      </c>
-      <c r="B229" t="n">
-        <v>234</v>
-      </c>
-      <c r="C229" t="n">
-        <v>88627.95104804836</v>
-      </c>
-      <c r="D229" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>228</v>
-      </c>
-      <c r="B230" t="n">
-        <v>234</v>
-      </c>
-      <c r="C230" t="n">
-        <v>90139.91753501115</v>
-      </c>
-      <c r="D230" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>229</v>
-      </c>
-      <c r="B231" t="n">
-        <v>238</v>
-      </c>
-      <c r="C231" t="n">
-        <v>89437.94509865581</v>
-      </c>
-      <c r="D231" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>230</v>
-      </c>
-      <c r="B232" t="n">
-        <v>228</v>
-      </c>
-      <c r="C232" t="n">
-        <v>88848.66581328752</v>
-      </c>
-      <c r="D232" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>231</v>
-      </c>
-      <c r="B233" t="n">
-        <v>234</v>
-      </c>
-      <c r="C233" t="n">
-        <v>89058.55670564137</v>
-      </c>
-      <c r="D233" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>232</v>
-      </c>
-      <c r="B234" t="n">
-        <v>234</v>
-      </c>
-      <c r="C234" t="n">
-        <v>89559.09081328753</v>
-      </c>
-      <c r="D234" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
-        <v>233</v>
-      </c>
-      <c r="B235" t="n">
-        <v>234</v>
-      </c>
-      <c r="C235" t="n">
-        <v>89266.74253941511</v>
-      </c>
-      <c r="D235" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
-        <v>234</v>
-      </c>
-      <c r="B236" t="n">
-        <v>238</v>
-      </c>
-      <c r="C236" t="n">
-        <v>89959.72968220933</v>
-      </c>
-      <c r="D236" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>235</v>
-      </c>
-      <c r="B237" t="n">
-        <v>238</v>
-      </c>
-      <c r="C237" t="n">
-        <v>89120.03158693979</v>
-      </c>
-      <c r="D237" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
-        <v>236</v>
-      </c>
-      <c r="B238" t="n">
-        <v>232</v>
-      </c>
-      <c r="C238" t="n">
-        <v>88580.97849189043</v>
-      </c>
-      <c r="D238" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
-        <v>237</v>
-      </c>
-      <c r="B239" t="n">
-        <v>230</v>
-      </c>
-      <c r="C239" t="n">
-        <v>88126.68253435059</v>
-      </c>
-      <c r="D239" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
-        <v>238</v>
-      </c>
-      <c r="B240" t="n">
-        <v>236</v>
-      </c>
-      <c r="C240" t="n">
-        <v>89236.02730157152</v>
-      </c>
-      <c r="D240" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
-        <v>239</v>
-      </c>
-      <c r="B241" t="n">
-        <v>238</v>
-      </c>
-      <c r="C241" t="n">
-        <v>88708.3030747834</v>
-      </c>
-      <c r="D241" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>240</v>
-      </c>
-      <c r="B242" t="n">
-        <v>234</v>
-      </c>
-      <c r="C242" t="n">
-        <v>89959.72968220933</v>
-      </c>
-      <c r="D242" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
-        <v>241</v>
-      </c>
-      <c r="B243" t="n">
-        <v>238</v>
-      </c>
-      <c r="C243" t="n">
-        <v>89629.77224189037</v>
-      </c>
-      <c r="D243" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>242</v>
-      </c>
-      <c r="B244" t="n">
-        <v>234</v>
-      </c>
-      <c r="C244" t="n">
-        <v>89669.18908715995</v>
-      </c>
-      <c r="D244" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>243</v>
-      </c>
-      <c r="B245" t="n">
-        <v>238</v>
-      </c>
-      <c r="C245" t="n">
-        <v>89511.52170608174</v>
-      </c>
-      <c r="D245" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
-        <v>244</v>
-      </c>
-      <c r="B246" t="n">
-        <v>238</v>
-      </c>
-      <c r="C246" t="n">
-        <v>89720.46247973402</v>
-      </c>
-      <c r="D246" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
-        <v>245</v>
-      </c>
-      <c r="B247" t="n">
-        <v>232</v>
-      </c>
-      <c r="C247" t="n">
-        <v>89319.88194414556</v>
-      </c>
-      <c r="D247" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>246</v>
-      </c>
-      <c r="B248" t="n">
-        <v>234</v>
-      </c>
-      <c r="C248" t="n">
-        <v>89528.44742049331</v>
-      </c>
-      <c r="D248" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>247</v>
-      </c>
-      <c r="B249" t="n">
-        <v>232</v>
-      </c>
-      <c r="C249" t="n">
-        <v>89643.15992049329</v>
-      </c>
-      <c r="D249" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>248</v>
-      </c>
-      <c r="B250" t="n">
-        <v>238</v>
-      </c>
-      <c r="C250" t="n">
-        <v>88335.82676576286</v>
-      </c>
-      <c r="D250" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>249</v>
-      </c>
-      <c r="B251" t="n">
-        <v>234</v>
-      </c>
-      <c r="C251" t="n">
-        <v>89512.47527373556</v>
-      </c>
-      <c r="D251" t="n">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3989,13 +2589,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="D2" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -4005,13 +2605,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>187.136</v>
+        <v>115.6533333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>65612.33051372593</v>
+        <v>-73.52268374533944</v>
       </c>
       <c r="D3" t="n">
-        <v>160.72</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="4">
@@ -4021,13 +2621,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58.61224346787405</v>
+        <v>70.3615768646598</v>
       </c>
       <c r="C4" t="n">
-        <v>17574.14601289595</v>
+        <v>55.56145410155364</v>
       </c>
       <c r="D4" t="n">
-        <v>62.13156141362281</v>
+        <v>63.8434620850617</v>
       </c>
     </row>
     <row r="5">
@@ -4037,13 +2637,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2</v>
+        <v>-26</v>
       </c>
       <c r="C5" t="n">
-        <v>28552.39108416848</v>
+        <v>-169.0617039009178</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="6">
@@ -4053,13 +2653,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>49591.40754833703</v>
+        <v>-122.7367103088527</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -4069,13 +2669,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>63036.17347779787</v>
+        <v>-83.64847877114642</v>
       </c>
       <c r="D7" t="n">
-        <v>168</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -4085,13 +2685,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>178.5</v>
       </c>
       <c r="C8" t="n">
-        <v>85827.7435486539</v>
+        <v>-32.82339389749115</v>
       </c>
       <c r="D8" t="n">
-        <v>217.5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
@@ -4104,10 +2704,10 @@
         <v>238</v>
       </c>
       <c r="C9" t="n">
-        <v>90139.91753501115</v>
+        <v>37.87673652999906</v>
       </c>
       <c r="D9" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
         <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>-56</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +465,7 @@
         <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>-60</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>-66</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +487,7 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>-72</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>-40</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>-52</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>190</v>
       </c>
       <c r="C9" t="n">
-        <v>-40</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         <v>190</v>
       </c>
       <c r="C10" t="n">
-        <v>-48</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>190</v>
       </c>
       <c r="C11" t="n">
-        <v>-66</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +564,7 @@
         <v>190</v>
       </c>
       <c r="C12" t="n">
-        <v>-48</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="13">
@@ -575,7 +575,7 @@
         <v>190</v>
       </c>
       <c r="C13" t="n">
-        <v>-52</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>190</v>
       </c>
       <c r="C14" t="n">
-        <v>-46</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         <v>190</v>
       </c>
       <c r="C15" t="n">
-        <v>-58</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16">
@@ -608,7 +608,7 @@
         <v>190</v>
       </c>
       <c r="C16" t="n">
-        <v>-36</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +619,7 @@
         <v>190</v>
       </c>
       <c r="C17" t="n">
-        <v>-20</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         <v>190</v>
       </c>
       <c r="C18" t="n">
-        <v>-66</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>190</v>
       </c>
       <c r="C19" t="n">
-        <v>-54</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="20">
@@ -652,7 +652,7 @@
         <v>190</v>
       </c>
       <c r="C20" t="n">
-        <v>-40</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="21">
@@ -663,7 +663,7 @@
         <v>190</v>
       </c>
       <c r="C21" t="n">
-        <v>-30</v>
+        <v>-76</v>
       </c>
     </row>
     <row r="22">
@@ -674,7 +674,7 @@
         <v>190</v>
       </c>
       <c r="C22" t="n">
-        <v>-52</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="23">
@@ -685,7 +685,7 @@
         <v>190</v>
       </c>
       <c r="C23" t="n">
-        <v>-22</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +696,7 @@
         <v>190</v>
       </c>
       <c r="C24" t="n">
-        <v>-44</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="25">
@@ -707,7 +707,7 @@
         <v>190</v>
       </c>
       <c r="C25" t="n">
-        <v>-12</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         <v>190</v>
       </c>
       <c r="C26" t="n">
-        <v>-34</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="27">
@@ -729,7 +729,7 @@
         <v>190</v>
       </c>
       <c r="C27" t="n">
-        <v>-28</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="28">
@@ -740,7 +740,7 @@
         <v>190</v>
       </c>
       <c r="C28" t="n">
-        <v>-56</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +751,7 @@
         <v>190</v>
       </c>
       <c r="C29" t="n">
-        <v>-44</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30">
@@ -762,7 +762,7 @@
         <v>190</v>
       </c>
       <c r="C30" t="n">
-        <v>-30</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="31">
@@ -773,7 +773,7 @@
         <v>190</v>
       </c>
       <c r="C31" t="n">
-        <v>-50</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="32">
@@ -784,7 +784,7 @@
         <v>190</v>
       </c>
       <c r="C32" t="n">
-        <v>-32</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="33">
@@ -795,7 +795,7 @@
         <v>190</v>
       </c>
       <c r="C33" t="n">
-        <v>-32</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="34">
@@ -806,7 +806,7 @@
         <v>190</v>
       </c>
       <c r="C34" t="n">
-        <v>-34</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="35">
@@ -817,7 +817,7 @@
         <v>190</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>190</v>
       </c>
       <c r="C36" t="n">
-        <v>-56</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="37">
@@ -839,7 +839,7 @@
         <v>190</v>
       </c>
       <c r="C37" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="38">
@@ -850,7 +850,7 @@
         <v>190</v>
       </c>
       <c r="C38" t="n">
-        <v>-28</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="39">
@@ -861,7 +861,7 @@
         <v>190</v>
       </c>
       <c r="C39" t="n">
-        <v>-4</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="40">
@@ -872,7 +872,7 @@
         <v>190</v>
       </c>
       <c r="C40" t="n">
-        <v>-6</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="41">
@@ -883,7 +883,7 @@
         <v>190</v>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="42">
@@ -894,7 +894,7 @@
         <v>190</v>
       </c>
       <c r="C42" t="n">
-        <v>-4</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="43">
@@ -905,7 +905,7 @@
         <v>190</v>
       </c>
       <c r="C43" t="n">
-        <v>-2</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="44">
@@ -916,7 +916,7 @@
         <v>190</v>
       </c>
       <c r="C44" t="n">
-        <v>-26</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="45">
@@ -927,7 +927,7 @@
         <v>190</v>
       </c>
       <c r="C45" t="n">
-        <v>-10</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="46">
@@ -938,7 +938,7 @@
         <v>190</v>
       </c>
       <c r="C46" t="n">
-        <v>-24</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="47">
@@ -949,7 +949,7 @@
         <v>190</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="48">
@@ -960,7 +960,7 @@
         <v>190</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="49">
@@ -971,7 +971,7 @@
         <v>190</v>
       </c>
       <c r="C49" t="n">
-        <v>-2</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="50">
@@ -982,7 +982,7 @@
         <v>190</v>
       </c>
       <c r="C50" t="n">
-        <v>-10</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +993,7 @@
         <v>190</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="52">
@@ -1004,7 +1004,7 @@
         <v>190</v>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="53">
@@ -1015,7 +1015,7 @@
         <v>190</v>
       </c>
       <c r="C53" t="n">
-        <v>-2</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="54">
@@ -1026,7 +1026,7 @@
         <v>190</v>
       </c>
       <c r="C54" t="n">
-        <v>16</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="55">
@@ -1037,7 +1037,7 @@
         <v>190</v>
       </c>
       <c r="C55" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="56">
@@ -1048,7 +1048,7 @@
         <v>190</v>
       </c>
       <c r="C56" t="n">
-        <v>-6</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="57">
@@ -1059,7 +1059,7 @@
         <v>190</v>
       </c>
       <c r="C57" t="n">
-        <v>16</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="58">
@@ -1070,7 +1070,7 @@
         <v>190</v>
       </c>
       <c r="C58" t="n">
-        <v>22</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="59">
@@ -1081,7 +1081,7 @@
         <v>190</v>
       </c>
       <c r="C59" t="n">
-        <v>20</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="60">
@@ -1092,7 +1092,7 @@
         <v>190</v>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="61">
@@ -1103,7 +1103,7 @@
         <v>190</v>
       </c>
       <c r="C61" t="n">
-        <v>30</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="62">
@@ -1114,7 +1114,7 @@
         <v>190</v>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="63">
@@ -1125,7 +1125,7 @@
         <v>190</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="64">
@@ -1136,7 +1136,7 @@
         <v>190</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="65">
@@ -1147,7 +1147,7 @@
         <v>190</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="66">
@@ -1158,7 +1158,7 @@
         <v>190</v>
       </c>
       <c r="C66" t="n">
-        <v>26</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="67">
@@ -1169,7 +1169,7 @@
         <v>190</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="68">
@@ -1180,7 +1180,7 @@
         <v>190</v>
       </c>
       <c r="C68" t="n">
-        <v>14</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="69">
@@ -1191,7 +1191,7 @@
         <v>190</v>
       </c>
       <c r="C69" t="n">
-        <v>14</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="70">
@@ -1202,7 +1202,7 @@
         <v>190</v>
       </c>
       <c r="C70" t="n">
-        <v>16</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="71">
@@ -1213,7 +1213,7 @@
         <v>190</v>
       </c>
       <c r="C71" t="n">
-        <v>46</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="72">
@@ -1224,7 +1224,7 @@
         <v>190</v>
       </c>
       <c r="C72" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="73">
@@ -1235,7 +1235,7 @@
         <v>190</v>
       </c>
       <c r="C73" t="n">
-        <v>26</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="74">
@@ -1246,7 +1246,7 @@
         <v>190</v>
       </c>
       <c r="C74" t="n">
-        <v>16</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="75">
@@ -1257,7 +1257,7 @@
         <v>190</v>
       </c>
       <c r="C75" t="n">
-        <v>36</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="76">
@@ -1268,7 +1268,7 @@
         <v>190</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="77">
@@ -1279,7 +1279,7 @@
         <v>190</v>
       </c>
       <c r="C77" t="n">
-        <v>16</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="78">
@@ -1290,7 +1290,7 @@
         <v>190</v>
       </c>
       <c r="C78" t="n">
-        <v>50</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="79">
@@ -1301,7 +1301,7 @@
         <v>190</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="80">
@@ -1312,7 +1312,7 @@
         <v>190</v>
       </c>
       <c r="C80" t="n">
-        <v>20</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="81">
@@ -1323,7 +1323,7 @@
         <v>190</v>
       </c>
       <c r="C81" t="n">
-        <v>46</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="82">
@@ -1334,7 +1334,7 @@
         <v>190</v>
       </c>
       <c r="C82" t="n">
-        <v>32</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="83">
@@ -1345,7 +1345,7 @@
         <v>190</v>
       </c>
       <c r="C83" t="n">
-        <v>36</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="84">
@@ -1356,7 +1356,7 @@
         <v>190</v>
       </c>
       <c r="C84" t="n">
-        <v>62</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="85">
@@ -1367,7 +1367,7 @@
         <v>190</v>
       </c>
       <c r="C85" t="n">
-        <v>32</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="86">
@@ -1378,7 +1378,7 @@
         <v>190</v>
       </c>
       <c r="C86" t="n">
-        <v>32</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="87">
@@ -1389,7 +1389,7 @@
         <v>190</v>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -1400,7 +1400,7 @@
         <v>190</v>
       </c>
       <c r="C88" t="n">
-        <v>42</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="89">
@@ -1411,7 +1411,7 @@
         <v>190</v>
       </c>
       <c r="C89" t="n">
-        <v>54</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="90">
@@ -1422,7 +1422,7 @@
         <v>190</v>
       </c>
       <c r="C90" t="n">
-        <v>42</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="91">
@@ -1433,7 +1433,7 @@
         <v>190</v>
       </c>
       <c r="C91" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -1444,7 +1444,7 @@
         <v>190</v>
       </c>
       <c r="C92" t="n">
-        <v>34</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="93">
@@ -1455,7 +1455,7 @@
         <v>190</v>
       </c>
       <c r="C93" t="n">
-        <v>68</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="94">
@@ -1466,7 +1466,7 @@
         <v>190</v>
       </c>
       <c r="C94" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -1477,7 +1477,7 @@
         <v>190</v>
       </c>
       <c r="C95" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -1488,7 +1488,7 @@
         <v>190</v>
       </c>
       <c r="C96" t="n">
-        <v>76</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="97">
@@ -1499,7 +1499,7 @@
         <v>190</v>
       </c>
       <c r="C97" t="n">
-        <v>66</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="98">
@@ -1510,7 +1510,7 @@
         <v>190</v>
       </c>
       <c r="C98" t="n">
-        <v>62</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="99">
@@ -1521,7 +1521,7 @@
         <v>190</v>
       </c>
       <c r="C99" t="n">
-        <v>76</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="100">
@@ -1532,7 +1532,7 @@
         <v>190</v>
       </c>
       <c r="C100" t="n">
-        <v>68</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="101">
@@ -1543,7 +1543,7 @@
         <v>190</v>
       </c>
       <c r="C101" t="n">
-        <v>72</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="102">
@@ -1554,7 +1554,7 @@
         <v>190</v>
       </c>
       <c r="C102" t="n">
-        <v>68</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="103">
@@ -1565,7 +1565,7 @@
         <v>190</v>
       </c>
       <c r="C103" t="n">
-        <v>72</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="104">
@@ -1576,7 +1576,7 @@
         <v>190</v>
       </c>
       <c r="C104" t="n">
-        <v>80</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="105">
@@ -1587,7 +1587,7 @@
         <v>190</v>
       </c>
       <c r="C105" t="n">
-        <v>92</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="106">
@@ -1598,7 +1598,7 @@
         <v>190</v>
       </c>
       <c r="C106" t="n">
-        <v>92</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="107">
@@ -1609,7 +1609,7 @@
         <v>190</v>
       </c>
       <c r="C107" t="n">
-        <v>72</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="108">
@@ -1620,7 +1620,7 @@
         <v>190</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="109">
@@ -1631,7 +1631,7 @@
         <v>190</v>
       </c>
       <c r="C109" t="n">
-        <v>76</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="110">
@@ -1642,7 +1642,7 @@
         <v>190</v>
       </c>
       <c r="C110" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -1653,7 +1653,7 @@
         <v>190</v>
       </c>
       <c r="C111" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -1664,7 +1664,7 @@
         <v>190</v>
       </c>
       <c r="C112" t="n">
-        <v>72</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="113">
@@ -1675,7 +1675,7 @@
         <v>190</v>
       </c>
       <c r="C113" t="n">
-        <v>58</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="114">
@@ -1686,7 +1686,7 @@
         <v>190</v>
       </c>
       <c r="C114" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
@@ -1697,7 +1697,7 @@
         <v>190</v>
       </c>
       <c r="C115" t="n">
-        <v>98</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="116">
@@ -1708,7 +1708,7 @@
         <v>190</v>
       </c>
       <c r="C116" t="n">
-        <v>88</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="117">
@@ -1719,7 +1719,7 @@
         <v>190</v>
       </c>
       <c r="C117" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
@@ -1730,7 +1730,7 @@
         <v>190</v>
       </c>
       <c r="C118" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119">
@@ -1741,7 +1741,7 @@
         <v>190</v>
       </c>
       <c r="C119" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -1752,7 +1752,7 @@
         <v>190</v>
       </c>
       <c r="C120" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121">
@@ -1763,7 +1763,7 @@
         <v>190</v>
       </c>
       <c r="C121" t="n">
-        <v>88</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="122">
@@ -1774,7 +1774,7 @@
         <v>190</v>
       </c>
       <c r="C122" t="n">
-        <v>74</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="123">
@@ -1785,7 +1785,7 @@
         <v>190</v>
       </c>
       <c r="C123" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
@@ -1796,7 +1796,7 @@
         <v>190</v>
       </c>
       <c r="C124" t="n">
-        <v>82</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="125">
@@ -1807,7 +1807,7 @@
         <v>190</v>
       </c>
       <c r="C125" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -1818,7 +1818,7 @@
         <v>190</v>
       </c>
       <c r="C126" t="n">
-        <v>112</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="127">
@@ -1829,7 +1829,7 @@
         <v>190</v>
       </c>
       <c r="C127" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
@@ -1840,7 +1840,7 @@
         <v>190</v>
       </c>
       <c r="C128" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
     </row>
     <row r="129">
@@ -1851,7 +1851,7 @@
         <v>190</v>
       </c>
       <c r="C129" t="n">
-        <v>92</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="130">
@@ -1862,7 +1862,7 @@
         <v>190</v>
       </c>
       <c r="C130" t="n">
-        <v>94</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="131">
@@ -1873,7 +1873,7 @@
         <v>190</v>
       </c>
       <c r="C131" t="n">
-        <v>110</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132">
@@ -1884,7 +1884,7 @@
         <v>190</v>
       </c>
       <c r="C132" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133">
@@ -1895,7 +1895,7 @@
         <v>190</v>
       </c>
       <c r="C133" t="n">
-        <v>118</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="134">
@@ -1906,7 +1906,7 @@
         <v>190</v>
       </c>
       <c r="C134" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135">
@@ -1917,7 +1917,7 @@
         <v>190</v>
       </c>
       <c r="C135" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
@@ -1928,7 +1928,7 @@
         <v>190</v>
       </c>
       <c r="C136" t="n">
-        <v>116</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137">
@@ -1939,7 +1939,7 @@
         <v>190</v>
       </c>
       <c r="C137" t="n">
-        <v>118</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138">
@@ -1950,7 +1950,7 @@
         <v>190</v>
       </c>
       <c r="C138" t="n">
-        <v>90</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="139">
@@ -1961,7 +1961,7 @@
         <v>190</v>
       </c>
       <c r="C139" t="n">
-        <v>136</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="140">
@@ -1972,7 +1972,7 @@
         <v>190</v>
       </c>
       <c r="C140" t="n">
-        <v>132</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
@@ -1983,7 +1983,7 @@
         <v>190</v>
       </c>
       <c r="C141" t="n">
-        <v>108</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
@@ -1994,7 +1994,7 @@
         <v>190</v>
       </c>
       <c r="C142" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -2005,7 +2005,7 @@
         <v>190</v>
       </c>
       <c r="C143" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2016,7 +2016,7 @@
         <v>190</v>
       </c>
       <c r="C144" t="n">
-        <v>128</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145">
@@ -2027,7 +2027,7 @@
         <v>190</v>
       </c>
       <c r="C145" t="n">
-        <v>122</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="146">
@@ -2038,7 +2038,7 @@
         <v>190</v>
       </c>
       <c r="C146" t="n">
-        <v>114</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
@@ -2049,7 +2049,7 @@
         <v>190</v>
       </c>
       <c r="C147" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -2060,7 +2060,7 @@
         <v>190</v>
       </c>
       <c r="C148" t="n">
-        <v>126</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149">
@@ -2071,7 +2071,7 @@
         <v>190</v>
       </c>
       <c r="C149" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -2082,7 +2082,7 @@
         <v>190</v>
       </c>
       <c r="C150" t="n">
-        <v>132</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -2093,7 +2093,7 @@
         <v>190</v>
       </c>
       <c r="C151" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
@@ -2104,7 +2104,7 @@
         <v>190</v>
       </c>
       <c r="C152" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
@@ -2115,7 +2115,7 @@
         <v>190</v>
       </c>
       <c r="C153" t="n">
-        <v>130</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="154">
@@ -2126,7 +2126,7 @@
         <v>190</v>
       </c>
       <c r="C154" t="n">
-        <v>146</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
@@ -2137,7 +2137,7 @@
         <v>190</v>
       </c>
       <c r="C155" t="n">
-        <v>122</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -2148,7 +2148,7 @@
         <v>190</v>
       </c>
       <c r="C156" t="n">
-        <v>114</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157">
@@ -2159,7 +2159,7 @@
         <v>190</v>
       </c>
       <c r="C157" t="n">
-        <v>130</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158">
@@ -2170,7 +2170,7 @@
         <v>190</v>
       </c>
       <c r="C158" t="n">
-        <v>138</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159">
@@ -2181,7 +2181,7 @@
         <v>190</v>
       </c>
       <c r="C159" t="n">
-        <v>148</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
@@ -2192,7 +2192,7 @@
         <v>190</v>
       </c>
       <c r="C160" t="n">
-        <v>144</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161">
@@ -2203,7 +2203,7 @@
         <v>190</v>
       </c>
       <c r="C161" t="n">
-        <v>136</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162">
@@ -2214,7 +2214,7 @@
         <v>190</v>
       </c>
       <c r="C162" t="n">
-        <v>138</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="163">
@@ -2225,7 +2225,7 @@
         <v>190</v>
       </c>
       <c r="C163" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164">
@@ -2236,7 +2236,7 @@
         <v>190</v>
       </c>
       <c r="C164" t="n">
-        <v>128</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -2247,7 +2247,7 @@
         <v>190</v>
       </c>
       <c r="C165" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166">
@@ -2258,7 +2258,7 @@
         <v>190</v>
       </c>
       <c r="C166" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167">
@@ -2269,7 +2269,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="n">
-        <v>132</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="168">
@@ -2280,7 +2280,7 @@
         <v>190</v>
       </c>
       <c r="C168" t="n">
-        <v>166</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169">
@@ -2291,7 +2291,7 @@
         <v>190</v>
       </c>
       <c r="C169" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170">
@@ -2302,7 +2302,7 @@
         <v>190</v>
       </c>
       <c r="C170" t="n">
-        <v>152</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171">
@@ -2313,7 +2313,7 @@
         <v>190</v>
       </c>
       <c r="C171" t="n">
-        <v>146</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172">
@@ -2324,7 +2324,7 @@
         <v>190</v>
       </c>
       <c r="C172" t="n">
-        <v>160</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173">
@@ -2335,7 +2335,7 @@
         <v>190</v>
       </c>
       <c r="C173" t="n">
-        <v>158</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174">
@@ -2346,7 +2346,7 @@
         <v>190</v>
       </c>
       <c r="C174" t="n">
-        <v>150</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175">
@@ -2357,7 +2357,7 @@
         <v>190</v>
       </c>
       <c r="C175" t="n">
-        <v>156</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176">
@@ -2368,7 +2368,7 @@
         <v>190</v>
       </c>
       <c r="C176" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
     </row>
     <row r="177">
@@ -2379,7 +2379,7 @@
         <v>190</v>
       </c>
       <c r="C177" t="n">
-        <v>150</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178">
@@ -2390,7 +2390,7 @@
         <v>190</v>
       </c>
       <c r="C178" t="n">
-        <v>170</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179">
@@ -2401,7 +2401,7 @@
         <v>190</v>
       </c>
       <c r="C179" t="n">
-        <v>170</v>
+        <v>42</v>
       </c>
     </row>
     <row r="180">
@@ -2412,7 +2412,7 @@
         <v>190</v>
       </c>
       <c r="C180" t="n">
-        <v>166</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181">
@@ -2423,7 +2423,7 @@
         <v>190</v>
       </c>
       <c r="C181" t="n">
-        <v>160</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182">
@@ -2434,7 +2434,7 @@
         <v>190</v>
       </c>
       <c r="C182" t="n">
-        <v>166</v>
+        <v>24</v>
       </c>
     </row>
     <row r="183">
@@ -2445,7 +2445,7 @@
         <v>190</v>
       </c>
       <c r="C183" t="n">
-        <v>168</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184">
@@ -2456,7 +2456,7 @@
         <v>190</v>
       </c>
       <c r="C184" t="n">
-        <v>164</v>
+        <v>54</v>
       </c>
     </row>
     <row r="185">
@@ -2467,7 +2467,7 @@
         <v>190</v>
       </c>
       <c r="C185" t="n">
-        <v>172</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186">
@@ -2478,7 +2478,7 @@
         <v>190</v>
       </c>
       <c r="C186" t="n">
-        <v>178</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187">
@@ -2489,7 +2489,7 @@
         <v>190</v>
       </c>
       <c r="C187" t="n">
-        <v>180</v>
+        <v>26</v>
       </c>
     </row>
     <row r="188">
@@ -2500,7 +2500,7 @@
         <v>190</v>
       </c>
       <c r="C188" t="n">
-        <v>160</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189">
@@ -2511,7 +2511,7 @@
         <v>190</v>
       </c>
       <c r="C189" t="n">
-        <v>170</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190">
@@ -2522,7 +2522,7 @@
         <v>190</v>
       </c>
       <c r="C190" t="n">
-        <v>184</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191">
@@ -2533,7 +2533,7 @@
         <v>190</v>
       </c>
       <c r="C191" t="n">
-        <v>178</v>
+        <v>18</v>
       </c>
     </row>
     <row r="192">
@@ -2544,7 +2544,7 @@
         <v>190</v>
       </c>
       <c r="C192" t="n">
-        <v>186</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193">
@@ -2555,7 +2555,7 @@
         <v>190</v>
       </c>
       <c r="C193" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
     </row>
     <row r="194">
@@ -2566,7 +2566,7 @@
         <v>190</v>
       </c>
       <c r="C194" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
     </row>
     <row r="195">
@@ -2577,7 +2577,7 @@
         <v>190</v>
       </c>
       <c r="C195" t="n">
-        <v>182</v>
+        <v>40</v>
       </c>
     </row>
     <row r="196">
@@ -2588,7 +2588,7 @@
         <v>190</v>
       </c>
       <c r="C196" t="n">
-        <v>184</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197">
@@ -2599,7 +2599,7 @@
         <v>190</v>
       </c>
       <c r="C197" t="n">
-        <v>184</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198">
@@ -2610,7 +2610,7 @@
         <v>190</v>
       </c>
       <c r="C198" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
     </row>
     <row r="199">
@@ -2621,7 +2621,7 @@
         <v>190</v>
       </c>
       <c r="C199" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
     </row>
     <row r="200">
@@ -2632,7 +2632,7 @@
         <v>190</v>
       </c>
       <c r="C200" t="n">
-        <v>188</v>
+        <v>48</v>
       </c>
     </row>
     <row r="201">
@@ -2643,6 +2643,3306 @@
         <v>190</v>
       </c>
       <c r="C201" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>190</v>
+      </c>
+      <c r="C202" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>190</v>
+      </c>
+      <c r="C203" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>190</v>
+      </c>
+      <c r="C204" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>190</v>
+      </c>
+      <c r="C205" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>190</v>
+      </c>
+      <c r="C206" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>190</v>
+      </c>
+      <c r="C207" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>190</v>
+      </c>
+      <c r="C208" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>190</v>
+      </c>
+      <c r="C209" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>190</v>
+      </c>
+      <c r="C210" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>190</v>
+      </c>
+      <c r="C211" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>190</v>
+      </c>
+      <c r="C212" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>190</v>
+      </c>
+      <c r="C213" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>190</v>
+      </c>
+      <c r="C214" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>190</v>
+      </c>
+      <c r="C215" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>190</v>
+      </c>
+      <c r="C216" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>190</v>
+      </c>
+      <c r="C217" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>190</v>
+      </c>
+      <c r="C218" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>190</v>
+      </c>
+      <c r="C219" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>190</v>
+      </c>
+      <c r="C220" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>190</v>
+      </c>
+      <c r="C221" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>190</v>
+      </c>
+      <c r="C222" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>190</v>
+      </c>
+      <c r="C223" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>190</v>
+      </c>
+      <c r="C224" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>190</v>
+      </c>
+      <c r="C225" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>190</v>
+      </c>
+      <c r="C226" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>190</v>
+      </c>
+      <c r="C227" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>190</v>
+      </c>
+      <c r="C228" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>190</v>
+      </c>
+      <c r="C229" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>190</v>
+      </c>
+      <c r="C230" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>190</v>
+      </c>
+      <c r="C231" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>190</v>
+      </c>
+      <c r="C232" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>190</v>
+      </c>
+      <c r="C233" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>190</v>
+      </c>
+      <c r="C234" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>190</v>
+      </c>
+      <c r="C235" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>190</v>
+      </c>
+      <c r="C236" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>190</v>
+      </c>
+      <c r="C237" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>190</v>
+      </c>
+      <c r="C238" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>190</v>
+      </c>
+      <c r="C239" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>190</v>
+      </c>
+      <c r="C240" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>190</v>
+      </c>
+      <c r="C241" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
+        <v>190</v>
+      </c>
+      <c r="C242" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
+        <v>190</v>
+      </c>
+      <c r="C243" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
+        <v>190</v>
+      </c>
+      <c r="C244" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
+        <v>190</v>
+      </c>
+      <c r="C245" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
+        <v>190</v>
+      </c>
+      <c r="C246" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
+        <v>190</v>
+      </c>
+      <c r="C247" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
+        <v>190</v>
+      </c>
+      <c r="C248" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
+        <v>190</v>
+      </c>
+      <c r="C249" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
+        <v>190</v>
+      </c>
+      <c r="C250" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
+        <v>190</v>
+      </c>
+      <c r="C251" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="n">
+        <v>190</v>
+      </c>
+      <c r="C252" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="n">
+        <v>190</v>
+      </c>
+      <c r="C253" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="n">
+        <v>190</v>
+      </c>
+      <c r="C254" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="n">
+        <v>190</v>
+      </c>
+      <c r="C255" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="n">
+        <v>190</v>
+      </c>
+      <c r="C256" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="n">
+        <v>190</v>
+      </c>
+      <c r="C257" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="n">
+        <v>190</v>
+      </c>
+      <c r="C258" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="n">
+        <v>190</v>
+      </c>
+      <c r="C259" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="n">
+        <v>190</v>
+      </c>
+      <c r="C260" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="n">
+        <v>190</v>
+      </c>
+      <c r="C261" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="n">
+        <v>190</v>
+      </c>
+      <c r="C262" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="n">
+        <v>190</v>
+      </c>
+      <c r="C263" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="n">
+        <v>190</v>
+      </c>
+      <c r="C264" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="n">
+        <v>190</v>
+      </c>
+      <c r="C265" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="n">
+        <v>190</v>
+      </c>
+      <c r="C266" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="n">
+        <v>190</v>
+      </c>
+      <c r="C267" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="n">
+        <v>190</v>
+      </c>
+      <c r="C268" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="n">
+        <v>190</v>
+      </c>
+      <c r="C269" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="n">
+        <v>190</v>
+      </c>
+      <c r="C270" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="n">
+        <v>190</v>
+      </c>
+      <c r="C271" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="n">
+        <v>190</v>
+      </c>
+      <c r="C272" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="n">
+        <v>190</v>
+      </c>
+      <c r="C273" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" t="n">
+        <v>190</v>
+      </c>
+      <c r="C274" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" t="n">
+        <v>190</v>
+      </c>
+      <c r="C275" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" t="n">
+        <v>190</v>
+      </c>
+      <c r="C276" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" t="n">
+        <v>190</v>
+      </c>
+      <c r="C277" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" t="n">
+        <v>190</v>
+      </c>
+      <c r="C278" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" t="n">
+        <v>190</v>
+      </c>
+      <c r="C279" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" t="n">
+        <v>190</v>
+      </c>
+      <c r="C280" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" t="n">
+        <v>190</v>
+      </c>
+      <c r="C281" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" t="n">
+        <v>190</v>
+      </c>
+      <c r="C282" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" t="n">
+        <v>190</v>
+      </c>
+      <c r="C283" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" t="n">
+        <v>190</v>
+      </c>
+      <c r="C284" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="n">
+        <v>190</v>
+      </c>
+      <c r="C285" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="n">
+        <v>190</v>
+      </c>
+      <c r="C286" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="n">
+        <v>190</v>
+      </c>
+      <c r="C287" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="n">
+        <v>190</v>
+      </c>
+      <c r="C288" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="n">
+        <v>190</v>
+      </c>
+      <c r="C289" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="n">
+        <v>190</v>
+      </c>
+      <c r="C290" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="n">
+        <v>190</v>
+      </c>
+      <c r="C291" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="n">
+        <v>190</v>
+      </c>
+      <c r="C292" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="n">
+        <v>190</v>
+      </c>
+      <c r="C293" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="n">
+        <v>190</v>
+      </c>
+      <c r="C294" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="n">
+        <v>190</v>
+      </c>
+      <c r="C295" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="n">
+        <v>190</v>
+      </c>
+      <c r="C296" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="n">
+        <v>190</v>
+      </c>
+      <c r="C297" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>296</v>
+      </c>
+      <c r="B298" t="n">
+        <v>190</v>
+      </c>
+      <c r="C298" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>297</v>
+      </c>
+      <c r="B299" t="n">
+        <v>190</v>
+      </c>
+      <c r="C299" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>298</v>
+      </c>
+      <c r="B300" t="n">
+        <v>190</v>
+      </c>
+      <c r="C300" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>299</v>
+      </c>
+      <c r="B301" t="n">
+        <v>190</v>
+      </c>
+      <c r="C301" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>300</v>
+      </c>
+      <c r="B302" t="n">
+        <v>190</v>
+      </c>
+      <c r="C302" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>301</v>
+      </c>
+      <c r="B303" t="n">
+        <v>190</v>
+      </c>
+      <c r="C303" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>302</v>
+      </c>
+      <c r="B304" t="n">
+        <v>190</v>
+      </c>
+      <c r="C304" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>303</v>
+      </c>
+      <c r="B305" t="n">
+        <v>190</v>
+      </c>
+      <c r="C305" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>304</v>
+      </c>
+      <c r="B306" t="n">
+        <v>190</v>
+      </c>
+      <c r="C306" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>305</v>
+      </c>
+      <c r="B307" t="n">
+        <v>190</v>
+      </c>
+      <c r="C307" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>306</v>
+      </c>
+      <c r="B308" t="n">
+        <v>190</v>
+      </c>
+      <c r="C308" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>307</v>
+      </c>
+      <c r="B309" t="n">
+        <v>190</v>
+      </c>
+      <c r="C309" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>308</v>
+      </c>
+      <c r="B310" t="n">
+        <v>190</v>
+      </c>
+      <c r="C310" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>309</v>
+      </c>
+      <c r="B311" t="n">
+        <v>190</v>
+      </c>
+      <c r="C311" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>310</v>
+      </c>
+      <c r="B312" t="n">
+        <v>190</v>
+      </c>
+      <c r="C312" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>311</v>
+      </c>
+      <c r="B313" t="n">
+        <v>190</v>
+      </c>
+      <c r="C313" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>312</v>
+      </c>
+      <c r="B314" t="n">
+        <v>190</v>
+      </c>
+      <c r="C314" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>313</v>
+      </c>
+      <c r="B315" t="n">
+        <v>190</v>
+      </c>
+      <c r="C315" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>314</v>
+      </c>
+      <c r="B316" t="n">
+        <v>190</v>
+      </c>
+      <c r="C316" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>315</v>
+      </c>
+      <c r="B317" t="n">
+        <v>190</v>
+      </c>
+      <c r="C317" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>316</v>
+      </c>
+      <c r="B318" t="n">
+        <v>190</v>
+      </c>
+      <c r="C318" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>317</v>
+      </c>
+      <c r="B319" t="n">
+        <v>190</v>
+      </c>
+      <c r="C319" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>318</v>
+      </c>
+      <c r="B320" t="n">
+        <v>190</v>
+      </c>
+      <c r="C320" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>319</v>
+      </c>
+      <c r="B321" t="n">
+        <v>190</v>
+      </c>
+      <c r="C321" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>320</v>
+      </c>
+      <c r="B322" t="n">
+        <v>190</v>
+      </c>
+      <c r="C322" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>321</v>
+      </c>
+      <c r="B323" t="n">
+        <v>190</v>
+      </c>
+      <c r="C323" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>322</v>
+      </c>
+      <c r="B324" t="n">
+        <v>190</v>
+      </c>
+      <c r="C324" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>323</v>
+      </c>
+      <c r="B325" t="n">
+        <v>190</v>
+      </c>
+      <c r="C325" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>324</v>
+      </c>
+      <c r="B326" t="n">
+        <v>190</v>
+      </c>
+      <c r="C326" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>325</v>
+      </c>
+      <c r="B327" t="n">
+        <v>190</v>
+      </c>
+      <c r="C327" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>326</v>
+      </c>
+      <c r="B328" t="n">
+        <v>190</v>
+      </c>
+      <c r="C328" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>327</v>
+      </c>
+      <c r="B329" t="n">
+        <v>190</v>
+      </c>
+      <c r="C329" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>328</v>
+      </c>
+      <c r="B330" t="n">
+        <v>190</v>
+      </c>
+      <c r="C330" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>329</v>
+      </c>
+      <c r="B331" t="n">
+        <v>190</v>
+      </c>
+      <c r="C331" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>330</v>
+      </c>
+      <c r="B332" t="n">
+        <v>190</v>
+      </c>
+      <c r="C332" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>331</v>
+      </c>
+      <c r="B333" t="n">
+        <v>190</v>
+      </c>
+      <c r="C333" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>332</v>
+      </c>
+      <c r="B334" t="n">
+        <v>190</v>
+      </c>
+      <c r="C334" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>333</v>
+      </c>
+      <c r="B335" t="n">
+        <v>190</v>
+      </c>
+      <c r="C335" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>334</v>
+      </c>
+      <c r="B336" t="n">
+        <v>190</v>
+      </c>
+      <c r="C336" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>335</v>
+      </c>
+      <c r="B337" t="n">
+        <v>190</v>
+      </c>
+      <c r="C337" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>336</v>
+      </c>
+      <c r="B338" t="n">
+        <v>190</v>
+      </c>
+      <c r="C338" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>337</v>
+      </c>
+      <c r="B339" t="n">
+        <v>190</v>
+      </c>
+      <c r="C339" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>338</v>
+      </c>
+      <c r="B340" t="n">
+        <v>190</v>
+      </c>
+      <c r="C340" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>339</v>
+      </c>
+      <c r="B341" t="n">
+        <v>190</v>
+      </c>
+      <c r="C341" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>340</v>
+      </c>
+      <c r="B342" t="n">
+        <v>190</v>
+      </c>
+      <c r="C342" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>341</v>
+      </c>
+      <c r="B343" t="n">
+        <v>190</v>
+      </c>
+      <c r="C343" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>342</v>
+      </c>
+      <c r="B344" t="n">
+        <v>190</v>
+      </c>
+      <c r="C344" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>343</v>
+      </c>
+      <c r="B345" t="n">
+        <v>190</v>
+      </c>
+      <c r="C345" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>344</v>
+      </c>
+      <c r="B346" t="n">
+        <v>190</v>
+      </c>
+      <c r="C346" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>345</v>
+      </c>
+      <c r="B347" t="n">
+        <v>190</v>
+      </c>
+      <c r="C347" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>346</v>
+      </c>
+      <c r="B348" t="n">
+        <v>190</v>
+      </c>
+      <c r="C348" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>347</v>
+      </c>
+      <c r="B349" t="n">
+        <v>190</v>
+      </c>
+      <c r="C349" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>348</v>
+      </c>
+      <c r="B350" t="n">
+        <v>190</v>
+      </c>
+      <c r="C350" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>349</v>
+      </c>
+      <c r="B351" t="n">
+        <v>190</v>
+      </c>
+      <c r="C351" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>350</v>
+      </c>
+      <c r="B352" t="n">
+        <v>190</v>
+      </c>
+      <c r="C352" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>351</v>
+      </c>
+      <c r="B353" t="n">
+        <v>190</v>
+      </c>
+      <c r="C353" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>352</v>
+      </c>
+      <c r="B354" t="n">
+        <v>190</v>
+      </c>
+      <c r="C354" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>353</v>
+      </c>
+      <c r="B355" t="n">
+        <v>190</v>
+      </c>
+      <c r="C355" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>354</v>
+      </c>
+      <c r="B356" t="n">
+        <v>190</v>
+      </c>
+      <c r="C356" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>355</v>
+      </c>
+      <c r="B357" t="n">
+        <v>190</v>
+      </c>
+      <c r="C357" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>356</v>
+      </c>
+      <c r="B358" t="n">
+        <v>190</v>
+      </c>
+      <c r="C358" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>357</v>
+      </c>
+      <c r="B359" t="n">
+        <v>190</v>
+      </c>
+      <c r="C359" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>358</v>
+      </c>
+      <c r="B360" t="n">
+        <v>190</v>
+      </c>
+      <c r="C360" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>359</v>
+      </c>
+      <c r="B361" t="n">
+        <v>190</v>
+      </c>
+      <c r="C361" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>360</v>
+      </c>
+      <c r="B362" t="n">
+        <v>190</v>
+      </c>
+      <c r="C362" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>361</v>
+      </c>
+      <c r="B363" t="n">
+        <v>190</v>
+      </c>
+      <c r="C363" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>362</v>
+      </c>
+      <c r="B364" t="n">
+        <v>190</v>
+      </c>
+      <c r="C364" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>363</v>
+      </c>
+      <c r="B365" t="n">
+        <v>190</v>
+      </c>
+      <c r="C365" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>364</v>
+      </c>
+      <c r="B366" t="n">
+        <v>190</v>
+      </c>
+      <c r="C366" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>365</v>
+      </c>
+      <c r="B367" t="n">
+        <v>190</v>
+      </c>
+      <c r="C367" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>366</v>
+      </c>
+      <c r="B368" t="n">
+        <v>190</v>
+      </c>
+      <c r="C368" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>367</v>
+      </c>
+      <c r="B369" t="n">
+        <v>190</v>
+      </c>
+      <c r="C369" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>368</v>
+      </c>
+      <c r="B370" t="n">
+        <v>190</v>
+      </c>
+      <c r="C370" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>369</v>
+      </c>
+      <c r="B371" t="n">
+        <v>190</v>
+      </c>
+      <c r="C371" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>370</v>
+      </c>
+      <c r="B372" t="n">
+        <v>190</v>
+      </c>
+      <c r="C372" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>371</v>
+      </c>
+      <c r="B373" t="n">
+        <v>190</v>
+      </c>
+      <c r="C373" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>372</v>
+      </c>
+      <c r="B374" t="n">
+        <v>190</v>
+      </c>
+      <c r="C374" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>373</v>
+      </c>
+      <c r="B375" t="n">
+        <v>190</v>
+      </c>
+      <c r="C375" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>374</v>
+      </c>
+      <c r="B376" t="n">
+        <v>190</v>
+      </c>
+      <c r="C376" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>375</v>
+      </c>
+      <c r="B377" t="n">
+        <v>190</v>
+      </c>
+      <c r="C377" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>376</v>
+      </c>
+      <c r="B378" t="n">
+        <v>190</v>
+      </c>
+      <c r="C378" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>377</v>
+      </c>
+      <c r="B379" t="n">
+        <v>190</v>
+      </c>
+      <c r="C379" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>378</v>
+      </c>
+      <c r="B380" t="n">
+        <v>190</v>
+      </c>
+      <c r="C380" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>379</v>
+      </c>
+      <c r="B381" t="n">
+        <v>190</v>
+      </c>
+      <c r="C381" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>380</v>
+      </c>
+      <c r="B382" t="n">
+        <v>190</v>
+      </c>
+      <c r="C382" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>381</v>
+      </c>
+      <c r="B383" t="n">
+        <v>190</v>
+      </c>
+      <c r="C383" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>382</v>
+      </c>
+      <c r="B384" t="n">
+        <v>190</v>
+      </c>
+      <c r="C384" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>383</v>
+      </c>
+      <c r="B385" t="n">
+        <v>190</v>
+      </c>
+      <c r="C385" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>384</v>
+      </c>
+      <c r="B386" t="n">
+        <v>190</v>
+      </c>
+      <c r="C386" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>385</v>
+      </c>
+      <c r="B387" t="n">
+        <v>190</v>
+      </c>
+      <c r="C387" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>386</v>
+      </c>
+      <c r="B388" t="n">
+        <v>190</v>
+      </c>
+      <c r="C388" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>387</v>
+      </c>
+      <c r="B389" t="n">
+        <v>190</v>
+      </c>
+      <c r="C389" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>388</v>
+      </c>
+      <c r="B390" t="n">
+        <v>190</v>
+      </c>
+      <c r="C390" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>389</v>
+      </c>
+      <c r="B391" t="n">
+        <v>190</v>
+      </c>
+      <c r="C391" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>390</v>
+      </c>
+      <c r="B392" t="n">
+        <v>190</v>
+      </c>
+      <c r="C392" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>391</v>
+      </c>
+      <c r="B393" t="n">
+        <v>190</v>
+      </c>
+      <c r="C393" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>392</v>
+      </c>
+      <c r="B394" t="n">
+        <v>190</v>
+      </c>
+      <c r="C394" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>393</v>
+      </c>
+      <c r="B395" t="n">
+        <v>190</v>
+      </c>
+      <c r="C395" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>394</v>
+      </c>
+      <c r="B396" t="n">
+        <v>190</v>
+      </c>
+      <c r="C396" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>395</v>
+      </c>
+      <c r="B397" t="n">
+        <v>190</v>
+      </c>
+      <c r="C397" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>396</v>
+      </c>
+      <c r="B398" t="n">
+        <v>190</v>
+      </c>
+      <c r="C398" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>397</v>
+      </c>
+      <c r="B399" t="n">
+        <v>190</v>
+      </c>
+      <c r="C399" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>398</v>
+      </c>
+      <c r="B400" t="n">
+        <v>190</v>
+      </c>
+      <c r="C400" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>399</v>
+      </c>
+      <c r="B401" t="n">
+        <v>190</v>
+      </c>
+      <c r="C401" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>400</v>
+      </c>
+      <c r="B402" t="n">
+        <v>190</v>
+      </c>
+      <c r="C402" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>401</v>
+      </c>
+      <c r="B403" t="n">
+        <v>190</v>
+      </c>
+      <c r="C403" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>402</v>
+      </c>
+      <c r="B404" t="n">
+        <v>190</v>
+      </c>
+      <c r="C404" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>403</v>
+      </c>
+      <c r="B405" t="n">
+        <v>190</v>
+      </c>
+      <c r="C405" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>404</v>
+      </c>
+      <c r="B406" t="n">
+        <v>190</v>
+      </c>
+      <c r="C406" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>405</v>
+      </c>
+      <c r="B407" t="n">
+        <v>190</v>
+      </c>
+      <c r="C407" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>406</v>
+      </c>
+      <c r="B408" t="n">
+        <v>190</v>
+      </c>
+      <c r="C408" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>407</v>
+      </c>
+      <c r="B409" t="n">
+        <v>190</v>
+      </c>
+      <c r="C409" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>408</v>
+      </c>
+      <c r="B410" t="n">
+        <v>190</v>
+      </c>
+      <c r="C410" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>409</v>
+      </c>
+      <c r="B411" t="n">
+        <v>190</v>
+      </c>
+      <c r="C411" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>410</v>
+      </c>
+      <c r="B412" t="n">
+        <v>190</v>
+      </c>
+      <c r="C412" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>411</v>
+      </c>
+      <c r="B413" t="n">
+        <v>190</v>
+      </c>
+      <c r="C413" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>412</v>
+      </c>
+      <c r="B414" t="n">
+        <v>190</v>
+      </c>
+      <c r="C414" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>413</v>
+      </c>
+      <c r="B415" t="n">
+        <v>190</v>
+      </c>
+      <c r="C415" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>414</v>
+      </c>
+      <c r="B416" t="n">
+        <v>190</v>
+      </c>
+      <c r="C416" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>415</v>
+      </c>
+      <c r="B417" t="n">
+        <v>190</v>
+      </c>
+      <c r="C417" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>416</v>
+      </c>
+      <c r="B418" t="n">
+        <v>190</v>
+      </c>
+      <c r="C418" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>417</v>
+      </c>
+      <c r="B419" t="n">
+        <v>190</v>
+      </c>
+      <c r="C419" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>418</v>
+      </c>
+      <c r="B420" t="n">
+        <v>190</v>
+      </c>
+      <c r="C420" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>419</v>
+      </c>
+      <c r="B421" t="n">
+        <v>190</v>
+      </c>
+      <c r="C421" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>420</v>
+      </c>
+      <c r="B422" t="n">
+        <v>190</v>
+      </c>
+      <c r="C422" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>421</v>
+      </c>
+      <c r="B423" t="n">
+        <v>190</v>
+      </c>
+      <c r="C423" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>422</v>
+      </c>
+      <c r="B424" t="n">
+        <v>190</v>
+      </c>
+      <c r="C424" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>423</v>
+      </c>
+      <c r="B425" t="n">
+        <v>190</v>
+      </c>
+      <c r="C425" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>424</v>
+      </c>
+      <c r="B426" t="n">
+        <v>190</v>
+      </c>
+      <c r="C426" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>425</v>
+      </c>
+      <c r="B427" t="n">
+        <v>190</v>
+      </c>
+      <c r="C427" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>426</v>
+      </c>
+      <c r="B428" t="n">
+        <v>190</v>
+      </c>
+      <c r="C428" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>427</v>
+      </c>
+      <c r="B429" t="n">
+        <v>190</v>
+      </c>
+      <c r="C429" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>428</v>
+      </c>
+      <c r="B430" t="n">
+        <v>190</v>
+      </c>
+      <c r="C430" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>429</v>
+      </c>
+      <c r="B431" t="n">
+        <v>190</v>
+      </c>
+      <c r="C431" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>430</v>
+      </c>
+      <c r="B432" t="n">
+        <v>190</v>
+      </c>
+      <c r="C432" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>431</v>
+      </c>
+      <c r="B433" t="n">
+        <v>190</v>
+      </c>
+      <c r="C433" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>432</v>
+      </c>
+      <c r="B434" t="n">
+        <v>190</v>
+      </c>
+      <c r="C434" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>433</v>
+      </c>
+      <c r="B435" t="n">
+        <v>190</v>
+      </c>
+      <c r="C435" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>434</v>
+      </c>
+      <c r="B436" t="n">
+        <v>190</v>
+      </c>
+      <c r="C436" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>435</v>
+      </c>
+      <c r="B437" t="n">
+        <v>190</v>
+      </c>
+      <c r="C437" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>436</v>
+      </c>
+      <c r="B438" t="n">
+        <v>190</v>
+      </c>
+      <c r="C438" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>437</v>
+      </c>
+      <c r="B439" t="n">
+        <v>190</v>
+      </c>
+      <c r="C439" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>438</v>
+      </c>
+      <c r="B440" t="n">
+        <v>190</v>
+      </c>
+      <c r="C440" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>439</v>
+      </c>
+      <c r="B441" t="n">
+        <v>190</v>
+      </c>
+      <c r="C441" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>440</v>
+      </c>
+      <c r="B442" t="n">
+        <v>190</v>
+      </c>
+      <c r="C442" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>441</v>
+      </c>
+      <c r="B443" t="n">
+        <v>190</v>
+      </c>
+      <c r="C443" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>442</v>
+      </c>
+      <c r="B444" t="n">
+        <v>190</v>
+      </c>
+      <c r="C444" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>443</v>
+      </c>
+      <c r="B445" t="n">
+        <v>190</v>
+      </c>
+      <c r="C445" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>444</v>
+      </c>
+      <c r="B446" t="n">
+        <v>190</v>
+      </c>
+      <c r="C446" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>445</v>
+      </c>
+      <c r="B447" t="n">
+        <v>190</v>
+      </c>
+      <c r="C447" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>446</v>
+      </c>
+      <c r="B448" t="n">
+        <v>190</v>
+      </c>
+      <c r="C448" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>447</v>
+      </c>
+      <c r="B449" t="n">
+        <v>190</v>
+      </c>
+      <c r="C449" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>448</v>
+      </c>
+      <c r="B450" t="n">
+        <v>190</v>
+      </c>
+      <c r="C450" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>449</v>
+      </c>
+      <c r="B451" t="n">
+        <v>190</v>
+      </c>
+      <c r="C451" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>450</v>
+      </c>
+      <c r="B452" t="n">
+        <v>190</v>
+      </c>
+      <c r="C452" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>451</v>
+      </c>
+      <c r="B453" t="n">
+        <v>190</v>
+      </c>
+      <c r="C453" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>452</v>
+      </c>
+      <c r="B454" t="n">
+        <v>190</v>
+      </c>
+      <c r="C454" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>453</v>
+      </c>
+      <c r="B455" t="n">
+        <v>190</v>
+      </c>
+      <c r="C455" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>454</v>
+      </c>
+      <c r="B456" t="n">
+        <v>190</v>
+      </c>
+      <c r="C456" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>455</v>
+      </c>
+      <c r="B457" t="n">
+        <v>190</v>
+      </c>
+      <c r="C457" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>456</v>
+      </c>
+      <c r="B458" t="n">
+        <v>190</v>
+      </c>
+      <c r="C458" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>457</v>
+      </c>
+      <c r="B459" t="n">
+        <v>190</v>
+      </c>
+      <c r="C459" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>458</v>
+      </c>
+      <c r="B460" t="n">
+        <v>190</v>
+      </c>
+      <c r="C460" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>459</v>
+      </c>
+      <c r="B461" t="n">
+        <v>190</v>
+      </c>
+      <c r="C461" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>460</v>
+      </c>
+      <c r="B462" t="n">
+        <v>190</v>
+      </c>
+      <c r="C462" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>461</v>
+      </c>
+      <c r="B463" t="n">
+        <v>190</v>
+      </c>
+      <c r="C463" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>462</v>
+      </c>
+      <c r="B464" t="n">
+        <v>190</v>
+      </c>
+      <c r="C464" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>463</v>
+      </c>
+      <c r="B465" t="n">
+        <v>190</v>
+      </c>
+      <c r="C465" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>464</v>
+      </c>
+      <c r="B466" t="n">
+        <v>190</v>
+      </c>
+      <c r="C466" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>465</v>
+      </c>
+      <c r="B467" t="n">
+        <v>190</v>
+      </c>
+      <c r="C467" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>466</v>
+      </c>
+      <c r="B468" t="n">
+        <v>190</v>
+      </c>
+      <c r="C468" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>467</v>
+      </c>
+      <c r="B469" t="n">
+        <v>190</v>
+      </c>
+      <c r="C469" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>468</v>
+      </c>
+      <c r="B470" t="n">
+        <v>190</v>
+      </c>
+      <c r="C470" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>469</v>
+      </c>
+      <c r="B471" t="n">
+        <v>190</v>
+      </c>
+      <c r="C471" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>470</v>
+      </c>
+      <c r="B472" t="n">
+        <v>190</v>
+      </c>
+      <c r="C472" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>471</v>
+      </c>
+      <c r="B473" t="n">
+        <v>190</v>
+      </c>
+      <c r="C473" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>472</v>
+      </c>
+      <c r="B474" t="n">
+        <v>190</v>
+      </c>
+      <c r="C474" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>473</v>
+      </c>
+      <c r="B475" t="n">
+        <v>190</v>
+      </c>
+      <c r="C475" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>474</v>
+      </c>
+      <c r="B476" t="n">
+        <v>190</v>
+      </c>
+      <c r="C476" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>475</v>
+      </c>
+      <c r="B477" t="n">
+        <v>190</v>
+      </c>
+      <c r="C477" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>476</v>
+      </c>
+      <c r="B478" t="n">
+        <v>190</v>
+      </c>
+      <c r="C478" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>477</v>
+      </c>
+      <c r="B479" t="n">
+        <v>190</v>
+      </c>
+      <c r="C479" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>478</v>
+      </c>
+      <c r="B480" t="n">
+        <v>190</v>
+      </c>
+      <c r="C480" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>479</v>
+      </c>
+      <c r="B481" t="n">
+        <v>190</v>
+      </c>
+      <c r="C481" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>480</v>
+      </c>
+      <c r="B482" t="n">
+        <v>190</v>
+      </c>
+      <c r="C482" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>481</v>
+      </c>
+      <c r="B483" t="n">
+        <v>190</v>
+      </c>
+      <c r="C483" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>482</v>
+      </c>
+      <c r="B484" t="n">
+        <v>190</v>
+      </c>
+      <c r="C484" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>483</v>
+      </c>
+      <c r="B485" t="n">
+        <v>190</v>
+      </c>
+      <c r="C485" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>484</v>
+      </c>
+      <c r="B486" t="n">
+        <v>190</v>
+      </c>
+      <c r="C486" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>485</v>
+      </c>
+      <c r="B487" t="n">
+        <v>190</v>
+      </c>
+      <c r="C487" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>486</v>
+      </c>
+      <c r="B488" t="n">
+        <v>190</v>
+      </c>
+      <c r="C488" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>487</v>
+      </c>
+      <c r="B489" t="n">
+        <v>190</v>
+      </c>
+      <c r="C489" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>488</v>
+      </c>
+      <c r="B490" t="n">
+        <v>190</v>
+      </c>
+      <c r="C490" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>489</v>
+      </c>
+      <c r="B491" t="n">
+        <v>190</v>
+      </c>
+      <c r="C491" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>490</v>
+      </c>
+      <c r="B492" t="n">
+        <v>190</v>
+      </c>
+      <c r="C492" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>491</v>
+      </c>
+      <c r="B493" t="n">
+        <v>190</v>
+      </c>
+      <c r="C493" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>492</v>
+      </c>
+      <c r="B494" t="n">
+        <v>190</v>
+      </c>
+      <c r="C494" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>493</v>
+      </c>
+      <c r="B495" t="n">
+        <v>190</v>
+      </c>
+      <c r="C495" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>494</v>
+      </c>
+      <c r="B496" t="n">
+        <v>190</v>
+      </c>
+      <c r="C496" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>495</v>
+      </c>
+      <c r="B497" t="n">
+        <v>190</v>
+      </c>
+      <c r="C497" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>496</v>
+      </c>
+      <c r="B498" t="n">
+        <v>190</v>
+      </c>
+      <c r="C498" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>497</v>
+      </c>
+      <c r="B499" t="n">
+        <v>190</v>
+      </c>
+      <c r="C499" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>498</v>
+      </c>
+      <c r="B500" t="n">
+        <v>190</v>
+      </c>
+      <c r="C500" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>499</v>
+      </c>
+      <c r="B501" t="n">
+        <v>190</v>
+      </c>
+      <c r="C501" t="n">
         <v>190</v>
       </c>
     </row>
@@ -2679,10 +5979,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -2695,7 +5995,7 @@
         <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>63.4</v>
+        <v>62.764</v>
       </c>
     </row>
     <row r="4">
@@ -2708,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>75.13793011997052</v>
+        <v>74.18689705999827</v>
       </c>
     </row>
     <row r="5">
@@ -2721,7 +6021,7 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>-72</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="6">
@@ -2734,7 +6034,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -2747,7 +6047,7 @@
         <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -2760,7 +6060,7 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C501"/>
+  <dimension ref="A1:D501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>solar#0</t>
+          <t>wind#0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -445,6 +445,11 @@
           <t>battery#0</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>grid#0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -454,7 +459,10 @@
         <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>-44</v>
+        <v>-46</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -465,7 +473,10 @@
         <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>-52</v>
+        <v>-30</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +487,10 @@
         <v>190</v>
       </c>
       <c r="C4" t="n">
-        <v>-60</v>
+        <v>-64</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.75</v>
       </c>
     </row>
     <row r="5">
@@ -487,7 +501,10 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>-44</v>
+        <v>-52</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-22.25</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +515,10 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>-52</v>
+        <v>-68</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +529,10 @@
         <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>-62</v>
+        <v>-48</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-16.75</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +543,10 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>-70</v>
+        <v>-64</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +557,10 @@
         <v>190</v>
       </c>
       <c r="C9" t="n">
-        <v>-46</v>
+        <v>-64</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +571,10 @@
         <v>190</v>
       </c>
       <c r="C10" t="n">
-        <v>-62</v>
+        <v>-48</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-40.75</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +585,10 @@
         <v>190</v>
       </c>
       <c r="C11" t="n">
-        <v>-50</v>
+        <v>-48</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-40.75</v>
       </c>
     </row>
     <row r="12">
@@ -564,7 +599,10 @@
         <v>190</v>
       </c>
       <c r="C12" t="n">
-        <v>-54</v>
+        <v>-72</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="13">
@@ -575,7 +613,10 @@
         <v>190</v>
       </c>
       <c r="C13" t="n">
-        <v>-50</v>
+        <v>-60</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-23.25</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +627,10 @@
         <v>190</v>
       </c>
       <c r="C14" t="n">
-        <v>-42</v>
+        <v>-60</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-5.25</v>
       </c>
     </row>
     <row r="15">
@@ -599,6 +643,9 @@
       <c r="C15" t="n">
         <v>-50</v>
       </c>
+      <c r="D15" t="n">
+        <v>-23.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -608,7 +655,10 @@
         <v>190</v>
       </c>
       <c r="C16" t="n">
-        <v>-52</v>
+        <v>-54</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="17">
@@ -619,7 +669,10 @@
         <v>190</v>
       </c>
       <c r="C17" t="n">
-        <v>-84</v>
+        <v>-80</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +683,10 @@
         <v>190</v>
       </c>
       <c r="C18" t="n">
-        <v>-68</v>
+        <v>-62</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +697,10 @@
         <v>190</v>
       </c>
       <c r="C19" t="n">
-        <v>-40</v>
+        <v>-72</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-7.75</v>
       </c>
     </row>
     <row r="20">
@@ -652,7 +711,10 @@
         <v>190</v>
       </c>
       <c r="C20" t="n">
-        <v>-60</v>
+        <v>-58</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="21">
@@ -663,7 +725,10 @@
         <v>190</v>
       </c>
       <c r="C21" t="n">
-        <v>-76</v>
+        <v>-50</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="22">
@@ -676,6 +741,9 @@
       <c r="C22" t="n">
         <v>-38</v>
       </c>
+      <c r="D22" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -685,7 +753,10 @@
         <v>190</v>
       </c>
       <c r="C23" t="n">
-        <v>-56</v>
+        <v>-68</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="24">
@@ -698,6 +769,9 @@
       <c r="C24" t="n">
         <v>-46</v>
       </c>
+      <c r="D24" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -707,7 +781,10 @@
         <v>190</v>
       </c>
       <c r="C25" t="n">
-        <v>-64</v>
+        <v>-54</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +795,10 @@
         <v>190</v>
       </c>
       <c r="C26" t="n">
-        <v>-56</v>
+        <v>-66</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
@@ -729,7 +809,10 @@
         <v>190</v>
       </c>
       <c r="C27" t="n">
-        <v>-48</v>
+        <v>-42</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="28">
@@ -740,7 +823,10 @@
         <v>190</v>
       </c>
       <c r="C28" t="n">
-        <v>-62</v>
+        <v>-74</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +837,10 @@
         <v>190</v>
       </c>
       <c r="C29" t="n">
-        <v>-60</v>
+        <v>-58</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
@@ -762,7 +851,10 @@
         <v>190</v>
       </c>
       <c r="C30" t="n">
-        <v>-62</v>
+        <v>-68</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="31">
@@ -773,7 +865,10 @@
         <v>190</v>
       </c>
       <c r="C31" t="n">
-        <v>-42</v>
+        <v>-46</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="32">
@@ -784,7 +879,10 @@
         <v>190</v>
       </c>
       <c r="C32" t="n">
-        <v>-72</v>
+        <v>-56</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="33">
@@ -795,7 +893,10 @@
         <v>190</v>
       </c>
       <c r="C33" t="n">
-        <v>-50</v>
+        <v>-56</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-19.75</v>
       </c>
     </row>
     <row r="34">
@@ -806,7 +907,10 @@
         <v>190</v>
       </c>
       <c r="C34" t="n">
-        <v>-50</v>
+        <v>-10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-24.5</v>
       </c>
     </row>
     <row r="35">
@@ -817,7 +921,10 @@
         <v>190</v>
       </c>
       <c r="C35" t="n">
-        <v>-38</v>
+        <v>-34</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-17.5</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +935,10 @@
         <v>190</v>
       </c>
       <c r="C36" t="n">
-        <v>-40</v>
+        <v>-60</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="37">
@@ -839,7 +949,10 @@
         <v>190</v>
       </c>
       <c r="C37" t="n">
-        <v>-22</v>
+        <v>-58</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="38">
@@ -850,7 +963,10 @@
         <v>190</v>
       </c>
       <c r="C38" t="n">
-        <v>-58</v>
+        <v>-34</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="39">
@@ -861,7 +977,10 @@
         <v>190</v>
       </c>
       <c r="C39" t="n">
-        <v>-48</v>
+        <v>-40</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-13.75</v>
       </c>
     </row>
     <row r="40">
@@ -874,6 +993,9 @@
       <c r="C40" t="n">
         <v>-60</v>
       </c>
+      <c r="D40" t="n">
+        <v>-13.25</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -883,7 +1005,10 @@
         <v>190</v>
       </c>
       <c r="C41" t="n">
-        <v>-32</v>
+        <v>-48</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="42">
@@ -894,7 +1019,10 @@
         <v>190</v>
       </c>
       <c r="C42" t="n">
-        <v>-34</v>
+        <v>-58</v>
+      </c>
+      <c r="D42" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="43">
@@ -905,7 +1033,10 @@
         <v>190</v>
       </c>
       <c r="C43" t="n">
-        <v>-36</v>
+        <v>-52</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11.75</v>
       </c>
     </row>
     <row r="44">
@@ -916,7 +1047,10 @@
         <v>190</v>
       </c>
       <c r="C44" t="n">
-        <v>-50</v>
+        <v>-56</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="45">
@@ -927,7 +1061,10 @@
         <v>190</v>
       </c>
       <c r="C45" t="n">
-        <v>-86</v>
+        <v>-48</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="46">
@@ -938,7 +1075,10 @@
         <v>190</v>
       </c>
       <c r="C46" t="n">
-        <v>-28</v>
+        <v>-36</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-12.25</v>
       </c>
     </row>
     <row r="47">
@@ -949,7 +1089,10 @@
         <v>190</v>
       </c>
       <c r="C47" t="n">
-        <v>-38</v>
+        <v>-54</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="48">
@@ -960,7 +1103,10 @@
         <v>190</v>
       </c>
       <c r="C48" t="n">
-        <v>-8</v>
+        <v>-32</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="49">
@@ -971,7 +1117,10 @@
         <v>190</v>
       </c>
       <c r="C49" t="n">
-        <v>-26</v>
+        <v>-50</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="50">
@@ -982,7 +1131,10 @@
         <v>190</v>
       </c>
       <c r="C50" t="n">
-        <v>-66</v>
+        <v>-40</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-13.75</v>
       </c>
     </row>
     <row r="51">
@@ -993,7 +1145,10 @@
         <v>190</v>
       </c>
       <c r="C51" t="n">
-        <v>-42</v>
+        <v>-30</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="52">
@@ -1004,7 +1159,10 @@
         <v>190</v>
       </c>
       <c r="C52" t="n">
-        <v>-38</v>
+        <v>-30</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="53">
@@ -1015,7 +1173,10 @@
         <v>190</v>
       </c>
       <c r="C53" t="n">
-        <v>-32</v>
+        <v>-16</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="54">
@@ -1026,7 +1187,10 @@
         <v>190</v>
       </c>
       <c r="C54" t="n">
-        <v>-34</v>
+        <v>-40</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="55">
@@ -1037,7 +1201,10 @@
         <v>190</v>
       </c>
       <c r="C55" t="n">
-        <v>-50</v>
+        <v>-28</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-15.25</v>
       </c>
     </row>
     <row r="56">
@@ -1048,7 +1215,10 @@
         <v>190</v>
       </c>
       <c r="C56" t="n">
-        <v>-20</v>
+        <v>-42</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="57">
@@ -1059,7 +1229,10 @@
         <v>190</v>
       </c>
       <c r="C57" t="n">
-        <v>-42</v>
+        <v>-52</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="58">
@@ -1070,7 +1243,10 @@
         <v>190</v>
       </c>
       <c r="C58" t="n">
-        <v>-18</v>
+        <v>-30</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="59">
@@ -1081,7 +1257,10 @@
         <v>190</v>
       </c>
       <c r="C59" t="n">
-        <v>-50</v>
+        <v>-36</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-20.25</v>
       </c>
     </row>
     <row r="60">
@@ -1092,7 +1271,10 @@
         <v>190</v>
       </c>
       <c r="C60" t="n">
-        <v>-34</v>
+        <v>-28</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="61">
@@ -1103,7 +1285,10 @@
         <v>190</v>
       </c>
       <c r="C61" t="n">
-        <v>-48</v>
+        <v>-32</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="62">
@@ -1114,7 +1299,10 @@
         <v>190</v>
       </c>
       <c r="C62" t="n">
-        <v>-56</v>
+        <v>-48</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="63">
@@ -1125,7 +1313,10 @@
         <v>190</v>
       </c>
       <c r="C63" t="n">
-        <v>-34</v>
+        <v>-30</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="64">
@@ -1136,7 +1327,10 @@
         <v>190</v>
       </c>
       <c r="C64" t="n">
-        <v>-20</v>
+        <v>-38</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="65">
@@ -1147,7 +1341,10 @@
         <v>190</v>
       </c>
       <c r="C65" t="n">
-        <v>-60</v>
+        <v>-20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-12.25</v>
       </c>
     </row>
     <row r="66">
@@ -1160,6 +1357,9 @@
       <c r="C66" t="n">
         <v>-18</v>
       </c>
+      <c r="D66" t="n">
+        <v>-25.5</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1169,7 +1369,10 @@
         <v>190</v>
       </c>
       <c r="C67" t="n">
-        <v>-38</v>
+        <v>-24</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="68">
@@ -1180,7 +1383,10 @@
         <v>190</v>
       </c>
       <c r="C68" t="n">
-        <v>-48</v>
+        <v>-46</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="69">
@@ -1191,7 +1397,10 @@
         <v>190</v>
       </c>
       <c r="C69" t="n">
-        <v>-30</v>
+        <v>-38</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-29</v>
       </c>
     </row>
     <row r="70">
@@ -1202,7 +1411,10 @@
         <v>190</v>
       </c>
       <c r="C70" t="n">
-        <v>-16</v>
+        <v>-26</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="71">
@@ -1213,7 +1425,10 @@
         <v>190</v>
       </c>
       <c r="C71" t="n">
-        <v>-46</v>
+        <v>-44</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="72">
@@ -1224,7 +1439,10 @@
         <v>190</v>
       </c>
       <c r="C72" t="n">
-        <v>-18</v>
+        <v>-22</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="73">
@@ -1235,7 +1453,10 @@
         <v>190</v>
       </c>
       <c r="C73" t="n">
-        <v>-18</v>
+        <v>-24</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="74">
@@ -1246,7 +1467,10 @@
         <v>190</v>
       </c>
       <c r="C74" t="n">
-        <v>-58</v>
+        <v>-52</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-14.25</v>
       </c>
     </row>
     <row r="75">
@@ -1257,7 +1481,10 @@
         <v>190</v>
       </c>
       <c r="C75" t="n">
-        <v>-26</v>
+        <v>-14</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="76">
@@ -1268,7 +1495,10 @@
         <v>190</v>
       </c>
       <c r="C76" t="n">
-        <v>-44</v>
+        <v>-12</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-19.25</v>
       </c>
     </row>
     <row r="77">
@@ -1279,7 +1509,10 @@
         <v>190</v>
       </c>
       <c r="C77" t="n">
-        <v>-40</v>
+        <v>-20</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-16.25</v>
       </c>
     </row>
     <row r="78">
@@ -1290,7 +1523,10 @@
         <v>190</v>
       </c>
       <c r="C78" t="n">
-        <v>-12</v>
+        <v>-20</v>
+      </c>
+      <c r="D78" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="79">
@@ -1301,7 +1537,10 @@
         <v>190</v>
       </c>
       <c r="C79" t="n">
-        <v>-18</v>
+        <v>-26</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="80">
@@ -1312,7 +1551,10 @@
         <v>190</v>
       </c>
       <c r="C80" t="n">
-        <v>-34</v>
+        <v>-40</v>
+      </c>
+      <c r="D80" t="n">
+        <v>10.25</v>
       </c>
     </row>
     <row r="81">
@@ -1323,7 +1565,10 @@
         <v>190</v>
       </c>
       <c r="C81" t="n">
-        <v>-28</v>
+        <v>-54</v>
+      </c>
+      <c r="D81" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -1334,7 +1579,10 @@
         <v>190</v>
       </c>
       <c r="C82" t="n">
-        <v>-14</v>
+        <v>-22</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="83">
@@ -1345,7 +1593,10 @@
         <v>190</v>
       </c>
       <c r="C83" t="n">
-        <v>-32</v>
+        <v>-8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>10.25</v>
       </c>
     </row>
     <row r="84">
@@ -1356,7 +1607,10 @@
         <v>190</v>
       </c>
       <c r="C84" t="n">
-        <v>-24</v>
+        <v>-6</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="85">
@@ -1367,7 +1621,10 @@
         <v>190</v>
       </c>
       <c r="C85" t="n">
-        <v>-18</v>
+        <v>-40</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4.25</v>
       </c>
     </row>
     <row r="86">
@@ -1378,7 +1635,10 @@
         <v>190</v>
       </c>
       <c r="C86" t="n">
-        <v>-4</v>
+        <v>-32</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-20.75</v>
       </c>
     </row>
     <row r="87">
@@ -1389,7 +1649,10 @@
         <v>190</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>-30</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="88">
@@ -1400,7 +1663,10 @@
         <v>190</v>
       </c>
       <c r="C88" t="n">
-        <v>-36</v>
+        <v>-16</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="89">
@@ -1411,7 +1677,10 @@
         <v>190</v>
       </c>
       <c r="C89" t="n">
-        <v>-10</v>
+        <v>-24</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="90">
@@ -1422,7 +1691,10 @@
         <v>190</v>
       </c>
       <c r="C90" t="n">
-        <v>-18</v>
+        <v>-4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="91">
@@ -1433,7 +1705,10 @@
         <v>190</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>-2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="92">
@@ -1444,7 +1719,10 @@
         <v>190</v>
       </c>
       <c r="C92" t="n">
-        <v>-34</v>
+        <v>-12</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="93">
@@ -1455,7 +1733,10 @@
         <v>190</v>
       </c>
       <c r="C93" t="n">
-        <v>-34</v>
+        <v>-28</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="94">
@@ -1466,7 +1747,10 @@
         <v>190</v>
       </c>
       <c r="C94" t="n">
-        <v>14</v>
+        <v>-32</v>
+      </c>
+      <c r="D94" t="n">
+        <v>9.25</v>
       </c>
     </row>
     <row r="95">
@@ -1477,7 +1761,10 @@
         <v>190</v>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>-48</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="96">
@@ -1488,7 +1775,10 @@
         <v>190</v>
       </c>
       <c r="C96" t="n">
-        <v>-16</v>
+        <v>-6</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -1499,7 +1789,10 @@
         <v>190</v>
       </c>
       <c r="C97" t="n">
-        <v>-2</v>
+        <v>-44</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12.75</v>
       </c>
     </row>
     <row r="98">
@@ -1510,7 +1803,10 @@
         <v>190</v>
       </c>
       <c r="C98" t="n">
-        <v>-18</v>
+        <v>-36</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="99">
@@ -1521,7 +1817,10 @@
         <v>190</v>
       </c>
       <c r="C99" t="n">
-        <v>-18</v>
+        <v>-8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="100">
@@ -1532,7 +1831,10 @@
         <v>190</v>
       </c>
       <c r="C100" t="n">
-        <v>-20</v>
+        <v>-28</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="101">
@@ -1543,7 +1845,10 @@
         <v>190</v>
       </c>
       <c r="C101" t="n">
-        <v>-40</v>
+        <v>10</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="102">
@@ -1554,7 +1859,10 @@
         <v>190</v>
       </c>
       <c r="C102" t="n">
-        <v>-18</v>
+        <v>-8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="103">
@@ -1565,7 +1873,10 @@
         <v>190</v>
       </c>
       <c r="C103" t="n">
-        <v>-18</v>
+        <v>-2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="104">
@@ -1576,7 +1887,10 @@
         <v>190</v>
       </c>
       <c r="C104" t="n">
-        <v>-38</v>
+        <v>-2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="105">
@@ -1587,7 +1901,10 @@
         <v>190</v>
       </c>
       <c r="C105" t="n">
-        <v>-16</v>
+        <v>-20</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="106">
@@ -1598,7 +1915,10 @@
         <v>190</v>
       </c>
       <c r="C106" t="n">
-        <v>-16</v>
+        <v>-10</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="107">
@@ -1609,7 +1929,10 @@
         <v>190</v>
       </c>
       <c r="C107" t="n">
-        <v>-6</v>
+        <v>-28</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="108">
@@ -1620,7 +1943,10 @@
         <v>190</v>
       </c>
       <c r="C108" t="n">
-        <v>-16</v>
+        <v>8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="109">
@@ -1631,7 +1957,10 @@
         <v>190</v>
       </c>
       <c r="C109" t="n">
-        <v>-28</v>
+        <v>-30</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="110">
@@ -1642,7 +1971,10 @@
         <v>190</v>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="111">
@@ -1653,7 +1985,10 @@
         <v>190</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="112">
@@ -1664,7 +1999,10 @@
         <v>190</v>
       </c>
       <c r="C112" t="n">
-        <v>-14</v>
+        <v>-34</v>
+      </c>
+      <c r="D112" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="113">
@@ -1675,7 +2013,10 @@
         <v>190</v>
       </c>
       <c r="C113" t="n">
-        <v>-22</v>
+        <v>-6</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="114">
@@ -1686,7 +2027,10 @@
         <v>190</v>
       </c>
       <c r="C114" t="n">
-        <v>12</v>
+        <v>-2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="115">
@@ -1697,7 +2041,10 @@
         <v>190</v>
       </c>
       <c r="C115" t="n">
-        <v>-18</v>
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -1708,7 +2055,10 @@
         <v>190</v>
       </c>
       <c r="C116" t="n">
-        <v>-18</v>
+        <v>-14</v>
+      </c>
+      <c r="D116" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="117">
@@ -1719,7 +2069,10 @@
         <v>190</v>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-18.5</v>
       </c>
     </row>
     <row r="118">
@@ -1730,7 +2083,10 @@
         <v>190</v>
       </c>
       <c r="C118" t="n">
-        <v>22</v>
+        <v>-10</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="119">
@@ -1741,7 +2097,10 @@
         <v>190</v>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-13</v>
       </c>
     </row>
     <row r="120">
@@ -1752,7 +2111,10 @@
         <v>190</v>
       </c>
       <c r="C120" t="n">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -1763,7 +2125,10 @@
         <v>190</v>
       </c>
       <c r="C121" t="n">
-        <v>-24</v>
+        <v>-10</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="122">
@@ -1774,7 +2139,10 @@
         <v>190</v>
       </c>
       <c r="C122" t="n">
-        <v>-4</v>
+        <v>-2</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="123">
@@ -1785,7 +2153,10 @@
         <v>190</v>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-8.75</v>
       </c>
     </row>
     <row r="124">
@@ -1796,7 +2167,10 @@
         <v>190</v>
       </c>
       <c r="C124" t="n">
-        <v>-2</v>
+        <v>-18</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="125">
@@ -1807,7 +2181,10 @@
         <v>190</v>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="126">
@@ -1818,7 +2195,10 @@
         <v>190</v>
       </c>
       <c r="C126" t="n">
-        <v>-24</v>
+        <v>8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="127">
@@ -1829,7 +2209,10 @@
         <v>190</v>
       </c>
       <c r="C127" t="n">
-        <v>16</v>
+        <v>-2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="128">
@@ -1840,7 +2223,10 @@
         <v>190</v>
       </c>
       <c r="C128" t="n">
-        <v>26</v>
+        <v>-2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="129">
@@ -1851,7 +2237,10 @@
         <v>190</v>
       </c>
       <c r="C129" t="n">
-        <v>-16</v>
+        <v>8</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-7.75</v>
       </c>
     </row>
     <row r="130">
@@ -1862,7 +2251,10 @@
         <v>190</v>
       </c>
       <c r="C130" t="n">
-        <v>-4</v>
+        <v>-10</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="131">
@@ -1873,7 +2265,10 @@
         <v>190</v>
       </c>
       <c r="C131" t="n">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="132">
@@ -1884,7 +2279,10 @@
         <v>190</v>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="133">
@@ -1895,7 +2293,10 @@
         <v>190</v>
       </c>
       <c r="C133" t="n">
-        <v>-16</v>
+        <v>-26</v>
+      </c>
+      <c r="D133" t="n">
+        <v>27.5</v>
       </c>
     </row>
     <row r="134">
@@ -1906,7 +2307,10 @@
         <v>190</v>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-8.25</v>
       </c>
     </row>
     <row r="135">
@@ -1917,7 +2321,10 @@
         <v>190</v>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="136">
@@ -1928,7 +2335,10 @@
         <v>190</v>
       </c>
       <c r="C136" t="n">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-16.75</v>
       </c>
     </row>
     <row r="137">
@@ -1939,7 +2349,10 @@
         <v>190</v>
       </c>
       <c r="C137" t="n">
-        <v>16</v>
+        <v>-30</v>
+      </c>
+      <c r="D137" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="138">
@@ -1950,7 +2363,10 @@
         <v>190</v>
       </c>
       <c r="C138" t="n">
-        <v>-40</v>
+        <v>4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="139">
@@ -1961,7 +2377,10 @@
         <v>190</v>
       </c>
       <c r="C139" t="n">
-        <v>-4</v>
+        <v>-2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
@@ -1972,7 +2391,10 @@
         <v>190</v>
       </c>
       <c r="C140" t="n">
-        <v>20</v>
+        <v>-6</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="141">
@@ -1983,7 +2405,10 @@
         <v>190</v>
       </c>
       <c r="C141" t="n">
-        <v>20</v>
+        <v>-12</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="142">
@@ -1994,7 +2419,10 @@
         <v>190</v>
       </c>
       <c r="C142" t="n">
-        <v>20</v>
+        <v>-2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-25.5</v>
       </c>
     </row>
     <row r="143">
@@ -2005,7 +2433,10 @@
         <v>190</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="D143" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="144">
@@ -2016,7 +2447,10 @@
         <v>190</v>
       </c>
       <c r="C144" t="n">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="145">
@@ -2027,7 +2461,10 @@
         <v>190</v>
       </c>
       <c r="C145" t="n">
-        <v>-6</v>
+        <v>20</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="146">
@@ -2038,7 +2475,10 @@
         <v>190</v>
       </c>
       <c r="C146" t="n">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-12.25</v>
       </c>
     </row>
     <row r="147">
@@ -2049,7 +2489,10 @@
         <v>190</v>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>22</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="148">
@@ -2060,7 +2503,10 @@
         <v>190</v>
       </c>
       <c r="C148" t="n">
-        <v>24</v>
+        <v>10</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="149">
@@ -2071,7 +2517,10 @@
         <v>190</v>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>-16</v>
+      </c>
+      <c r="D149" t="n">
+        <v>17.25</v>
       </c>
     </row>
     <row r="150">
@@ -2082,7 +2531,10 @@
         <v>190</v>
       </c>
       <c r="C150" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="151">
@@ -2093,7 +2545,10 @@
         <v>190</v>
       </c>
       <c r="C151" t="n">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="152">
@@ -2104,7 +2559,10 @@
         <v>190</v>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="153">
@@ -2115,7 +2573,10 @@
         <v>190</v>
       </c>
       <c r="C153" t="n">
-        <v>-6</v>
+        <v>26</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-25</v>
       </c>
     </row>
     <row r="154">
@@ -2126,7 +2587,10 @@
         <v>190</v>
       </c>
       <c r="C154" t="n">
-        <v>10</v>
+        <v>48</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="155">
@@ -2137,7 +2601,10 @@
         <v>190</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="D155" t="n">
+        <v>15.25</v>
       </c>
     </row>
     <row r="156">
@@ -2148,7 +2615,10 @@
         <v>190</v>
       </c>
       <c r="C156" t="n">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="157">
@@ -2159,7 +2629,10 @@
         <v>190</v>
       </c>
       <c r="C157" t="n">
-        <v>16</v>
+        <v>48</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-14.75</v>
       </c>
     </row>
     <row r="158">
@@ -2170,7 +2643,10 @@
         <v>190</v>
       </c>
       <c r="C158" t="n">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="159">
@@ -2181,7 +2657,10 @@
         <v>190</v>
       </c>
       <c r="C159" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-8.75</v>
       </c>
     </row>
     <row r="160">
@@ -2192,7 +2671,10 @@
         <v>190</v>
       </c>
       <c r="C160" t="n">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D160" t="n">
+        <v>15.75</v>
       </c>
     </row>
     <row r="161">
@@ -2203,7 +2685,10 @@
         <v>190</v>
       </c>
       <c r="C161" t="n">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="162">
@@ -2214,7 +2699,10 @@
         <v>190</v>
       </c>
       <c r="C162" t="n">
-        <v>-8</v>
+        <v>4</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-7.25</v>
       </c>
     </row>
     <row r="163">
@@ -2225,7 +2713,10 @@
         <v>190</v>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D163" t="n">
+        <v>10.75</v>
       </c>
     </row>
     <row r="164">
@@ -2236,7 +2727,10 @@
         <v>190</v>
       </c>
       <c r="C164" t="n">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="165">
@@ -2247,7 +2741,10 @@
         <v>190</v>
       </c>
       <c r="C165" t="n">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="166">
@@ -2258,7 +2755,10 @@
         <v>190</v>
       </c>
       <c r="C166" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="167">
@@ -2269,7 +2769,10 @@
         <v>190</v>
       </c>
       <c r="C167" t="n">
-        <v>-10</v>
+        <v>2</v>
+      </c>
+      <c r="D167" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="168">
@@ -2280,7 +2783,10 @@
         <v>190</v>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="169">
@@ -2291,7 +2797,10 @@
         <v>190</v>
       </c>
       <c r="C169" t="n">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="D169" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="170">
@@ -2302,7 +2811,10 @@
         <v>190</v>
       </c>
       <c r="C170" t="n">
-        <v>40</v>
+        <v>20</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="171">
@@ -2313,7 +2825,10 @@
         <v>190</v>
       </c>
       <c r="C171" t="n">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="172">
@@ -2324,7 +2839,10 @@
         <v>190</v>
       </c>
       <c r="C172" t="n">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="D172" t="n">
+        <v>9.25</v>
       </c>
     </row>
     <row r="173">
@@ -2335,7 +2853,10 @@
         <v>190</v>
       </c>
       <c r="C173" t="n">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="174">
@@ -2346,7 +2867,10 @@
         <v>190</v>
       </c>
       <c r="C174" t="n">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="D174" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="175">
@@ -2357,7 +2881,10 @@
         <v>190</v>
       </c>
       <c r="C175" t="n">
-        <v>58</v>
+        <v>26</v>
+      </c>
+      <c r="D175" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="176">
@@ -2368,7 +2895,10 @@
         <v>190</v>
       </c>
       <c r="C176" t="n">
-        <v>36</v>
+        <v>50</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="177">
@@ -2379,7 +2909,10 @@
         <v>190</v>
       </c>
       <c r="C177" t="n">
-        <v>14</v>
+        <v>60</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="178">
@@ -2390,7 +2923,10 @@
         <v>190</v>
       </c>
       <c r="C178" t="n">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-13.5</v>
       </c>
     </row>
     <row r="179">
@@ -2401,7 +2937,10 @@
         <v>190</v>
       </c>
       <c r="C179" t="n">
-        <v>42</v>
+        <v>10</v>
+      </c>
+      <c r="D179" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="180">
@@ -2412,7 +2951,10 @@
         <v>190</v>
       </c>
       <c r="C180" t="n">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="181">
@@ -2423,7 +2965,10 @@
         <v>190</v>
       </c>
       <c r="C181" t="n">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="182">
@@ -2436,6 +2981,9 @@
       <c r="C182" t="n">
         <v>24</v>
       </c>
+      <c r="D182" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2445,7 +2993,10 @@
         <v>190</v>
       </c>
       <c r="C183" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+      <c r="D183" t="n">
+        <v>10.75</v>
       </c>
     </row>
     <row r="184">
@@ -2456,7 +3007,10 @@
         <v>190</v>
       </c>
       <c r="C184" t="n">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="185">
@@ -2467,7 +3021,10 @@
         <v>190</v>
       </c>
       <c r="C185" t="n">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="186">
@@ -2478,7 +3035,10 @@
         <v>190</v>
       </c>
       <c r="C186" t="n">
-        <v>18</v>
+        <v>38</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="187">
@@ -2489,7 +3049,10 @@
         <v>190</v>
       </c>
       <c r="C187" t="n">
-        <v>26</v>
+        <v>50</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="188">
@@ -2500,7 +3063,10 @@
         <v>190</v>
       </c>
       <c r="C188" t="n">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="189">
@@ -2511,7 +3077,10 @@
         <v>190</v>
       </c>
       <c r="C189" t="n">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="D189" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="190">
@@ -2522,7 +3091,10 @@
         <v>190</v>
       </c>
       <c r="C190" t="n">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="D190" t="n">
+        <v>12.25</v>
       </c>
     </row>
     <row r="191">
@@ -2533,7 +3105,10 @@
         <v>190</v>
       </c>
       <c r="C191" t="n">
-        <v>18</v>
+        <v>36</v>
+      </c>
+      <c r="D191" t="n">
+        <v>18.75</v>
       </c>
     </row>
     <row r="192">
@@ -2544,7 +3119,10 @@
         <v>190</v>
       </c>
       <c r="C192" t="n">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D192" t="n">
+        <v>17.75</v>
       </c>
     </row>
     <row r="193">
@@ -2555,7 +3133,10 @@
         <v>190</v>
       </c>
       <c r="C193" t="n">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="194">
@@ -2566,7 +3147,10 @@
         <v>190</v>
       </c>
       <c r="C194" t="n">
-        <v>48</v>
+        <v>36</v>
+      </c>
+      <c r="D194" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="195">
@@ -2577,7 +3161,10 @@
         <v>190</v>
       </c>
       <c r="C195" t="n">
-        <v>40</v>
+        <v>26</v>
+      </c>
+      <c r="D195" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="196">
@@ -2588,7 +3175,10 @@
         <v>190</v>
       </c>
       <c r="C196" t="n">
-        <v>16</v>
+        <v>42</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -2599,7 +3189,10 @@
         <v>190</v>
       </c>
       <c r="C197" t="n">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="198">
@@ -2610,7 +3203,10 @@
         <v>190</v>
       </c>
       <c r="C198" t="n">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="D198" t="n">
+        <v>7.75</v>
       </c>
     </row>
     <row r="199">
@@ -2621,7 +3217,10 @@
         <v>190</v>
       </c>
       <c r="C199" t="n">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="D199" t="n">
+        <v>-10.75</v>
       </c>
     </row>
     <row r="200">
@@ -2632,7 +3231,10 @@
         <v>190</v>
       </c>
       <c r="C200" t="n">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="D200" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="201">
@@ -2643,7 +3245,10 @@
         <v>190</v>
       </c>
       <c r="C201" t="n">
-        <v>26</v>
+        <v>46</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="202">
@@ -2654,7 +3259,10 @@
         <v>190</v>
       </c>
       <c r="C202" t="n">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="D202" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="203">
@@ -2665,7 +3273,10 @@
         <v>190</v>
       </c>
       <c r="C203" t="n">
-        <v>16</v>
+        <v>50</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="204">
@@ -2676,7 +3287,10 @@
         <v>190</v>
       </c>
       <c r="C204" t="n">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="D204" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="205">
@@ -2687,7 +3301,10 @@
         <v>190</v>
       </c>
       <c r="C205" t="n">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-10.25</v>
       </c>
     </row>
     <row r="206">
@@ -2698,7 +3315,10 @@
         <v>190</v>
       </c>
       <c r="C206" t="n">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="207">
@@ -2709,7 +3329,10 @@
         <v>190</v>
       </c>
       <c r="C207" t="n">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="D207" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="208">
@@ -2720,7 +3343,10 @@
         <v>190</v>
       </c>
       <c r="C208" t="n">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="D208" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="209">
@@ -2731,7 +3357,10 @@
         <v>190</v>
       </c>
       <c r="C209" t="n">
-        <v>58</v>
+        <v>36</v>
+      </c>
+      <c r="D209" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="210">
@@ -2742,7 +3371,10 @@
         <v>190</v>
       </c>
       <c r="C210" t="n">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="D210" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="211">
@@ -2753,7 +3385,10 @@
         <v>190</v>
       </c>
       <c r="C211" t="n">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -2764,7 +3399,10 @@
         <v>190</v>
       </c>
       <c r="C212" t="n">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="213">
@@ -2775,7 +3413,10 @@
         <v>190</v>
       </c>
       <c r="C213" t="n">
-        <v>30</v>
+        <v>14</v>
+      </c>
+      <c r="D213" t="n">
+        <v>24.5</v>
       </c>
     </row>
     <row r="214">
@@ -2786,7 +3427,10 @@
         <v>190</v>
       </c>
       <c r="C214" t="n">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="215">
@@ -2797,7 +3441,10 @@
         <v>190</v>
       </c>
       <c r="C215" t="n">
-        <v>40</v>
+        <v>56</v>
+      </c>
+      <c r="D215" t="n">
+        <v>10.25</v>
       </c>
     </row>
     <row r="216">
@@ -2808,7 +3455,10 @@
         <v>190</v>
       </c>
       <c r="C216" t="n">
-        <v>64</v>
+        <v>48</v>
+      </c>
+      <c r="D216" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="217">
@@ -2819,7 +3469,10 @@
         <v>190</v>
       </c>
       <c r="C217" t="n">
-        <v>56</v>
+        <v>46</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="218">
@@ -2830,7 +3483,10 @@
         <v>190</v>
       </c>
       <c r="C218" t="n">
-        <v>20</v>
+        <v>46</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="219">
@@ -2841,7 +3497,10 @@
         <v>190</v>
       </c>
       <c r="C219" t="n">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="D219" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -2852,7 +3511,10 @@
         <v>190</v>
       </c>
       <c r="C220" t="n">
-        <v>62</v>
+        <v>74</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="221">
@@ -2863,7 +3525,10 @@
         <v>190</v>
       </c>
       <c r="C221" t="n">
-        <v>22</v>
+        <v>36</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="222">
@@ -2876,6 +3541,9 @@
       <c r="C222" t="n">
         <v>52</v>
       </c>
+      <c r="D222" t="n">
+        <v>-3.25</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -2885,7 +3553,10 @@
         <v>190</v>
       </c>
       <c r="C223" t="n">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="224">
@@ -2896,7 +3567,10 @@
         <v>190</v>
       </c>
       <c r="C224" t="n">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="225">
@@ -2907,7 +3581,10 @@
         <v>190</v>
       </c>
       <c r="C225" t="n">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="226">
@@ -2918,7 +3595,10 @@
         <v>190</v>
       </c>
       <c r="C226" t="n">
-        <v>30</v>
+        <v>68</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-19.25</v>
       </c>
     </row>
     <row r="227">
@@ -2929,7 +3609,10 @@
         <v>190</v>
       </c>
       <c r="C227" t="n">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="228">
@@ -2940,7 +3623,10 @@
         <v>190</v>
       </c>
       <c r="C228" t="n">
-        <v>74</v>
+        <v>52</v>
+      </c>
+      <c r="D228" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="229">
@@ -2951,7 +3637,10 @@
         <v>190</v>
       </c>
       <c r="C229" t="n">
-        <v>46</v>
+        <v>22</v>
+      </c>
+      <c r="D229" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="230">
@@ -2962,7 +3651,10 @@
         <v>190</v>
       </c>
       <c r="C230" t="n">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="231">
@@ -2973,7 +3665,10 @@
         <v>190</v>
       </c>
       <c r="C231" t="n">
-        <v>54</v>
+        <v>30</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="232">
@@ -2984,7 +3679,10 @@
         <v>190</v>
       </c>
       <c r="C232" t="n">
-        <v>44</v>
+        <v>36</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="233">
@@ -2995,7 +3693,10 @@
         <v>190</v>
       </c>
       <c r="C233" t="n">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-13.75</v>
       </c>
     </row>
     <row r="234">
@@ -3006,7 +3707,10 @@
         <v>190</v>
       </c>
       <c r="C234" t="n">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="235">
@@ -3017,7 +3721,10 @@
         <v>190</v>
       </c>
       <c r="C235" t="n">
-        <v>64</v>
+        <v>98</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="236">
@@ -3028,7 +3735,10 @@
         <v>190</v>
       </c>
       <c r="C236" t="n">
-        <v>52</v>
+        <v>36</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="237">
@@ -3039,7 +3749,10 @@
         <v>190</v>
       </c>
       <c r="C237" t="n">
-        <v>54</v>
+        <v>32</v>
+      </c>
+      <c r="D237" t="n">
+        <v>19.25</v>
       </c>
     </row>
     <row r="238">
@@ -3050,7 +3763,10 @@
         <v>190</v>
       </c>
       <c r="C238" t="n">
-        <v>54</v>
+        <v>68</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="239">
@@ -3061,7 +3777,10 @@
         <v>190</v>
       </c>
       <c r="C239" t="n">
-        <v>56</v>
+        <v>74</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="240">
@@ -3072,7 +3791,10 @@
         <v>190</v>
       </c>
       <c r="C240" t="n">
-        <v>38</v>
+        <v>48</v>
+      </c>
+      <c r="D240" t="n">
+        <v>11.25</v>
       </c>
     </row>
     <row r="241">
@@ -3083,7 +3805,10 @@
         <v>190</v>
       </c>
       <c r="C241" t="n">
-        <v>36</v>
+        <v>62</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="242">
@@ -3094,7 +3819,10 @@
         <v>190</v>
       </c>
       <c r="C242" t="n">
-        <v>92</v>
+        <v>44</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="243">
@@ -3105,7 +3833,10 @@
         <v>190</v>
       </c>
       <c r="C243" t="n">
-        <v>74</v>
+        <v>54</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="244">
@@ -3116,7 +3847,10 @@
         <v>190</v>
       </c>
       <c r="C244" t="n">
-        <v>66</v>
+        <v>56</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-11.75</v>
       </c>
     </row>
     <row r="245">
@@ -3127,7 +3861,10 @@
         <v>190</v>
       </c>
       <c r="C245" t="n">
-        <v>56</v>
+        <v>84</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-11.25</v>
       </c>
     </row>
     <row r="246">
@@ -3138,7 +3875,10 @@
         <v>190</v>
       </c>
       <c r="C246" t="n">
-        <v>90</v>
+        <v>52</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="247">
@@ -3149,7 +3889,10 @@
         <v>190</v>
       </c>
       <c r="C247" t="n">
-        <v>66</v>
+        <v>76</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="248">
@@ -3160,7 +3903,10 @@
         <v>190</v>
       </c>
       <c r="C248" t="n">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="249">
@@ -3171,7 +3917,10 @@
         <v>190</v>
       </c>
       <c r="C249" t="n">
-        <v>78</v>
+        <v>62</v>
+      </c>
+      <c r="D249" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="250">
@@ -3182,7 +3931,10 @@
         <v>190</v>
       </c>
       <c r="C250" t="n">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="D250" t="n">
+        <v>7.75</v>
       </c>
     </row>
     <row r="251">
@@ -3193,7 +3945,10 @@
         <v>190</v>
       </c>
       <c r="C251" t="n">
-        <v>52</v>
+        <v>74</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="252">
@@ -3204,7 +3959,10 @@
         <v>190</v>
       </c>
       <c r="C252" t="n">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="253">
@@ -3215,7 +3973,10 @@
         <v>190</v>
       </c>
       <c r="C253" t="n">
-        <v>64</v>
+        <v>80</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="254">
@@ -3226,7 +3987,10 @@
         <v>190</v>
       </c>
       <c r="C254" t="n">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -3237,7 +4001,10 @@
         <v>190</v>
       </c>
       <c r="C255" t="n">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="256">
@@ -3248,7 +4015,10 @@
         <v>190</v>
       </c>
       <c r="C256" t="n">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="D256" t="n">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="257">
@@ -3261,6 +4031,9 @@
       <c r="C257" t="n">
         <v>74</v>
       </c>
+      <c r="D257" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -3270,7 +4043,10 @@
         <v>190</v>
       </c>
       <c r="C258" t="n">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="259">
@@ -3281,7 +4057,10 @@
         <v>190</v>
       </c>
       <c r="C259" t="n">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="260">
@@ -3292,7 +4071,10 @@
         <v>190</v>
       </c>
       <c r="C260" t="n">
-        <v>54</v>
+        <v>32</v>
+      </c>
+      <c r="D260" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="261">
@@ -3303,7 +4085,10 @@
         <v>190</v>
       </c>
       <c r="C261" t="n">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="262">
@@ -3314,7 +4099,10 @@
         <v>190</v>
       </c>
       <c r="C262" t="n">
-        <v>96</v>
+        <v>70</v>
+      </c>
+      <c r="D262" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="263">
@@ -3325,7 +4113,10 @@
         <v>190</v>
       </c>
       <c r="C263" t="n">
-        <v>82</v>
+        <v>66</v>
+      </c>
+      <c r="D263" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="264">
@@ -3336,7 +4127,10 @@
         <v>190</v>
       </c>
       <c r="C264" t="n">
-        <v>78</v>
+        <v>54</v>
+      </c>
+      <c r="D264" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="265">
@@ -3347,7 +4141,10 @@
         <v>190</v>
       </c>
       <c r="C265" t="n">
-        <v>62</v>
+        <v>76</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="266">
@@ -3358,7 +4155,10 @@
         <v>190</v>
       </c>
       <c r="C266" t="n">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="267">
@@ -3369,7 +4169,10 @@
         <v>190</v>
       </c>
       <c r="C267" t="n">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="268">
@@ -3380,7 +4183,10 @@
         <v>190</v>
       </c>
       <c r="C268" t="n">
-        <v>92</v>
+        <v>68</v>
+      </c>
+      <c r="D268" t="n">
+        <v>14.75</v>
       </c>
     </row>
     <row r="269">
@@ -3391,7 +4197,10 @@
         <v>190</v>
       </c>
       <c r="C269" t="n">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="270">
@@ -3402,7 +4211,10 @@
         <v>190</v>
       </c>
       <c r="C270" t="n">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-8.25</v>
       </c>
     </row>
     <row r="271">
@@ -3413,7 +4225,10 @@
         <v>190</v>
       </c>
       <c r="C271" t="n">
-        <v>60</v>
+        <v>72</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="272">
@@ -3426,6 +4241,9 @@
       <c r="C272" t="n">
         <v>62</v>
       </c>
+      <c r="D272" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -3437,6 +4255,9 @@
       <c r="C273" t="n">
         <v>70</v>
       </c>
+      <c r="D273" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -3446,7 +4267,10 @@
         <v>190</v>
       </c>
       <c r="C274" t="n">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="275">
@@ -3457,7 +4281,10 @@
         <v>190</v>
       </c>
       <c r="C275" t="n">
-        <v>74</v>
+        <v>58</v>
+      </c>
+      <c r="D275" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -3468,7 +4295,10 @@
         <v>190</v>
       </c>
       <c r="C276" t="n">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-14.25</v>
       </c>
     </row>
     <row r="277">
@@ -3479,7 +4309,10 @@
         <v>190</v>
       </c>
       <c r="C277" t="n">
-        <v>60</v>
+        <v>88</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="278">
@@ -3490,7 +4323,10 @@
         <v>190</v>
       </c>
       <c r="C278" t="n">
-        <v>78</v>
+        <v>86</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="279">
@@ -3501,7 +4337,10 @@
         <v>190</v>
       </c>
       <c r="C279" t="n">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="280">
@@ -3512,7 +4351,10 @@
         <v>190</v>
       </c>
       <c r="C280" t="n">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="281">
@@ -3523,7 +4365,10 @@
         <v>190</v>
       </c>
       <c r="C281" t="n">
-        <v>98</v>
+        <v>88</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="282">
@@ -3534,7 +4379,10 @@
         <v>190</v>
       </c>
       <c r="C282" t="n">
-        <v>78</v>
+        <v>84</v>
+      </c>
+      <c r="D282" t="n">
+        <v>-7.25</v>
       </c>
     </row>
     <row r="283">
@@ -3545,7 +4393,10 @@
         <v>190</v>
       </c>
       <c r="C283" t="n">
-        <v>64</v>
+        <v>90</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="284">
@@ -3556,7 +4407,10 @@
         <v>190</v>
       </c>
       <c r="C284" t="n">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="285">
@@ -3567,7 +4421,10 @@
         <v>190</v>
       </c>
       <c r="C285" t="n">
-        <v>98</v>
+        <v>72</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-7.75</v>
       </c>
     </row>
     <row r="286">
@@ -3578,7 +4435,10 @@
         <v>190</v>
       </c>
       <c r="C286" t="n">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="D286" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="287">
@@ -3589,7 +4449,10 @@
         <v>190</v>
       </c>
       <c r="C287" t="n">
-        <v>74</v>
+        <v>100</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-15.25</v>
       </c>
     </row>
     <row r="288">
@@ -3600,7 +4463,10 @@
         <v>190</v>
       </c>
       <c r="C288" t="n">
-        <v>84</v>
+        <v>54</v>
+      </c>
+      <c r="D288" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="289">
@@ -3611,7 +4477,10 @@
         <v>190</v>
       </c>
       <c r="C289" t="n">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="290">
@@ -3622,7 +4491,10 @@
         <v>190</v>
       </c>
       <c r="C290" t="n">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="D290" t="n">
+        <v>11.25</v>
       </c>
     </row>
     <row r="291">
@@ -3633,7 +4505,10 @@
         <v>190</v>
       </c>
       <c r="C291" t="n">
-        <v>74</v>
+        <v>88</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-17.75</v>
       </c>
     </row>
     <row r="292">
@@ -3646,6 +4521,9 @@
       <c r="C292" t="n">
         <v>80</v>
       </c>
+      <c r="D292" t="n">
+        <v>-2.75</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -3655,7 +4533,10 @@
         <v>190</v>
       </c>
       <c r="C293" t="n">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="294">
@@ -3666,7 +4547,10 @@
         <v>190</v>
       </c>
       <c r="C294" t="n">
-        <v>84</v>
+        <v>92</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-8.25</v>
       </c>
     </row>
     <row r="295">
@@ -3677,7 +4561,10 @@
         <v>190</v>
       </c>
       <c r="C295" t="n">
-        <v>92</v>
+        <v>86</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-4.5</v>
       </c>
     </row>
     <row r="296">
@@ -3688,7 +4575,10 @@
         <v>190</v>
       </c>
       <c r="C296" t="n">
-        <v>88</v>
+        <v>106</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-7</v>
       </c>
     </row>
     <row r="297">
@@ -3699,7 +4589,10 @@
         <v>190</v>
       </c>
       <c r="C297" t="n">
-        <v>84</v>
+        <v>104</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="298">
@@ -3710,7 +4603,10 @@
         <v>190</v>
       </c>
       <c r="C298" t="n">
-        <v>86</v>
+        <v>96</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-10.75</v>
       </c>
     </row>
     <row r="299">
@@ -3723,6 +4619,9 @@
       <c r="C299" t="n">
         <v>94</v>
       </c>
+      <c r="D299" t="n">
+        <v>-13.5</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -3732,7 +4631,10 @@
         <v>190</v>
       </c>
       <c r="C300" t="n">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="D300" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -3743,7 +4645,10 @@
         <v>190</v>
       </c>
       <c r="C301" t="n">
-        <v>88</v>
+        <v>114</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="302">
@@ -3754,7 +4659,10 @@
         <v>190</v>
       </c>
       <c r="C302" t="n">
-        <v>110</v>
+        <v>86</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="303">
@@ -3765,7 +4673,10 @@
         <v>190</v>
       </c>
       <c r="C303" t="n">
-        <v>78</v>
+        <v>82</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="304">
@@ -3776,7 +4687,10 @@
         <v>190</v>
       </c>
       <c r="C304" t="n">
-        <v>98</v>
+        <v>70</v>
+      </c>
+      <c r="D304" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="305">
@@ -3789,6 +4703,9 @@
       <c r="C305" t="n">
         <v>98</v>
       </c>
+      <c r="D305" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -3798,7 +4715,10 @@
         <v>190</v>
       </c>
       <c r="C306" t="n">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="307">
@@ -3809,7 +4729,10 @@
         <v>190</v>
       </c>
       <c r="C307" t="n">
-        <v>102</v>
+        <v>94</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="308">
@@ -3820,7 +4743,10 @@
         <v>190</v>
       </c>
       <c r="C308" t="n">
-        <v>78</v>
+        <v>90</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="309">
@@ -3831,7 +4757,10 @@
         <v>190</v>
       </c>
       <c r="C309" t="n">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="310">
@@ -3842,7 +4771,10 @@
         <v>190</v>
       </c>
       <c r="C310" t="n">
-        <v>90</v>
+        <v>78</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="311">
@@ -3853,7 +4785,10 @@
         <v>190</v>
       </c>
       <c r="C311" t="n">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-17.75</v>
       </c>
     </row>
     <row r="312">
@@ -3864,7 +4799,10 @@
         <v>190</v>
       </c>
       <c r="C312" t="n">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="D312" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="313">
@@ -3875,7 +4813,10 @@
         <v>190</v>
       </c>
       <c r="C313" t="n">
-        <v>88</v>
+        <v>94</v>
+      </c>
+      <c r="D313" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="314">
@@ -3886,7 +4827,10 @@
         <v>190</v>
       </c>
       <c r="C314" t="n">
-        <v>114</v>
+        <v>84</v>
+      </c>
+      <c r="D314" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="315">
@@ -3897,7 +4841,10 @@
         <v>190</v>
       </c>
       <c r="C315" t="n">
-        <v>110</v>
+        <v>82</v>
+      </c>
+      <c r="D315" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="316">
@@ -3908,7 +4855,10 @@
         <v>190</v>
       </c>
       <c r="C316" t="n">
-        <v>86</v>
+        <v>110</v>
+      </c>
+      <c r="D316" t="n">
+        <v>-17.5</v>
       </c>
     </row>
     <row r="317">
@@ -3919,7 +4869,10 @@
         <v>190</v>
       </c>
       <c r="C317" t="n">
-        <v>88</v>
+        <v>104</v>
+      </c>
+      <c r="D317" t="n">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="318">
@@ -3930,7 +4883,10 @@
         <v>190</v>
       </c>
       <c r="C318" t="n">
-        <v>82</v>
+        <v>116</v>
+      </c>
+      <c r="D318" t="n">
+        <v>-19.25</v>
       </c>
     </row>
     <row r="319">
@@ -3941,7 +4897,10 @@
         <v>190</v>
       </c>
       <c r="C319" t="n">
-        <v>96</v>
+        <v>116</v>
+      </c>
+      <c r="D319" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="320">
@@ -3952,7 +4911,10 @@
         <v>190</v>
       </c>
       <c r="C320" t="n">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="D320" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="321">
@@ -3963,7 +4925,10 @@
         <v>190</v>
       </c>
       <c r="C321" t="n">
-        <v>120</v>
+        <v>104</v>
+      </c>
+      <c r="D321" t="n">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="322">
@@ -3974,7 +4939,10 @@
         <v>190</v>
       </c>
       <c r="C322" t="n">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="323">
@@ -3985,7 +4953,10 @@
         <v>190</v>
       </c>
       <c r="C323" t="n">
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="D323" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="324">
@@ -3996,7 +4967,10 @@
         <v>190</v>
       </c>
       <c r="C324" t="n">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="D324" t="n">
+        <v>-20.5</v>
       </c>
     </row>
     <row r="325">
@@ -4007,7 +4981,10 @@
         <v>190</v>
       </c>
       <c r="C325" t="n">
-        <v>92</v>
+        <v>110</v>
+      </c>
+      <c r="D325" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="326">
@@ -4018,7 +4995,10 @@
         <v>190</v>
       </c>
       <c r="C326" t="n">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="D326" t="n">
+        <v>-12.75</v>
       </c>
     </row>
     <row r="327">
@@ -4031,6 +5011,9 @@
       <c r="C327" t="n">
         <v>102</v>
       </c>
+      <c r="D327" t="n">
+        <v>-8.5</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -4040,7 +5023,10 @@
         <v>190</v>
       </c>
       <c r="C328" t="n">
-        <v>108</v>
+        <v>94</v>
+      </c>
+      <c r="D328" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="329">
@@ -4051,7 +5037,10 @@
         <v>190</v>
       </c>
       <c r="C329" t="n">
-        <v>130</v>
+        <v>102</v>
+      </c>
+      <c r="D329" t="n">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="330">
@@ -4062,7 +5051,10 @@
         <v>190</v>
       </c>
       <c r="C330" t="n">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="D330" t="n">
+        <v>-16.75</v>
       </c>
     </row>
     <row r="331">
@@ -4073,7 +5065,10 @@
         <v>190</v>
       </c>
       <c r="C331" t="n">
-        <v>110</v>
+        <v>96</v>
+      </c>
+      <c r="D331" t="n">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="332">
@@ -4084,7 +5079,10 @@
         <v>190</v>
       </c>
       <c r="C332" t="n">
-        <v>118</v>
+        <v>98</v>
+      </c>
+      <c r="D332" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="333">
@@ -4095,7 +5093,10 @@
         <v>190</v>
       </c>
       <c r="C333" t="n">
-        <v>108</v>
+        <v>78</v>
+      </c>
+      <c r="D333" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="334">
@@ -4106,7 +5107,10 @@
         <v>190</v>
       </c>
       <c r="C334" t="n">
-        <v>80</v>
+        <v>110</v>
+      </c>
+      <c r="D334" t="n">
+        <v>-15.5</v>
       </c>
     </row>
     <row r="335">
@@ -4117,7 +5121,10 @@
         <v>190</v>
       </c>
       <c r="C335" t="n">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="D335" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="336">
@@ -4128,7 +5135,10 @@
         <v>190</v>
       </c>
       <c r="C336" t="n">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="D336" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="337">
@@ -4139,7 +5149,10 @@
         <v>190</v>
       </c>
       <c r="C337" t="n">
-        <v>74</v>
+        <v>98</v>
+      </c>
+      <c r="D337" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="338">
@@ -4150,7 +5163,10 @@
         <v>190</v>
       </c>
       <c r="C338" t="n">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="D338" t="n">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="339">
@@ -4161,7 +5177,10 @@
         <v>190</v>
       </c>
       <c r="C339" t="n">
-        <v>80</v>
+        <v>106</v>
+      </c>
+      <c r="D339" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="340">
@@ -4172,7 +5191,10 @@
         <v>190</v>
       </c>
       <c r="C340" t="n">
-        <v>76</v>
+        <v>102</v>
+      </c>
+      <c r="D340" t="n">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="341">
@@ -4183,7 +5205,10 @@
         <v>190</v>
       </c>
       <c r="C341" t="n">
-        <v>116</v>
+        <v>94</v>
+      </c>
+      <c r="D341" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="342">
@@ -4194,7 +5219,10 @@
         <v>190</v>
       </c>
       <c r="C342" t="n">
-        <v>112</v>
+        <v>122</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-23</v>
       </c>
     </row>
     <row r="343">
@@ -4205,7 +5233,10 @@
         <v>190</v>
       </c>
       <c r="C343" t="n">
-        <v>118</v>
+        <v>124</v>
+      </c>
+      <c r="D343" t="n">
+        <v>-14.25</v>
       </c>
     </row>
     <row r="344">
@@ -4216,7 +5247,10 @@
         <v>190</v>
       </c>
       <c r="C344" t="n">
-        <v>92</v>
+        <v>128</v>
+      </c>
+      <c r="D344" t="n">
+        <v>-18.75</v>
       </c>
     </row>
     <row r="345">
@@ -4227,7 +5261,10 @@
         <v>190</v>
       </c>
       <c r="C345" t="n">
-        <v>114</v>
+        <v>122</v>
+      </c>
+      <c r="D345" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="346">
@@ -4238,7 +5275,10 @@
         <v>190</v>
       </c>
       <c r="C346" t="n">
-        <v>98</v>
+        <v>100</v>
+      </c>
+      <c r="D346" t="n">
+        <v>-5.25</v>
       </c>
     </row>
     <row r="347">
@@ -4249,7 +5289,10 @@
         <v>190</v>
       </c>
       <c r="C347" t="n">
-        <v>122</v>
+        <v>104</v>
+      </c>
+      <c r="D347" t="n">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="348">
@@ -4260,7 +5303,10 @@
         <v>190</v>
       </c>
       <c r="C348" t="n">
-        <v>124</v>
+        <v>108</v>
+      </c>
+      <c r="D348" t="n">
+        <v>-14.25</v>
       </c>
     </row>
     <row r="349">
@@ -4271,7 +5317,10 @@
         <v>190</v>
       </c>
       <c r="C349" t="n">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="D349" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="350">
@@ -4282,7 +5331,10 @@
         <v>190</v>
       </c>
       <c r="C350" t="n">
-        <v>104</v>
+        <v>120</v>
+      </c>
+      <c r="D350" t="n">
+        <v>-17.75</v>
       </c>
     </row>
     <row r="351">
@@ -4293,7 +5345,10 @@
         <v>190</v>
       </c>
       <c r="C351" t="n">
-        <v>140</v>
+        <v>128</v>
+      </c>
+      <c r="D351" t="n">
+        <v>-24.75</v>
       </c>
     </row>
     <row r="352">
@@ -4304,7 +5359,10 @@
         <v>190</v>
       </c>
       <c r="C352" t="n">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="D352" t="n">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="353">
@@ -4315,7 +5373,10 @@
         <v>190</v>
       </c>
       <c r="C353" t="n">
-        <v>110</v>
+        <v>120</v>
+      </c>
+      <c r="D353" t="n">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="354">
@@ -4326,7 +5387,10 @@
         <v>190</v>
       </c>
       <c r="C354" t="n">
-        <v>116</v>
+        <v>132</v>
+      </c>
+      <c r="D354" t="n">
+        <v>-19.25</v>
       </c>
     </row>
     <row r="355">
@@ -4337,7 +5401,10 @@
         <v>190</v>
       </c>
       <c r="C355" t="n">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="D355" t="n">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="356">
@@ -4350,6 +5417,9 @@
       <c r="C356" t="n">
         <v>122</v>
       </c>
+      <c r="D356" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -4359,7 +5429,10 @@
         <v>190</v>
       </c>
       <c r="C357" t="n">
-        <v>116</v>
+        <v>122</v>
+      </c>
+      <c r="D357" t="n">
+        <v>-13</v>
       </c>
     </row>
     <row r="358">
@@ -4370,7 +5443,10 @@
         <v>190</v>
       </c>
       <c r="C358" t="n">
-        <v>94</v>
+        <v>128</v>
+      </c>
+      <c r="D358" t="n">
+        <v>-24.75</v>
       </c>
     </row>
     <row r="359">
@@ -4381,7 +5457,10 @@
         <v>190</v>
       </c>
       <c r="C359" t="n">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="D359" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="360">
@@ -4392,7 +5471,10 @@
         <v>190</v>
       </c>
       <c r="C360" t="n">
-        <v>122</v>
+        <v>106</v>
+      </c>
+      <c r="D360" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="361">
@@ -4403,7 +5485,10 @@
         <v>190</v>
       </c>
       <c r="C361" t="n">
-        <v>98</v>
+        <v>118</v>
+      </c>
+      <c r="D361" t="n">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="362">
@@ -4414,7 +5499,10 @@
         <v>190</v>
       </c>
       <c r="C362" t="n">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="D362" t="n">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="363">
@@ -4425,7 +5513,10 @@
         <v>190</v>
       </c>
       <c r="C363" t="n">
-        <v>126</v>
+        <v>124</v>
+      </c>
+      <c r="D363" t="n">
+        <v>-20.25</v>
       </c>
     </row>
     <row r="364">
@@ -4436,7 +5527,10 @@
         <v>190</v>
       </c>
       <c r="C364" t="n">
-        <v>132</v>
+        <v>110</v>
+      </c>
+      <c r="D364" t="n">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="365">
@@ -4447,7 +5541,10 @@
         <v>190</v>
       </c>
       <c r="C365" t="n">
-        <v>110</v>
+        <v>140</v>
+      </c>
+      <c r="D365" t="n">
+        <v>-26.25</v>
       </c>
     </row>
     <row r="366">
@@ -4458,7 +5555,10 @@
         <v>190</v>
       </c>
       <c r="C366" t="n">
-        <v>106</v>
+        <v>128</v>
+      </c>
+      <c r="D366" t="n">
+        <v>-22.75</v>
       </c>
     </row>
     <row r="367">
@@ -4469,7 +5569,10 @@
         <v>190</v>
       </c>
       <c r="C367" t="n">
-        <v>116</v>
+        <v>104</v>
+      </c>
+      <c r="D367" t="n">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="368">
@@ -4480,7 +5583,10 @@
         <v>190</v>
       </c>
       <c r="C368" t="n">
-        <v>120</v>
+        <v>126</v>
+      </c>
+      <c r="D368" t="n">
+        <v>-23.5</v>
       </c>
     </row>
     <row r="369">
@@ -4491,7 +5597,10 @@
         <v>190</v>
       </c>
       <c r="C369" t="n">
-        <v>124</v>
+        <v>96</v>
+      </c>
+      <c r="D369" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="370">
@@ -4502,7 +5611,10 @@
         <v>190</v>
       </c>
       <c r="C370" t="n">
-        <v>110</v>
+        <v>122</v>
+      </c>
+      <c r="D370" t="n">
+        <v>-19</v>
       </c>
     </row>
     <row r="371">
@@ -4513,7 +5625,10 @@
         <v>190</v>
       </c>
       <c r="C371" t="n">
-        <v>140</v>
+        <v>124</v>
+      </c>
+      <c r="D371" t="n">
+        <v>-8.25</v>
       </c>
     </row>
     <row r="372">
@@ -4524,7 +5639,10 @@
         <v>190</v>
       </c>
       <c r="C372" t="n">
-        <v>124</v>
+        <v>106</v>
+      </c>
+      <c r="D372" t="n">
+        <v>-9</v>
       </c>
     </row>
     <row r="373">
@@ -4535,7 +5653,10 @@
         <v>190</v>
       </c>
       <c r="C373" t="n">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="D373" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="374">
@@ -4546,7 +5667,10 @@
         <v>190</v>
       </c>
       <c r="C374" t="n">
-        <v>148</v>
+        <v>120</v>
+      </c>
+      <c r="D374" t="n">
+        <v>-13.75</v>
       </c>
     </row>
     <row r="375">
@@ -4557,7 +5681,10 @@
         <v>190</v>
       </c>
       <c r="C375" t="n">
-        <v>124</v>
+        <v>136</v>
+      </c>
+      <c r="D375" t="n">
+        <v>-25.75</v>
       </c>
     </row>
     <row r="376">
@@ -4568,7 +5695,10 @@
         <v>190</v>
       </c>
       <c r="C376" t="n">
-        <v>136</v>
+        <v>134</v>
+      </c>
+      <c r="D376" t="n">
+        <v>-18.5</v>
       </c>
     </row>
     <row r="377">
@@ -4579,7 +5709,10 @@
         <v>190</v>
       </c>
       <c r="C377" t="n">
-        <v>122</v>
+        <v>112</v>
+      </c>
+      <c r="D377" t="n">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="378">
@@ -4590,7 +5723,10 @@
         <v>190</v>
       </c>
       <c r="C378" t="n">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D378" t="n">
+        <v>-13</v>
       </c>
     </row>
     <row r="379">
@@ -4603,6 +5739,9 @@
       <c r="C379" t="n">
         <v>122</v>
       </c>
+      <c r="D379" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -4612,7 +5751,10 @@
         <v>190</v>
       </c>
       <c r="C380" t="n">
-        <v>134</v>
+        <v>124</v>
+      </c>
+      <c r="D380" t="n">
+        <v>-18.25</v>
       </c>
     </row>
     <row r="381">
@@ -4623,7 +5765,10 @@
         <v>190</v>
       </c>
       <c r="C381" t="n">
-        <v>138</v>
+        <v>134</v>
+      </c>
+      <c r="D381" t="n">
+        <v>-14.5</v>
       </c>
     </row>
     <row r="382">
@@ -4634,7 +5779,10 @@
         <v>190</v>
       </c>
       <c r="C382" t="n">
-        <v>130</v>
+        <v>116</v>
+      </c>
+      <c r="D382" t="n">
+        <v>-11.25</v>
       </c>
     </row>
     <row r="383">
@@ -4645,7 +5793,10 @@
         <v>190</v>
       </c>
       <c r="C383" t="n">
-        <v>124</v>
+        <v>122</v>
+      </c>
+      <c r="D383" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="384">
@@ -4656,7 +5807,10 @@
         <v>190</v>
       </c>
       <c r="C384" t="n">
-        <v>142</v>
+        <v>150</v>
+      </c>
+      <c r="D384" t="n">
+        <v>-28.5</v>
       </c>
     </row>
     <row r="385">
@@ -4667,7 +5821,10 @@
         <v>190</v>
       </c>
       <c r="C385" t="n">
-        <v>132</v>
+        <v>150</v>
+      </c>
+      <c r="D385" t="n">
+        <v>-40.5</v>
       </c>
     </row>
     <row r="386">
@@ -4678,7 +5835,10 @@
         <v>190</v>
       </c>
       <c r="C386" t="n">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="D386" t="n">
+        <v>-24.75</v>
       </c>
     </row>
     <row r="387">
@@ -4689,7 +5849,10 @@
         <v>190</v>
       </c>
       <c r="C387" t="n">
-        <v>114</v>
+        <v>130</v>
+      </c>
+      <c r="D387" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="388">
@@ -4700,7 +5863,10 @@
         <v>190</v>
       </c>
       <c r="C388" t="n">
-        <v>126</v>
+        <v>130</v>
+      </c>
+      <c r="D388" t="n">
+        <v>-20</v>
       </c>
     </row>
     <row r="389">
@@ -4713,6 +5879,9 @@
       <c r="C389" t="n">
         <v>134</v>
       </c>
+      <c r="D389" t="n">
+        <v>-28.5</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -4722,7 +5891,10 @@
         <v>190</v>
       </c>
       <c r="C390" t="n">
-        <v>140</v>
+        <v>122</v>
+      </c>
+      <c r="D390" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="391">
@@ -4733,7 +5905,10 @@
         <v>190</v>
       </c>
       <c r="C391" t="n">
-        <v>128</v>
+        <v>142</v>
+      </c>
+      <c r="D391" t="n">
+        <v>-17.5</v>
       </c>
     </row>
     <row r="392">
@@ -4744,7 +5919,10 @@
         <v>190</v>
       </c>
       <c r="C392" t="n">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="D392" t="n">
+        <v>-30.75</v>
       </c>
     </row>
     <row r="393">
@@ -4755,7 +5933,10 @@
         <v>190</v>
       </c>
       <c r="C393" t="n">
-        <v>134</v>
+        <v>124</v>
+      </c>
+      <c r="D393" t="n">
+        <v>-12.25</v>
       </c>
     </row>
     <row r="394">
@@ -4766,7 +5947,10 @@
         <v>190</v>
       </c>
       <c r="C394" t="n">
-        <v>124</v>
+        <v>142</v>
+      </c>
+      <c r="D394" t="n">
+        <v>-25.5</v>
       </c>
     </row>
     <row r="395">
@@ -4777,7 +5961,10 @@
         <v>190</v>
       </c>
       <c r="C395" t="n">
-        <v>130</v>
+        <v>134</v>
+      </c>
+      <c r="D395" t="n">
+        <v>-22.5</v>
       </c>
     </row>
     <row r="396">
@@ -4788,7 +5975,10 @@
         <v>190</v>
       </c>
       <c r="C396" t="n">
-        <v>140</v>
+        <v>128</v>
+      </c>
+      <c r="D396" t="n">
+        <v>-14.75</v>
       </c>
     </row>
     <row r="397">
@@ -4799,7 +5989,10 @@
         <v>190</v>
       </c>
       <c r="C397" t="n">
-        <v>166</v>
+        <v>140</v>
+      </c>
+      <c r="D397" t="n">
+        <v>-32.25</v>
       </c>
     </row>
     <row r="398">
@@ -4810,7 +6003,10 @@
         <v>190</v>
       </c>
       <c r="C398" t="n">
-        <v>134</v>
+        <v>146</v>
+      </c>
+      <c r="D398" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="399">
@@ -4821,7 +6017,10 @@
         <v>190</v>
       </c>
       <c r="C399" t="n">
-        <v>148</v>
+        <v>122</v>
+      </c>
+      <c r="D399" t="n">
+        <v>-23</v>
       </c>
     </row>
     <row r="400">
@@ -4832,7 +6031,10 @@
         <v>190</v>
       </c>
       <c r="C400" t="n">
-        <v>122</v>
+        <v>134</v>
+      </c>
+      <c r="D400" t="n">
+        <v>-26.5</v>
       </c>
     </row>
     <row r="401">
@@ -4843,7 +6045,10 @@
         <v>190</v>
       </c>
       <c r="C401" t="n">
-        <v>126</v>
+        <v>136</v>
+      </c>
+      <c r="D401" t="n">
+        <v>-19.75</v>
       </c>
     </row>
     <row r="402">
@@ -4854,7 +6059,10 @@
         <v>190</v>
       </c>
       <c r="C402" t="n">
-        <v>132</v>
+        <v>148</v>
+      </c>
+      <c r="D402" t="n">
+        <v>-23.25</v>
       </c>
     </row>
     <row r="403">
@@ -4865,7 +6073,10 @@
         <v>190</v>
       </c>
       <c r="C403" t="n">
-        <v>118</v>
+        <v>146</v>
+      </c>
+      <c r="D403" t="n">
+        <v>-36</v>
       </c>
     </row>
     <row r="404">
@@ -4876,7 +6087,10 @@
         <v>190</v>
       </c>
       <c r="C404" t="n">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="D404" t="n">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="405">
@@ -4887,7 +6101,10 @@
         <v>190</v>
       </c>
       <c r="C405" t="n">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="D405" t="n">
+        <v>-24.75</v>
       </c>
     </row>
     <row r="406">
@@ -4898,7 +6115,10 @@
         <v>190</v>
       </c>
       <c r="C406" t="n">
-        <v>136</v>
+        <v>144</v>
+      </c>
+      <c r="D406" t="n">
+        <v>-28.75</v>
       </c>
     </row>
     <row r="407">
@@ -4909,7 +6129,10 @@
         <v>190</v>
       </c>
       <c r="C407" t="n">
-        <v>136</v>
+        <v>150</v>
+      </c>
+      <c r="D407" t="n">
+        <v>-26.5</v>
       </c>
     </row>
     <row r="408">
@@ -4920,7 +6143,10 @@
         <v>190</v>
       </c>
       <c r="C408" t="n">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="D408" t="n">
+        <v>-17</v>
       </c>
     </row>
     <row r="409">
@@ -4931,7 +6157,10 @@
         <v>190</v>
       </c>
       <c r="C409" t="n">
-        <v>128</v>
+        <v>138</v>
+      </c>
+      <c r="D409" t="n">
+        <v>-15</v>
       </c>
     </row>
     <row r="410">
@@ -4942,7 +6171,10 @@
         <v>190</v>
       </c>
       <c r="C410" t="n">
-        <v>142</v>
+        <v>154</v>
+      </c>
+      <c r="D410" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="411">
@@ -4953,7 +6185,10 @@
         <v>190</v>
       </c>
       <c r="C411" t="n">
-        <v>152</v>
+        <v>130</v>
+      </c>
+      <c r="D411" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="412">
@@ -4964,7 +6199,10 @@
         <v>190</v>
       </c>
       <c r="C412" t="n">
-        <v>128</v>
+        <v>148</v>
+      </c>
+      <c r="D412" t="n">
+        <v>-31.25</v>
       </c>
     </row>
     <row r="413">
@@ -4975,7 +6213,10 @@
         <v>190</v>
       </c>
       <c r="C413" t="n">
-        <v>128</v>
+        <v>144</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-22.75</v>
       </c>
     </row>
     <row r="414">
@@ -4986,7 +6227,10 @@
         <v>190</v>
       </c>
       <c r="C414" t="n">
-        <v>132</v>
+        <v>130</v>
+      </c>
+      <c r="D414" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="415">
@@ -4997,7 +6241,10 @@
         <v>190</v>
       </c>
       <c r="C415" t="n">
-        <v>142</v>
+        <v>146</v>
+      </c>
+      <c r="D415" t="n">
+        <v>-24</v>
       </c>
     </row>
     <row r="416">
@@ -5008,7 +6255,10 @@
         <v>190</v>
       </c>
       <c r="C416" t="n">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="D416" t="n">
+        <v>-31</v>
       </c>
     </row>
     <row r="417">
@@ -5019,7 +6269,10 @@
         <v>190</v>
       </c>
       <c r="C417" t="n">
-        <v>142</v>
+        <v>148</v>
+      </c>
+      <c r="D417" t="n">
+        <v>-23.25</v>
       </c>
     </row>
     <row r="418">
@@ -5030,7 +6283,10 @@
         <v>190</v>
       </c>
       <c r="C418" t="n">
-        <v>154</v>
+        <v>134</v>
+      </c>
+      <c r="D418" t="n">
+        <v>-16.5</v>
       </c>
     </row>
     <row r="419">
@@ -5041,7 +6297,10 @@
         <v>190</v>
       </c>
       <c r="C419" t="n">
-        <v>140</v>
+        <v>152</v>
+      </c>
+      <c r="D419" t="n">
+        <v>-33.75</v>
       </c>
     </row>
     <row r="420">
@@ -5052,7 +6311,10 @@
         <v>190</v>
       </c>
       <c r="C420" t="n">
-        <v>156</v>
+        <v>164</v>
+      </c>
+      <c r="D420" t="n">
+        <v>-37.25</v>
       </c>
     </row>
     <row r="421">
@@ -5063,7 +6325,10 @@
         <v>190</v>
       </c>
       <c r="C421" t="n">
-        <v>154</v>
+        <v>146</v>
+      </c>
+      <c r="D421" t="n">
+        <v>-28</v>
       </c>
     </row>
     <row r="422">
@@ -5074,7 +6339,10 @@
         <v>190</v>
       </c>
       <c r="C422" t="n">
-        <v>138</v>
+        <v>150</v>
+      </c>
+      <c r="D422" t="n">
+        <v>-26.5</v>
       </c>
     </row>
     <row r="423">
@@ -5085,7 +6353,10 @@
         <v>190</v>
       </c>
       <c r="C423" t="n">
-        <v>140</v>
+        <v>146</v>
+      </c>
+      <c r="D423" t="n">
+        <v>-22</v>
       </c>
     </row>
     <row r="424">
@@ -5096,7 +6367,10 @@
         <v>190</v>
       </c>
       <c r="C424" t="n">
-        <v>144</v>
+        <v>152</v>
+      </c>
+      <c r="D424" t="n">
+        <v>-29.75</v>
       </c>
     </row>
     <row r="425">
@@ -5107,7 +6381,10 @@
         <v>190</v>
       </c>
       <c r="C425" t="n">
-        <v>152</v>
+        <v>160</v>
+      </c>
+      <c r="D425" t="n">
+        <v>-34.75</v>
       </c>
     </row>
     <row r="426">
@@ -5118,7 +6395,10 @@
         <v>190</v>
       </c>
       <c r="C426" t="n">
-        <v>158</v>
+        <v>156</v>
+      </c>
+      <c r="D426" t="n">
+        <v>-30.25</v>
       </c>
     </row>
     <row r="427">
@@ -5129,7 +6409,10 @@
         <v>190</v>
       </c>
       <c r="C427" t="n">
-        <v>146</v>
+        <v>156</v>
+      </c>
+      <c r="D427" t="n">
+        <v>-36.25</v>
       </c>
     </row>
     <row r="428">
@@ -5140,7 +6423,10 @@
         <v>190</v>
       </c>
       <c r="C428" t="n">
-        <v>152</v>
+        <v>162</v>
+      </c>
+      <c r="D428" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="429">
@@ -5151,7 +6437,10 @@
         <v>190</v>
       </c>
       <c r="C429" t="n">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="D429" t="n">
+        <v>-33.5</v>
       </c>
     </row>
     <row r="430">
@@ -5162,7 +6451,10 @@
         <v>190</v>
       </c>
       <c r="C430" t="n">
-        <v>166</v>
+        <v>148</v>
+      </c>
+      <c r="D430" t="n">
+        <v>-31.25</v>
       </c>
     </row>
     <row r="431">
@@ -5173,7 +6465,10 @@
         <v>190</v>
       </c>
       <c r="C431" t="n">
-        <v>150</v>
+        <v>162</v>
+      </c>
+      <c r="D431" t="n">
+        <v>-30</v>
       </c>
     </row>
     <row r="432">
@@ -5184,7 +6479,10 @@
         <v>190</v>
       </c>
       <c r="C432" t="n">
-        <v>150</v>
+        <v>152</v>
+      </c>
+      <c r="D432" t="n">
+        <v>-25.75</v>
       </c>
     </row>
     <row r="433">
@@ -5195,7 +6493,10 @@
         <v>190</v>
       </c>
       <c r="C433" t="n">
-        <v>152</v>
+        <v>156</v>
+      </c>
+      <c r="D433" t="n">
+        <v>-34.25</v>
       </c>
     </row>
     <row r="434">
@@ -5206,7 +6507,10 @@
         <v>190</v>
       </c>
       <c r="C434" t="n">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="D434" t="n">
+        <v>-24.5</v>
       </c>
     </row>
     <row r="435">
@@ -5217,7 +6521,10 @@
         <v>190</v>
       </c>
       <c r="C435" t="n">
-        <v>156</v>
+        <v>164</v>
+      </c>
+      <c r="D435" t="n">
+        <v>-37.25</v>
       </c>
     </row>
     <row r="436">
@@ -5228,7 +6535,10 @@
         <v>190</v>
       </c>
       <c r="C436" t="n">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="D436" t="n">
+        <v>-24.5</v>
       </c>
     </row>
     <row r="437">
@@ -5239,7 +6549,10 @@
         <v>190</v>
       </c>
       <c r="C437" t="n">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="D437" t="n">
+        <v>-29.5</v>
       </c>
     </row>
     <row r="438">
@@ -5250,7 +6563,10 @@
         <v>190</v>
       </c>
       <c r="C438" t="n">
-        <v>152</v>
+        <v>158</v>
+      </c>
+      <c r="D438" t="n">
+        <v>-35.5</v>
       </c>
     </row>
     <row r="439">
@@ -5261,7 +6577,10 @@
         <v>190</v>
       </c>
       <c r="C439" t="n">
-        <v>164</v>
+        <v>158</v>
+      </c>
+      <c r="D439" t="n">
+        <v>-27.5</v>
       </c>
     </row>
     <row r="440">
@@ -5272,7 +6591,10 @@
         <v>190</v>
       </c>
       <c r="C440" t="n">
-        <v>164</v>
+        <v>150</v>
+      </c>
+      <c r="D440" t="n">
+        <v>-30.5</v>
       </c>
     </row>
     <row r="441">
@@ -5283,7 +6605,10 @@
         <v>190</v>
       </c>
       <c r="C441" t="n">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="D441" t="n">
+        <v>-22.5</v>
       </c>
     </row>
     <row r="442">
@@ -5294,7 +6619,10 @@
         <v>190</v>
       </c>
       <c r="C442" t="n">
-        <v>160</v>
+        <v>152</v>
+      </c>
+      <c r="D442" t="n">
+        <v>-23.75</v>
       </c>
     </row>
     <row r="443">
@@ -5305,7 +6633,10 @@
         <v>190</v>
       </c>
       <c r="C443" t="n">
-        <v>154</v>
+        <v>172</v>
+      </c>
+      <c r="D443" t="n">
+        <v>-44.25</v>
       </c>
     </row>
     <row r="444">
@@ -5316,7 +6647,10 @@
         <v>190</v>
       </c>
       <c r="C444" t="n">
-        <v>152</v>
+        <v>166</v>
+      </c>
+      <c r="D444" t="n">
+        <v>-34.5</v>
       </c>
     </row>
     <row r="445">
@@ -5327,7 +6661,10 @@
         <v>190</v>
       </c>
       <c r="C445" t="n">
-        <v>156</v>
+        <v>162</v>
+      </c>
+      <c r="D445" t="n">
+        <v>-34</v>
       </c>
     </row>
     <row r="446">
@@ -5338,7 +6675,10 @@
         <v>190</v>
       </c>
       <c r="C446" t="n">
-        <v>166</v>
+        <v>160</v>
+      </c>
+      <c r="D446" t="n">
+        <v>-44.75</v>
       </c>
     </row>
     <row r="447">
@@ -5349,7 +6689,10 @@
         <v>190</v>
       </c>
       <c r="C447" t="n">
-        <v>158</v>
+        <v>180</v>
+      </c>
+      <c r="D447" t="n">
+        <v>-49.25</v>
       </c>
     </row>
     <row r="448">
@@ -5360,7 +6703,10 @@
         <v>190</v>
       </c>
       <c r="C448" t="n">
-        <v>168</v>
+        <v>160</v>
+      </c>
+      <c r="D448" t="n">
+        <v>-30.75</v>
       </c>
     </row>
     <row r="449">
@@ -5371,7 +6717,10 @@
         <v>190</v>
       </c>
       <c r="C449" t="n">
-        <v>162</v>
+        <v>158</v>
+      </c>
+      <c r="D449" t="n">
+        <v>-27.5</v>
       </c>
     </row>
     <row r="450">
@@ -5382,7 +6731,10 @@
         <v>190</v>
       </c>
       <c r="C450" t="n">
-        <v>162</v>
+        <v>170</v>
+      </c>
+      <c r="D450" t="n">
+        <v>-37</v>
       </c>
     </row>
     <row r="451">
@@ -5393,7 +6745,10 @@
         <v>190</v>
       </c>
       <c r="C451" t="n">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="D451" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="452">
@@ -5404,7 +6759,10 @@
         <v>190</v>
       </c>
       <c r="C452" t="n">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="D452" t="n">
+        <v>-30.75</v>
       </c>
     </row>
     <row r="453">
@@ -5417,6 +6775,9 @@
       <c r="C453" t="n">
         <v>164</v>
       </c>
+      <c r="D453" t="n">
+        <v>-33.25</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -5428,6 +6789,9 @@
       <c r="C454" t="n">
         <v>172</v>
       </c>
+      <c r="D454" t="n">
+        <v>-38.25</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -5437,7 +6801,10 @@
         <v>190</v>
       </c>
       <c r="C455" t="n">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="D455" t="n">
+        <v>-38.25</v>
       </c>
     </row>
     <row r="456">
@@ -5450,6 +6817,9 @@
       <c r="C456" t="n">
         <v>162</v>
       </c>
+      <c r="D456" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -5459,7 +6829,10 @@
         <v>190</v>
       </c>
       <c r="C457" t="n">
-        <v>166</v>
+        <v>182</v>
+      </c>
+      <c r="D457" t="n">
+        <v>-44.5</v>
       </c>
     </row>
     <row r="458">
@@ -5470,7 +6843,10 @@
         <v>190</v>
       </c>
       <c r="C458" t="n">
-        <v>160</v>
+        <v>172</v>
+      </c>
+      <c r="D458" t="n">
+        <v>-40.25</v>
       </c>
     </row>
     <row r="459">
@@ -5481,7 +6857,10 @@
         <v>190</v>
       </c>
       <c r="C459" t="n">
-        <v>172</v>
+        <v>174</v>
+      </c>
+      <c r="D459" t="n">
+        <v>-39.5</v>
       </c>
     </row>
     <row r="460">
@@ -5492,7 +6871,10 @@
         <v>190</v>
       </c>
       <c r="C460" t="n">
-        <v>170</v>
+        <v>186</v>
+      </c>
+      <c r="D460" t="n">
+        <v>-47</v>
       </c>
     </row>
     <row r="461">
@@ -5503,7 +6885,10 @@
         <v>190</v>
       </c>
       <c r="C461" t="n">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="D461" t="n">
+        <v>-32.5</v>
       </c>
     </row>
     <row r="462">
@@ -5514,7 +6899,10 @@
         <v>190</v>
       </c>
       <c r="C462" t="n">
-        <v>172</v>
+        <v>168</v>
+      </c>
+      <c r="D462" t="n">
+        <v>-35.75</v>
       </c>
     </row>
     <row r="463">
@@ -5525,7 +6913,10 @@
         <v>190</v>
       </c>
       <c r="C463" t="n">
-        <v>170</v>
+        <v>164</v>
+      </c>
+      <c r="D463" t="n">
+        <v>-31.25</v>
       </c>
     </row>
     <row r="464">
@@ -5538,6 +6929,9 @@
       <c r="C464" t="n">
         <v>172</v>
       </c>
+      <c r="D464" t="n">
+        <v>-36.25</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -5547,7 +6941,10 @@
         <v>190</v>
       </c>
       <c r="C465" t="n">
-        <v>174</v>
+        <v>160</v>
+      </c>
+      <c r="D465" t="n">
+        <v>-28.75</v>
       </c>
     </row>
     <row r="466">
@@ -5558,7 +6955,10 @@
         <v>190</v>
       </c>
       <c r="C466" t="n">
-        <v>166</v>
+        <v>170</v>
+      </c>
+      <c r="D466" t="n">
+        <v>-39</v>
       </c>
     </row>
     <row r="467">
@@ -5569,7 +6969,10 @@
         <v>190</v>
       </c>
       <c r="C467" t="n">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="D467" t="n">
+        <v>-35.75</v>
       </c>
     </row>
     <row r="468">
@@ -5580,7 +6983,10 @@
         <v>190</v>
       </c>
       <c r="C468" t="n">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="D468" t="n">
+        <v>-43.75</v>
       </c>
     </row>
     <row r="469">
@@ -5593,6 +6999,9 @@
       <c r="C469" t="n">
         <v>176</v>
       </c>
+      <c r="D469" t="n">
+        <v>-40.75</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -5602,7 +7011,10 @@
         <v>190</v>
       </c>
       <c r="C470" t="n">
-        <v>176</v>
+        <v>168</v>
+      </c>
+      <c r="D470" t="n">
+        <v>-33.75</v>
       </c>
     </row>
     <row r="471">
@@ -5613,7 +7025,10 @@
         <v>190</v>
       </c>
       <c r="C471" t="n">
-        <v>182</v>
+        <v>176</v>
+      </c>
+      <c r="D471" t="n">
+        <v>-42.75</v>
       </c>
     </row>
     <row r="472">
@@ -5624,7 +7039,10 @@
         <v>190</v>
       </c>
       <c r="C472" t="n">
-        <v>176</v>
+        <v>170</v>
+      </c>
+      <c r="D472" t="n">
+        <v>-39</v>
       </c>
     </row>
     <row r="473">
@@ -5635,7 +7053,10 @@
         <v>190</v>
       </c>
       <c r="C473" t="n">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="D473" t="n">
+        <v>-41.5</v>
       </c>
     </row>
     <row r="474">
@@ -5646,7 +7067,10 @@
         <v>190</v>
       </c>
       <c r="C474" t="n">
-        <v>174</v>
+        <v>188</v>
+      </c>
+      <c r="D474" t="n">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="475">
@@ -5657,7 +7081,10 @@
         <v>190</v>
       </c>
       <c r="C475" t="n">
-        <v>176</v>
+        <v>170</v>
+      </c>
+      <c r="D475" t="n">
+        <v>-35</v>
       </c>
     </row>
     <row r="476">
@@ -5668,7 +7095,10 @@
         <v>190</v>
       </c>
       <c r="C476" t="n">
-        <v>184</v>
+        <v>178</v>
+      </c>
+      <c r="D476" t="n">
+        <v>-40</v>
       </c>
     </row>
     <row r="477">
@@ -5679,7 +7109,10 @@
         <v>190</v>
       </c>
       <c r="C477" t="n">
-        <v>180</v>
+        <v>184</v>
+      </c>
+      <c r="D477" t="n">
+        <v>-43.75</v>
       </c>
     </row>
     <row r="478">
@@ -5692,6 +7125,9 @@
       <c r="C478" t="n">
         <v>180</v>
       </c>
+      <c r="D478" t="n">
+        <v>-45.25</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -5703,6 +7139,9 @@
       <c r="C479" t="n">
         <v>180</v>
       </c>
+      <c r="D479" t="n">
+        <v>-47.25</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -5712,7 +7151,10 @@
         <v>190</v>
       </c>
       <c r="C480" t="n">
-        <v>180</v>
+        <v>176</v>
+      </c>
+      <c r="D480" t="n">
+        <v>-40.75</v>
       </c>
     </row>
     <row r="481">
@@ -5723,7 +7165,10 @@
         <v>190</v>
       </c>
       <c r="C481" t="n">
-        <v>184</v>
+        <v>188</v>
+      </c>
+      <c r="D481" t="n">
+        <v>-48.25</v>
       </c>
     </row>
     <row r="482">
@@ -5734,7 +7179,10 @@
         <v>190</v>
       </c>
       <c r="C482" t="n">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="D482" t="n">
+        <v>-33.75</v>
       </c>
     </row>
     <row r="483">
@@ -5745,7 +7193,10 @@
         <v>190</v>
       </c>
       <c r="C483" t="n">
-        <v>184</v>
+        <v>180</v>
+      </c>
+      <c r="D483" t="n">
+        <v>-41.25</v>
       </c>
     </row>
     <row r="484">
@@ -5756,7 +7207,10 @@
         <v>190</v>
       </c>
       <c r="C484" t="n">
-        <v>186</v>
+        <v>180</v>
+      </c>
+      <c r="D484" t="n">
+        <v>-43.25</v>
       </c>
     </row>
     <row r="485">
@@ -5769,6 +7223,9 @@
       <c r="C485" t="n">
         <v>176</v>
       </c>
+      <c r="D485" t="n">
+        <v>-46.75</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -5778,7 +7235,10 @@
         <v>190</v>
       </c>
       <c r="C486" t="n">
-        <v>176</v>
+        <v>186</v>
+      </c>
+      <c r="D486" t="n">
+        <v>-45</v>
       </c>
     </row>
     <row r="487">
@@ -5789,7 +7249,10 @@
         <v>190</v>
       </c>
       <c r="C487" t="n">
-        <v>186</v>
+        <v>180</v>
+      </c>
+      <c r="D487" t="n">
+        <v>-41.25</v>
       </c>
     </row>
     <row r="488">
@@ -5800,7 +7263,10 @@
         <v>190</v>
       </c>
       <c r="C488" t="n">
-        <v>188</v>
+        <v>176</v>
+      </c>
+      <c r="D488" t="n">
+        <v>-38.75</v>
       </c>
     </row>
     <row r="489">
@@ -5811,7 +7277,10 @@
         <v>190</v>
       </c>
       <c r="C489" t="n">
-        <v>180</v>
+        <v>182</v>
+      </c>
+      <c r="D489" t="n">
+        <v>-42.5</v>
       </c>
     </row>
     <row r="490">
@@ -5824,6 +7293,9 @@
       <c r="C490" t="n">
         <v>186</v>
       </c>
+      <c r="D490" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -5833,7 +7305,10 @@
         <v>190</v>
       </c>
       <c r="C491" t="n">
-        <v>186</v>
+        <v>188</v>
+      </c>
+      <c r="D491" t="n">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="492">
@@ -5846,6 +7321,9 @@
       <c r="C492" t="n">
         <v>186</v>
       </c>
+      <c r="D492" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -5855,7 +7333,10 @@
         <v>190</v>
       </c>
       <c r="C493" t="n">
-        <v>186</v>
+        <v>188</v>
+      </c>
+      <c r="D493" t="n">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="494">
@@ -5866,7 +7347,10 @@
         <v>190</v>
       </c>
       <c r="C494" t="n">
-        <v>184</v>
+        <v>186</v>
+      </c>
+      <c r="D494" t="n">
+        <v>-47</v>
       </c>
     </row>
     <row r="495">
@@ -5877,7 +7361,10 @@
         <v>190</v>
       </c>
       <c r="C495" t="n">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="D495" t="n">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="496">
@@ -5888,7 +7375,10 @@
         <v>190</v>
       </c>
       <c r="C496" t="n">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="D496" t="n">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="497">
@@ -5899,7 +7389,10 @@
         <v>190</v>
       </c>
       <c r="C497" t="n">
-        <v>186</v>
+        <v>190</v>
+      </c>
+      <c r="D497" t="n">
+        <v>-47.5</v>
       </c>
     </row>
     <row r="498">
@@ -5912,6 +7405,9 @@
       <c r="C498" t="n">
         <v>188</v>
       </c>
+      <c r="D498" t="n">
+        <v>-48.25</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -5921,7 +7417,10 @@
         <v>190</v>
       </c>
       <c r="C499" t="n">
-        <v>188</v>
+        <v>190</v>
+      </c>
+      <c r="D499" t="n">
+        <v>-47.5</v>
       </c>
     </row>
     <row r="500">
@@ -5934,6 +7433,9 @@
       <c r="C500" t="n">
         <v>190</v>
       </c>
+      <c r="D500" t="n">
+        <v>-47.5</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -5944,6 +7446,9 @@
       </c>
       <c r="C501" t="n">
         <v>190</v>
+      </c>
+      <c r="D501" t="n">
+        <v>-47.5</v>
       </c>
     </row>
   </sheetData>
@@ -5957,18 +7462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>solar#0</t>
+          <t>wind#0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>battery#0</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>grid#0</t>
         </is>
       </c>
     </row>
@@ -5984,6 +7494,9 @@
       <c r="C2" t="n">
         <v>500</v>
       </c>
+      <c r="D2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -5995,7 +7508,10 @@
         <v>190</v>
       </c>
       <c r="C3" t="n">
-        <v>62.764</v>
+        <v>62.864</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-11.72</v>
       </c>
     </row>
     <row r="4">
@@ -6008,7 +7524,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>74.18689705999827</v>
+        <v>74.65375993038452</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15.84981176752999</v>
       </c>
     </row>
     <row r="5">
@@ -6021,7 +7540,10 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>-86</v>
+        <v>-80</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-49.25</v>
       </c>
     </row>
     <row r="6">
@@ -6034,7 +7556,10 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-20.3125</v>
       </c>
     </row>
     <row r="7">
@@ -6047,7 +7572,10 @@
         <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-9.125</v>
       </c>
     </row>
     <row r="8">
@@ -6060,7 +7588,10 @@
         <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>124.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="9">
@@ -6075,6 +7606,9 @@
       <c r="C9" t="n">
         <v>190</v>
       </c>
+      <c r="D9" t="n">
+        <v>27.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,41 +456,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-13</v>
+        <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>-70.92273448912802</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>41</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-85.12437388463309</v>
-      </c>
-      <c r="D3" t="n">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>85</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-95</v>
-      </c>
-      <c r="D4" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -531,13 +503,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +519,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.66666666666666</v>
+        <v>148</v>
       </c>
       <c r="C3" t="n">
-        <v>-83.68236945792036</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D3" t="n">
-        <v>19.33333333333333</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -562,15 +534,9 @@
           <t>std</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>49.08496035786658</v>
-      </c>
-      <c r="C4" t="n">
-        <v>12.10323143607734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>18.1130707869575</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -579,13 +545,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-13</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>-95</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -595,13 +561,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>-90.06218694231654</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D6" t="n">
-        <v>9.75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -611,13 +577,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>-85.12437388463309</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -627,13 +593,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>-78.02355418688055</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D8" t="n">
-        <v>27.75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -643,13 +609,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="C9" t="n">
-        <v>-70.92273448912802</v>
+        <v>-115.255559837265</v>
       </c>
       <c r="D9" t="n">
-        <v>38.5</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/results/logs/episode_rewards.xlsx
+++ b/results/logs/episode_rewards.xlsx
@@ -459,10 +459,10 @@
         <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -522,10 +522,10 @@
         <v>148</v>
       </c>
       <c r="C3" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -548,10 +548,10 @@
         <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -580,10 +580,10 @@
         <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -596,10 +596,10 @@
         <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -612,10 +612,10 @@
         <v>148</v>
       </c>
       <c r="C9" t="n">
-        <v>-115.255559837265</v>
+        <v>-131.5339542548244</v>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
